--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable" displayName="AveragesTable" ref="A1:EC15" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_Greece_Sup" displayName="AveragesTable_Greece_Sup" ref="A1:EC15" headerRowCount="1">
   <autoFilter ref="A1:EC15"/>
   <tableColumns count="133">
     <tableColumn id="1" name="team_name"/>

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
         <v>5</v>
@@ -1394,79 +1394,79 @@
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="H2" t="n">
-        <v>100.6</v>
+        <v>103.17</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="K2" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="M2" t="n">
-        <v>68.40000000000001</v>
+        <v>68</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>15.6</v>
+        <v>15.17</v>
       </c>
       <c r="Q2" t="n">
-        <v>13</v>
+        <v>12.67</v>
       </c>
       <c r="R2" t="n">
         <v>4</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>60.8</v>
+        <v>61.67</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="Z2" t="n">
-        <v>17</v>
+        <v>18.67</v>
       </c>
       <c r="AA2" t="n">
-        <v>12.6</v>
+        <v>13.83</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.4</v>
+        <v>4.83</v>
       </c>
       <c r="AC2" t="n">
-        <v>22.2</v>
+        <v>21.67</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,70 +1550,70 @@
         <v>2.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="BN2" t="n">
         <v>1</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.6</v>
+        <v>3.73</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.6</v>
+        <v>4.73</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BT2" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BU2" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BV2" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="BZ2" t="n">
         <v>1.45</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.81</v>
+        <v>4.77</v>
       </c>
       <c r="CB2" t="n">
-        <v>5.12</v>
+        <v>5.06</v>
       </c>
       <c r="CC2" t="n">
         <v>1.99</v>
@@ -1622,31 +1622,31 @@
         <v>2.16</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CI2" t="n">
         <v>1.69</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="CM2" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="CN2" t="n">
         <v>1.58</v>
@@ -1655,22 +1655,22 @@
         <v>1.25</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.99</v>
+        <v>3.03</v>
       </c>
       <c r="CR2" t="n">
         <v>1.36</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CV2" t="n">
         <v>1.75</v>
@@ -1691,88 +1691,88 @@
         <v>1.61</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="DG2" t="n">
-        <v>3</v>
+        <v>3.27</v>
       </c>
       <c r="DH2" t="n">
-        <v>95.8</v>
+        <v>97.64</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DJ2" t="n">
         <v>3</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="DM2" t="n">
-        <v>64.7</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="DN2" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="DP2" t="n">
-        <v>16.4</v>
+        <v>16.09</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="DR2" t="n">
-        <v>6</v>
+        <v>5.82</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>59</v>
+        <v>59.64</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DX2" t="n">
-        <v>16.6</v>
+        <v>17.55</v>
       </c>
       <c r="DY2" t="n">
-        <v>12.3</v>
+        <v>13</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.3</v>
+        <v>4.54</v>
       </c>
       <c r="EA2" t="n">
-        <v>22</v>
+        <v>21.73</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" t="n">
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1872,127 +1872,127 @@
         <v>1.4</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG3" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AH3" t="n">
-        <v>4.4</v>
+        <v>3.67</v>
       </c>
       <c r="AI3" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL3" t="n">
-        <v>6</v>
+        <v>5.17</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AN3" t="n">
-        <v>45.2</v>
+        <v>40.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>17.2</v>
+        <v>16.17</v>
       </c>
       <c r="AR3" t="n">
-        <v>13.8</v>
+        <v>13.67</v>
       </c>
       <c r="AS3" t="n">
-        <v>5</v>
+        <v>6.17</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AU3" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>50.6</v>
+        <v>47.83</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>11.6</v>
+        <v>10.67</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.4</v>
+        <v>6.67</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BD3" t="n">
-        <v>19.6</v>
+        <v>18.5</v>
       </c>
       <c r="BE3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="BN3" t="n">
         <v>1.36</v>
       </c>
-      <c r="BF3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>1.4</v>
-      </c>
       <c r="BO3" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="BP3" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.6</v>
+        <v>6.55</v>
       </c>
       <c r="BR3" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BS3" t="n">
-        <v>80</v>
+        <v>72.73</v>
       </c>
       <c r="BT3" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BU3" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BY3" t="n">
         <v>1.94</v>
@@ -2013,31 +2013,31 @@
         <v>2.03</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.66</v>
+        <v>3.72</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.96</v>
+        <v>4.01</v>
       </c>
       <c r="CC3" t="n">
-        <v>3.45</v>
+        <v>4.04</v>
       </c>
       <c r="CD3" t="n">
-        <v>4.67</v>
+        <v>5.22</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CF3" t="n">
         <v>2.91</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CH3" t="n">
         <v>1.36</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CJ3" t="n">
         <v>2.01</v>
@@ -2046,40 +2046,40 @@
         <v>1.85</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.69</v>
+        <v>3.66</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="CU3" t="n">
         <v>1.4</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CX3" t="n">
         <v>1.87</v>
@@ -2094,88 +2094,88 @@
         <v>1.57</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.76</v>
+        <v>3.72</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="DG3" t="n">
-        <v>4.1</v>
+        <v>3.73</v>
       </c>
       <c r="DH3" t="n">
-        <v>98.2</v>
+        <v>95.27</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.8</v>
+        <v>5.37</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="DM3" t="n">
-        <v>48.6</v>
+        <v>45.73</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="DP3" t="n">
-        <v>15.7</v>
+        <v>15.27</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.9</v>
+        <v>14.73</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.2</v>
+        <v>6.73</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>54.6</v>
+        <v>52.73</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX3" t="n">
-        <v>13.3</v>
+        <v>12.64</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.1</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.2</v>
+        <v>4.09</v>
       </c>
       <c r="EA3" t="n">
-        <v>23.1</v>
+        <v>22.18</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="4">
@@ -2185,61 +2185,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
         <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F4" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>62.75</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J4" t="n">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="K4" t="n">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="L4" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="M4" t="n">
-        <v>45.25</v>
+        <v>42.4</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="O4" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="P4" t="n">
-        <v>12</v>
+        <v>11.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.25</v>
+        <v>15.4</v>
       </c>
       <c r="R4" t="n">
-        <v>6.25</v>
+        <v>6.6</v>
       </c>
       <c r="S4" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="T4" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2251,28 +2251,28 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>48.75</v>
+        <v>46.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>11.75</v>
+        <v>10.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.75</v>
+        <v>6</v>
       </c>
       <c r="AB4" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>20.25</v>
+        <v>20.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AE4" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,70 +2356,70 @@
         <v>3.67</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.1</v>
+        <v>8.82</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BL4" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="BP4" t="n">
         <v>4</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.1</v>
+        <v>4.82</v>
       </c>
       <c r="BR4" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BS4" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>60</v>
+        <v>54.55</v>
       </c>
       <c r="BU4" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BV4" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BW4" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BX4" t="n">
-        <v>50</v>
+        <v>54.55</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.16</v>
+        <v>2.91</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.02</v>
+        <v>3.93</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.31</v>
+        <v>4.2</v>
       </c>
       <c r="CC4" t="n">
         <v>8.199999999999999</v>
@@ -2428,40 +2428,40 @@
         <v>8.74</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="CG4" t="n">
         <v>2.78</v>
-      </c>
-      <c r="CG4" t="n">
-        <v>2.81</v>
       </c>
       <c r="CH4" t="n">
         <v>1.38</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CM4" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CO4" t="n">
         <v>1.31</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CQ4" t="n">
         <v>3.48</v>
@@ -2470,25 +2470,25 @@
         <v>1.41</v>
       </c>
       <c r="CS4" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="CT4" t="n">
         <v>2.9</v>
-      </c>
-      <c r="CT4" t="n">
-        <v>2.91</v>
       </c>
       <c r="CU4" t="n">
         <v>1.41</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CZ4" t="n">
         <v>1.98</v>
@@ -2500,85 +2500,85 @@
         <v>1.31</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="DH4" t="n">
-        <v>72.59999999999999</v>
+        <v>72.55</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="DJ4" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.3</v>
+        <v>4.18</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="DM4" t="n">
-        <v>35.3</v>
+        <v>34.91</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.8</v>
+        <v>13.36</v>
       </c>
       <c r="DQ4" t="n">
-        <v>16.5</v>
+        <v>16.45</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.7</v>
+        <v>7.73</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>46.4</v>
+        <v>45.73</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="DX4" t="n">
-        <v>9.1</v>
+        <v>8.82</v>
       </c>
       <c r="DY4" t="n">
-        <v>5.5</v>
+        <v>5.27</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="EA4" t="n">
-        <v>18</v>
+        <v>18.27</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="EC4" t="n">
-        <v>4</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" t="n">
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2681,50 +2681,50 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AI5" t="n">
-        <v>72.8</v>
+        <v>70.17</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AK5" t="n">
         <v>3</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.4</v>
+        <v>3.83</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AN5" t="n">
-        <v>33.2</v>
+        <v>31.33</v>
       </c>
       <c r="AO5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AU5" t="n">
         <v>1</v>
       </c>
-      <c r="AP5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AV5" t="n">
         <v>0</v>
       </c>
@@ -2735,73 +2735,73 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>45.8</v>
+        <v>44</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BA5" t="n">
-        <v>8</v>
+        <v>7.67</v>
       </c>
       <c r="BB5" t="n">
-        <v>6</v>
+        <v>5.67</v>
       </c>
       <c r="BC5" t="n">
         <v>2</v>
       </c>
       <c r="BD5" t="n">
-        <v>21</v>
+        <v>21.33</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.300000000000001</v>
+        <v>8.27</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.6</v>
+        <v>4.64</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>70</v>
+        <v>72.73</v>
       </c>
       <c r="BT5" t="n">
-        <v>40</v>
+        <v>45.45</v>
       </c>
       <c r="BU5" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BV5" t="n">
         <v>0</v>
@@ -2810,7 +2810,7 @@
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>60</v>
+        <v>54.55</v>
       </c>
       <c r="BY5" t="n">
         <v>2.58</v>
@@ -2819,40 +2819,40 @@
         <v>2.84</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.46</v>
+        <v>3.6</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.53</v>
+        <v>3.79</v>
       </c>
       <c r="CC5" t="n">
-        <v>4.5</v>
+        <v>5.75</v>
       </c>
       <c r="CD5" t="n">
-        <v>5.85</v>
+        <v>6.98</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.03</v>
+        <v>2.97</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.66</v>
+        <v>2.71</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="CM5" t="n">
         <v>1.83</v>
@@ -2861,127 +2861,127 @@
         <v>1.49</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.06</v>
+        <v>2.97</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="CZ5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.96</v>
+        <v>3.82</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DH5" t="n">
-        <v>79.90000000000001</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.9</v>
+        <v>3.63</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DM5" t="n">
-        <v>40.6</v>
+        <v>38.91</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="DO5" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="DP5" t="n">
-        <v>15.8</v>
+        <v>15.55</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.5</v>
+        <v>14.55</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.800000000000001</v>
+        <v>10.18</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>51.2</v>
+        <v>49.73</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.1</v>
+        <v>10.64</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.5</v>
+        <v>8.09</v>
       </c>
       <c r="DZ5" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.8</v>
+        <v>21.91</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
         <v>0.2</v>
@@ -3084,136 +3084,136 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AI6" t="n">
-        <v>75.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AK6" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AL6" t="n">
-        <v>5.6</v>
+        <v>5.33</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AN6" t="n">
-        <v>40.6</v>
+        <v>37</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.4</v>
+        <v>4.17</v>
       </c>
       <c r="AQ6" t="n">
-        <v>19.8</v>
+        <v>19.33</v>
       </c>
       <c r="AR6" t="n">
-        <v>12.8</v>
+        <v>12.17</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.4</v>
+        <v>9.17</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AU6" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>50.2</v>
+        <v>47.67</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="BA6" t="n">
-        <v>17.6</v>
+        <v>15.67</v>
       </c>
       <c r="BB6" t="n">
-        <v>10.6</v>
+        <v>9.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>7</v>
+        <v>6.17</v>
       </c>
       <c r="BD6" t="n">
-        <v>19.2</v>
+        <v>17.83</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.89</v>
+        <v>1.68</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.6</v>
+        <v>4.83</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BH6" t="n">
-        <v>8.9</v>
+        <v>9.18</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="BN6" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="BP6" t="n">
-        <v>5.2</v>
+        <v>5.36</v>
       </c>
       <c r="BQ6" t="n">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BT6" t="n">
-        <v>70</v>
+        <v>72.73</v>
       </c>
       <c r="BU6" t="n">
-        <v>60</v>
+        <v>54.55</v>
       </c>
       <c r="BV6" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>90</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BY6" t="n">
         <v>6.07</v>
@@ -3222,169 +3222,169 @@
         <v>6.18</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.63</v>
+        <v>3.89</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.71</v>
+        <v>3.99</v>
       </c>
       <c r="CC6" t="n">
-        <v>3.51</v>
+        <v>4.64</v>
       </c>
       <c r="CD6" t="n">
-        <v>3.61</v>
+        <v>4.86</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.04</v>
+        <v>2.98</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="CI6" t="n">
         <v>1.77</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CK6" t="n">
         <v>1.74</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="CM6" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="CN6" t="n">
         <v>1.53</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.79</v>
+        <v>3.67</v>
       </c>
       <c r="CR6" t="n">
         <v>1.46</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.16</v>
+        <v>3.04</v>
       </c>
       <c r="CT6" t="n">
         <v>2.74</v>
       </c>
       <c r="CU6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="DB6" t="n">
         <v>1.36</v>
       </c>
-      <c r="CV6" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="CW6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="CX6" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="CY6" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="CZ6" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="DA6" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="DB6" t="n">
-        <v>1.38</v>
-      </c>
       <c r="DC6" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.01</v>
+        <v>3.86</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="DH6" t="n">
-        <v>70.7</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ6" t="n">
-        <v>4.7</v>
+        <v>4.91</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.4</v>
+        <v>4.36</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="DM6" t="n">
-        <v>36.7</v>
+        <v>35.09</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="DO6" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="DP6" t="n">
-        <v>18.5</v>
+        <v>18.36</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14.9</v>
+        <v>14.37</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>42</v>
+        <v>41.37</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.3</v>
+        <v>0.37</v>
       </c>
       <c r="DX6" t="n">
-        <v>14</v>
+        <v>13.27</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.699999999999999</v>
+        <v>8.27</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="EC6" t="n">
-        <v>4.2</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="7">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
         <v>5</v>
@@ -3409,79 +3409,79 @@
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6</v>
+        <v>3.17</v>
       </c>
       <c r="H7" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="M7" t="n">
-        <v>31</v>
+        <v>33.83</v>
       </c>
       <c r="N7" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="O7" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="P7" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>16.4</v>
+        <v>15.83</v>
       </c>
       <c r="R7" t="n">
-        <v>8.6</v>
+        <v>7.67</v>
       </c>
       <c r="S7" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>44.8</v>
+        <v>46.33</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>12.6</v>
+        <v>13.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.8</v>
+        <v>4.17</v>
       </c>
       <c r="AC7" t="n">
-        <v>16.8</v>
+        <v>17.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="AE7" t="n">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,70 +3565,70 @@
         <v>3.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.5</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.2</v>
+        <v>4.09</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.3</v>
+        <v>4.45</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BT7" t="n">
-        <v>30</v>
+        <v>36.36</v>
       </c>
       <c r="BU7" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BV7" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BW7" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BX7" t="n">
-        <v>50</v>
+        <v>54.55</v>
       </c>
       <c r="BY7" t="n">
-        <v>5.85</v>
+        <v>5.28</v>
       </c>
       <c r="BZ7" t="n">
-        <v>6.13</v>
+        <v>5.48</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.81</v>
+        <v>3.76</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.9</v>
+        <v>3.84</v>
       </c>
       <c r="CC7" t="n">
         <v>5.05</v>
@@ -3640,7 +3640,7 @@
         <v>1.43</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="CG7" t="n">
         <v>2.71</v>
@@ -3649,31 +3649,31 @@
         <v>1.36</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CO7" t="n">
         <v>1.35</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.81</v>
+        <v>3.75</v>
       </c>
       <c r="CR7" t="n">
         <v>1.45</v>
@@ -3682,25 +3682,25 @@
         <v>2.94</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="CU7" t="n">
         <v>1.41</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CZ7" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="DA7" t="n">
         <v>1.54</v>
@@ -3709,85 +3709,85 @@
         <v>1.37</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.94</v>
+        <v>3.89</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.1</v>
+        <v>2.46</v>
       </c>
       <c r="DH7" t="n">
-        <v>81.09999999999999</v>
+        <v>83.64</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.5</v>
+        <v>3.73</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="DM7" t="n">
-        <v>33.9</v>
+        <v>35.18</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.2</v>
+        <v>15</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.2</v>
+        <v>14.09</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.6</v>
+        <v>8.09</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>44.8</v>
+        <v>45.63</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.7</v>
+        <v>13.18</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.9</v>
+        <v>9.18</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="EA7" t="n">
-        <v>15.9</v>
+        <v>16.36</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" t="n">
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
         <v>0.33</v>
@@ -3890,136 +3890,136 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="AI8" t="n">
-        <v>82</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AL8" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AN8" t="n">
-        <v>32.25</v>
+        <v>33.2</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13.5</v>
+        <v>13.8</v>
       </c>
       <c r="AR8" t="n">
-        <v>14.25</v>
+        <v>14.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.75</v>
+        <v>7.8</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>52.25</v>
+        <v>51.4</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB8" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="BD8" t="n">
-        <v>20</v>
+        <v>19.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.8</v>
+        <v>3.73</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.3</v>
+        <v>9.73</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.8</v>
+        <v>3.73</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.7</v>
+        <v>4.45</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.6</v>
+        <v>5.27</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
       </c>
       <c r="BS8" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BT8" t="n">
-        <v>60</v>
+        <v>63.64</v>
       </c>
       <c r="BU8" t="n">
-        <v>60</v>
+        <v>54.55</v>
       </c>
       <c r="BV8" t="n">
-        <v>40</v>
+        <v>36.36</v>
       </c>
       <c r="BW8" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BX8" t="n">
-        <v>60</v>
+        <v>63.64</v>
       </c>
       <c r="BY8" t="n">
         <v>2.4</v>
@@ -4028,16 +4028,16 @@
         <v>2.45</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.85</v>
+        <v>3.79</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.03</v>
+        <v>3.96</v>
       </c>
       <c r="CC8" t="n">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="CD8" t="n">
-        <v>6.62</v>
+        <v>5.77</v>
       </c>
       <c r="CE8" t="n">
         <v>1.39</v>
@@ -4046,25 +4046,25 @@
         <v>2.9</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="CH8" t="n">
         <v>1.39</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="CM8" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CN8" t="n">
         <v>1.56</v>
@@ -4073,10 +4073,10 @@
         <v>1.31</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.58</v>
+        <v>3.63</v>
       </c>
       <c r="CR8" t="n">
         <v>1.42</v>
@@ -4085,112 +4085,112 @@
         <v>3.08</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CU8" t="n">
         <v>1.38</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CW8" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CZ8" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="DB8" t="n">
         <v>1.34</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.65</v>
+        <v>3.67</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="DG8" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="DH8" t="n">
-        <v>99.40000000000001</v>
+        <v>99.81999999999999</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.5</v>
+        <v>5.18</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DM8" t="n">
-        <v>43.2</v>
+        <v>42.64</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="DP8" t="n">
-        <v>12.5</v>
+        <v>12.73</v>
       </c>
       <c r="DQ8" t="n">
-        <v>15.4</v>
+        <v>15.46</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.1</v>
+        <v>7.18</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>59.7</v>
+        <v>58.64</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.6</v>
+        <v>12.54</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.4</v>
+        <v>7.36</v>
       </c>
       <c r="DZ8" t="n">
-        <v>5.2</v>
+        <v>5.18</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.8</v>
+        <v>21.36</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4290,139 +4290,139 @@
         <v>2.4</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AI9" t="n">
-        <v>54.5</v>
+        <v>59.2</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AN9" t="n">
-        <v>28.25</v>
+        <v>27.4</v>
       </c>
       <c r="AO9" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12.75</v>
+        <v>12.8</v>
       </c>
       <c r="AR9" t="n">
-        <v>13.5</v>
+        <v>15.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.25</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>42</v>
+        <v>42.8</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="BA9" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BC9" t="n">
         <v>4</v>
       </c>
       <c r="BD9" t="n">
-        <v>13.25</v>
+        <v>13.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.109999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="BN9" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="BP9" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.11</v>
+        <v>4.3</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BT9" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BU9" t="n">
-        <v>44.44</v>
+        <v>40</v>
       </c>
       <c r="BV9" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BW9" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BX9" t="n">
-        <v>44.44</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
         <v>4.39</v>
@@ -4431,40 +4431,40 @@
         <v>4.7</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.73</v>
+        <v>3.69</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.06</v>
+        <v>3.02</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.25</v>
+        <v>3.29</v>
       </c>
       <c r="CE9" t="n">
         <v>1.38</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="CH9" t="n">
         <v>1.39</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CK9" t="n">
         <v>1.76</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CM9" t="n">
         <v>1.98</v>
@@ -4476,10 +4476,10 @@
         <v>1.28</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="CR9" t="n">
         <v>1.4</v>
@@ -4488,22 +4488,22 @@
         <v>2.93</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CU9" t="n">
         <v>1.41</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CX9" t="n">
         <v>1.77</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.03</v>
@@ -4518,82 +4518,82 @@
         <v>1.99</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="DE9" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="DH9" t="n">
-        <v>63.22</v>
+        <v>64.7</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DM9" t="n">
-        <v>27.67</v>
+        <v>27.3</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.33</v>
+        <v>14.2</v>
       </c>
       <c r="DQ9" t="n">
-        <v>15.89</v>
+        <v>16.6</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.779999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>41.11</v>
+        <v>41.6</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.33</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DY9" t="n">
-        <v>6.11</v>
+        <v>5.9</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="EA9" t="n">
-        <v>17</v>
+        <v>16.8</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="10">
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
         <v>5</v>
@@ -4615,82 +4615,82 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="G10" t="n">
-        <v>3.6</v>
+        <v>3.33</v>
       </c>
       <c r="H10" t="n">
-        <v>130</v>
+        <v>120.33</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="K10" t="n">
-        <v>8.4</v>
+        <v>8.17</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="M10" t="n">
-        <v>76.2</v>
+        <v>75.17</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="O10" t="n">
-        <v>4.8</v>
+        <v>4.83</v>
       </c>
       <c r="P10" t="n">
-        <v>10.4</v>
+        <v>9.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>13.4</v>
+        <v>13.17</v>
       </c>
       <c r="R10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="T10" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>62.6</v>
+        <v>63</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>18.6</v>
+        <v>20</v>
       </c>
       <c r="AA10" t="n">
-        <v>12.6</v>
+        <v>13.83</v>
       </c>
       <c r="AB10" t="n">
-        <v>6</v>
+        <v>6.17</v>
       </c>
       <c r="AC10" t="n">
-        <v>25.6</v>
+        <v>24</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AF10" t="n">
         <v>0.2</v>
@@ -4777,34 +4777,34 @@
         <v>3</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.800000000000001</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BI10" t="n">
         <v>3</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.6</v>
+        <v>4.64</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
@@ -4813,31 +4813,31 @@
         <v>100</v>
       </c>
       <c r="BT10" t="n">
-        <v>50</v>
+        <v>54.55</v>
       </c>
       <c r="BU10" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BV10" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="CA10" t="n">
-        <v>5.12</v>
+        <v>5.11</v>
       </c>
       <c r="CB10" t="n">
-        <v>5.72</v>
+        <v>5.78</v>
       </c>
       <c r="CC10" t="n">
         <v>1.74</v>
@@ -4846,52 +4846,52 @@
         <v>1.77</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="CJ10" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="CM10" t="n">
         <v>1.87</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.76</v>
+        <v>2.71</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="CU10" t="n">
         <v>1.48</v>
@@ -4900,103 +4900,103 @@
         <v>1.68</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CZ10" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.17</v>
+        <v>3.11</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="DG10" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="DH10" t="n">
-        <v>114.9</v>
+        <v>111</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="DK10" t="n">
-        <v>7.3</v>
+        <v>7.27</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="DM10" t="n">
-        <v>63.3</v>
+        <v>63.91</v>
       </c>
       <c r="DN10" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DO10" t="n">
-        <v>3.8</v>
+        <v>3.91</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.3</v>
+        <v>12.55</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.5</v>
+        <v>13.37</v>
       </c>
       <c r="DR10" t="n">
-        <v>4.3</v>
+        <v>4.36</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>60.8</v>
+        <v>61.18</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX10" t="n">
-        <v>15.7</v>
+        <v>16.73</v>
       </c>
       <c r="DY10" t="n">
-        <v>10.2</v>
+        <v>11.09</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.5</v>
+        <v>5.64</v>
       </c>
       <c r="EA10" t="n">
-        <v>26.1</v>
+        <v>25.18</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="11">
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
@@ -5018,82 +5018,82 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="G11" t="n">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="H11" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="J11" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="K11" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="M11" t="n">
-        <v>71.40000000000001</v>
+        <v>69</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2</v>
+        <v>3.33</v>
       </c>
       <c r="P11" t="n">
-        <v>10.6</v>
+        <v>10.33</v>
       </c>
       <c r="Q11" t="n">
-        <v>14.8</v>
+        <v>15.17</v>
       </c>
       <c r="R11" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="T11" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>66.40000000000001</v>
+        <v>66.17</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>17.4</v>
+        <v>17.67</v>
       </c>
       <c r="AA11" t="n">
-        <v>11.8</v>
+        <v>12</v>
       </c>
       <c r="AB11" t="n">
-        <v>5.6</v>
+        <v>5.67</v>
       </c>
       <c r="AC11" t="n">
-        <v>25.8</v>
+        <v>25.67</v>
       </c>
       <c r="AD11" t="n">
         <v>2.01</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AF11" t="n">
         <v>0.4</v>
@@ -5177,70 +5177,70 @@
         <v>1.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="BH11" t="n">
-        <v>7.8</v>
+        <v>8.18</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.6</v>
+        <v>3.91</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.2</v>
+        <v>4.27</v>
       </c>
       <c r="BR11" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BS11" t="n">
-        <v>70</v>
+        <v>72.73</v>
       </c>
       <c r="BT11" t="n">
-        <v>60</v>
+        <v>63.64</v>
       </c>
       <c r="BU11" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BV11" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BW11" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BX11" t="n">
-        <v>40</v>
+        <v>36.36</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.57</v>
+        <v>4.74</v>
       </c>
       <c r="CB11" t="n">
-        <v>5.06</v>
+        <v>5.22</v>
       </c>
       <c r="CC11" t="n">
         <v>2.02</v>
@@ -5252,13 +5252,13 @@
         <v>1.34</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CI11" t="n">
         <v>1.77</v>
@@ -5267,37 +5267,37 @@
         <v>2</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="CM11" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CN11" t="n">
         <v>1.59</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.98</v>
+        <v>2.93</v>
       </c>
       <c r="CR11" t="n">
         <v>1.37</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.67</v>
+        <v>2.61</v>
       </c>
       <c r="CT11" t="n">
         <v>3.08</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="CV11" t="n">
         <v>1.81</v>
@@ -5309,97 +5309,97 @@
         <v>1.78</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.04</v>
+        <v>2.98</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="DG11" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="DH11" t="n">
-        <v>115.5</v>
+        <v>113.82</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.2</v>
+        <v>5.45</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.2</v>
+        <v>0.36</v>
       </c>
       <c r="DM11" t="n">
-        <v>60.5</v>
+        <v>60.18</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.8</v>
+        <v>11.54</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13.6</v>
+        <v>13.91</v>
       </c>
       <c r="DR11" t="n">
-        <v>4.8</v>
+        <v>4.73</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>63.1</v>
+        <v>63.27</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>14.8</v>
+        <v>15.18</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.9</v>
+        <v>10.18</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="EA11" t="n">
-        <v>24.4</v>
+        <v>24.46</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5502,49 +5502,49 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH12" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AI12" t="n">
-        <v>58</v>
+        <v>65.83</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AK12" t="n">
-        <v>4.2</v>
+        <v>3.67</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AN12" t="n">
-        <v>19.6</v>
+        <v>28.33</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14</v>
+        <v>14.33</v>
       </c>
       <c r="AR12" t="n">
-        <v>12.6</v>
+        <v>11.83</v>
       </c>
       <c r="AS12" t="n">
-        <v>10.6</v>
+        <v>9.67</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,82 +5556,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>33.2</v>
+        <v>37.83</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>7.8</v>
+        <v>7.83</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.6</v>
+        <v>5.33</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>13.4</v>
+        <v>14.67</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.79</v>
+        <v>0.88</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.699999999999999</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.3</v>
+        <v>4.27</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.4</v>
+        <v>4.18</v>
       </c>
       <c r="BR12" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BS12" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT12" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BU12" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BV12" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BW12" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BX12" t="n">
-        <v>40</v>
+        <v>45.45</v>
       </c>
       <c r="BY12" t="n">
         <v>3.26</v>
@@ -5640,79 +5640,79 @@
         <v>3.44</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.02</v>
+        <v>3.93</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.28</v>
+        <v>4.18</v>
       </c>
       <c r="CC12" t="n">
-        <v>8.4</v>
+        <v>7.67</v>
       </c>
       <c r="CD12" t="n">
-        <v>10.95</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF12" t="n">
         <v>3.02</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="CJ12" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="CK12" t="n">
         <v>1.88</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="CM12" t="n">
         <v>1.86</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CP12" t="n">
         <v>2.1</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.83</v>
+        <v>3.8</v>
       </c>
       <c r="CR12" t="n">
         <v>1.43</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="CT12" t="n">
         <v>2.83</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="CX12" t="n">
         <v>1.91</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CZ12" t="n">
         <v>1.9</v>
@@ -5733,76 +5733,76 @@
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="DH12" t="n">
-        <v>68.59999999999999</v>
+        <v>71.91</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ12" t="n">
-        <v>3.6</v>
+        <v>3.37</v>
       </c>
       <c r="DK12" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DM12" t="n">
-        <v>25.8</v>
+        <v>30</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.9</v>
+        <v>13.18</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.2</v>
+        <v>11.82</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.300000000000001</v>
+        <v>8.91</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>41.1</v>
+        <v>42.91</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="DX12" t="n">
-        <v>8.4</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DY12" t="n">
-        <v>6.1</v>
+        <v>5.91</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="EA12" t="n">
-        <v>16.4</v>
+        <v>16.82</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="EC12" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E13" t="n">
         <v>0.2</v>
@@ -5902,139 +5902,139 @@
         <v>2.6</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="AI13" t="n">
-        <v>105.25</v>
+        <v>103</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AL13" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>58.5</v>
+        <v>57</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AR13" t="n">
-        <v>15.75</v>
+        <v>15.2</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.25</v>
+        <v>5.6</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>64.25</v>
+        <v>61.2</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>13.25</v>
+        <v>14.2</v>
       </c>
       <c r="BB13" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="BH13" t="n">
-        <v>7.11</v>
+        <v>7.5</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="BO13" t="n">
         <v>1</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.56</v>
+        <v>3.8</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BT13" t="n">
-        <v>33.33</v>
+        <v>40</v>
       </c>
       <c r="BU13" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BV13" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>66.67</v>
+        <v>60</v>
       </c>
       <c r="BY13" t="n">
         <v>1.9</v>
@@ -6043,169 +6043,169 @@
         <v>2.16</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.12</v>
+        <v>4.18</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.43</v>
+        <v>4.47</v>
       </c>
       <c r="CC13" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="CD13" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="CE13" t="n">
         <v>1.38</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.89</v>
+        <v>2.93</v>
       </c>
       <c r="CH13" t="n">
         <v>1.42</v>
       </c>
       <c r="CI13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="CM13" t="n">
         <v>1.79</v>
       </c>
-      <c r="CJ13" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="CK13" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="CL13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="CM13" t="n">
-        <v>1.78</v>
-      </c>
       <c r="CN13" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.86</v>
+        <v>2.81</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="DB13" t="n">
         <v>1.3</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.41</v>
+        <v>3.35</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF13" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="DH13" t="n">
-        <v>102.78</v>
+        <v>101.9</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.56</v>
+        <v>4.9</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DM13" t="n">
-        <v>57</v>
+        <v>56.4</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="DP13" t="n">
-        <v>16.33</v>
+        <v>15.4</v>
       </c>
       <c r="DQ13" t="n">
-        <v>15.33</v>
+        <v>15.1</v>
       </c>
       <c r="DR13" t="n">
-        <v>5.44</v>
+        <v>5.6</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>56.67</v>
+        <v>55.9</v>
       </c>
       <c r="DW13" t="n">
         <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>13.44</v>
+        <v>13.9</v>
       </c>
       <c r="DY13" t="n">
-        <v>9.33</v>
+        <v>9.6</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.11</v>
+        <v>4.3</v>
       </c>
       <c r="EA13" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="14">
@@ -6215,10 +6215,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
         <v>5</v>
@@ -6227,49 +6227,49 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="H14" t="n">
-        <v>81.40000000000001</v>
+        <v>80.33</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="M14" t="n">
-        <v>34.2</v>
+        <v>33.5</v>
       </c>
       <c r="N14" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="O14" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="P14" t="n">
-        <v>16.6</v>
+        <v>16</v>
       </c>
       <c r="Q14" t="n">
-        <v>15.4</v>
+        <v>14</v>
       </c>
       <c r="R14" t="n">
-        <v>7.2</v>
+        <v>7.33</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6281,28 +6281,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>43.4</v>
+        <v>44.67</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="Z14" t="n">
-        <v>10.8</v>
+        <v>10.67</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.4</v>
+        <v>9.17</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>22.6</v>
+        <v>21.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6386,70 +6386,70 @@
         <v>3</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.300000000000001</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.1</v>
+        <v>4.27</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.1</v>
+        <v>5.09</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BT14" t="n">
-        <v>50</v>
+        <v>54.55</v>
       </c>
       <c r="BU14" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BV14" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BW14" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BX14" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BY14" t="n">
-        <v>4.64</v>
+        <v>4.95</v>
       </c>
       <c r="BZ14" t="n">
-        <v>5.28</v>
+        <v>5.62</v>
       </c>
       <c r="CA14" t="n">
         <v>4.65</v>
       </c>
       <c r="CB14" t="n">
-        <v>5.45</v>
+        <v>5.39</v>
       </c>
       <c r="CC14" t="n">
         <v>10.03</v>
@@ -6461,25 +6461,25 @@
         <v>1.35</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CM14" t="n">
         <v>1.93</v>
@@ -6488,40 +6488,40 @@
         <v>1.58</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="CQ14" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="CT14" t="n">
         <v>3.04</v>
-      </c>
-      <c r="CR14" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="CS14" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="CT14" t="n">
-        <v>3</v>
       </c>
       <c r="CU14" t="n">
         <v>1.51</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CZ14" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="DA14" t="n">
         <v>1.59</v>
@@ -6530,85 +6530,85 @@
         <v>1.26</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="DG14" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DH14" t="n">
-        <v>63.9</v>
+        <v>64.91</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="DK14" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DM14" t="n">
-        <v>25.7</v>
+        <v>26.09</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="DP14" t="n">
-        <v>15.3</v>
+        <v>15.09</v>
       </c>
       <c r="DQ14" t="n">
-        <v>12</v>
+        <v>11.55</v>
       </c>
       <c r="DR14" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>35.9</v>
+        <v>37.27</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DX14" t="n">
-        <v>8.5</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="DY14" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="DZ14" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.5</v>
+        <v>17.36</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="15">
@@ -6618,61 +6618,61 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F15" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="G15" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="H15" t="n">
-        <v>46.5</v>
+        <v>56</v>
       </c>
       <c r="I15" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="K15" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="M15" t="n">
-        <v>19.25</v>
+        <v>26.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="O15" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="P15" t="n">
-        <v>13.5</v>
+        <v>14.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="R15" t="n">
-        <v>8.75</v>
+        <v>7.8</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="T15" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -6684,28 +6684,28 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>44</v>
+        <v>45.6</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>13</v>
+        <v>14.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.75</v>
+        <v>10</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>19</v>
+        <v>19.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.82</v>
+        <v>1.06</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AF15" t="n">
         <v>0.17</v>
@@ -6789,70 +6789,70 @@
         <v>3.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="BH15" t="n">
-        <v>8.800000000000001</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="BO15" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.4</v>
+        <v>5.09</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>70</v>
+        <v>72.73</v>
       </c>
       <c r="BT15" t="n">
-        <v>50</v>
+        <v>54.55</v>
       </c>
       <c r="BU15" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BV15" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BW15" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BX15" t="n">
-        <v>40</v>
+        <v>45.45</v>
       </c>
       <c r="BY15" t="n">
-        <v>5.62</v>
+        <v>5.11</v>
       </c>
       <c r="BZ15" t="n">
-        <v>5.78</v>
+        <v>5.28</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.88</v>
+        <v>3.82</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.01</v>
+        <v>3.94</v>
       </c>
       <c r="CC15" t="n">
         <v>5.94</v>
@@ -6864,67 +6864,67 @@
         <v>1.4</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CH15" t="n">
         <v>1.37</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CJ15" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CM15" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.58</v>
+        <v>3.63</v>
       </c>
       <c r="CR15" t="n">
         <v>1.43</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CU15" t="n">
         <v>1.4</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CW15" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CY15" t="n">
         <v>2.31</v>
       </c>
       <c r="CZ15" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DA15" t="n">
         <v>1.59</v>
@@ -6933,52 +6933,52 @@
         <v>1.34</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.66</v>
+        <v>3.68</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF15" t="n">
         <v>2</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="DH15" t="n">
-        <v>63.6</v>
+        <v>66.36</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DM15" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="DP15" t="n">
-        <v>15.1</v>
+        <v>15.27</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.9</v>
+        <v>15.82</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>43.4</v>
+        <v>44.18</v>
       </c>
       <c r="DW15" t="n">
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.1</v>
+        <v>11</v>
       </c>
       <c r="DY15" t="n">
-        <v>5.9</v>
+        <v>6.73</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.2</v>
+        <v>4.27</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.4</v>
+        <v>19.73</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.93</v>
+        <v>1.03</v>
       </c>
       <c r="EC15" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -3475,7 +3475,7 @@
         <v>4.17</v>
       </c>
       <c r="AC7" t="n">
-        <v>17.5</v>
+        <v>17.67</v>
       </c>
       <c r="AD7" t="n">
         <v>1.39</v>
@@ -3622,13 +3622,13 @@
         <v>5.28</v>
       </c>
       <c r="BZ7" t="n">
-        <v>5.48</v>
+        <v>5.49</v>
       </c>
       <c r="CA7" t="n">
         <v>3.76</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.84</v>
+        <v>3.83</v>
       </c>
       <c r="CC7" t="n">
         <v>5.05</v>
@@ -3682,7 +3682,7 @@
         <v>2.94</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="CU7" t="n">
         <v>1.41</v>
@@ -3781,7 +3781,7 @@
         <v>4</v>
       </c>
       <c r="EA7" t="n">
-        <v>16.36</v>
+        <v>16.46</v>
       </c>
       <c r="EB7" t="n">
         <v>1.37</v>
@@ -4434,13 +4434,13 @@
         <v>3.6</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.69</v>
+        <v>3.68</v>
       </c>
       <c r="CC9" t="n">
         <v>3.02</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="CE9" t="n">
         <v>1.38</v>
@@ -4488,7 +4488,7 @@
         <v>2.93</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="CU9" t="n">
         <v>1.41</v>
@@ -4515,10 +4515,10 @@
         <v>1.3</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="DE9" t="n">
         <v>0.1</v>

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1472,136 +1472,136 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>91</v>
+        <v>88.83</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.8</v>
+        <v>3.17</v>
       </c>
       <c r="AL2" t="n">
-        <v>5.4</v>
+        <v>4.83</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="AN2" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AQ2" t="n">
-        <v>17.2</v>
+        <v>18</v>
       </c>
       <c r="AR2" t="n">
-        <v>13.4</v>
+        <v>13.83</v>
       </c>
       <c r="AS2" t="n">
-        <v>8</v>
+        <v>7.67</v>
       </c>
       <c r="AT2" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>57.2</v>
+        <v>56</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="BA2" t="n">
-        <v>16.2</v>
+        <v>14.67</v>
       </c>
       <c r="BB2" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.2</v>
+        <v>4.17</v>
       </c>
       <c r="BD2" t="n">
-        <v>21.8</v>
+        <v>22.33</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.449999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.18</v>
+        <v>0.33</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="BN2" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.73</v>
+        <v>3.83</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.73</v>
+        <v>4.5</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BT2" t="n">
-        <v>9.09</v>
+        <v>16.67</v>
       </c>
       <c r="BU2" t="n">
-        <v>9.09</v>
+        <v>16.67</v>
       </c>
       <c r="BV2" t="n">
-        <v>9.09</v>
+        <v>16.67</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>18.18</v>
+        <v>25</v>
       </c>
       <c r="BY2" t="n">
         <v>1.44</v>
@@ -1610,79 +1610,79 @@
         <v>1.45</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.77</v>
+        <v>4.62</v>
       </c>
       <c r="CB2" t="n">
-        <v>5.06</v>
+        <v>4.89</v>
       </c>
       <c r="CC2" t="n">
-        <v>1.99</v>
+        <v>2.11</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.16</v>
+        <v>2.29</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CK2" t="n">
         <v>1.78</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CM2" t="n">
         <v>1.95</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="CX2" t="n">
         <v>1.81</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CZ2" t="n">
         <v>2</v>
@@ -1691,88 +1691,88 @@
         <v>1.61</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.09</v>
+        <v>3.16</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.27</v>
+        <v>3</v>
       </c>
       <c r="DH2" t="n">
-        <v>97.64</v>
+        <v>96</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="DK2" t="n">
-        <v>6</v>
+        <v>5.66</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="DM2" t="n">
-        <v>64.81999999999999</v>
+        <v>62</v>
       </c>
       <c r="DN2" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.73</v>
+        <v>2.66</v>
       </c>
       <c r="DP2" t="n">
-        <v>16.09</v>
+        <v>16.58</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13</v>
+        <v>13.25</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.82</v>
+        <v>5.84</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.18</v>
+        <v>0.34</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.18</v>
+        <v>0.34</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>59.64</v>
+        <v>58.84</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="DX2" t="n">
-        <v>17.55</v>
+        <v>16.67</v>
       </c>
       <c r="DY2" t="n">
-        <v>13</v>
+        <v>12.16</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.54</v>
+        <v>4.5</v>
       </c>
       <c r="EA2" t="n">
-        <v>21.73</v>
+        <v>22</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
         <v>6</v>
@@ -1794,49 +1794,49 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="G3" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>106.4</v>
+        <v>108.17</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="K3" t="n">
-        <v>5.6</v>
+        <v>5.83</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="M3" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="P3" t="n">
-        <v>14.2</v>
+        <v>14.17</v>
       </c>
       <c r="Q3" t="n">
-        <v>16</v>
+        <v>16.83</v>
       </c>
       <c r="R3" t="n">
-        <v>7.4</v>
+        <v>6.33</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>58.6</v>
+        <v>59.83</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="Z3" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>10.8</v>
+        <v>10.67</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.2</v>
+        <v>4.83</v>
       </c>
       <c r="AC3" t="n">
-        <v>26.6</v>
+        <v>24.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="AF3" t="n">
         <v>0.17</v>
@@ -1953,46 +1953,46 @@
         <v>1.83</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.27</v>
+        <v>9.08</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="BP3" t="n">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.55</v>
+        <v>6.42</v>
       </c>
       <c r="BR3" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS3" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BT3" t="n">
-        <v>27.27</v>
+        <v>33.33</v>
       </c>
       <c r="BU3" t="n">
         <v>0</v>
@@ -2004,19 +2004,19 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BY3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BZ3" t="n">
         <v>1.94</v>
       </c>
-      <c r="BZ3" t="n">
-        <v>2.03</v>
-      </c>
       <c r="CA3" t="n">
-        <v>3.72</v>
+        <v>3.76</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.01</v>
+        <v>4.03</v>
       </c>
       <c r="CC3" t="n">
         <v>4.04</v>
@@ -2028,13 +2028,13 @@
         <v>1.41</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CI3" t="n">
         <v>1.73</v>
@@ -2043,16 +2043,16 @@
         <v>2.01</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CL3" t="n">
         <v>2.53</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CO3" t="n">
         <v>1.33</v>
@@ -2061,16 +2061,16 @@
         <v>2.05</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="CR3" t="n">
         <v>1.42</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="CU3" t="n">
         <v>1.4</v>
@@ -2085,97 +2085,97 @@
         <v>1.87</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CZ3" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="DB3" t="n">
         <v>1.34</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.72</v>
+        <v>3.69</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.73</v>
+        <v>3.83</v>
       </c>
       <c r="DH3" t="n">
-        <v>95.27</v>
+        <v>97.08</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.37</v>
+        <v>5.5</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="DM3" t="n">
-        <v>45.73</v>
+        <v>45.75</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.55</v>
+        <v>0.59</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="DP3" t="n">
-        <v>15.27</v>
+        <v>15.17</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.73</v>
+        <v>15.25</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.73</v>
+        <v>6.25</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>52.73</v>
+        <v>53.83</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX3" t="n">
-        <v>12.64</v>
+        <v>13.08</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.550000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.09</v>
+        <v>4.42</v>
       </c>
       <c r="EA3" t="n">
-        <v>22.18</v>
+        <v>21.5</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" t="n">
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
         <v>0.2</v>
@@ -2278,136 +2278,136 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="AI4" t="n">
-        <v>79.17</v>
+        <v>79.86</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.67</v>
+        <v>3.29</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AN4" t="n">
-        <v>28.67</v>
+        <v>28.57</v>
       </c>
       <c r="AO4" t="n">
         <v>1</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AQ4" t="n">
-        <v>15</v>
+        <v>15.43</v>
       </c>
       <c r="AR4" t="n">
-        <v>17.33</v>
+        <v>17</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.67</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>44.83</v>
+        <v>43.43</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>7.33</v>
+        <v>7.57</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.67</v>
+        <v>4.43</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.67</v>
+        <v>3.14</v>
       </c>
       <c r="BD4" t="n">
-        <v>16.5</v>
+        <v>17.29</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.67</v>
+        <v>3.29</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.82</v>
+        <v>9.17</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BP4" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.82</v>
+        <v>4.92</v>
       </c>
       <c r="BR4" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS4" t="n">
-        <v>81.81999999999999</v>
+        <v>75</v>
       </c>
       <c r="BT4" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BU4" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BV4" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW4" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX4" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BY4" t="n">
         <v>2.66</v>
@@ -2416,169 +2416,169 @@
         <v>2.91</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.93</v>
+        <v>3.86</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.2</v>
+        <v>4.09</v>
       </c>
       <c r="CC4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="CD4" t="n">
-        <v>8.74</v>
+        <v>7.97</v>
       </c>
       <c r="CE4" t="n">
         <v>1.42</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CI4" t="n">
         <v>1.77</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CK4" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CV4" t="n">
         <v>1.82</v>
       </c>
-      <c r="CL4" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="CM4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="CN4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="CO4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="CP4" t="n">
-        <v>2</v>
-      </c>
-      <c r="CQ4" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="CS4" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="CT4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="CU4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="CV4" t="n">
-        <v>1.81</v>
-      </c>
       <c r="CW4" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="CZ4" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.51</v>
+        <v>3.58</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.27</v>
+        <v>2.41</v>
       </c>
       <c r="DH4" t="n">
-        <v>72.55</v>
+        <v>73.5</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DJ4" t="n">
-        <v>4.09</v>
+        <v>3.84</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.18</v>
+        <v>4.33</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DM4" t="n">
-        <v>34.91</v>
+        <v>34.33</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.36</v>
+        <v>13.75</v>
       </c>
       <c r="DQ4" t="n">
-        <v>16.45</v>
+        <v>16.33</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.73</v>
+        <v>7.59</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>45.73</v>
+        <v>44.83</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX4" t="n">
-        <v>8.82</v>
+        <v>8.83</v>
       </c>
       <c r="DY4" t="n">
-        <v>5.27</v>
+        <v>5.08</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.27</v>
+        <v>18.59</v>
       </c>
       <c r="EB4" t="n">
         <v>1.07</v>
       </c>
       <c r="EC4" t="n">
-        <v>3.91</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="5">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
         <v>6</v>
@@ -2600,13 +2600,13 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="H5" t="n">
-        <v>87</v>
+        <v>88.67</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -2615,64 +2615,64 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="M5" t="n">
-        <v>48</v>
+        <v>47.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="P5" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="Q5" t="n">
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="R5" t="n">
-        <v>6.2</v>
+        <v>5.83</v>
       </c>
       <c r="S5" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>56.6</v>
+        <v>58</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>14.2</v>
+        <v>13.67</v>
       </c>
       <c r="AA5" t="n">
-        <v>11</v>
+        <v>10.33</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.2</v>
+        <v>3.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>22.6</v>
+        <v>23.67</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AE5" t="n">
         <v>2</v>
@@ -2759,49 +2759,49 @@
         <v>2.83</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.27</v>
+        <v>8.67</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.64</v>
+        <v>4.83</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3.64</v>
+        <v>3.83</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>72.73</v>
+        <v>66.67</v>
       </c>
       <c r="BT5" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BU5" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BV5" t="n">
         <v>0</v>
@@ -2810,19 +2810,19 @@
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.84</v>
+        <v>2.79</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.79</v>
+        <v>3.71</v>
       </c>
       <c r="CC5" t="n">
         <v>5.75</v>
@@ -2831,67 +2831,67 @@
         <v>6.98</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="CH5" t="n">
         <v>1.37</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="CM5" t="n">
         <v>1.83</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="CR5" t="n">
         <v>1.44</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.97</v>
+        <v>3.01</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CX5" t="n">
         <v>1.94</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="CZ5" t="n">
         <v>1.87</v>
@@ -2900,88 +2900,88 @@
         <v>1.53</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.82</v>
+        <v>3.86</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="DH5" t="n">
-        <v>77.81999999999999</v>
+        <v>79.42</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.63</v>
+        <v>3.92</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="DM5" t="n">
-        <v>38.91</v>
+        <v>39.42</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.82</v>
+        <v>2.08</v>
       </c>
       <c r="DP5" t="n">
-        <v>15.55</v>
+        <v>15.5</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.55</v>
+        <v>14.75</v>
       </c>
       <c r="DR5" t="n">
-        <v>10.18</v>
+        <v>9.67</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>49.73</v>
+        <v>51</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.64</v>
+        <v>10.67</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.09</v>
+        <v>8</v>
       </c>
       <c r="DZ5" t="n">
-        <v>2.55</v>
+        <v>2.66</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.91</v>
+        <v>22.5</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="6">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="H6" t="n">
-        <v>65.8</v>
+        <v>68.33</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>4.8</v>
+        <v>4.67</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2</v>
+        <v>3.33</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="M6" t="n">
-        <v>32.8</v>
+        <v>34.17</v>
       </c>
       <c r="N6" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="O6" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="P6" t="n">
-        <v>17.2</v>
+        <v>16.17</v>
       </c>
       <c r="Q6" t="n">
-        <v>17</v>
+        <v>16.33</v>
       </c>
       <c r="R6" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3057,28 +3057,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>33.8</v>
+        <v>37.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="Z6" t="n">
-        <v>10.4</v>
+        <v>12.17</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.8</v>
+        <v>8.17</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AC6" t="n">
-        <v>13.8</v>
+        <v>13.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AE6" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,67 +3162,67 @@
         <v>4.83</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.18</v>
+        <v>9.08</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="BL6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BM6" t="n">
         <v>1</v>
       </c>
-      <c r="BM6" t="n">
-        <v>1.09</v>
-      </c>
       <c r="BN6" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="BP6" t="n">
-        <v>5.36</v>
+        <v>5.17</v>
       </c>
       <c r="BQ6" t="n">
-        <v>3.82</v>
+        <v>3.92</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BT6" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BU6" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BV6" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>81.81999999999999</v>
+        <v>75</v>
       </c>
       <c r="BY6" t="n">
-        <v>6.07</v>
+        <v>5.31</v>
       </c>
       <c r="BZ6" t="n">
-        <v>6.18</v>
+        <v>5.42</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.89</v>
+        <v>3.86</v>
       </c>
       <c r="CB6" t="n">
         <v>3.99</v>
@@ -3237,7 +3237,7 @@
         <v>1.43</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="CG6" t="n">
         <v>2.72</v>
@@ -3255,10 +3255,10 @@
         <v>1.74</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CM6" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CN6" t="n">
         <v>1.53</v>
@@ -3267,124 +3267,124 @@
         <v>1.34</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CS6" t="n">
         <v>3.04</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="CU6" t="n">
         <v>1.4</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CZ6" t="n">
         <v>1.88</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="DB6" t="n">
         <v>1.36</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.86</v>
+        <v>3.83</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF6" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="DH6" t="n">
-        <v>70.81999999999999</v>
+        <v>71.67</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ6" t="n">
-        <v>4.91</v>
+        <v>4.84</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.36</v>
+        <v>4.33</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="DM6" t="n">
-        <v>35.09</v>
+        <v>35.58</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="DO6" t="n">
-        <v>3.09</v>
+        <v>2.92</v>
       </c>
       <c r="DP6" t="n">
-        <v>18.36</v>
+        <v>17.75</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14.37</v>
+        <v>14.25</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.640000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>41.37</v>
+        <v>42.58</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.37</v>
+        <v>0.42</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.27</v>
+        <v>13.92</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.27</v>
+        <v>8.83</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5</v>
+        <v>5.08</v>
       </c>
       <c r="EA6" t="n">
-        <v>16</v>
+        <v>15.66</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="EC6" t="n">
-        <v>4.36</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3487,136 +3487,136 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AI7" t="n">
-        <v>89.2</v>
+        <v>86.5</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AL7" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AN7" t="n">
-        <v>36.8</v>
+        <v>32.67</v>
       </c>
       <c r="AO7" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AQ7" t="n">
-        <v>14.4</v>
+        <v>15.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>12</v>
+        <v>12.17</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.6</v>
+        <v>8.67</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AU7" t="n">
         <v>1</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>44.8</v>
+        <v>43</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="BA7" t="n">
-        <v>12.8</v>
+        <v>11</v>
       </c>
       <c r="BB7" t="n">
-        <v>9</v>
+        <v>7.67</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.8</v>
+        <v>3.33</v>
       </c>
       <c r="BD7" t="n">
-        <v>15</v>
+        <v>15.83</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.550000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.09</v>
+        <v>3.92</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BT7" t="n">
-        <v>36.36</v>
+        <v>41.67</v>
       </c>
       <c r="BU7" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BV7" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW7" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX7" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BY7" t="n">
         <v>5.28</v>
@@ -3625,28 +3625,28 @@
         <v>5.49</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.76</v>
+        <v>3.8</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.83</v>
+        <v>3.87</v>
       </c>
       <c r="CC7" t="n">
-        <v>5.05</v>
+        <v>5.09</v>
       </c>
       <c r="CD7" t="n">
-        <v>5.31</v>
+        <v>5.52</v>
       </c>
       <c r="CE7" t="n">
         <v>1.43</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CI7" t="n">
         <v>1.77</v>
@@ -3655,34 +3655,34 @@
         <v>1.99</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CN7" t="n">
         <v>1.51</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="CU7" t="n">
         <v>1.41</v>
@@ -3697,7 +3697,7 @@
         <v>1.92</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CZ7" t="n">
         <v>1.9</v>
@@ -3706,88 +3706,88 @@
         <v>1.54</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.89</v>
+        <v>3.84</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.46</v>
+        <v>2.25</v>
       </c>
       <c r="DH7" t="n">
-        <v>83.64</v>
+        <v>82.75</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.64</v>
+        <v>3.83</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.73</v>
+        <v>3.42</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DM7" t="n">
-        <v>35.18</v>
+        <v>33.25</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="DP7" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.09</v>
+        <v>14</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.09</v>
+        <v>8.17</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>45.63</v>
+        <v>44.66</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
       <c r="DX7" t="n">
-        <v>13.18</v>
+        <v>12.25</v>
       </c>
       <c r="DY7" t="n">
-        <v>9.18</v>
+        <v>8.5</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="EA7" t="n">
-        <v>16.46</v>
+        <v>16.75</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.46</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="8">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
         <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="F8" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="G8" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="H8" t="n">
+        <v>103.86</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M8" t="n">
+        <v>46.14</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="P8" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>15.86</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T8" t="n">
         <v>3</v>
       </c>
-      <c r="H8" t="n">
-        <v>111</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="M8" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P8" t="n">
-        <v>11.83</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>16.17</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="U8" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>61.43</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>23.43</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>64.67</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>15.33</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>23</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.17</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3968,70 +3968,70 @@
         <v>2.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.73</v>
+        <v>3.83</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.73</v>
+        <v>9.5</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.73</v>
+        <v>3.83</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.27</v>
+        <v>5.17</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
       </c>
       <c r="BS8" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BT8" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BU8" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BV8" t="n">
-        <v>36.36</v>
+        <v>41.67</v>
       </c>
       <c r="BW8" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BX8" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.45</v>
+        <v>2.66</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.79</v>
+        <v>3.75</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="CC8" t="n">
         <v>5.9</v>
@@ -4040,67 +4040,67 @@
         <v>5.77</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="CH8" t="n">
         <v>1.39</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="CM8" t="n">
         <v>1.92</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CO8" t="n">
         <v>1.31</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.63</v>
+        <v>3.57</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="CW8" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="CX8" t="n">
         <v>1.85</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CZ8" t="n">
         <v>1.96</v>
@@ -4109,88 +4109,88 @@
         <v>1.57</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="DC8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>96.58</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DO8" t="n">
         <v>2.08</v>
       </c>
-      <c r="DD8" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="DE8" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="DF8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="DG8" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="DH8" t="n">
-        <v>99.81999999999999</v>
-      </c>
-      <c r="DI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ8" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="DK8" t="n">
-        <v>5.18</v>
-      </c>
-      <c r="DL8" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="DM8" t="n">
-        <v>42.64</v>
-      </c>
-      <c r="DN8" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="DO8" t="n">
-        <v>2.27</v>
-      </c>
       <c r="DP8" t="n">
-        <v>12.73</v>
+        <v>12.83</v>
       </c>
       <c r="DQ8" t="n">
-        <v>15.46</v>
+        <v>15.34</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.18</v>
+        <v>7</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>58.64</v>
+        <v>57.25</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.54</v>
+        <v>12.58</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.36</v>
+        <v>7.42</v>
       </c>
       <c r="DZ8" t="n">
-        <v>5.18</v>
+        <v>5.16</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.36</v>
+        <v>21.75</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="9">
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
         <v>5</v>
@@ -4212,49 +4212,49 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="H9" t="n">
-        <v>70.2</v>
+        <v>70.5</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="J9" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="K9" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="M9" t="n">
-        <v>27.2</v>
+        <v>25.67</v>
       </c>
       <c r="N9" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="P9" t="n">
-        <v>15.6</v>
+        <v>15.67</v>
       </c>
       <c r="Q9" t="n">
-        <v>17.8</v>
+        <v>18.67</v>
       </c>
       <c r="R9" t="n">
-        <v>10.2</v>
+        <v>11.17</v>
       </c>
       <c r="S9" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="T9" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4266,28 +4266,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>40.4</v>
+        <v>41.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.2</v>
+        <v>5.67</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AC9" t="n">
-        <v>20</v>
+        <v>19.67</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AF9" t="n">
         <v>0.2</v>
@@ -4371,70 +4371,70 @@
         <v>2.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.1</v>
+        <v>8.82</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="BN9" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.8</v>
+        <v>4.64</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.3</v>
+        <v>4.18</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>80</v>
+        <v>72.73</v>
       </c>
       <c r="BT9" t="n">
-        <v>80</v>
+        <v>72.73</v>
       </c>
       <c r="BU9" t="n">
-        <v>40</v>
+        <v>36.36</v>
       </c>
       <c r="BV9" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BW9" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BX9" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BY9" t="n">
-        <v>4.39</v>
+        <v>4.07</v>
       </c>
       <c r="BZ9" t="n">
-        <v>4.7</v>
+        <v>4.33</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.68</v>
+        <v>3.63</v>
       </c>
       <c r="CC9" t="n">
         <v>3.02</v>
@@ -4443,25 +4443,25 @@
         <v>3.3</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CH9" t="n">
         <v>1.39</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CL9" t="n">
         <v>2.38</v>
@@ -4470,16 +4470,16 @@
         <v>1.98</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CO9" t="n">
         <v>1.28</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="CR9" t="n">
         <v>1.4</v>
@@ -4494,22 +4494,22 @@
         <v>1.41</v>
       </c>
       <c r="CV9" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="DB9" t="n">
         <v>1.3</v>
@@ -4518,82 +4518,82 @@
         <v>2</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="DH9" t="n">
-        <v>64.7</v>
+        <v>65.36</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DM9" t="n">
-        <v>27.3</v>
+        <v>26.46</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.2</v>
+        <v>14.37</v>
       </c>
       <c r="DQ9" t="n">
-        <v>16.6</v>
+        <v>17.18</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.699999999999999</v>
+        <v>10.27</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>41.6</v>
+        <v>42.09</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.199999999999999</v>
+        <v>8.73</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.9</v>
+        <v>5.64</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.8</v>
+        <v>16.91</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.01</v>
+        <v>0.96</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4693,139 +4693,139 @@
         <v>1.17</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>99.8</v>
+        <v>107.5</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>6.2</v>
+        <v>6.67</v>
       </c>
       <c r="AM10" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="AO10" t="n">
         <v>1</v>
       </c>
-      <c r="AN10" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AP10" t="n">
-        <v>2.8</v>
+        <v>3.17</v>
       </c>
       <c r="AQ10" t="n">
-        <v>16.2</v>
+        <v>15.33</v>
       </c>
       <c r="AR10" t="n">
-        <v>13.6</v>
+        <v>12.67</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.2</v>
+        <v>4.17</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>59</v>
+        <v>59.5</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>12.8</v>
+        <v>14.67</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.8</v>
+        <v>9.67</v>
       </c>
       <c r="BC10" t="n">
         <v>5</v>
       </c>
       <c r="BD10" t="n">
-        <v>26.6</v>
+        <v>26</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.640000000000001</v>
+        <v>9.83</v>
       </c>
       <c r="BI10" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.64</v>
+        <v>4.75</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5</v>
+        <v>5.08</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>100</v>
+        <v>91.67</v>
       </c>
       <c r="BT10" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BU10" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BV10" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BY10" t="n">
         <v>1.3</v>
@@ -4834,43 +4834,43 @@
         <v>1.29</v>
       </c>
       <c r="CA10" t="n">
-        <v>5.11</v>
+        <v>5.13</v>
       </c>
       <c r="CB10" t="n">
         <v>5.78</v>
       </c>
       <c r="CC10" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="CD10" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="CE10" t="n">
         <v>1.35</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="CH10" t="n">
         <v>1.46</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CJ10" t="n">
         <v>2.3</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="CM10" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CN10" t="n">
         <v>1.55</v>
@@ -4885,31 +4885,31 @@
         <v>3</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CS10" t="n">
         <v>2.71</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="CU10" t="n">
         <v>1.48</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CY10" t="n">
         <v>2.36</v>
       </c>
       <c r="CZ10" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="DA10" t="n">
         <v>1.57</v>
@@ -4921,82 +4921,82 @@
         <v>1.85</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.64</v>
+        <v>0.59</v>
       </c>
       <c r="DG10" t="n">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="DH10" t="n">
-        <v>111</v>
+        <v>113.92</v>
       </c>
       <c r="DI10" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="DK10" t="n">
-        <v>7.27</v>
+        <v>7.42</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="DM10" t="n">
-        <v>63.91</v>
+        <v>65.33</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.91</v>
+        <v>0.84</v>
       </c>
       <c r="DO10" t="n">
-        <v>3.91</v>
+        <v>4</v>
       </c>
       <c r="DP10" t="n">
-        <v>12.55</v>
+        <v>12.42</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.37</v>
+        <v>12.92</v>
       </c>
       <c r="DR10" t="n">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>61.18</v>
+        <v>61.25</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX10" t="n">
-        <v>16.73</v>
+        <v>17.33</v>
       </c>
       <c r="DY10" t="n">
-        <v>11.09</v>
+        <v>11.75</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.64</v>
+        <v>5.58</v>
       </c>
       <c r="EA10" t="n">
-        <v>25.18</v>
+        <v>25</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" t="n">
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -5096,139 +5096,139 @@
         <v>1.67</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AI11" t="n">
-        <v>104</v>
+        <v>106.17</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0.2</v>
+        <v>-0.17</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.6</v>
+        <v>3.83</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AN11" t="n">
-        <v>49.6</v>
+        <v>51.17</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13</v>
+        <v>13.17</v>
       </c>
       <c r="AR11" t="n">
-        <v>12.4</v>
+        <v>12.67</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.2</v>
+        <v>5.67</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>59.8</v>
+        <v>59.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="BA11" t="n">
-        <v>12.2</v>
+        <v>12.5</v>
       </c>
       <c r="BB11" t="n">
         <v>8</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>23</v>
+        <v>24.67</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.73</v>
+        <v>2.92</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.18</v>
+        <v>8.08</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.73</v>
+        <v>2.92</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BL11" t="n">
         <v>1</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.91</v>
+        <v>3.83</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="BR11" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS11" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BT11" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BU11" t="n">
-        <v>18.18</v>
+        <v>25</v>
       </c>
       <c r="BV11" t="n">
-        <v>18.18</v>
+        <v>25</v>
       </c>
       <c r="BW11" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX11" t="n">
-        <v>36.36</v>
+        <v>41.67</v>
       </c>
       <c r="BY11" t="n">
         <v>1.49</v>
@@ -5237,85 +5237,85 @@
         <v>1.56</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.74</v>
+        <v>4.63</v>
       </c>
       <c r="CB11" t="n">
-        <v>5.22</v>
+        <v>5.1</v>
       </c>
       <c r="CC11" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="CD11" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CH11" t="n">
         <v>1.47</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CJ11" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="CM11" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CO11" t="n">
         <v>1.24</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CQ11" t="n">
         <v>2.93</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="CU11" t="n">
         <v>1.5</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="DB11" t="n">
         <v>1.25</v>
@@ -5324,82 +5324,82 @@
         <v>1.8</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="DH11" t="n">
-        <v>113.82</v>
+        <v>114.08</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.45</v>
+        <v>5.42</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DM11" t="n">
-        <v>60.18</v>
+        <v>60.08</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.54</v>
+        <v>11.75</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13.91</v>
+        <v>13.92</v>
       </c>
       <c r="DR11" t="n">
-        <v>4.73</v>
+        <v>4.58</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>63.27</v>
+        <v>62.84</v>
       </c>
       <c r="DW11" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DX11" t="n">
-        <v>15.18</v>
+        <v>15.08</v>
       </c>
       <c r="DY11" t="n">
-        <v>10.18</v>
+        <v>10</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5</v>
+        <v>5.08</v>
       </c>
       <c r="EA11" t="n">
-        <v>24.46</v>
+        <v>25.17</v>
       </c>
       <c r="EB11" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="EC11" t="n">
         <v>1.75</v>
-      </c>
-      <c r="EC11" t="n">
-        <v>1.73</v>
       </c>
     </row>
     <row r="12">
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
         <v>6</v>
@@ -5421,82 +5421,82 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="G12" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="H12" t="n">
-        <v>79.2</v>
+        <v>78</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="K12" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>32</v>
+        <v>32.5</v>
       </c>
       <c r="N12" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="P12" t="n">
-        <v>11.8</v>
+        <v>11.17</v>
       </c>
       <c r="Q12" t="n">
-        <v>11.8</v>
+        <v>11.67</v>
       </c>
       <c r="R12" t="n">
-        <v>8</v>
+        <v>10.33</v>
       </c>
       <c r="S12" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="T12" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>49</v>
+        <v>47.17</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>6.6</v>
+        <v>6.17</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AC12" t="n">
-        <v>19.4</v>
+        <v>18.33</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.97</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5580,70 +5580,70 @@
         <v>3</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.449999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.27</v>
+        <v>4.42</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.18</v>
+        <v>4.33</v>
       </c>
       <c r="BR12" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BS12" t="n">
-        <v>81.81999999999999</v>
+        <v>75</v>
       </c>
       <c r="BT12" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BU12" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BV12" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BW12" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BX12" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BY12" t="n">
-        <v>3.26</v>
+        <v>4.88</v>
       </c>
       <c r="BZ12" t="n">
-        <v>3.44</v>
+        <v>4.93</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.93</v>
+        <v>4.05</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.18</v>
+        <v>4.32</v>
       </c>
       <c r="CC12" t="n">
         <v>7.67</v>
@@ -5652,31 +5652,31 @@
         <v>9.970000000000001</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="CJ12" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CK12" t="n">
         <v>1.88</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CN12" t="n">
         <v>1.5</v>
@@ -5685,28 +5685,28 @@
         <v>1.34</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.8</v>
+        <v>3.73</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="CX12" t="n">
         <v>1.91</v>
@@ -5724,85 +5724,85 @@
         <v>1.35</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.84</v>
+        <v>3.78</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.82</v>
+        <v>1.66</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="DH12" t="n">
-        <v>71.91</v>
+        <v>71.92</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>3.37</v>
+        <v>3.08</v>
       </c>
       <c r="DK12" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DM12" t="n">
-        <v>30</v>
+        <v>30.42</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.18</v>
+        <v>12.75</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11.82</v>
+        <v>11.75</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.91</v>
+        <v>10</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>42.91</v>
+        <v>42.5</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DX12" t="n">
-        <v>8.359999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="DY12" t="n">
-        <v>5.91</v>
+        <v>5.75</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="EA12" t="n">
-        <v>16.82</v>
+        <v>16.5</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="13">
@@ -5812,94 +5812,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
         <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="G13" t="n">
         <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>100.8</v>
+        <v>100.33</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="J13" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>4.6</v>
+        <v>4.67</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="M13" t="n">
-        <v>55.8</v>
+        <v>55</v>
       </c>
       <c r="N13" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="O13" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="P13" t="n">
-        <v>15.8</v>
+        <v>16.17</v>
       </c>
       <c r="Q13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R13" t="n">
-        <v>5.6</v>
+        <v>5.17</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>13.6</v>
+        <v>13.67</v>
       </c>
       <c r="AA13" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>4</v>
+        <v>4.17</v>
       </c>
       <c r="AC13" t="n">
-        <v>22</v>
+        <v>22.67</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.6</v>
+        <v>2.83</v>
       </c>
       <c r="AF13" t="n">
         <v>0.2</v>
@@ -5983,70 +5983,70 @@
         <v>2.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="BH13" t="n">
-        <v>7.5</v>
+        <v>7.45</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="BO13" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.8</v>
+        <v>3.91</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT13" t="n">
-        <v>40</v>
+        <v>45.45</v>
       </c>
       <c r="BU13" t="n">
-        <v>10</v>
+        <v>18.18</v>
       </c>
       <c r="BV13" t="n">
-        <v>10</v>
+        <v>18.18</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>60</v>
+        <v>63.64</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.18</v>
+        <v>4.07</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.47</v>
+        <v>4.34</v>
       </c>
       <c r="CC13" t="n">
         <v>1.59</v>
@@ -6055,67 +6055,67 @@
         <v>1.63</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="CH13" t="n">
         <v>1.42</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="CL13" t="n">
         <v>2.26</v>
       </c>
       <c r="CM13" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.81</v>
+        <v>2.86</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CX13" t="n">
         <v>1.81</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CZ13" t="n">
         <v>2</v>
@@ -6127,85 +6127,85 @@
         <v>1.3</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="DH13" t="n">
-        <v>101.9</v>
+        <v>101.54</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.9</v>
+        <v>4.91</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DM13" t="n">
-        <v>56.4</v>
+        <v>55.91</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="DP13" t="n">
-        <v>15.4</v>
+        <v>15.64</v>
       </c>
       <c r="DQ13" t="n">
-        <v>15.1</v>
+        <v>15.64</v>
       </c>
       <c r="DR13" t="n">
-        <v>5.6</v>
+        <v>5.37</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>55.9</v>
+        <v>55.36</v>
       </c>
       <c r="DW13" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="DX13" t="n">
-        <v>13.9</v>
+        <v>13.91</v>
       </c>
       <c r="DY13" t="n">
-        <v>9.6</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.3</v>
+        <v>4.37</v>
       </c>
       <c r="EA13" t="n">
-        <v>21.9</v>
+        <v>22.27</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6308,136 +6308,136 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AI14" t="n">
-        <v>46.4</v>
+        <v>51</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.4</v>
+        <v>3.67</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AM14" t="n">
         <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>17.2</v>
+        <v>18.5</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="AQ14" t="n">
-        <v>14</v>
+        <v>13.83</v>
       </c>
       <c r="AR14" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AS14" t="n">
-        <v>11</v>
+        <v>10.67</v>
       </c>
       <c r="AT14" t="n">
         <v>3</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>28.4</v>
+        <v>31</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="BA14" t="n">
-        <v>6.2</v>
+        <v>6.17</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="BD14" t="n">
-        <v>12.4</v>
+        <v>13.17</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.49</v>
+        <v>0.52</v>
       </c>
       <c r="BF14" t="n">
         <v>3</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.449999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BL14" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.27</v>
+        <v>4.17</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.09</v>
+        <v>5.08</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BT14" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BU14" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BV14" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BW14" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX14" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BY14" t="n">
         <v>4.95</v>
@@ -6446,169 +6446,169 @@
         <v>5.62</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.65</v>
+        <v>4.56</v>
       </c>
       <c r="CB14" t="n">
-        <v>5.39</v>
+        <v>5.27</v>
       </c>
       <c r="CC14" t="n">
-        <v>10.03</v>
+        <v>9.26</v>
       </c>
       <c r="CD14" t="n">
-        <v>15.58</v>
+        <v>13.97</v>
       </c>
       <c r="CE14" t="n">
         <v>1.35</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CK14" t="n">
         <v>1.82</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CM14" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="CR14" t="n">
         <v>1.38</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CV14" t="n">
         <v>1.81</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CX14" t="n">
         <v>1.85</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CZ14" t="n">
         <v>1.96</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.05</v>
+        <v>3.09</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="DG14" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="DH14" t="n">
-        <v>64.91</v>
+        <v>65.67</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.18</v>
+        <v>3.33</v>
       </c>
       <c r="DK14" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DM14" t="n">
-        <v>26.09</v>
+        <v>26</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="DO14" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="DP14" t="n">
-        <v>15.09</v>
+        <v>14.92</v>
       </c>
       <c r="DQ14" t="n">
-        <v>11.55</v>
+        <v>11.5</v>
       </c>
       <c r="DR14" t="n">
         <v>9</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>37.27</v>
+        <v>37.84</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="DX14" t="n">
-        <v>8.640000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="DY14" t="n">
-        <v>7</v>
+        <v>6.84</v>
       </c>
       <c r="DZ14" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.36</v>
+        <v>17.33</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
         <v>0.2</v>
@@ -6708,139 +6708,139 @@
         <v>2.6</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AI15" t="n">
-        <v>75</v>
+        <v>77.56999999999999</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.67</v>
+        <v>2.14</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AN15" t="n">
-        <v>27.17</v>
+        <v>30.57</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>16.17</v>
+        <v>17.14</v>
       </c>
       <c r="AR15" t="n">
-        <v>14.83</v>
+        <v>15</v>
       </c>
       <c r="AS15" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>44.43</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BH15" t="n">
         <v>8.17</v>
       </c>
-      <c r="AT15" t="n">
+      <c r="BI15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BN15" t="n">
         <v>1.5</v>
       </c>
-      <c r="AU15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>43</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>8.17</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>19.67</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>8.359999999999999</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>1.55</v>
-      </c>
       <c r="BO15" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.09</v>
+        <v>4.92</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>72.73</v>
+        <v>66.67</v>
       </c>
       <c r="BT15" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BU15" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BV15" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW15" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX15" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BY15" t="n">
         <v>5.11</v>
@@ -6849,22 +6849,22 @@
         <v>5.28</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.94</v>
+        <v>3.88</v>
       </c>
       <c r="CC15" t="n">
-        <v>5.94</v>
+        <v>5.51</v>
       </c>
       <c r="CD15" t="n">
-        <v>5.87</v>
+        <v>5.47</v>
       </c>
       <c r="CE15" t="n">
         <v>1.4</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="CG15" t="n">
         <v>2.73</v>
@@ -6873,16 +6873,16 @@
         <v>1.37</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="CJ15" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="CM15" t="n">
         <v>1.88</v>
@@ -6891,13 +6891,13 @@
         <v>1.51</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.63</v>
+        <v>3.58</v>
       </c>
       <c r="CR15" t="n">
         <v>1.43</v>
@@ -6912,73 +6912,73 @@
         <v>1.4</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="CW15" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="CX15" t="n">
         <v>1.88</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CZ15" t="n">
         <v>1.93</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="DB15" t="n">
         <v>1.34</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DF15" t="n">
         <v>2</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="DH15" t="n">
-        <v>66.36</v>
+        <v>68.58</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.09</v>
+        <v>3.25</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.27</v>
+        <v>0.34</v>
       </c>
       <c r="DM15" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="DN15" t="n">
         <v>1.09</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="DP15" t="n">
-        <v>15.27</v>
+        <v>15.92</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.82</v>
+        <v>15.83</v>
       </c>
       <c r="DR15" t="n">
-        <v>8</v>
+        <v>7.67</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>44.18</v>
+        <v>44.92</v>
       </c>
       <c r="DW15" t="n">
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>11</v>
+        <v>11.42</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.73</v>
+        <v>7.16</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.73</v>
+        <v>19.33</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="EC15" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
         <v>6</v>
@@ -1391,82 +1391,82 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="G2" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="H2" t="n">
-        <v>103.17</v>
+        <v>104.71</v>
       </c>
       <c r="I2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J2" t="n">
-        <v>3.17</v>
+        <v>2.86</v>
       </c>
       <c r="K2" t="n">
-        <v>6.5</v>
+        <v>6.29</v>
       </c>
       <c r="L2" t="n">
-        <v>0.33</v>
+        <v>0.57</v>
       </c>
       <c r="M2" t="n">
-        <v>68</v>
+        <v>66.56999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="O2" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="P2" t="n">
-        <v>15.17</v>
+        <v>15</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.67</v>
+        <v>12.71</v>
       </c>
       <c r="R2" t="n">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="S2" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="U2" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="V2" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>61.67</v>
+        <v>61.29</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.67</v>
+        <v>18.43</v>
       </c>
       <c r="AA2" t="n">
-        <v>13.83</v>
+        <v>13</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.83</v>
+        <v>5.43</v>
       </c>
       <c r="AC2" t="n">
-        <v>21.67</v>
+        <v>21.14</v>
       </c>
       <c r="AD2" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.83</v>
+        <v>2.57</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,70 +1550,70 @@
         <v>2.67</v>
       </c>
       <c r="BG2" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.33</v>
+        <v>8.08</v>
       </c>
       <c r="BI2" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.83</v>
+        <v>3.69</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.5</v>
+        <v>4.38</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BT2" t="n">
-        <v>16.67</v>
+        <v>23.08</v>
       </c>
       <c r="BU2" t="n">
-        <v>16.67</v>
+        <v>23.08</v>
       </c>
       <c r="BV2" t="n">
-        <v>16.67</v>
+        <v>23.08</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>25</v>
+        <v>30.77</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.62</v>
+        <v>4.66</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.89</v>
+        <v>5.05</v>
       </c>
       <c r="CC2" t="n">
         <v>2.11</v>
@@ -1628,25 +1628,25 @@
         <v>2.63</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="CH2" t="n">
         <v>1.45</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CM2" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CN2" t="n">
         <v>1.59</v>
@@ -1655,28 +1655,28 @@
         <v>1.26</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CR2" t="n">
         <v>1.37</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="CX2" t="n">
         <v>1.81</v>
@@ -1691,88 +1691,88 @@
         <v>1.61</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.16</v>
+        <v>3.13</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="DG2" t="n">
         <v>3</v>
       </c>
       <c r="DH2" t="n">
-        <v>96</v>
+        <v>97.38</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.66</v>
+        <v>5.62</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="DM2" t="n">
-        <v>62</v>
+        <v>61.69</v>
       </c>
       <c r="DN2" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="DP2" t="n">
-        <v>16.58</v>
+        <v>16.38</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.25</v>
+        <v>13.23</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.84</v>
+        <v>5.77</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.34</v>
+        <v>0.39</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.34</v>
+        <v>0.39</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>58.84</v>
+        <v>58.85</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DX2" t="n">
-        <v>16.67</v>
+        <v>16.69</v>
       </c>
       <c r="DY2" t="n">
-        <v>12.16</v>
+        <v>11.85</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.5</v>
+        <v>4.85</v>
       </c>
       <c r="EA2" t="n">
-        <v>22</v>
+        <v>21.69</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="n">
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1872,130 +1872,130 @@
         <v>1.83</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.67</v>
+        <v>3.43</v>
       </c>
       <c r="AI3" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AL3" t="n">
-        <v>5.17</v>
+        <v>4.71</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AN3" t="n">
-        <v>40.5</v>
+        <v>36.71</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AQ3" t="n">
-        <v>16.17</v>
+        <v>15.43</v>
       </c>
       <c r="AR3" t="n">
-        <v>13.67</v>
+        <v>13.29</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.17</v>
+        <v>7.14</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>47.83</v>
+        <v>46</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.67</v>
+        <v>10.43</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.67</v>
+        <v>6.57</v>
       </c>
       <c r="BC3" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="BD3" t="n">
-        <v>18.5</v>
+        <v>18.14</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="BG3" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="BH3" t="n">
         <v>9.08</v>
       </c>
       <c r="BI3" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.33</v>
+        <v>0.46</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="BP3" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.42</v>
+        <v>6.46</v>
       </c>
       <c r="BR3" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS3" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT3" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="BV3" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BY3" t="n">
         <v>1.86</v>
@@ -2013,52 +2013,52 @@
         <v>1.94</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.03</v>
+        <v>4.06</v>
       </c>
       <c r="CC3" t="n">
-        <v>4.04</v>
+        <v>4.5</v>
       </c>
       <c r="CD3" t="n">
-        <v>5.22</v>
+        <v>5.67</v>
       </c>
       <c r="CE3" t="n">
         <v>1.41</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CH3" t="n">
         <v>1.37</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CJ3" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CN3" t="n">
         <v>1.52</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CQ3" t="n">
         <v>3.64</v>
@@ -2067,7 +2067,7 @@
         <v>1.42</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="CT3" t="n">
         <v>2.87</v>
@@ -2076,10 +2076,10 @@
         <v>1.4</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CX3" t="n">
         <v>1.87</v>
@@ -2100,49 +2100,49 @@
         <v>2.08</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.69</v>
+        <v>3.7</v>
       </c>
       <c r="DE3" t="n">
         <v>0.08</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.83</v>
+        <v>3.69</v>
       </c>
       <c r="DH3" t="n">
-        <v>97.08</v>
+        <v>94.08</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.5</v>
+        <v>5.23</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM3" t="n">
-        <v>45.75</v>
+        <v>43.31</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.59</v>
+        <v>0.54</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="DP3" t="n">
-        <v>15.17</v>
+        <v>14.85</v>
       </c>
       <c r="DQ3" t="n">
-        <v>15.25</v>
+        <v>14.92</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.25</v>
+        <v>6.77</v>
       </c>
       <c r="DS3" t="n">
         <v>0.08</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>53.83</v>
+        <v>52.38</v>
       </c>
       <c r="DW3" t="n">
         <v>0.08</v>
       </c>
       <c r="DX3" t="n">
-        <v>13.08</v>
+        <v>12.77</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.67</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.42</v>
+        <v>4.31</v>
       </c>
       <c r="EA3" t="n">
-        <v>21.5</v>
+        <v>21.08</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="4">
@@ -2185,62 +2185,62 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
         <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="G4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H4" t="n">
+        <v>65.67</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M4" t="n">
+        <v>39.17</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P4" t="n">
+        <v>12.67</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>13.83</v>
+      </c>
+      <c r="R4" t="n">
+        <v>8</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T4" t="n">
         <v>2</v>
       </c>
-      <c r="H4" t="n">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M4" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P4" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.2</v>
-      </c>
       <c r="U4" t="n">
         <v>0</v>
       </c>
@@ -2251,28 +2251,28 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>46.8</v>
+        <v>43.67</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="Z4" t="n">
-        <v>10.6</v>
+        <v>9.83</v>
       </c>
       <c r="AA4" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="AC4" t="n">
-        <v>20.4</v>
+        <v>21.33</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AE4" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,70 +2356,70 @@
         <v>3.29</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.17</v>
+        <v>9.31</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.25</v>
+        <v>4.46</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.92</v>
+        <v>4.85</v>
       </c>
       <c r="BR4" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS4" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT4" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BU4" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV4" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX4" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.86</v>
+        <v>3.82</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.09</v>
+        <v>4.02</v>
       </c>
       <c r="CC4" t="n">
         <v>7.5</v>
@@ -2431,28 +2431,28 @@
         <v>1.42</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="CH4" t="n">
         <v>1.37</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CK4" t="n">
         <v>1.84</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="CM4" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CN4" t="n">
         <v>1.54</v>
@@ -2467,25 +2467,25 @@
         <v>3.52</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="CU4" t="n">
         <v>1.4</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CY4" t="n">
         <v>2.38</v>
@@ -2503,49 +2503,49 @@
         <v>2.04</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="DH4" t="n">
-        <v>73.5</v>
+        <v>73.31</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.84</v>
+        <v>3.77</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="DM4" t="n">
-        <v>34.33</v>
+        <v>33.46</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.75</v>
+        <v>14.16</v>
       </c>
       <c r="DQ4" t="n">
-        <v>16.33</v>
+        <v>15.54</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.59</v>
+        <v>8.16</v>
       </c>
       <c r="DS4" t="n">
         <v>0.08</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>44.83</v>
+        <v>43.54</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DX4" t="n">
-        <v>8.83</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="DY4" t="n">
-        <v>5.08</v>
+        <v>4.92</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.75</v>
+        <v>3.69</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.59</v>
+        <v>19.15</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="EC4" t="n">
-        <v>3.67</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" t="n">
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2681,46 +2681,46 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AI5" t="n">
-        <v>70.17</v>
+        <v>67</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK5" t="n">
         <v>3</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.83</v>
+        <v>3.29</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AN5" t="n">
-        <v>31.33</v>
+        <v>28.86</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="AQ5" t="n">
-        <v>17</v>
+        <v>16.57</v>
       </c>
       <c r="AR5" t="n">
-        <v>13.5</v>
+        <v>13.57</v>
       </c>
       <c r="AS5" t="n">
-        <v>13.5</v>
+        <v>12.71</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="AU5" t="n">
         <v>1</v>
@@ -2735,82 +2735,82 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>44</v>
+        <v>43.57</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.67</v>
+        <v>7.29</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.67</v>
+        <v>5.29</v>
       </c>
       <c r="BC5" t="n">
         <v>2</v>
       </c>
       <c r="BD5" t="n">
-        <v>21.33</v>
+        <v>20.14</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.86</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.25</v>
+        <v>2.46</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.67</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.25</v>
+        <v>2.46</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="BO5" t="n">
         <v>1.08</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.83</v>
+        <v>4.62</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3.83</v>
+        <v>3.77</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BT5" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BU5" t="n">
-        <v>16.67</v>
+        <v>23.08</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BY5" t="n">
         <v>2.54</v>
@@ -2819,73 +2819,73 @@
         <v>2.79</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.56</v>
+        <v>3.68</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.71</v>
+        <v>3.96</v>
       </c>
       <c r="CC5" t="n">
-        <v>5.75</v>
+        <v>6.88</v>
       </c>
       <c r="CD5" t="n">
-        <v>6.98</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CF5" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="CH5" t="n">
         <v>1.37</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="CM5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CV5" t="n">
         <v>1.83</v>
       </c>
-      <c r="CN5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="CO5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="CP5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="CQ5" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="CS5" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="CT5" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="CU5" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="CV5" t="n">
-        <v>1.86</v>
-      </c>
       <c r="CW5" t="n">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="CX5" t="n">
         <v>1.94</v>
@@ -2900,55 +2900,55 @@
         <v>1.53</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.84</v>
+        <v>1.69</v>
       </c>
       <c r="DH5" t="n">
-        <v>79.42</v>
+        <v>77</v>
       </c>
       <c r="DI5" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.92</v>
+        <v>3.62</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DM5" t="n">
-        <v>39.42</v>
+        <v>37.46</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="DP5" t="n">
-        <v>15.5</v>
+        <v>15.38</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.75</v>
+        <v>14.69</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.67</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="DS5" t="n">
         <v>0.08</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>51</v>
+        <v>50.23</v>
       </c>
       <c r="DW5" t="n">
         <v>0.08</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.67</v>
+        <v>10.23</v>
       </c>
       <c r="DY5" t="n">
-        <v>8</v>
+        <v>7.62</v>
       </c>
       <c r="DZ5" t="n">
-        <v>2.66</v>
+        <v>2.61</v>
       </c>
       <c r="EA5" t="n">
-        <v>22.5</v>
+        <v>21.77</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" t="n">
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
         <v>0.17</v>
@@ -3084,136 +3084,136 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.33</v>
+        <v>3.29</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.17</v>
+        <v>1.86</v>
       </c>
       <c r="AI6" t="n">
-        <v>75</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK6" t="n">
-        <v>5</v>
+        <v>4.86</v>
       </c>
       <c r="AL6" t="n">
-        <v>5.33</v>
+        <v>5.71</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AN6" t="n">
         <v>37</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.17</v>
+        <v>3.86</v>
       </c>
       <c r="AQ6" t="n">
-        <v>19.33</v>
+        <v>18.71</v>
       </c>
       <c r="AR6" t="n">
-        <v>12.17</v>
+        <v>12.29</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.17</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>47.67</v>
+        <v>47.57</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA6" t="n">
-        <v>15.67</v>
+        <v>16.43</v>
       </c>
       <c r="BB6" t="n">
-        <v>9.5</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.17</v>
+        <v>6.57</v>
       </c>
       <c r="BD6" t="n">
-        <v>17.83</v>
+        <v>17.57</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.83</v>
+        <v>4.71</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.42</v>
+        <v>3.31</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.08</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.42</v>
+        <v>3.31</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL6" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="BM6" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BN6" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="BP6" t="n">
-        <v>5.17</v>
+        <v>5.31</v>
       </c>
       <c r="BQ6" t="n">
-        <v>3.92</v>
+        <v>4.31</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BT6" t="n">
-        <v>75</v>
+        <v>69.23</v>
       </c>
       <c r="BU6" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BV6" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BY6" t="n">
         <v>5.31</v>
@@ -3222,55 +3222,55 @@
         <v>5.42</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.86</v>
+        <v>3.82</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.99</v>
+        <v>3.92</v>
       </c>
       <c r="CC6" t="n">
-        <v>4.64</v>
+        <v>4.45</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.86</v>
+        <v>4.67</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CM6" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.66</v>
+        <v>3.59</v>
       </c>
       <c r="CR6" t="n">
         <v>1.45</v>
@@ -3285,16 +3285,16 @@
         <v>1.4</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="CX6" t="n">
         <v>1.93</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CZ6" t="n">
         <v>1.88</v>
@@ -3303,55 +3303,55 @@
         <v>1.54</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.83</v>
+        <v>3.78</v>
       </c>
       <c r="DE6" t="n">
         <v>0.08</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.42</v>
+        <v>1.77</v>
       </c>
       <c r="DH6" t="n">
-        <v>71.67</v>
+        <v>72.3</v>
       </c>
       <c r="DI6" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ6" t="n">
-        <v>4.84</v>
+        <v>4.77</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.33</v>
+        <v>4.61</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DM6" t="n">
-        <v>35.58</v>
+        <v>35.69</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="DP6" t="n">
-        <v>17.75</v>
+        <v>17.54</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14.25</v>
+        <v>14.15</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.33</v>
+        <v>8.15</v>
       </c>
       <c r="DS6" t="n">
         <v>0.08</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>42.58</v>
+        <v>42.92</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.92</v>
+        <v>14.46</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.83</v>
+        <v>9.08</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.08</v>
+        <v>5.38</v>
       </c>
       <c r="EA6" t="n">
-        <v>15.66</v>
+        <v>15.69</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="EC6" t="n">
-        <v>4.16</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="7">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
@@ -3406,82 +3406,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="G7" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="K7" t="n">
-        <v>4.33</v>
+        <v>4.29</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="M7" t="n">
-        <v>33.83</v>
+        <v>31.86</v>
       </c>
       <c r="N7" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="O7" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="P7" t="n">
-        <v>15.5</v>
+        <v>14.86</v>
       </c>
       <c r="Q7" t="n">
-        <v>15.83</v>
+        <v>14.86</v>
       </c>
       <c r="R7" t="n">
-        <v>7.67</v>
+        <v>7.71</v>
       </c>
       <c r="S7" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="T7" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="V7" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>46.33</v>
+        <v>44.14</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.33</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.17</v>
+        <v>4.14</v>
       </c>
       <c r="AC7" t="n">
-        <v>17.67</v>
+        <v>17.14</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AE7" t="n">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,70 +3565,70 @@
         <v>3.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.42</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="BP7" t="n">
         <v>3.92</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.5</v>
+        <v>4.38</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BT7" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BU7" t="n">
-        <v>16.67</v>
+        <v>23.08</v>
       </c>
       <c r="BV7" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW7" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX7" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BY7" t="n">
-        <v>5.28</v>
+        <v>5.84</v>
       </c>
       <c r="BZ7" t="n">
-        <v>5.49</v>
+        <v>6.09</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.8</v>
+        <v>3.86</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.87</v>
+        <v>3.95</v>
       </c>
       <c r="CC7" t="n">
         <v>5.09</v>
@@ -3637,19 +3637,19 @@
         <v>5.52</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.99</v>
@@ -3658,22 +3658,22 @@
         <v>1.88</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.72</v>
+        <v>3.66</v>
       </c>
       <c r="CR7" t="n">
         <v>1.44</v>
@@ -3688,10 +3688,10 @@
         <v>1.41</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="CX7" t="n">
         <v>1.92</v>
@@ -3700,7 +3700,7 @@
         <v>2.42</v>
       </c>
       <c r="CZ7" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="DA7" t="n">
         <v>1.54</v>
@@ -3709,85 +3709,85 @@
         <v>1.36</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="DH7" t="n">
-        <v>82.75</v>
+        <v>83</v>
       </c>
       <c r="DI7" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.83</v>
+        <v>3.84</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.42</v>
+        <v>3.46</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.34</v>
+        <v>0.39</v>
       </c>
       <c r="DM7" t="n">
-        <v>33.25</v>
+        <v>32.23</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="DP7" t="n">
-        <v>15.5</v>
+        <v>15.16</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14</v>
+        <v>13.62</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.17</v>
+        <v>8.15</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>44.66</v>
+        <v>43.61</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.25</v>
+        <v>12.08</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.5</v>
+        <v>8.31</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.75</v>
+        <v>3.77</v>
       </c>
       <c r="EA7" t="n">
-        <v>16.75</v>
+        <v>16.54</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.58</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
         <v>0.43</v>
@@ -3890,136 +3890,136 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AI8" t="n">
-        <v>86.40000000000001</v>
+        <v>91</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AN8" t="n">
-        <v>33.2</v>
+        <v>38.17</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
       </c>
       <c r="AP8" t="n">
-        <v>2</v>
+        <v>2.67</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13.8</v>
+        <v>12.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>14.6</v>
+        <v>15.33</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>51.4</v>
+        <v>54.83</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BD8" t="n">
-        <v>19.4</v>
+        <v>20.17</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.83</v>
+        <v>3.69</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.5</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.83</v>
+        <v>3.69</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.33</v>
+        <v>4.54</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.17</v>
+        <v>5.08</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
       </c>
       <c r="BS8" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BT8" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BU8" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BV8" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BW8" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BX8" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BY8" t="n">
         <v>2.62</v>
@@ -4028,34 +4028,34 @@
         <v>2.66</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.95</v>
+        <v>3.89</v>
       </c>
       <c r="CC8" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="CD8" t="n">
-        <v>5.77</v>
+        <v>5.19</v>
       </c>
       <c r="CE8" t="n">
         <v>1.38</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="CH8" t="n">
         <v>1.39</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CK8" t="n">
         <v>1.82</v>
@@ -4064,7 +4064,7 @@
         <v>2.39</v>
       </c>
       <c r="CM8" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CN8" t="n">
         <v>1.55</v>
@@ -4082,31 +4082,31 @@
         <v>1.41</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CU8" t="n">
         <v>1.39</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CY8" t="n">
         <v>2.36</v>
       </c>
       <c r="CZ8" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="DB8" t="n">
         <v>1.33</v>
@@ -4115,82 +4115,82 @@
         <v>2.06</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF8" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="DH8" t="n">
-        <v>96.58</v>
+        <v>97.92</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.92</v>
+        <v>5.23</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="DM8" t="n">
-        <v>40.75</v>
+        <v>42.46</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="DP8" t="n">
-        <v>12.83</v>
+        <v>12.31</v>
       </c>
       <c r="DQ8" t="n">
-        <v>15.34</v>
+        <v>15.62</v>
       </c>
       <c r="DR8" t="n">
-        <v>7</v>
+        <v>6.69</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>57.25</v>
+        <v>58.38</v>
       </c>
       <c r="DW8" t="n">
         <v>0.08</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.58</v>
+        <v>12.69</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.42</v>
+        <v>7.54</v>
       </c>
       <c r="DZ8" t="n">
-        <v>5.16</v>
+        <v>5.15</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.75</v>
+        <v>21.93</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4290,139 +4290,139 @@
         <v>2.33</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AI9" t="n">
-        <v>59.2</v>
+        <v>59.17</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.6</v>
+        <v>3.33</v>
       </c>
       <c r="AL9" t="n">
-        <v>4</v>
+        <v>3.33</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AN9" t="n">
-        <v>27.4</v>
+        <v>24.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12.8</v>
+        <v>12</v>
       </c>
       <c r="AR9" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>42.8</v>
+        <v>41.67</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="BA9" t="n">
-        <v>9.6</v>
+        <v>8.33</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.6</v>
+        <v>4.83</v>
       </c>
       <c r="BC9" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>13.6</v>
+        <v>14.33</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.08</v>
+        <v>0.95</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="BG9" t="n">
         <v>3</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.82</v>
+        <v>8.67</v>
       </c>
       <c r="BI9" t="n">
         <v>3</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="BN9" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="BO9" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.64</v>
+        <v>4.75</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.18</v>
+        <v>3.92</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BT9" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BU9" t="n">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="BV9" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW9" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX9" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BY9" t="n">
         <v>4.07</v>
@@ -4431,169 +4431,169 @@
         <v>4.33</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.54</v>
+        <v>4.04</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.63</v>
+        <v>4.39</v>
       </c>
       <c r="CC9" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="CG9" t="n">
         <v>3.02</v>
       </c>
-      <c r="CD9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="CE9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="CF9" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="CG9" t="n">
-        <v>2.84</v>
-      </c>
       <c r="CH9" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CM9" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="CR9" t="n">
         <v>1.4</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.93</v>
+        <v>2.82</v>
       </c>
       <c r="CT9" t="n">
         <v>2.96</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="DC9" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.44</v>
+        <v>3.31</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="DH9" t="n">
-        <v>65.36</v>
+        <v>64.83</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.18</v>
+        <v>2.92</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DM9" t="n">
-        <v>26.46</v>
+        <v>25.08</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.37</v>
+        <v>13.84</v>
       </c>
       <c r="DQ9" t="n">
-        <v>17.18</v>
+        <v>17.08</v>
       </c>
       <c r="DR9" t="n">
-        <v>10.27</v>
+        <v>10.42</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>42.09</v>
+        <v>41.58</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.73</v>
+        <v>8.17</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.64</v>
+        <v>5.25</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.09</v>
+        <v>2.92</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.91</v>
+        <v>17</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.96</v>
+        <v>0.9</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="10">
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
         <v>6</v>
@@ -4615,82 +4615,82 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="G10" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>120.33</v>
+        <v>126.29</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="K10" t="n">
-        <v>8.17</v>
+        <v>8</v>
       </c>
       <c r="L10" t="n">
-        <v>0.17</v>
+        <v>0.43</v>
       </c>
       <c r="M10" t="n">
-        <v>75.17</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="O10" t="n">
-        <v>4.83</v>
+        <v>5</v>
       </c>
       <c r="P10" t="n">
-        <v>9.5</v>
+        <v>10.43</v>
       </c>
       <c r="Q10" t="n">
-        <v>13.17</v>
+        <v>12.43</v>
       </c>
       <c r="R10" t="n">
-        <v>4.5</v>
+        <v>4.29</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="T10" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="U10" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="V10" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>63</v>
+        <v>63.14</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>20</v>
+        <v>21.71</v>
       </c>
       <c r="AA10" t="n">
-        <v>13.83</v>
+        <v>14.71</v>
       </c>
       <c r="AB10" t="n">
-        <v>6.17</v>
+        <v>7</v>
       </c>
       <c r="AC10" t="n">
-        <v>24</v>
+        <v>25.71</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AF10" t="n">
         <v>0.17</v>
@@ -4774,70 +4774,70 @@
         <v>1.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.83</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.25</v>
+        <v>0.38</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.75</v>
+        <v>4.85</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.08</v>
+        <v>4.77</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BT10" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BU10" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV10" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="CA10" t="n">
-        <v>5.13</v>
+        <v>5.47</v>
       </c>
       <c r="CB10" t="n">
-        <v>5.78</v>
+        <v>6.32</v>
       </c>
       <c r="CC10" t="n">
         <v>1.66</v>
@@ -4846,157 +4846,157 @@
         <v>1.69</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.03</v>
+        <v>3.18</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CJ10" t="n">
         <v>2.3</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="CM10" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="CR10" t="n">
         <v>1.37</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="CT10" t="n">
         <v>3.04</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="CZ10" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.12</v>
+        <v>3.02</v>
       </c>
       <c r="DE10" t="n">
         <v>0.08</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.59</v>
+        <v>0.54</v>
       </c>
       <c r="DG10" t="n">
-        <v>3.42</v>
+        <v>3.23</v>
       </c>
       <c r="DH10" t="n">
-        <v>113.92</v>
+        <v>117.62</v>
       </c>
       <c r="DI10" t="n">
         <v>-0.08</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="DK10" t="n">
-        <v>7.42</v>
+        <v>7.39</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.5</v>
+        <v>0.61</v>
       </c>
       <c r="DM10" t="n">
-        <v>65.33</v>
+        <v>66.31</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.84</v>
+        <v>0.77</v>
       </c>
       <c r="DO10" t="n">
-        <v>4</v>
+        <v>4.16</v>
       </c>
       <c r="DP10" t="n">
-        <v>12.42</v>
+        <v>12.69</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.92</v>
+        <v>12.54</v>
       </c>
       <c r="DR10" t="n">
-        <v>4.34</v>
+        <v>4.23</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>61.25</v>
+        <v>61.46</v>
       </c>
       <c r="DW10" t="n">
         <v>0.08</v>
       </c>
       <c r="DX10" t="n">
-        <v>17.33</v>
+        <v>18.46</v>
       </c>
       <c r="DY10" t="n">
-        <v>11.75</v>
+        <v>12.38</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.58</v>
+        <v>6.08</v>
       </c>
       <c r="EA10" t="n">
-        <v>25</v>
+        <v>25.84</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.96</v>
+        <v>2.07</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="11">
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
         <v>6</v>
@@ -5018,82 +5018,82 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="G11" t="n">
-        <v>3.67</v>
+        <v>3.86</v>
       </c>
       <c r="H11" t="n">
-        <v>122</v>
+        <v>120.57</v>
       </c>
       <c r="I11" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="J11" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="K11" t="n">
         <v>7</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="M11" t="n">
-        <v>69</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="O11" t="n">
-        <v>3.33</v>
+        <v>3.14</v>
       </c>
       <c r="P11" t="n">
-        <v>10.33</v>
+        <v>10.43</v>
       </c>
       <c r="Q11" t="n">
-        <v>15.17</v>
+        <v>14.43</v>
       </c>
       <c r="R11" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="S11" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="T11" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="U11" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="V11" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>66.17</v>
+        <v>66</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>17.67</v>
+        <v>17.86</v>
       </c>
       <c r="AA11" t="n">
-        <v>12</v>
+        <v>12.14</v>
       </c>
       <c r="AB11" t="n">
-        <v>5.67</v>
+        <v>5.71</v>
       </c>
       <c r="AC11" t="n">
-        <v>25.67</v>
+        <v>25.43</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AF11" t="n">
         <v>0.33</v>
@@ -5177,70 +5177,70 @@
         <v>1.83</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.08</v>
+        <v>8.15</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BL11" t="n">
         <v>1</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.83</v>
+        <v>3.69</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.25</v>
+        <v>4.46</v>
       </c>
       <c r="BR11" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS11" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT11" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BU11" t="n">
-        <v>25</v>
+        <v>30.77</v>
       </c>
       <c r="BV11" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BW11" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX11" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BY11" t="n">
         <v>1.49</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.63</v>
+        <v>4.59</v>
       </c>
       <c r="CB11" t="n">
-        <v>5.1</v>
+        <v>5.05</v>
       </c>
       <c r="CC11" t="n">
         <v>1.99</v>
@@ -5249,28 +5249,28 @@
         <v>1.94</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="CK11" t="n">
         <v>1.76</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CM11" t="n">
         <v>1.98</v>
@@ -5279,31 +5279,31 @@
         <v>1.58</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.93</v>
+        <v>2.98</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="CX11" t="n">
         <v>1.79</v>
@@ -5318,88 +5318,88 @@
         <v>1.61</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="DG11" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="DH11" t="n">
-        <v>114.08</v>
+        <v>113.92</v>
       </c>
       <c r="DI11" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DJ11" t="n">
         <v>1.92</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.42</v>
+        <v>5.54</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DM11" t="n">
-        <v>60.08</v>
+        <v>59.85</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.75</v>
+        <v>11.69</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13.92</v>
+        <v>13.62</v>
       </c>
       <c r="DR11" t="n">
-        <v>4.58</v>
+        <v>4.54</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>62.84</v>
+        <v>63</v>
       </c>
       <c r="DW11" t="n">
         <v>0.08</v>
       </c>
       <c r="DX11" t="n">
-        <v>15.08</v>
+        <v>15.39</v>
       </c>
       <c r="DY11" t="n">
-        <v>10</v>
+        <v>10.23</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.08</v>
+        <v>5.15</v>
       </c>
       <c r="EA11" t="n">
-        <v>25.17</v>
+        <v>25.08</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="12">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
         <v>0.17</v>
@@ -5902,139 +5902,139 @@
         <v>2.83</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="AI13" t="n">
-        <v>103</v>
+        <v>106.33</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.2</v>
+        <v>5.17</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>57</v>
+        <v>56.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AP13" t="n">
         <v>2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>15</v>
+        <v>14.17</v>
       </c>
       <c r="AR13" t="n">
-        <v>15.2</v>
+        <v>14.33</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>61.2</v>
+        <v>62.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="BA13" t="n">
-        <v>14.2</v>
+        <v>14.17</v>
       </c>
       <c r="BB13" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.6</v>
+        <v>5.17</v>
       </c>
       <c r="BD13" t="n">
-        <v>21.8</v>
+        <v>22.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="BH13" t="n">
-        <v>7.45</v>
+        <v>7.58</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.91</v>
+        <v>3.92</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT13" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BU13" t="n">
-        <v>18.18</v>
+        <v>25</v>
       </c>
       <c r="BV13" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BY13" t="n">
         <v>2.01</v>
@@ -6043,22 +6043,22 @@
         <v>2.25</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.07</v>
+        <v>4.12</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.34</v>
+        <v>4.38</v>
       </c>
       <c r="CC13" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="CD13" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="CG13" t="n">
         <v>2.89</v>
@@ -6073,25 +6073,25 @@
         <v>1.93</v>
       </c>
       <c r="CK13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="CN13" t="n">
         <v>1.61</v>
       </c>
-      <c r="CL13" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="CM13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="CN13" t="n">
-        <v>1.63</v>
-      </c>
       <c r="CO13" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="CR13" t="n">
         <v>1.39</v>
@@ -6106,22 +6106,22 @@
         <v>1.43</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="DB13" t="n">
         <v>1.3</v>
@@ -6130,82 +6130,82 @@
         <v>1.95</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="DH13" t="n">
-        <v>101.54</v>
+        <v>103.33</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.91</v>
+        <v>4.92</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DM13" t="n">
-        <v>55.91</v>
+        <v>55.75</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="DP13" t="n">
-        <v>15.64</v>
+        <v>15.17</v>
       </c>
       <c r="DQ13" t="n">
-        <v>15.64</v>
+        <v>15.16</v>
       </c>
       <c r="DR13" t="n">
-        <v>5.37</v>
+        <v>5.58</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>55.36</v>
+        <v>56.5</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="DX13" t="n">
-        <v>13.91</v>
+        <v>13.92</v>
       </c>
       <c r="DY13" t="n">
-        <v>9.550000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.37</v>
+        <v>4.67</v>
       </c>
       <c r="EA13" t="n">
-        <v>22.27</v>
+        <v>22.58</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="14">
@@ -6618,94 +6618,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="G15" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="H15" t="n">
-        <v>56</v>
+        <v>60.17</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="J15" t="n">
-        <v>2.6</v>
+        <v>2.83</v>
       </c>
       <c r="K15" t="n">
-        <v>4.8</v>
+        <v>5.33</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="M15" t="n">
-        <v>26.8</v>
+        <v>29</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="O15" t="n">
-        <v>2.2</v>
+        <v>2.67</v>
       </c>
       <c r="P15" t="n">
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="Q15" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="R15" t="n">
-        <v>7.8</v>
+        <v>7.67</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>45.6</v>
+        <v>46.83</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>14.4</v>
+        <v>14.67</v>
       </c>
       <c r="AA15" t="n">
-        <v>10</v>
+        <v>10.17</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>19.8</v>
+        <v>20.33</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.6</v>
+        <v>2.83</v>
       </c>
       <c r="AF15" t="n">
         <v>0.14</v>
@@ -6789,70 +6789,70 @@
         <v>3.43</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="BH15" t="n">
-        <v>8.17</v>
+        <v>8.77</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="BO15" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.17</v>
+        <v>3.46</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.92</v>
+        <v>5.23</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BT15" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BU15" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BV15" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW15" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX15" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BY15" t="n">
-        <v>5.11</v>
+        <v>4.59</v>
       </c>
       <c r="BZ15" t="n">
-        <v>5.28</v>
+        <v>4.78</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.88</v>
+        <v>3.82</v>
       </c>
       <c r="CC15" t="n">
         <v>5.51</v>
@@ -6864,25 +6864,25 @@
         <v>1.4</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="CJ15" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="CK15" t="n">
         <v>1.86</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="CM15" t="n">
         <v>1.88</v>
@@ -6891,13 +6891,13 @@
         <v>1.51</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.58</v>
+        <v>3.52</v>
       </c>
       <c r="CR15" t="n">
         <v>1.43</v>
@@ -6912,106 +6912,106 @@
         <v>1.4</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="CW15" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="CZ15" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="DA15" t="n">
         <v>1.58</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF15" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="DH15" t="n">
-        <v>68.58</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.25</v>
+        <v>3.61</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.34</v>
+        <v>0.47</v>
       </c>
       <c r="DM15" t="n">
-        <v>29</v>
+        <v>29.85</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="DP15" t="n">
-        <v>15.92</v>
+        <v>15.69</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.83</v>
+        <v>15.69</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.67</v>
+        <v>7.62</v>
       </c>
       <c r="DS15" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DT15" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>44.92</v>
+        <v>45.54</v>
       </c>
       <c r="DW15" t="n">
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>11.42</v>
+        <v>11.77</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.16</v>
+        <v>7.46</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.25</v>
+        <v>4.31</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.33</v>
+        <v>19.61</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="EC15" t="n">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -3147,16 +3147,16 @@
         <v>16.43</v>
       </c>
       <c r="BB6" t="n">
-        <v>9.859999999999999</v>
+        <v>10</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.57</v>
+        <v>6.43</v>
       </c>
       <c r="BD6" t="n">
         <v>17.57</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="BF6" t="n">
         <v>4.71</v>
@@ -3372,16 +3372,16 @@
         <v>14.46</v>
       </c>
       <c r="DY6" t="n">
-        <v>9.08</v>
+        <v>9.16</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.38</v>
+        <v>5.31</v>
       </c>
       <c r="EA6" t="n">
         <v>15.69</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="EC6" t="n">
         <v>4.15</v>
@@ -4347,7 +4347,7 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>41.67</v>
+        <v>41.83</v>
       </c>
       <c r="AZ9" t="n">
         <v>0.67</v>
@@ -4572,7 +4572,7 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>41.58</v>
+        <v>41.66</v>
       </c>
       <c r="DW9" t="n">
         <v>0.42</v>
@@ -4669,7 +4669,7 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>63.14</v>
+        <v>63</v>
       </c>
       <c r="Y10" t="n">
         <v>0.14</v>
@@ -4975,7 +4975,7 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>61.46</v>
+        <v>61.38</v>
       </c>
       <c r="DW10" t="n">
         <v>0.08</v>
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5502,49 +5502,49 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>69.70999999999999</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AL12" t="n">
         <v>2</v>
       </c>
-      <c r="AH12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>65.83</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>2.33</v>
-      </c>
       <c r="AM12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN12" t="n">
-        <v>28.33</v>
+        <v>28.43</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14.33</v>
+        <v>14.14</v>
       </c>
       <c r="AR12" t="n">
-        <v>11.83</v>
+        <v>13</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.67</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,82 +5556,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>37.83</v>
+        <v>39.14</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BA12" t="n">
-        <v>7.83</v>
+        <v>7.57</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.33</v>
+        <v>5.14</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="BD12" t="n">
-        <v>14.67</v>
+        <v>16.71</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="BF12" t="n">
         <v>3</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.75</v>
+        <v>8.23</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="BO12" t="n">
         <v>1.08</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.42</v>
+        <v>4.08</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="BR12" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS12" t="n">
-        <v>75</v>
+        <v>69.23</v>
       </c>
       <c r="BT12" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BU12" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV12" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW12" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BX12" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BY12" t="n">
         <v>4.88</v>
@@ -5640,43 +5640,43 @@
         <v>4.93</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.05</v>
+        <v>3.97</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.32</v>
+        <v>4.21</v>
       </c>
       <c r="CC12" t="n">
-        <v>7.67</v>
+        <v>6.97</v>
       </c>
       <c r="CD12" t="n">
-        <v>9.970000000000001</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF12" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="CH12" t="n">
         <v>1.36</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CJ12" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CL12" t="n">
         <v>2.61</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CN12" t="n">
         <v>1.5</v>
@@ -5685,10 +5685,10 @@
         <v>1.34</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.73</v>
+        <v>3.79</v>
       </c>
       <c r="CR12" t="n">
         <v>1.42</v>
@@ -5703,106 +5703,106 @@
         <v>1.41</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CZ12" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.78</v>
+        <v>3.84</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="DH12" t="n">
-        <v>71.92</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="DI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DJ12" t="n">
         <v>3.08</v>
       </c>
       <c r="DK12" t="n">
-        <v>2.92</v>
+        <v>2.69</v>
       </c>
       <c r="DL12" t="n">
         <v>0.08</v>
       </c>
       <c r="DM12" t="n">
-        <v>30.42</v>
+        <v>30.31</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.75</v>
+        <v>12.77</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11.75</v>
+        <v>12.39</v>
       </c>
       <c r="DR12" t="n">
-        <v>10</v>
+        <v>9.77</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>42.5</v>
+        <v>42.85</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DX12" t="n">
-        <v>8.17</v>
+        <v>8</v>
       </c>
       <c r="DY12" t="n">
-        <v>5.75</v>
+        <v>5.62</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="EA12" t="n">
-        <v>16.5</v>
+        <v>17.46</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="13">
@@ -6215,10 +6215,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
         <v>6</v>
@@ -6227,49 +6227,49 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="G14" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>80.33</v>
+        <v>84.29000000000001</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="K14" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="L14" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="M14" t="n">
-        <v>33.5</v>
+        <v>34.14</v>
       </c>
       <c r="N14" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="P14" t="n">
-        <v>16</v>
+        <v>16.57</v>
       </c>
       <c r="Q14" t="n">
         <v>14</v>
       </c>
       <c r="R14" t="n">
-        <v>7.33</v>
+        <v>6.86</v>
       </c>
       <c r="S14" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6281,28 +6281,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>44.67</v>
+        <v>45.86</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z14" t="n">
-        <v>10.67</v>
+        <v>11.14</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.17</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AC14" t="n">
-        <v>21.5</v>
+        <v>21.57</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6386,70 +6386,70 @@
         <v>3</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.33</v>
+        <v>8.77</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.17</v>
+        <v>3.85</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.08</v>
+        <v>4.85</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>91.67</v>
+        <v>84.62</v>
       </c>
       <c r="BT14" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BU14" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV14" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BW14" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX14" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BY14" t="n">
-        <v>4.95</v>
+        <v>4.6</v>
       </c>
       <c r="BZ14" t="n">
-        <v>5.62</v>
+        <v>5.23</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.56</v>
+        <v>4.44</v>
       </c>
       <c r="CB14" t="n">
-        <v>5.27</v>
+        <v>5.09</v>
       </c>
       <c r="CC14" t="n">
         <v>9.26</v>
@@ -6458,43 +6458,43 @@
         <v>13.97</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.07</v>
+        <v>3.02</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CI14" t="n">
         <v>1.78</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CM14" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="CR14" t="n">
         <v>1.38</v>
@@ -6509,49 +6509,49 @@
         <v>1.5</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CW14" t="n">
         <v>2.07</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="CZ14" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.09</v>
+        <v>3.2</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="DG14" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="DH14" t="n">
-        <v>65.67</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="DI14" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
       <c r="DK14" t="n">
         <v>2.16</v>
@@ -6560,22 +6560,22 @@
         <v>0.08</v>
       </c>
       <c r="DM14" t="n">
-        <v>26</v>
+        <v>26.92</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="DO14" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DP14" t="n">
-        <v>14.92</v>
+        <v>15.31</v>
       </c>
       <c r="DQ14" t="n">
-        <v>11.5</v>
+        <v>11.69</v>
       </c>
       <c r="DR14" t="n">
-        <v>9</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DS14" t="n">
         <v>0.08</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>37.84</v>
+        <v>39</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DX14" t="n">
-        <v>8.42</v>
+        <v>8.85</v>
       </c>
       <c r="DY14" t="n">
-        <v>6.84</v>
+        <v>7.39</v>
       </c>
       <c r="DZ14" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.33</v>
+        <v>17.69</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.77</v>
+        <v>0.8</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="15">

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -2227,7 +2227,7 @@
         <v>2.5</v>
       </c>
       <c r="P4" t="n">
-        <v>12.67</v>
+        <v>12.5</v>
       </c>
       <c r="Q4" t="n">
         <v>13.83</v>
@@ -2539,7 +2539,7 @@
         <v>1.85</v>
       </c>
       <c r="DP4" t="n">
-        <v>14.16</v>
+        <v>14.08</v>
       </c>
       <c r="DQ4" t="n">
         <v>15.54</v>
@@ -5532,7 +5532,7 @@
         <v>1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14.14</v>
+        <v>14.29</v>
       </c>
       <c r="AR12" t="n">
         <v>13</v>
@@ -5763,7 +5763,7 @@
         <v>1.31</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.77</v>
+        <v>12.85</v>
       </c>
       <c r="DQ12" t="n">
         <v>12.39</v>

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1472,136 +1472,136 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>89.14</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>53.86</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>13.71</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>56.57</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>20.86</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="BN2" t="n">
         <v>1.5</v>
       </c>
-      <c r="AH2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>88.83</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>56</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>13.83</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>56</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>14.67</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>22.33</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>8.08</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>1.38</v>
-      </c>
       <c r="BO2" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.69</v>
+        <v>3.71</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.38</v>
+        <v>4.14</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BT2" t="n">
-        <v>23.08</v>
+        <v>28.57</v>
       </c>
       <c r="BU2" t="n">
-        <v>23.08</v>
+        <v>28.57</v>
       </c>
       <c r="BV2" t="n">
-        <v>23.08</v>
+        <v>28.57</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BY2" t="n">
         <v>1.42</v>
@@ -1610,43 +1610,43 @@
         <v>1.41</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.66</v>
+        <v>4.65</v>
       </c>
       <c r="CB2" t="n">
-        <v>5.05</v>
+        <v>5.02</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.11</v>
+        <v>2.01</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.29</v>
+        <v>2.16</v>
       </c>
       <c r="CE2" t="n">
         <v>1.35</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CJ2" t="n">
         <v>2.1</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CM2" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CN2" t="n">
         <v>1.59</v>
@@ -1655,28 +1655,28 @@
         <v>1.26</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="CR2" t="n">
         <v>1.37</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CX2" t="n">
         <v>1.81</v>
@@ -1691,88 +1691,88 @@
         <v>1.61</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="DG2" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="DH2" t="n">
-        <v>97.38</v>
+        <v>96.92</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.62</v>
+        <v>5.43</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="DM2" t="n">
-        <v>61.69</v>
+        <v>60.22</v>
       </c>
       <c r="DN2" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="DP2" t="n">
-        <v>16.38</v>
+        <v>16.22</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.23</v>
+        <v>13.21</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.77</v>
+        <v>5.92</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>58.85</v>
+        <v>58.93</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX2" t="n">
-        <v>16.69</v>
+        <v>16.43</v>
       </c>
       <c r="DY2" t="n">
-        <v>11.85</v>
+        <v>11.22</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.85</v>
+        <v>5.21</v>
       </c>
       <c r="EA2" t="n">
-        <v>21.69</v>
+        <v>21</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
         <v>7</v>
@@ -1794,49 +1794,49 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="H3" t="n">
-        <v>108.17</v>
+        <v>104.29</v>
       </c>
       <c r="I3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J3" t="n">
-        <v>2.17</v>
+        <v>2.71</v>
       </c>
       <c r="K3" t="n">
-        <v>5.83</v>
+        <v>5.43</v>
       </c>
       <c r="L3" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="M3" t="n">
-        <v>51</v>
+        <v>47.71</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="O3" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="P3" t="n">
-        <v>14.17</v>
+        <v>13.14</v>
       </c>
       <c r="Q3" t="n">
-        <v>16.83</v>
+        <v>16.14</v>
       </c>
       <c r="R3" t="n">
-        <v>6.33</v>
+        <v>7.14</v>
       </c>
       <c r="S3" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>59.83</v>
+        <v>57.29</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="Z3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA3" t="n">
-        <v>10.67</v>
+        <v>10.86</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.83</v>
+        <v>4.14</v>
       </c>
       <c r="AC3" t="n">
-        <v>24.5</v>
+        <v>23.14</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="AF3" t="n">
         <v>0.14</v>
@@ -1953,49 +1953,49 @@
         <v>1.57</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.08</v>
+        <v>9</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BP3" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.46</v>
+        <v>6.5</v>
       </c>
       <c r="BR3" t="n">
-        <v>92.31</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS3" t="n">
-        <v>76.92</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT3" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BU3" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BV3" t="n">
         <v>0</v>
@@ -2004,19 +2004,19 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.86</v>
+        <v>2.38</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.94</v>
+        <v>2.53</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.06</v>
+        <v>4.05</v>
       </c>
       <c r="CC3" t="n">
         <v>4.5</v>
@@ -2028,10 +2028,10 @@
         <v>1.41</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CH3" t="n">
         <v>1.37</v>
@@ -2046,16 +2046,16 @@
         <v>1.85</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CN3" t="n">
         <v>1.52</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CP3" t="n">
         <v>2.04</v>
@@ -2067,13 +2067,13 @@
         <v>1.42</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="CT3" t="n">
         <v>2.87</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CV3" t="n">
         <v>1.78</v>
@@ -2082,16 +2082,16 @@
         <v>2.09</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CZ3" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="DB3" t="n">
         <v>1.34</v>
@@ -2100,82 +2100,82 @@
         <v>2.08</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.23</v>
+        <v>1.5</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.69</v>
+        <v>3.64</v>
       </c>
       <c r="DH3" t="n">
-        <v>94.08</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.85</v>
+        <v>2.14</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.23</v>
+        <v>5.07</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.47</v>
+        <v>0.43</v>
       </c>
       <c r="DM3" t="n">
-        <v>43.31</v>
+        <v>42.21</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="DP3" t="n">
-        <v>14.85</v>
+        <v>14.28</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.92</v>
+        <v>14.72</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.77</v>
+        <v>7.14</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>52.38</v>
+        <v>51.64</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DX3" t="n">
-        <v>12.77</v>
+        <v>12.72</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.460000000000001</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.31</v>
+        <v>4</v>
       </c>
       <c r="EA3" t="n">
-        <v>21.08</v>
+        <v>20.64</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
         <v>0.33</v>
@@ -2278,136 +2278,136 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="AI4" t="n">
-        <v>79.86</v>
+        <v>79.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="AL4" t="n">
         <v>4</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN4" t="n">
-        <v>28.57</v>
+        <v>31.12</v>
       </c>
       <c r="AO4" t="n">
         <v>1</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AQ4" t="n">
-        <v>15.43</v>
+        <v>14.75</v>
       </c>
       <c r="AR4" t="n">
         <v>17</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.289999999999999</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>43.43</v>
+        <v>42.62</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>7.57</v>
+        <v>7.75</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.43</v>
+        <v>4.62</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="BD4" t="n">
-        <v>17.29</v>
+        <v>18.25</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.91</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.31</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.46</v>
+        <v>4.57</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.85</v>
+        <v>4.79</v>
       </c>
       <c r="BR4" t="n">
-        <v>92.31</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>76.92</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT4" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BU4" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV4" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX4" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BY4" t="n">
         <v>2.69</v>
@@ -2416,25 +2416,25 @@
         <v>3</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.82</v>
+        <v>3.77</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.02</v>
+        <v>3.96</v>
       </c>
       <c r="CC4" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="CD4" t="n">
-        <v>7.97</v>
+        <v>7.49</v>
       </c>
       <c r="CE4" t="n">
         <v>1.42</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="CH4" t="n">
         <v>1.37</v>
@@ -2443,55 +2443,55 @@
         <v>1.79</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CK4" t="n">
         <v>1.84</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CM4" t="n">
         <v>1.93</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CO4" t="n">
         <v>1.32</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CU4" t="n">
         <v>1.4</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="CX4" t="n">
         <v>1.86</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CZ4" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="DA4" t="n">
         <v>1.56</v>
@@ -2500,85 +2500,85 @@
         <v>1.32</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.56</v>
+        <v>3.59</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="DH4" t="n">
-        <v>73.31</v>
+        <v>73.56999999999999</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.77</v>
+        <v>3.71</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.15</v>
+        <v>4.14</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.47</v>
+        <v>0.43</v>
       </c>
       <c r="DM4" t="n">
-        <v>33.46</v>
+        <v>34.57</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DP4" t="n">
-        <v>14.08</v>
+        <v>13.79</v>
       </c>
       <c r="DQ4" t="n">
-        <v>15.54</v>
+        <v>15.64</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.16</v>
+        <v>8.35</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>43.54</v>
+        <v>43.07</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX4" t="n">
-        <v>8.609999999999999</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="DY4" t="n">
-        <v>4.92</v>
+        <v>5</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.69</v>
+        <v>3.64</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.15</v>
+        <v>19.57</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="EC4" t="n">
-        <v>3.62</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="5">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
         <v>7</v>
@@ -2600,82 +2600,82 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="H5" t="n">
-        <v>88.67</v>
+        <v>86.14</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="L5" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="M5" t="n">
-        <v>47.5</v>
+        <v>45</v>
       </c>
       <c r="N5" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="O5" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="P5" t="n">
-        <v>14</v>
+        <v>14.29</v>
       </c>
       <c r="Q5" t="n">
-        <v>16</v>
+        <v>15.14</v>
       </c>
       <c r="R5" t="n">
-        <v>5.83</v>
+        <v>5.71</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="T5" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="V5" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>13.67</v>
+        <v>12.71</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.33</v>
+        <v>9.57</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.33</v>
+        <v>3.14</v>
       </c>
       <c r="AC5" t="n">
-        <v>23.67</v>
+        <v>23.14</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AE5" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,70 +2759,70 @@
         <v>2.86</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.380000000000001</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.62</v>
+        <v>4.64</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3.77</v>
+        <v>4</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT5" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BU5" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV5" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.54</v>
+        <v>3.11</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.79</v>
+        <v>3.43</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.68</v>
+        <v>3.72</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.96</v>
+        <v>4.02</v>
       </c>
       <c r="CC5" t="n">
         <v>6.88</v>
@@ -2834,16 +2834,16 @@
         <v>1.42</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CJ5" t="n">
         <v>2.02</v>
@@ -2852,34 +2852,34 @@
         <v>1.88</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="CM5" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CN5" t="n">
         <v>1.49</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CV5" t="n">
         <v>1.83</v>
@@ -2891,7 +2891,7 @@
         <v>1.94</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CZ5" t="n">
         <v>1.87</v>
@@ -2900,88 +2900,88 @@
         <v>1.53</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.78</v>
+        <v>3.72</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="DH5" t="n">
-        <v>77</v>
+        <v>76.56999999999999</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.62</v>
+        <v>3.58</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DM5" t="n">
-        <v>37.46</v>
+        <v>36.93</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
       <c r="DO5" t="n">
         <v>1.93</v>
       </c>
       <c r="DP5" t="n">
-        <v>15.38</v>
+        <v>15.43</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.69</v>
+        <v>14.36</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.529999999999999</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>50.23</v>
+        <v>48.78</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.23</v>
+        <v>10</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.62</v>
+        <v>7.43</v>
       </c>
       <c r="DZ5" t="n">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.77</v>
+        <v>21.64</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="6">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
         <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="G6" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="H6" t="n">
-        <v>68.33</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>4.67</v>
+        <v>4.14</v>
       </c>
       <c r="K6" t="n">
-        <v>3.33</v>
+        <v>3.71</v>
       </c>
       <c r="L6" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="M6" t="n">
-        <v>34.17</v>
+        <v>39.57</v>
       </c>
       <c r="N6" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="O6" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>16.17</v>
+        <v>16.29</v>
       </c>
       <c r="Q6" t="n">
-        <v>16.33</v>
+        <v>15.43</v>
       </c>
       <c r="R6" t="n">
-        <v>7.5</v>
+        <v>7.86</v>
       </c>
       <c r="S6" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="T6" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3057,28 +3057,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>37.5</v>
+        <v>41.14</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="Z6" t="n">
-        <v>12.17</v>
+        <v>13.29</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.17</v>
+        <v>9</v>
       </c>
       <c r="AB6" t="n">
-        <v>4</v>
+        <v>4.29</v>
       </c>
       <c r="AC6" t="n">
-        <v>13.5</v>
+        <v>15.29</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AE6" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,70 +3162,70 @@
         <v>4.71</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.31</v>
+        <v>3.07</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.619999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.31</v>
+        <v>3.07</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BL6" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="BP6" t="n">
-        <v>5.31</v>
+        <v>5.36</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.31</v>
+        <v>4.29</v>
       </c>
       <c r="BR6" t="n">
-        <v>100</v>
+        <v>92.86</v>
       </c>
       <c r="BS6" t="n">
-        <v>92.31</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU6" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BV6" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>76.92</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY6" t="n">
-        <v>5.31</v>
+        <v>4.85</v>
       </c>
       <c r="BZ6" t="n">
-        <v>5.42</v>
+        <v>4.94</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.82</v>
+        <v>3.76</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.92</v>
+        <v>3.87</v>
       </c>
       <c r="CC6" t="n">
         <v>4.45</v>
@@ -3240,16 +3240,16 @@
         <v>2.93</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CI6" t="n">
         <v>1.81</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CK6" t="n">
         <v>1.76</v>
@@ -3258,7 +3258,7 @@
         <v>2.47</v>
       </c>
       <c r="CM6" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CN6" t="n">
         <v>1.52</v>
@@ -3267,28 +3267,28 @@
         <v>1.33</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.59</v>
+        <v>3.61</v>
       </c>
       <c r="CR6" t="n">
         <v>1.45</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CT6" t="n">
         <v>2.76</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CX6" t="n">
         <v>1.93</v>
@@ -3297,94 +3297,94 @@
         <v>2.44</v>
       </c>
       <c r="CZ6" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="DB6" t="n">
         <v>1.35</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.78</v>
+        <v>3.79</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF6" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>75.70999999999999</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>38.29</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DO6" t="n">
         <v>2.93</v>
       </c>
-      <c r="DG6" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="DH6" t="n">
-        <v>72.3</v>
-      </c>
-      <c r="DI6" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="DJ6" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="DK6" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="DL6" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="DM6" t="n">
-        <v>35.69</v>
-      </c>
-      <c r="DN6" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="DO6" t="n">
-        <v>2.85</v>
-      </c>
       <c r="DP6" t="n">
-        <v>17.54</v>
+        <v>17.5</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14.15</v>
+        <v>13.86</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.15</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>42.92</v>
+        <v>44.36</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DX6" t="n">
-        <v>14.46</v>
+        <v>14.86</v>
       </c>
       <c r="DY6" t="n">
-        <v>9.16</v>
+        <v>9.5</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.31</v>
+        <v>5.36</v>
       </c>
       <c r="EA6" t="n">
-        <v>15.69</v>
+        <v>16.43</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="EC6" t="n">
-        <v>4.15</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" t="n">
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3487,136 +3487,136 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AI7" t="n">
-        <v>86.5</v>
+        <v>83.70999999999999</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK7" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AN7" t="n">
-        <v>32.67</v>
+        <v>31</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AQ7" t="n">
-        <v>15.5</v>
+        <v>16.14</v>
       </c>
       <c r="AR7" t="n">
-        <v>12.17</v>
+        <v>11.71</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.67</v>
+        <v>9</v>
       </c>
       <c r="AT7" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>16.14</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="BN7" t="n">
         <v>1.5</v>
       </c>
-      <c r="AU7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>43</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>15.83</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>8.460000000000001</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>1.46</v>
-      </c>
       <c r="BO7" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.92</v>
+        <v>4.14</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.38</v>
+        <v>4.36</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BT7" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BU7" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV7" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW7" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX7" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BY7" t="n">
         <v>5.84</v>
@@ -3625,22 +3625,22 @@
         <v>6.09</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.86</v>
+        <v>3.92</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.95</v>
+        <v>4.01</v>
       </c>
       <c r="CC7" t="n">
-        <v>5.09</v>
+        <v>5.5</v>
       </c>
       <c r="CD7" t="n">
-        <v>5.52</v>
+        <v>5.94</v>
       </c>
       <c r="CE7" t="n">
         <v>1.42</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CG7" t="n">
         <v>2.74</v>
@@ -3661,7 +3661,7 @@
         <v>2.53</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CN7" t="n">
         <v>1.5</v>
@@ -3670,34 +3670,34 @@
         <v>1.33</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.66</v>
+        <v>3.61</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.81</v>
+        <v>2.87</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CV7" t="n">
         <v>1.81</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CX7" t="n">
         <v>1.92</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CZ7" t="n">
         <v>1.89</v>
@@ -3706,88 +3706,88 @@
         <v>1.54</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.31</v>
+        <v>2.22</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="DH7" t="n">
-        <v>83</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.84</v>
+        <v>3.78</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.46</v>
+        <v>3.36</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.39</v>
+        <v>0.43</v>
       </c>
       <c r="DM7" t="n">
-        <v>32.23</v>
+        <v>31.43</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="DP7" t="n">
-        <v>15.16</v>
+        <v>15.5</v>
       </c>
       <c r="DQ7" t="n">
-        <v>13.62</v>
+        <v>13.28</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.15</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>43.61</v>
+        <v>42.07</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.08</v>
+        <v>11.43</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.31</v>
+        <v>7.86</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.77</v>
+        <v>3.57</v>
       </c>
       <c r="EA7" t="n">
-        <v>16.54</v>
+        <v>16.64</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.61</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="8">
@@ -3797,91 +3797,91 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="F8" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="G8" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>103.86</v>
+        <v>108.75</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="L8" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="M8" t="n">
-        <v>46.14</v>
+        <v>46.25</v>
       </c>
       <c r="N8" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="O8" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="P8" t="n">
-        <v>12.14</v>
+        <v>11.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>15.86</v>
+        <v>16.25</v>
       </c>
       <c r="R8" t="n">
-        <v>6.43</v>
+        <v>5.88</v>
       </c>
       <c r="S8" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="T8" t="n">
         <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="V8" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>61.43</v>
+        <v>63.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z8" t="n">
-        <v>15</v>
+        <v>15.38</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.859999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.14</v>
+        <v>6.12</v>
       </c>
       <c r="AC8" t="n">
-        <v>23.43</v>
+        <v>23</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -3968,70 +3968,70 @@
         <v>2.17</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.69</v>
+        <v>3.64</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.619999999999999</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.69</v>
+        <v>3.64</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BL8" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.54</v>
+        <v>4.71</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.08</v>
+        <v>5</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
       </c>
       <c r="BS8" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BT8" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU8" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BV8" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BW8" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BX8" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.72</v>
+        <v>3.79</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.89</v>
+        <v>3.96</v>
       </c>
       <c r="CC8" t="n">
         <v>5.3</v>
@@ -4043,7 +4043,7 @@
         <v>1.38</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="CG8" t="n">
         <v>2.85</v>
@@ -4055,55 +4055,55 @@
         <v>1.79</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CM8" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.57</v>
+        <v>3.52</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CW8" t="n">
         <v>1.98</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="CZ8" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="DA8" t="n">
         <v>1.56</v>
@@ -4112,85 +4112,85 @@
         <v>1.33</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.85</v>
+        <v>2.93</v>
       </c>
       <c r="DH8" t="n">
-        <v>97.92</v>
+        <v>101.14</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.23</v>
+        <v>5.5</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.46</v>
+        <v>0.57</v>
       </c>
       <c r="DM8" t="n">
-        <v>42.46</v>
+        <v>42.79</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.38</v>
+        <v>2.57</v>
       </c>
       <c r="DP8" t="n">
-        <v>12.31</v>
+        <v>12.07</v>
       </c>
       <c r="DQ8" t="n">
-        <v>15.62</v>
+        <v>15.86</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.69</v>
+        <v>6.36</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>58.38</v>
+        <v>59.78</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.69</v>
+        <v>13.07</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.54</v>
+        <v>7.86</v>
       </c>
       <c r="DZ8" t="n">
-        <v>5.15</v>
+        <v>5.21</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.93</v>
+        <v>21.79</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="9">
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
         <v>6</v>
@@ -4212,82 +4212,82 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="G9" t="n">
-        <v>1.67</v>
+        <v>2.29</v>
       </c>
       <c r="H9" t="n">
-        <v>70.5</v>
+        <v>71.29000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="J9" t="n">
-        <v>2.67</v>
+        <v>2.86</v>
       </c>
       <c r="K9" t="n">
-        <v>2.5</v>
+        <v>3.29</v>
       </c>
       <c r="L9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="M9" t="n">
-        <v>25.67</v>
+        <v>26.29</v>
       </c>
       <c r="N9" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="O9" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>15.67</v>
+        <v>15.71</v>
       </c>
       <c r="Q9" t="n">
-        <v>18.67</v>
+        <v>17.57</v>
       </c>
       <c r="R9" t="n">
-        <v>11.17</v>
+        <v>10.86</v>
       </c>
       <c r="S9" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>41.5</v>
+        <v>43.71</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z9" t="n">
-        <v>8</v>
+        <v>8.43</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.67</v>
+        <v>5.86</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="AC9" t="n">
-        <v>19.67</v>
+        <v>18.86</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="AF9" t="n">
         <v>0.17</v>
@@ -4374,67 +4374,67 @@
         <v>3</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.67</v>
+        <v>9</v>
       </c>
       <c r="BI9" t="n">
         <v>3</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.75</v>
+        <v>4.92</v>
       </c>
       <c r="BQ9" t="n">
-        <v>3.92</v>
+        <v>4.08</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT9" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BU9" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BV9" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX9" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BY9" t="n">
-        <v>4.07</v>
+        <v>3.73</v>
       </c>
       <c r="BZ9" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.04</v>
+        <v>4</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.39</v>
+        <v>4.31</v>
       </c>
       <c r="CC9" t="n">
         <v>6.85</v>
@@ -4449,37 +4449,37 @@
         <v>2.72</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CI9" t="n">
         <v>1.94</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CK9" t="n">
         <v>1.75</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="CM9" t="n">
         <v>2</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CO9" t="n">
         <v>1.26</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CR9" t="n">
         <v>1.4</v>
@@ -4494,10 +4494,10 @@
         <v>1.46</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CX9" t="n">
         <v>1.76</v>
@@ -4524,76 +4524,76 @@
         <v>0.08</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.42</v>
+        <v>1.77</v>
       </c>
       <c r="DH9" t="n">
-        <v>64.83</v>
+        <v>65.7</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="DJ9" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>25.46</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>14</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>16.61</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>42.84</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="DZ9" t="n">
         <v>3</v>
       </c>
-      <c r="DK9" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="DL9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="DM9" t="n">
-        <v>25.08</v>
-      </c>
-      <c r="DN9" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="DO9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DP9" t="n">
-        <v>13.84</v>
-      </c>
-      <c r="DQ9" t="n">
-        <v>17.08</v>
-      </c>
-      <c r="DR9" t="n">
-        <v>10.42</v>
-      </c>
-      <c r="DS9" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="DT9" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="DU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV9" t="n">
-        <v>41.66</v>
-      </c>
-      <c r="DW9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="DX9" t="n">
-        <v>8.17</v>
-      </c>
-      <c r="DY9" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="DZ9" t="n">
-        <v>2.92</v>
-      </c>
       <c r="EA9" t="n">
-        <v>17</v>
+        <v>16.77</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
         <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4693,139 +4693,139 @@
         <v>1</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="AI10" t="n">
-        <v>107.5</v>
+        <v>111.86</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AL10" t="n">
-        <v>6.67</v>
+        <v>6.43</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AN10" t="n">
-        <v>55.5</v>
+        <v>57.86</v>
       </c>
       <c r="AO10" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.17</v>
+        <v>2.86</v>
       </c>
       <c r="AQ10" t="n">
-        <v>15.33</v>
+        <v>14.86</v>
       </c>
       <c r="AR10" t="n">
-        <v>12.67</v>
+        <v>11.86</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.17</v>
+        <v>4.86</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>59.5</v>
+        <v>59.29</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="BA10" t="n">
-        <v>14.67</v>
+        <v>14.71</v>
       </c>
       <c r="BB10" t="n">
-        <v>9.67</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BC10" t="n">
         <v>5</v>
       </c>
       <c r="BD10" t="n">
-        <v>26</v>
+        <v>25.14</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.85</v>
+        <v>2.64</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.619999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.85</v>
+        <v>2.64</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.85</v>
+        <v>4.57</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.77</v>
+        <v>4.93</v>
       </c>
       <c r="BR10" t="n">
-        <v>100</v>
+        <v>92.86</v>
       </c>
       <c r="BS10" t="n">
-        <v>92.31</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BU10" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV10" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BY10" t="n">
         <v>1.27</v>
@@ -4834,43 +4834,43 @@
         <v>1.26</v>
       </c>
       <c r="CA10" t="n">
-        <v>5.47</v>
+        <v>5.36</v>
       </c>
       <c r="CB10" t="n">
-        <v>6.32</v>
+        <v>6.15</v>
       </c>
       <c r="CC10" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CD10" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CE10" t="n">
         <v>1.34</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CJ10" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CL10" t="n">
         <v>2.59</v>
       </c>
       <c r="CM10" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="CN10" t="n">
         <v>1.56</v>
@@ -4879,124 +4879,124 @@
         <v>1.22</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CW10" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="CY10" t="n">
         <v>2.34</v>
       </c>
-      <c r="CX10" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="CY10" t="n">
-        <v>2.33</v>
-      </c>
       <c r="CZ10" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="DB10" t="n">
         <v>1.26</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="DG10" t="n">
-        <v>3.23</v>
+        <v>3.28</v>
       </c>
       <c r="DH10" t="n">
-        <v>117.62</v>
+        <v>119.08</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="DK10" t="n">
-        <v>7.39</v>
+        <v>7.21</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="DM10" t="n">
-        <v>66.31</v>
+        <v>66.72</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.77</v>
+        <v>0.85</v>
       </c>
       <c r="DO10" t="n">
-        <v>4.16</v>
+        <v>3.93</v>
       </c>
       <c r="DP10" t="n">
-        <v>12.69</v>
+        <v>12.64</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.54</v>
+        <v>12.14</v>
       </c>
       <c r="DR10" t="n">
-        <v>4.23</v>
+        <v>4.58</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>61.38</v>
+        <v>61.14</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DX10" t="n">
-        <v>18.46</v>
+        <v>18.21</v>
       </c>
       <c r="DY10" t="n">
-        <v>12.38</v>
+        <v>12.21</v>
       </c>
       <c r="DZ10" t="n">
-        <v>6.08</v>
+        <v>6</v>
       </c>
       <c r="EA10" t="n">
-        <v>25.84</v>
+        <v>25.43</v>
       </c>
       <c r="EB10" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" t="n">
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -5096,139 +5096,139 @@
         <v>1.71</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.33</v>
+        <v>2.86</v>
       </c>
       <c r="AI11" t="n">
-        <v>106.17</v>
+        <v>107.71</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.83</v>
+        <v>4.57</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN11" t="n">
-        <v>51.17</v>
+        <v>54</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.17</v>
+        <v>12.86</v>
       </c>
       <c r="AR11" t="n">
-        <v>12.67</v>
+        <v>13.14</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.67</v>
+        <v>5.14</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>59.5</v>
+        <v>61</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA11" t="n">
-        <v>12.5</v>
+        <v>12.29</v>
       </c>
       <c r="BB11" t="n">
-        <v>8</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.5</v>
+        <v>4.14</v>
       </c>
       <c r="BD11" t="n">
-        <v>24.67</v>
+        <v>24.57</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="BG11" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.15</v>
+        <v>8.43</v>
       </c>
       <c r="BI11" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BL11" t="n">
         <v>1</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.46</v>
+        <v>4.64</v>
       </c>
       <c r="BR11" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS11" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT11" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU11" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BV11" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX11" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BY11" t="n">
         <v>1.49</v>
@@ -5237,25 +5237,25 @@
         <v>1.54</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.59</v>
+        <v>4.57</v>
       </c>
       <c r="CB11" t="n">
-        <v>5.05</v>
+        <v>5.03</v>
       </c>
       <c r="CC11" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="CD11" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="CE11" t="n">
         <v>1.34</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="CH11" t="n">
         <v>1.46</v>
@@ -5267,34 +5267,34 @@
         <v>1.99</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CL11" t="n">
         <v>2.33</v>
       </c>
       <c r="CM11" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CO11" t="n">
         <v>1.25</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CQ11" t="n">
         <v>2.98</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="CU11" t="n">
         <v>1.49</v>
@@ -5303,16 +5303,16 @@
         <v>1.82</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DA11" t="n">
         <v>1.61</v>
@@ -5321,85 +5321,85 @@
         <v>1.26</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="DD11" t="n">
         <v>3.05</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.15</v>
+        <v>3.36</v>
       </c>
       <c r="DH11" t="n">
-        <v>113.92</v>
+        <v>114.14</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.54</v>
+        <v>5.79</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DM11" t="n">
-        <v>59.85</v>
+        <v>60.64</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.69</v>
+        <v>11.64</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13.62</v>
+        <v>13.78</v>
       </c>
       <c r="DR11" t="n">
-        <v>4.54</v>
+        <v>4.35</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>63</v>
+        <v>63.5</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX11" t="n">
-        <v>15.39</v>
+        <v>15.08</v>
       </c>
       <c r="DY11" t="n">
-        <v>10.23</v>
+        <v>10.14</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.15</v>
+        <v>4.92</v>
       </c>
       <c r="EA11" t="n">
-        <v>25.08</v>
+        <v>25</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="12">
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
         <v>7</v>
@@ -5421,82 +5421,82 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="G12" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="H12" t="n">
-        <v>78</v>
+        <v>77.56999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="J12" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="K12" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>32.5</v>
+        <v>31.57</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="O12" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="P12" t="n">
-        <v>11.17</v>
+        <v>11.43</v>
       </c>
       <c r="Q12" t="n">
-        <v>11.67</v>
+        <v>12</v>
       </c>
       <c r="R12" t="n">
-        <v>10.33</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T12" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="U12" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="V12" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>47.17</v>
+        <v>46.14</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z12" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AA12" t="n">
-        <v>6.17</v>
+        <v>6</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AC12" t="n">
-        <v>18.33</v>
+        <v>17.14</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5580,70 +5580,70 @@
         <v>3</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.46</v>
+        <v>2.64</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.23</v>
+        <v>8</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.46</v>
+        <v>2.64</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.15</v>
+        <v>3.93</v>
       </c>
       <c r="BR12" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS12" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>38.46</v>
+        <v>42.86</v>
       </c>
       <c r="BU12" t="n">
-        <v>15.38</v>
+        <v>21.43</v>
       </c>
       <c r="BV12" t="n">
-        <v>15.38</v>
+        <v>21.43</v>
       </c>
       <c r="BW12" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BX12" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BY12" t="n">
-        <v>4.88</v>
+        <v>5.41</v>
       </c>
       <c r="BZ12" t="n">
-        <v>4.93</v>
+        <v>5.5</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.97</v>
+        <v>4.01</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.21</v>
+        <v>4.24</v>
       </c>
       <c r="CC12" t="n">
         <v>6.97</v>
@@ -5655,10 +5655,10 @@
         <v>1.44</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="CH12" t="n">
         <v>1.36</v>
@@ -5670,10 +5670,10 @@
         <v>2.11</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="CM12" t="n">
         <v>1.84</v>
@@ -5685,10 +5685,10 @@
         <v>1.34</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.79</v>
+        <v>3.76</v>
       </c>
       <c r="CR12" t="n">
         <v>1.42</v>
@@ -5697,112 +5697,112 @@
         <v>2.94</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="CU12" t="n">
         <v>1.41</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CW12" t="n">
         <v>2.18</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CY12" t="n">
         <v>2.39</v>
       </c>
       <c r="CZ12" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="DB12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DG12" t="n">
         <v>1.36</v>
       </c>
-      <c r="DC12" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="DD12" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="DE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF12" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="DG12" t="n">
-        <v>1.38</v>
-      </c>
       <c r="DH12" t="n">
-        <v>73.54000000000001</v>
+        <v>73.64</v>
       </c>
       <c r="DI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="DK12" t="n">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DM12" t="n">
-        <v>30.31</v>
+        <v>30</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.85</v>
+        <v>12.86</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.39</v>
+        <v>12.5</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.77</v>
+        <v>9.58</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>42.85</v>
+        <v>42.64</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DX12" t="n">
-        <v>8</v>
+        <v>7.79</v>
       </c>
       <c r="DY12" t="n">
-        <v>5.62</v>
+        <v>5.57</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="EA12" t="n">
-        <v>17.46</v>
+        <v>16.92</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="13">
@@ -5812,94 +5812,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
         <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="F13" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="H13" t="n">
-        <v>100.33</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J13" t="n">
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>4.67</v>
+        <v>4.86</v>
       </c>
       <c r="L13" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="M13" t="n">
-        <v>55</v>
+        <v>51.71</v>
       </c>
       <c r="N13" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="O13" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="P13" t="n">
-        <v>16.17</v>
+        <v>16.71</v>
       </c>
       <c r="Q13" t="n">
-        <v>16</v>
+        <v>16.14</v>
       </c>
       <c r="R13" t="n">
-        <v>5.17</v>
+        <v>5.14</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="U13" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="V13" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>50.5</v>
+        <v>49.57</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z13" t="n">
-        <v>13.67</v>
+        <v>12.71</v>
       </c>
       <c r="AA13" t="n">
-        <v>9.5</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.17</v>
+        <v>3.86</v>
       </c>
       <c r="AC13" t="n">
-        <v>22.67</v>
+        <v>23.29</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="AF13" t="n">
         <v>0.17</v>
@@ -5983,70 +5983,70 @@
         <v>2.33</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="BH13" t="n">
-        <v>7.58</v>
+        <v>7.85</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.92</v>
+        <v>4.15</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT13" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BU13" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV13" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.12</v>
+        <v>4.17</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.38</v>
+        <v>4.47</v>
       </c>
       <c r="CC13" t="n">
         <v>1.55</v>
@@ -6058,19 +6058,19 @@
         <v>1.38</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CK13" t="n">
         <v>1.63</v>
@@ -6079,37 +6079,37 @@
         <v>2.27</v>
       </c>
       <c r="CM13" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CO13" t="n">
         <v>1.28</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.23</v>
+        <v>3.19</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CX13" t="n">
         <v>1.82</v>
@@ -6127,85 +6127,85 @@
         <v>1.3</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.39</v>
+        <v>3.35</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="DF13" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="DH13" t="n">
-        <v>103.33</v>
+        <v>102.23</v>
       </c>
       <c r="DI13" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.92</v>
+        <v>5</v>
       </c>
       <c r="DL13" t="n">
         <v>0.16</v>
       </c>
       <c r="DM13" t="n">
-        <v>55.75</v>
+        <v>53.92</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="DP13" t="n">
-        <v>15.17</v>
+        <v>15.54</v>
       </c>
       <c r="DQ13" t="n">
-        <v>15.16</v>
+        <v>15.3</v>
       </c>
       <c r="DR13" t="n">
-        <v>5.58</v>
+        <v>5.54</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>56.5</v>
+        <v>55.54</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DX13" t="n">
-        <v>13.92</v>
+        <v>13.38</v>
       </c>
       <c r="DY13" t="n">
-        <v>9.25</v>
+        <v>8.92</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.67</v>
+        <v>4.46</v>
       </c>
       <c r="EA13" t="n">
-        <v>22.58</v>
+        <v>22.93</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
         <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6308,79 +6308,79 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AI14" t="n">
-        <v>51</v>
+        <v>57.43</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.67</v>
+        <v>3.57</v>
       </c>
       <c r="AL14" t="n">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>0.57</v>
       </c>
       <c r="AN14" t="n">
-        <v>18.5</v>
+        <v>19.86</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.67</v>
+        <v>1.29</v>
       </c>
       <c r="AQ14" t="n">
-        <v>13.83</v>
+        <v>13.57</v>
       </c>
       <c r="AR14" t="n">
-        <v>9</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="AS14" t="n">
-        <v>10.67</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AT14" t="n">
         <v>3</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>31</v>
+        <v>32.71</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BA14" t="n">
-        <v>6.17</v>
+        <v>6.43</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.5</v>
+        <v>4.57</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="BD14" t="n">
-        <v>13.17</v>
+        <v>14.43</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.52</v>
+        <v>0.57</v>
       </c>
       <c r="BF14" t="n">
         <v>3</v>
@@ -6389,55 +6389,55 @@
         <v>3</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.77</v>
+        <v>9.07</v>
       </c>
       <c r="BI14" t="n">
         <v>3</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BL14" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="BP14" t="n">
-        <v>3.85</v>
+        <v>4.07</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.85</v>
+        <v>4.93</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BU14" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV14" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BW14" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX14" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BY14" t="n">
         <v>4.6</v>
@@ -6446,43 +6446,43 @@
         <v>5.23</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.44</v>
+        <v>4.37</v>
       </c>
       <c r="CB14" t="n">
-        <v>5.09</v>
+        <v>4.97</v>
       </c>
       <c r="CC14" t="n">
-        <v>9.26</v>
+        <v>8.5</v>
       </c>
       <c r="CD14" t="n">
-        <v>13.97</v>
+        <v>12.58</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CF14" t="n">
         <v>2.72</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CH14" t="n">
         <v>1.44</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="CM14" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CN14" t="n">
         <v>1.56</v>
@@ -6491,7 +6491,7 @@
         <v>1.25</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CQ14" t="n">
         <v>3.15</v>
@@ -6509,22 +6509,22 @@
         <v>1.5</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CZ14" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="DB14" t="n">
         <v>1.28</v>
@@ -6533,82 +6533,82 @@
         <v>1.89</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="DG14" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="DH14" t="n">
-        <v>68.93000000000001</v>
+        <v>70.86</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="DK14" t="n">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.08</v>
+        <v>0.36</v>
       </c>
       <c r="DM14" t="n">
-        <v>26.92</v>
+        <v>27</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="DO14" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="DP14" t="n">
-        <v>15.31</v>
+        <v>15.07</v>
       </c>
       <c r="DQ14" t="n">
-        <v>11.69</v>
+        <v>11.93</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.619999999999999</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>39</v>
+        <v>39.29</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX14" t="n">
-        <v>8.85</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.39</v>
+        <v>7.21</v>
       </c>
       <c r="DZ14" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.69</v>
+        <v>18</v>
       </c>
       <c r="EB14" t="n">
         <v>0.8</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
         <v>0.17</v>
@@ -6708,52 +6708,52 @@
         <v>2.83</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AI15" t="n">
-        <v>77.56999999999999</v>
+        <v>80.12</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.43</v>
+        <v>3.75</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AN15" t="n">
-        <v>30.57</v>
+        <v>31.62</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AP15" t="n">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="AQ15" t="n">
-        <v>17.14</v>
+        <v>17.25</v>
       </c>
       <c r="AR15" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.57</v>
+        <v>7.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6765,82 +6765,82 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>44.43</v>
+        <v>45.88</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.289999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.14</v>
+        <v>5.38</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.14</v>
+        <v>4.12</v>
       </c>
       <c r="BD15" t="n">
         <v>19</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.43</v>
+        <v>3.75</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="BH15" t="n">
-        <v>8.77</v>
+        <v>8.93</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.54</v>
+        <v>0.64</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.46</v>
+        <v>3.71</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.23</v>
+        <v>5.14</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT15" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BU15" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BV15" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW15" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX15" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BY15" t="n">
         <v>4.59</v>
@@ -6849,73 +6849,73 @@
         <v>4.78</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.72</v>
+        <v>3.79</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.82</v>
+        <v>3.94</v>
       </c>
       <c r="CC15" t="n">
-        <v>5.51</v>
+        <v>5.82</v>
       </c>
       <c r="CD15" t="n">
-        <v>5.47</v>
+        <v>6.02</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.99</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="CM15" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CO15" t="n">
         <v>1.31</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.52</v>
+        <v>3.46</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CW15" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CX15" t="n">
         <v>1.89</v>
@@ -6933,85 +6933,85 @@
         <v>1.33</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.62</v>
+        <v>3.56</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF15" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="DH15" t="n">
-        <v>69.54000000000001</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.15</v>
+        <v>3.36</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.61</v>
+        <v>3.71</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DM15" t="n">
-        <v>29.85</v>
+        <v>30.5</v>
       </c>
       <c r="DN15" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="DP15" t="n">
-        <v>15.69</v>
+        <v>15.86</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.69</v>
+        <v>15.93</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.62</v>
+        <v>7.57</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>45.54</v>
+        <v>46.29</v>
       </c>
       <c r="DW15" t="n">
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>11.77</v>
+        <v>11.72</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.46</v>
+        <v>7.43</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.31</v>
+        <v>4.28</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.61</v>
+        <v>19.57</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="EC15" t="n">
-        <v>3.15</v>
+        <v>3.36</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -1794,7 +1794,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="G3" t="n">
         <v>3.86</v>
@@ -1806,7 +1806,7 @@
         <v>0.14</v>
       </c>
       <c r="J3" t="n">
-        <v>2.71</v>
+        <v>2.86</v>
       </c>
       <c r="K3" t="n">
         <v>5.43</v>
@@ -1869,7 +1869,7 @@
         <v>1.59</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.14</v>
+        <v>2.29</v>
       </c>
       <c r="AF3" t="n">
         <v>0.14</v>
@@ -2010,13 +2010,13 @@
         <v>2.38</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="CA3" t="n">
         <v>3.8</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.05</v>
+        <v>4.04</v>
       </c>
       <c r="CC3" t="n">
         <v>4.5</v>
@@ -2106,7 +2106,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="DG3" t="n">
         <v>3.64</v>
@@ -2118,7 +2118,7 @@
         <v>0.14</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="DK3" t="n">
         <v>5.07</v>
@@ -2175,7 +2175,7 @@
         <v>1.4</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="4">
@@ -2332,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>42.62</v>
+        <v>42.75</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>43.07</v>
+        <v>43.14</v>
       </c>
       <c r="DW4" t="n">
         <v>0.14</v>
@@ -2630,7 +2630,7 @@
         <v>1.57</v>
       </c>
       <c r="P5" t="n">
-        <v>14.29</v>
+        <v>14.14</v>
       </c>
       <c r="Q5" t="n">
         <v>15.14</v>
@@ -2942,7 +2942,7 @@
         <v>1.93</v>
       </c>
       <c r="DP5" t="n">
-        <v>15.43</v>
+        <v>15.36</v>
       </c>
       <c r="DQ5" t="n">
         <v>14.36</v>
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>41.14</v>
+        <v>41</v>
       </c>
       <c r="Y6" t="n">
         <v>0.57</v>
@@ -3363,7 +3363,7 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>44.36</v>
+        <v>44.28</v>
       </c>
       <c r="DW6" t="n">
         <v>0.36</v>
@@ -3556,7 +3556,7 @@
         <v>3</v>
       </c>
       <c r="BD7" t="n">
-        <v>16.14</v>
+        <v>16</v>
       </c>
       <c r="BE7" t="n">
         <v>1.06</v>
@@ -3781,7 +3781,7 @@
         <v>3.57</v>
       </c>
       <c r="EA7" t="n">
-        <v>16.64</v>
+        <v>16.57</v>
       </c>
       <c r="EB7" t="n">
         <v>1.2</v>
@@ -4837,7 +4837,7 @@
         <v>5.36</v>
       </c>
       <c r="CB10" t="n">
-        <v>6.15</v>
+        <v>6.14</v>
       </c>
       <c r="CC10" t="n">
         <v>1.65</v>
@@ -5129,7 +5129,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12.86</v>
+        <v>12.71</v>
       </c>
       <c r="AR11" t="n">
         <v>13.14</v>
@@ -5360,7 +5360,7 @@
         <v>2.43</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.64</v>
+        <v>11.57</v>
       </c>
       <c r="DQ11" t="n">
         <v>13.78</v>
@@ -5854,10 +5854,10 @@
         <v>2.71</v>
       </c>
       <c r="P13" t="n">
-        <v>16.71</v>
+        <v>16.86</v>
       </c>
       <c r="Q13" t="n">
-        <v>16.14</v>
+        <v>16</v>
       </c>
       <c r="R13" t="n">
         <v>5.14</v>
@@ -5893,7 +5893,7 @@
         <v>3.86</v>
       </c>
       <c r="AC13" t="n">
-        <v>23.29</v>
+        <v>23.43</v>
       </c>
       <c r="AD13" t="n">
         <v>1.45</v>
@@ -6046,7 +6046,7 @@
         <v>4.17</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.47</v>
+        <v>4.46</v>
       </c>
       <c r="CC13" t="n">
         <v>1.55</v>
@@ -6094,22 +6094,22 @@
         <v>3.19</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CV13" t="n">
         <v>1.81</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CX13" t="n">
         <v>1.82</v>
@@ -6127,10 +6127,10 @@
         <v>1.3</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.35</v>
+        <v>3.37</v>
       </c>
       <c r="DE13" t="n">
         <v>0.23</v>
@@ -6166,10 +6166,10 @@
         <v>2.38</v>
       </c>
       <c r="DP13" t="n">
-        <v>15.54</v>
+        <v>15.62</v>
       </c>
       <c r="DQ13" t="n">
-        <v>15.3</v>
+        <v>15.23</v>
       </c>
       <c r="DR13" t="n">
         <v>5.54</v>
@@ -6199,7 +6199,7 @@
         <v>4.46</v>
       </c>
       <c r="EA13" t="n">
-        <v>22.93</v>
+        <v>23</v>
       </c>
       <c r="EB13" t="n">
         <v>1.55</v>
@@ -6741,10 +6741,10 @@
         <v>1.38</v>
       </c>
       <c r="AQ15" t="n">
-        <v>17.25</v>
+        <v>17.12</v>
       </c>
       <c r="AR15" t="n">
-        <v>15.5</v>
+        <v>15.62</v>
       </c>
       <c r="AS15" t="n">
         <v>7.5</v>
@@ -6852,13 +6852,13 @@
         <v>3.79</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.94</v>
+        <v>3.93</v>
       </c>
       <c r="CC15" t="n">
         <v>5.82</v>
       </c>
       <c r="CD15" t="n">
-        <v>6.02</v>
+        <v>5.97</v>
       </c>
       <c r="CE15" t="n">
         <v>1.39</v>
@@ -6903,19 +6903,19 @@
         <v>1.42</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CV15" t="n">
         <v>1.86</v>
       </c>
       <c r="CW15" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CX15" t="n">
         <v>1.89</v>
@@ -6933,10 +6933,10 @@
         <v>1.33</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="DE15" t="n">
         <v>0.14</v>
@@ -6972,10 +6972,10 @@
         <v>1.93</v>
       </c>
       <c r="DP15" t="n">
-        <v>15.86</v>
+        <v>15.78</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.93</v>
+        <v>16</v>
       </c>
       <c r="DR15" t="n">
         <v>7.57</v>

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -2630,7 +2630,7 @@
         <v>1.57</v>
       </c>
       <c r="P5" t="n">
-        <v>14.14</v>
+        <v>14.29</v>
       </c>
       <c r="Q5" t="n">
         <v>15.14</v>
@@ -2942,7 +2942,7 @@
         <v>1.93</v>
       </c>
       <c r="DP5" t="n">
-        <v>15.36</v>
+        <v>15.43</v>
       </c>
       <c r="DQ5" t="n">
         <v>14.36</v>
@@ -5129,7 +5129,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12.71</v>
+        <v>12.86</v>
       </c>
       <c r="AR11" t="n">
         <v>13.14</v>
@@ -5360,7 +5360,7 @@
         <v>2.43</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.57</v>
+        <v>11.64</v>
       </c>
       <c r="DQ11" t="n">
         <v>13.78</v>

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1872,130 +1872,130 @@
         <v>2.29</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG3" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.43</v>
+        <v>3.25</v>
       </c>
       <c r="AI3" t="n">
-        <v>82</v>
+        <v>82.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.71</v>
+        <v>4.5</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AN3" t="n">
-        <v>36.71</v>
+        <v>37.12</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15.43</v>
+        <v>15.88</v>
       </c>
       <c r="AR3" t="n">
-        <v>13.29</v>
+        <v>13.12</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.14</v>
+        <v>6.88</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>46</v>
+        <v>45.62</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.43</v>
+        <v>10.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.57</v>
+        <v>7</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>18.14</v>
+        <v>19.62</v>
       </c>
       <c r="BE3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>9.07</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="BN3" t="n">
         <v>1.2</v>
       </c>
-      <c r="BF3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>9</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>1.29</v>
-      </c>
       <c r="BO3" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BP3" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="BR3" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS3" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT3" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BU3" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BV3" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BY3" t="n">
         <v>2.38</v>
@@ -2013,40 +2013,40 @@
         <v>2.51</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.04</v>
+        <v>3.96</v>
       </c>
       <c r="CC3" t="n">
-        <v>4.5</v>
+        <v>4.26</v>
       </c>
       <c r="CD3" t="n">
-        <v>5.67</v>
+        <v>5.35</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CJ3" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CK3" t="n">
         <v>1.85</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="CM3" t="n">
         <v>1.86</v>
@@ -2055,22 +2055,22 @@
         <v>1.52</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.64</v>
+        <v>3.69</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="CU3" t="n">
         <v>1.39</v>
@@ -2079,7 +2079,7 @@
         <v>1.78</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CX3" t="n">
         <v>1.88</v>
@@ -2094,88 +2094,88 @@
         <v>1.55</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.71</v>
+        <v>3.83</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.64</v>
+        <v>3.53</v>
       </c>
       <c r="DH3" t="n">
-        <v>93.15000000000001</v>
+        <v>92.67</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.07</v>
+        <v>4.93</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="DM3" t="n">
-        <v>42.21</v>
+        <v>42.06</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="DP3" t="n">
-        <v>14.28</v>
+        <v>14.6</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.72</v>
+        <v>14.53</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.14</v>
+        <v>7</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>51.64</v>
+        <v>51.07</v>
       </c>
       <c r="DW3" t="n">
         <v>0.14</v>
       </c>
       <c r="DX3" t="n">
-        <v>12.72</v>
+        <v>12.6</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.720000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.64</v>
+        <v>21.26</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -2185,61 +2185,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="F4" t="n">
-        <v>2.83</v>
+        <v>2.57</v>
       </c>
       <c r="G4" t="n">
-        <v>1.83</v>
+        <v>2.43</v>
       </c>
       <c r="H4" t="n">
-        <v>65.67</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J4" t="n">
-        <v>4.33</v>
+        <v>4.14</v>
       </c>
       <c r="K4" t="n">
-        <v>4.33</v>
+        <v>4.71</v>
       </c>
       <c r="L4" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="M4" t="n">
-        <v>39.17</v>
+        <v>38.86</v>
       </c>
       <c r="N4" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="O4" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="P4" t="n">
-        <v>12.5</v>
+        <v>12.43</v>
       </c>
       <c r="Q4" t="n">
-        <v>13.83</v>
+        <v>14.57</v>
       </c>
       <c r="R4" t="n">
-        <v>8</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2251,28 +2251,28 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>43.67</v>
+        <v>45.57</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.83</v>
+        <v>9.43</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.5</v>
+        <v>5.14</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.33</v>
+        <v>4.29</v>
       </c>
       <c r="AC4" t="n">
-        <v>21.33</v>
+        <v>22.14</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE4" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,70 +2356,70 @@
         <v>3.25</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.359999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.57</v>
+        <v>4.4</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.79</v>
+        <v>5</v>
       </c>
       <c r="BR4" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS4" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT4" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BU4" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV4" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX4" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.77</v>
+        <v>3.71</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.96</v>
+        <v>3.89</v>
       </c>
       <c r="CC4" t="n">
         <v>7</v>
@@ -2428,19 +2428,19 @@
         <v>7.49</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CJ4" t="n">
         <v>2</v>
@@ -2449,40 +2449,40 @@
         <v>1.84</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="CM4" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CN4" t="n">
         <v>1.53</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CX4" t="n">
         <v>1.86</v>
@@ -2497,88 +2497,88 @@
         <v>1.56</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.59</v>
+        <v>3.73</v>
       </c>
       <c r="DE4" t="n">
         <v>0.14</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.28</v>
+        <v>2.53</v>
       </c>
       <c r="DH4" t="n">
-        <v>73.56999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.71</v>
+        <v>3.67</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.14</v>
+        <v>4.33</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DM4" t="n">
-        <v>34.57</v>
+        <v>34.73</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.79</v>
+        <v>13.67</v>
       </c>
       <c r="DQ4" t="n">
-        <v>15.64</v>
+        <v>15.87</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.35</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>43.14</v>
+        <v>44.07</v>
       </c>
       <c r="DW4" t="n">
         <v>0.14</v>
       </c>
       <c r="DX4" t="n">
-        <v>8.640000000000001</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="DY4" t="n">
-        <v>5</v>
+        <v>4.86</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.64</v>
+        <v>3.67</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.57</v>
+        <v>20.07</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="EC4" t="n">
-        <v>3.57</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="5">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="n">
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
         <v>0.14</v>
@@ -3084,136 +3084,136 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AI6" t="n">
-        <v>75.70999999999999</v>
+        <v>74.75</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK6" t="n">
-        <v>4.86</v>
+        <v>4.88</v>
       </c>
       <c r="AL6" t="n">
-        <v>5.71</v>
+        <v>5.12</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AN6" t="n">
-        <v>37</v>
+        <v>34.38</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>18.71</v>
+        <v>18.62</v>
       </c>
       <c r="AR6" t="n">
-        <v>12.29</v>
+        <v>12.12</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.710000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>47.57</v>
+        <v>45.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="BA6" t="n">
-        <v>16.43</v>
+        <v>15</v>
       </c>
       <c r="BB6" t="n">
-        <v>10</v>
+        <v>9.25</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.43</v>
+        <v>5.75</v>
       </c>
       <c r="BD6" t="n">
-        <v>17.57</v>
+        <v>16.88</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.71</v>
+        <v>4.62</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.640000000000001</v>
+        <v>10.27</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BP6" t="n">
-        <v>5.36</v>
+        <v>5.73</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.29</v>
+        <v>4.47</v>
       </c>
       <c r="BR6" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS6" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT6" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BU6" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BV6" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BY6" t="n">
         <v>4.85</v>
@@ -3222,169 +3222,169 @@
         <v>4.94</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.76</v>
+        <v>4.01</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.87</v>
+        <v>4.03</v>
       </c>
       <c r="CC6" t="n">
-        <v>4.45</v>
+        <v>5.64</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.67</v>
+        <v>5.36</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.72</v>
+        <v>2.79</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="CM6" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.61</v>
+        <v>3.51</v>
       </c>
       <c r="CR6" t="n">
         <v>1.45</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="CT6" t="n">
         <v>2.76</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CW6" t="n">
         <v>2.01</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="CZ6" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.79</v>
+        <v>3.68</v>
       </c>
       <c r="DE6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="DH6" t="n">
-        <v>75.70999999999999</v>
+        <v>75.2</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ6" t="n">
-        <v>4.5</v>
+        <v>4.53</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.71</v>
+        <v>4.46</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="DM6" t="n">
-        <v>38.29</v>
+        <v>36.8</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="DP6" t="n">
-        <v>17.5</v>
+        <v>17.53</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.86</v>
+        <v>13.66</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.279999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>44.28</v>
+        <v>43.4</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="DX6" t="n">
-        <v>14.86</v>
+        <v>14.2</v>
       </c>
       <c r="DY6" t="n">
-        <v>9.5</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.36</v>
+        <v>5.07</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.43</v>
+        <v>16.14</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="EC6" t="n">
-        <v>3.92</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="7">
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
         <v>7</v>
@@ -4615,82 +4615,82 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="H10" t="n">
-        <v>126.29</v>
+        <v>128.5</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="K10" t="n">
-        <v>8</v>
+        <v>9.25</v>
       </c>
       <c r="L10" t="n">
-        <v>0.43</v>
+        <v>0.62</v>
       </c>
       <c r="M10" t="n">
-        <v>75.56999999999999</v>
+        <v>76.12</v>
       </c>
       <c r="N10" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="O10" t="n">
-        <v>5</v>
+        <v>5.62</v>
       </c>
       <c r="P10" t="n">
-        <v>10.43</v>
+        <v>10.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.43</v>
+        <v>13</v>
       </c>
       <c r="R10" t="n">
-        <v>4.29</v>
+        <v>4.38</v>
       </c>
       <c r="S10" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="T10" t="n">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="U10" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="V10" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>63</v>
+        <v>63.75</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z10" t="n">
-        <v>21.71</v>
+        <v>22.62</v>
       </c>
       <c r="AA10" t="n">
-        <v>14.71</v>
+        <v>15.75</v>
       </c>
       <c r="AB10" t="n">
-        <v>7</v>
+        <v>6.88</v>
       </c>
       <c r="AC10" t="n">
-        <v>25.71</v>
+        <v>26</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="AE10" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AF10" t="n">
         <v>0.14</v>
@@ -4774,70 +4774,70 @@
         <v>1.57</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.5</v>
+        <v>10.13</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BN10" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.57</v>
+        <v>5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.93</v>
+        <v>5.07</v>
       </c>
       <c r="BR10" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS10" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT10" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BU10" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV10" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CA10" t="n">
-        <v>5.36</v>
+        <v>5.5</v>
       </c>
       <c r="CB10" t="n">
-        <v>6.14</v>
+        <v>6.15</v>
       </c>
       <c r="CC10" t="n">
         <v>1.65</v>
@@ -4846,157 +4846,157 @@
         <v>1.68</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CJ10" t="n">
         <v>2.28</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="CM10" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="CR10" t="n">
         <v>1.38</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="CT10" t="n">
         <v>3.02</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CW10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="CY10" t="n">
         <v>2.32</v>
       </c>
-      <c r="CX10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="CY10" t="n">
-        <v>2.34</v>
-      </c>
       <c r="CZ10" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="DB10" t="n">
         <v>1.26</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="DE10" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="DG10" t="n">
-        <v>3.28</v>
+        <v>3.53</v>
       </c>
       <c r="DH10" t="n">
-        <v>119.08</v>
+        <v>120.73</v>
       </c>
       <c r="DI10" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DK10" t="n">
-        <v>7.21</v>
+        <v>7.93</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="DM10" t="n">
-        <v>66.72</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="DO10" t="n">
-        <v>3.93</v>
+        <v>4.33</v>
       </c>
       <c r="DP10" t="n">
-        <v>12.64</v>
+        <v>12.53</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.14</v>
+        <v>12.47</v>
       </c>
       <c r="DR10" t="n">
-        <v>4.58</v>
+        <v>4.6</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>61.14</v>
+        <v>61.67</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX10" t="n">
-        <v>18.21</v>
+        <v>18.93</v>
       </c>
       <c r="DY10" t="n">
-        <v>12.21</v>
+        <v>12.93</v>
       </c>
       <c r="DZ10" t="n">
         <v>6</v>
       </c>
       <c r="EA10" t="n">
-        <v>25.43</v>
+        <v>25.6</v>
       </c>
       <c r="EB10" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="11">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
         <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5502,49 +5502,49 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AH12" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="AI12" t="n">
-        <v>69.70999999999999</v>
+        <v>70.38</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.57</v>
+        <v>3.25</v>
       </c>
       <c r="AL12" t="n">
-        <v>2</v>
+        <v>2.88</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AN12" t="n">
-        <v>28.43</v>
+        <v>30.88</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AP12" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14.29</v>
+        <v>14.25</v>
       </c>
       <c r="AR12" t="n">
         <v>13</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.289999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,82 +5556,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>39.14</v>
+        <v>39.62</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BA12" t="n">
-        <v>7.57</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.14</v>
+        <v>5.75</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="BD12" t="n">
-        <v>16.71</v>
+        <v>16.12</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.86</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BF12" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="BH12" t="n">
-        <v>8</v>
+        <v>8.33</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="BP12" t="n">
         <v>4.07</v>
       </c>
       <c r="BQ12" t="n">
-        <v>3.93</v>
+        <v>4.27</v>
       </c>
       <c r="BR12" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS12" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT12" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BU12" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV12" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW12" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BX12" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BY12" t="n">
         <v>5.41</v>
@@ -5640,46 +5640,46 @@
         <v>5.5</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.01</v>
+        <v>3.95</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.24</v>
+        <v>4.18</v>
       </c>
       <c r="CC12" t="n">
-        <v>6.97</v>
+        <v>6.67</v>
       </c>
       <c r="CD12" t="n">
-        <v>8.960000000000001</v>
+        <v>8.41</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CI12" t="n">
         <v>1.69</v>
       </c>
       <c r="CJ12" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CK12" t="n">
         <v>1.88</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CO12" t="n">
         <v>1.34</v>
@@ -5688,25 +5688,25 @@
         <v>2.1</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.76</v>
+        <v>3.77</v>
       </c>
       <c r="CR12" t="n">
         <v>1.42</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CX12" t="n">
         <v>1.91</v>
@@ -5718,91 +5718,91 @@
         <v>1.9</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="DC12" t="n">
         <v>2.13</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="DH12" t="n">
-        <v>73.64</v>
+        <v>73.73999999999999</v>
       </c>
       <c r="DI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="DK12" t="n">
-        <v>2.64</v>
+        <v>3.07</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DM12" t="n">
-        <v>30</v>
+        <v>31.2</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.86</v>
+        <v>12.93</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.5</v>
+        <v>12.53</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.58</v>
+        <v>9.4</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>42.64</v>
+        <v>42.66</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DX12" t="n">
-        <v>7.79</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DY12" t="n">
-        <v>5.57</v>
+        <v>5.87</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2.22</v>
+        <v>2.33</v>
       </c>
       <c r="EA12" t="n">
-        <v>16.92</v>
+        <v>16.6</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.57</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="13">
@@ -6618,94 +6618,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
         <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F15" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="G15" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="H15" t="n">
-        <v>60.17</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J15" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="K15" t="n">
-        <v>5.33</v>
+        <v>5.14</v>
       </c>
       <c r="L15" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="M15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N15" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="O15" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="P15" t="n">
-        <v>14</v>
+        <v>13.86</v>
       </c>
       <c r="Q15" t="n">
-        <v>16.5</v>
+        <v>16.14</v>
       </c>
       <c r="R15" t="n">
-        <v>7.67</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="U15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>46.83</v>
+        <v>48.29</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>14.67</v>
+        <v>13.86</v>
       </c>
       <c r="AA15" t="n">
-        <v>10.17</v>
+        <v>9.57</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.5</v>
+        <v>4.29</v>
       </c>
       <c r="AC15" t="n">
-        <v>20.33</v>
+        <v>19.71</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="AF15" t="n">
         <v>0.12</v>
@@ -6789,70 +6789,70 @@
         <v>3.75</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="BH15" t="n">
-        <v>8.93</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.71</v>
+        <v>3.73</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.14</v>
+        <v>5.4</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT15" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BU15" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BV15" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW15" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX15" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BY15" t="n">
-        <v>4.59</v>
+        <v>4.2</v>
       </c>
       <c r="BZ15" t="n">
-        <v>4.78</v>
+        <v>4.37</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.79</v>
+        <v>3.75</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.93</v>
+        <v>3.89</v>
       </c>
       <c r="CC15" t="n">
         <v>5.82</v>
@@ -6861,19 +6861,19 @@
         <v>5.97</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.99</v>
@@ -6882,10 +6882,10 @@
         <v>1.84</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CM15" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CN15" t="n">
         <v>1.52</v>
@@ -6894,22 +6894,22 @@
         <v>1.31</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.46</v>
+        <v>3.49</v>
       </c>
       <c r="CR15" t="n">
         <v>1.42</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CV15" t="n">
         <v>1.86</v>
@@ -6921,64 +6921,64 @@
         <v>1.89</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CZ15" t="n">
         <v>1.92</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="DB15" t="n">
         <v>1.33</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.58</v>
+        <v>3.61</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF15" t="n">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="DH15" t="n">
-        <v>71.56999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.36</v>
+        <v>3.33</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.71</v>
+        <v>3.73</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM15" t="n">
-        <v>30.5</v>
+        <v>30.86</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="DP15" t="n">
-        <v>15.78</v>
+        <v>15.6</v>
       </c>
       <c r="DQ15" t="n">
-        <v>16</v>
+        <v>15.86</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.57</v>
+        <v>7.87</v>
       </c>
       <c r="DS15" t="n">
         <v>0.07000000000000001</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>46.29</v>
+        <v>47</v>
       </c>
       <c r="DW15" t="n">
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>11.72</v>
+        <v>11.53</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.43</v>
+        <v>7.34</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.28</v>
+        <v>4.2</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.57</v>
+        <v>19.33</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="EC15" t="n">
-        <v>3.36</v>
+        <v>3.33</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
         <v>7</v>
@@ -1391,82 +1391,82 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>3.43</v>
+        <v>3.12</v>
       </c>
       <c r="H2" t="n">
-        <v>104.71</v>
+        <v>103.5</v>
       </c>
       <c r="I2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J2" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>6.29</v>
+        <v>6.12</v>
       </c>
       <c r="L2" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="M2" t="n">
-        <v>66.56999999999999</v>
+        <v>66.75</v>
       </c>
       <c r="N2" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="O2" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>15</v>
+        <v>15.62</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.71</v>
+        <v>12.88</v>
       </c>
       <c r="R2" t="n">
-        <v>4.14</v>
+        <v>4.88</v>
       </c>
       <c r="S2" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="T2" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="U2" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V2" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>61.29</v>
+        <v>61</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.43</v>
+        <v>18</v>
       </c>
       <c r="AA2" t="n">
-        <v>13</v>
+        <v>12.62</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.43</v>
+        <v>5.38</v>
       </c>
       <c r="AC2" t="n">
-        <v>21.14</v>
+        <v>22</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,70 +1550,70 @@
         <v>2.57</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="BH2" t="n">
-        <v>7.86</v>
+        <v>7.87</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BO2" t="n">
         <v>0.93</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.71</v>
+        <v>3.73</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.14</v>
+        <v>4.13</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BT2" t="n">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="BU2" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV2" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.65</v>
+        <v>4.84</v>
       </c>
       <c r="CB2" t="n">
-        <v>5.02</v>
+        <v>5.26</v>
       </c>
       <c r="CC2" t="n">
         <v>2.01</v>
@@ -1625,127 +1625,127 @@
         <v>1.35</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CL2" t="n">
         <v>2.4</v>
       </c>
       <c r="CM2" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.09</v>
+        <v>3.03</v>
       </c>
       <c r="CR2" t="n">
         <v>1.37</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="CT2" t="n">
         <v>3.07</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.15</v>
+        <v>3.09</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="DH2" t="n">
-        <v>96.92</v>
+        <v>96.8</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.43</v>
+        <v>5.4</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="DM2" t="n">
-        <v>60.22</v>
+        <v>60.73</v>
       </c>
       <c r="DN2" t="n">
         <v>1.14</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.64</v>
+        <v>2.73</v>
       </c>
       <c r="DP2" t="n">
-        <v>16.22</v>
+        <v>16.46</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.21</v>
+        <v>13.27</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.92</v>
+        <v>6.2</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
@@ -1754,25 +1754,25 @@
         <v>58.93</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DX2" t="n">
-        <v>16.43</v>
+        <v>16.33</v>
       </c>
       <c r="DY2" t="n">
-        <v>11.22</v>
+        <v>11.13</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.21</v>
+        <v>5.2</v>
       </c>
       <c r="EA2" t="n">
-        <v>21</v>
+        <v>21.47</v>
       </c>
       <c r="EB2" t="n">
         <v>1.83</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.57</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="3">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="n">
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2684,133 +2684,133 @@
         <v>2</v>
       </c>
       <c r="AH5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>30.12</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>45.62</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BO5" t="n">
         <v>1</v>
       </c>
-      <c r="AI5" t="n">
-        <v>67</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>28.86</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>16.57</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>13.57</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>12.71</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>43.57</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>7.29</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>20.14</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>8.640000000000001</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>1.07</v>
-      </c>
       <c r="BP5" t="n">
-        <v>4.64</v>
+        <v>4.4</v>
       </c>
       <c r="BQ5" t="n">
         <v>4</v>
       </c>
       <c r="BR5" t="n">
-        <v>100</v>
+        <v>93.33</v>
       </c>
       <c r="BS5" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT5" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BU5" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV5" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BY5" t="n">
         <v>3.11</v>
@@ -2819,25 +2819,25 @@
         <v>3.43</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.72</v>
+        <v>3.67</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.02</v>
+        <v>3.95</v>
       </c>
       <c r="CC5" t="n">
-        <v>6.88</v>
+        <v>6.33</v>
       </c>
       <c r="CD5" t="n">
-        <v>8.359999999999999</v>
+        <v>7.65</v>
       </c>
       <c r="CE5" t="n">
         <v>1.42</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CH5" t="n">
         <v>1.38</v>
@@ -2846,13 +2846,13 @@
         <v>1.74</v>
       </c>
       <c r="CJ5" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CK5" t="n">
         <v>1.88</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CM5" t="n">
         <v>1.84</v>
@@ -2864,22 +2864,22 @@
         <v>1.34</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.65</v>
+        <v>3.67</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CV5" t="n">
         <v>1.83</v>
@@ -2888,67 +2888,67 @@
         <v>2.03</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CZ5" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.72</v>
+        <v>3.78</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="DH5" t="n">
-        <v>76.56999999999999</v>
+        <v>77.27</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.57</v>
+        <v>2.73</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="DM5" t="n">
-        <v>36.93</v>
+        <v>37.06</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.78</v>
+        <v>0.93</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="DP5" t="n">
-        <v>15.43</v>
+        <v>15.6</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.36</v>
+        <v>14.67</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.210000000000001</v>
+        <v>8.66</v>
       </c>
       <c r="DS5" t="n">
         <v>0.14</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>48.78</v>
+        <v>49.53</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX5" t="n">
-        <v>10</v>
+        <v>9.93</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.43</v>
+        <v>7.53</v>
       </c>
       <c r="DZ5" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.64</v>
+        <v>22</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="6">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
         <v>7</v>
@@ -3406,82 +3406,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="H7" t="n">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>3.71</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>4.29</v>
+        <v>3.88</v>
       </c>
       <c r="L7" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="M7" t="n">
-        <v>31.86</v>
+        <v>31.88</v>
       </c>
       <c r="N7" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="O7" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="P7" t="n">
-        <v>14.86</v>
+        <v>15.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>14.86</v>
+        <v>15.25</v>
       </c>
       <c r="R7" t="n">
-        <v>7.71</v>
+        <v>7.12</v>
       </c>
       <c r="S7" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="U7" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V7" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>44.14</v>
+        <v>43.62</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>13</v>
+        <v>11.88</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.859999999999999</v>
+        <v>8</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.14</v>
+        <v>3.88</v>
       </c>
       <c r="AC7" t="n">
-        <v>17.14</v>
+        <v>18</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AE7" t="n">
-        <v>3.71</v>
+        <v>3.5</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,70 +3565,70 @@
         <v>3.43</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.86</v>
+        <v>2.67</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.640000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.86</v>
+        <v>2.67</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.14</v>
+        <v>3.93</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.36</v>
+        <v>4.33</v>
       </c>
       <c r="BR7" t="n">
-        <v>100</v>
+        <v>93.33</v>
       </c>
       <c r="BS7" t="n">
-        <v>92.86</v>
+        <v>86.67</v>
       </c>
       <c r="BT7" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BU7" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV7" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW7" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX7" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BY7" t="n">
-        <v>5.84</v>
+        <v>5.46</v>
       </c>
       <c r="BZ7" t="n">
-        <v>6.09</v>
+        <v>5.71</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.92</v>
+        <v>3.86</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.01</v>
+        <v>3.94</v>
       </c>
       <c r="CC7" t="n">
         <v>5.5</v>
@@ -3640,19 +3640,19 @@
         <v>1.42</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CI7" t="n">
         <v>1.76</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="CK7" t="n">
         <v>1.88</v>
@@ -3670,22 +3670,22 @@
         <v>1.33</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.61</v>
+        <v>3.63</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.89</v>
+        <v>2.93</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CV7" t="n">
         <v>1.81</v>
@@ -3694,100 +3694,100 @@
         <v>2.06</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CZ7" t="n">
         <v>1.89</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.22</v>
+        <v>2.07</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="DH7" t="n">
-        <v>81.84999999999999</v>
+        <v>83.06</v>
       </c>
       <c r="DI7" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.78</v>
+        <v>3.67</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.36</v>
+        <v>3.2</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DM7" t="n">
-        <v>31.43</v>
+        <v>31.47</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="DP7" t="n">
-        <v>15.5</v>
+        <v>15.73</v>
       </c>
       <c r="DQ7" t="n">
-        <v>13.28</v>
+        <v>13.6</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.359999999999999</v>
+        <v>8</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>42.07</v>
+        <v>41.93</v>
       </c>
       <c r="DW7" t="n">
         <v>0.14</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.43</v>
+        <v>10.94</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.86</v>
+        <v>7.47</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.57</v>
+        <v>3.47</v>
       </c>
       <c r="EA7" t="n">
-        <v>16.57</v>
+        <v>17.07</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.57</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
         <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
         <v>0.38</v>
@@ -3890,136 +3890,136 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="AI8" t="n">
-        <v>91</v>
+        <v>92.14</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AL8" t="n">
-        <v>5.5</v>
+        <v>5.71</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AN8" t="n">
-        <v>38.17</v>
+        <v>41.71</v>
       </c>
       <c r="AO8" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>15.14</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>56</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="BL8" t="n">
         <v>1</v>
       </c>
-      <c r="AP8" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>15.33</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AU8" t="n">
+      <c r="BM8" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BO8" t="n">
         <v>1.67</v>
       </c>
-      <c r="AV8" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>54.83</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>20.17</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>9.710000000000001</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>1.79</v>
-      </c>
       <c r="BP8" t="n">
-        <v>4.71</v>
+        <v>4.8</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5</v>
+        <v>4.87</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
       </c>
       <c r="BS8" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BT8" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BU8" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BV8" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BW8" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BX8" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BY8" t="n">
         <v>2.47</v>
@@ -4031,31 +4031,31 @@
         <v>3.79</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.96</v>
+        <v>3.98</v>
       </c>
       <c r="CC8" t="n">
-        <v>5.3</v>
+        <v>4.77</v>
       </c>
       <c r="CD8" t="n">
-        <v>5.19</v>
+        <v>4.67</v>
       </c>
       <c r="CE8" t="n">
         <v>1.38</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CH8" t="n">
         <v>1.39</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CK8" t="n">
         <v>1.83</v>
@@ -4076,7 +4076,7 @@
         <v>2.01</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.52</v>
+        <v>3.49</v>
       </c>
       <c r="CR8" t="n">
         <v>1.4</v>
@@ -4097,7 +4097,7 @@
         <v>1.98</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CY8" t="n">
         <v>2.38</v>
@@ -4109,88 +4109,88 @@
         <v>1.56</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.93</v>
+        <v>2.86</v>
       </c>
       <c r="DH8" t="n">
-        <v>101.14</v>
+        <v>101</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="DM8" t="n">
-        <v>42.79</v>
+        <v>44.13</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.57</v>
+        <v>2.73</v>
       </c>
       <c r="DP8" t="n">
-        <v>12.07</v>
+        <v>11.93</v>
       </c>
       <c r="DQ8" t="n">
-        <v>15.86</v>
+        <v>15.73</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.36</v>
+        <v>6.27</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>59.78</v>
+        <v>60</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX8" t="n">
-        <v>13.07</v>
+        <v>13.34</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.86</v>
+        <v>8.06</v>
       </c>
       <c r="DZ8" t="n">
-        <v>5.21</v>
+        <v>5.27</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.79</v>
+        <v>22.27</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4290,139 +4290,139 @@
         <v>2.57</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AI9" t="n">
-        <v>59.17</v>
+        <v>63.14</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.33</v>
+        <v>3.43</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.33</v>
+        <v>3.29</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AN9" t="n">
-        <v>24.5</v>
+        <v>24.29</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12</v>
+        <v>12.43</v>
       </c>
       <c r="AR9" t="n">
-        <v>15.5</v>
+        <v>16.14</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.67</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>41.83</v>
+        <v>41.71</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.33</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.83</v>
+        <v>5.43</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="BD9" t="n">
-        <v>14.33</v>
+        <v>14.86</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="BG9" t="n">
         <v>3</v>
       </c>
       <c r="BH9" t="n">
-        <v>9</v>
+        <v>8.93</v>
       </c>
       <c r="BI9" t="n">
         <v>3</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.92</v>
+        <v>4.86</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT9" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BU9" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BV9" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW9" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX9" t="n">
-        <v>38.46</v>
+        <v>42.86</v>
       </c>
       <c r="BY9" t="n">
         <v>3.73</v>
@@ -4431,169 +4431,169 @@
         <v>4</v>
       </c>
       <c r="CA9" t="n">
-        <v>4</v>
+        <v>4.26</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.31</v>
+        <v>4.62</v>
       </c>
       <c r="CC9" t="n">
-        <v>6.85</v>
+        <v>8.23</v>
       </c>
       <c r="CD9" t="n">
-        <v>8.25</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CL9" t="n">
         <v>2.35</v>
       </c>
       <c r="CM9" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="CR9" t="n">
         <v>1.4</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="CT9" t="n">
         <v>2.96</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.31</v>
+        <v>3.23</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="DH9" t="n">
-        <v>65.7</v>
+        <v>67.22</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DM9" t="n">
-        <v>25.46</v>
+        <v>25.29</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="DP9" t="n">
-        <v>14</v>
+        <v>14.07</v>
       </c>
       <c r="DQ9" t="n">
-        <v>16.61</v>
+        <v>16.86</v>
       </c>
       <c r="DR9" t="n">
-        <v>10.31</v>
+        <v>10</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>42.84</v>
+        <v>42.71</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.380000000000001</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.38</v>
+        <v>5.64</v>
       </c>
       <c r="DZ9" t="n">
         <v>3</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.77</v>
+        <v>16.86</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="10">
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
         <v>7</v>
@@ -5018,82 +5018,82 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="G11" t="n">
-        <v>3.86</v>
+        <v>3.88</v>
       </c>
       <c r="H11" t="n">
-        <v>120.57</v>
+        <v>116.38</v>
       </c>
       <c r="I11" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="J11" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="K11" t="n">
         <v>7</v>
       </c>
       <c r="L11" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="M11" t="n">
-        <v>67.29000000000001</v>
+        <v>64</v>
       </c>
       <c r="N11" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="O11" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="P11" t="n">
-        <v>10.43</v>
+        <v>10.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>14.43</v>
+        <v>14</v>
       </c>
       <c r="R11" t="n">
-        <v>3.57</v>
+        <v>3.75</v>
       </c>
       <c r="S11" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="T11" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="U11" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V11" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>66</v>
+        <v>64.25</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>17.86</v>
+        <v>17.62</v>
       </c>
       <c r="AA11" t="n">
-        <v>12.14</v>
+        <v>11.25</v>
       </c>
       <c r="AB11" t="n">
-        <v>5.71</v>
+        <v>6.38</v>
       </c>
       <c r="AC11" t="n">
-        <v>25.43</v>
+        <v>25</v>
       </c>
       <c r="AD11" t="n">
         <v>2.02</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AF11" t="n">
         <v>0.29</v>
@@ -5177,70 +5177,70 @@
         <v>1.71</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.43</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BL11" t="n">
         <v>1</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.79</v>
+        <v>3.73</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.64</v>
+        <v>4.8</v>
       </c>
       <c r="BR11" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS11" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT11" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BU11" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV11" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX11" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.57</v>
+        <v>4.48</v>
       </c>
       <c r="CB11" t="n">
-        <v>5.03</v>
+        <v>4.94</v>
       </c>
       <c r="CC11" t="n">
         <v>1.91</v>
@@ -5252,25 +5252,25 @@
         <v>1.34</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="CK11" t="n">
         <v>1.77</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="CM11" t="n">
         <v>1.97</v>
@@ -5279,31 +5279,31 @@
         <v>1.57</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CV11" t="n">
         <v>1.82</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CX11" t="n">
         <v>1.8</v>
@@ -5321,85 +5321,85 @@
         <v>1.26</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.05</v>
+        <v>3.11</v>
       </c>
       <c r="DE11" t="n">
         <v>0.14</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
       <c r="DH11" t="n">
-        <v>114.14</v>
+        <v>112.33</v>
       </c>
       <c r="DI11" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.79</v>
+        <v>5.87</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DM11" t="n">
-        <v>60.64</v>
+        <v>59.33</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.64</v>
+        <v>11.73</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13.78</v>
+        <v>13.6</v>
       </c>
       <c r="DR11" t="n">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>63.5</v>
+        <v>62.73</v>
       </c>
       <c r="DW11" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX11" t="n">
-        <v>15.08</v>
+        <v>15.13</v>
       </c>
       <c r="DY11" t="n">
-        <v>10.14</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.92</v>
+        <v>5.33</v>
       </c>
       <c r="EA11" t="n">
-        <v>25</v>
+        <v>24.8</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="12">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C13" t="n">
         <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
         <v>0.29</v>
@@ -5902,139 +5902,139 @@
         <v>2.86</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="AI13" t="n">
-        <v>106.33</v>
+        <v>102.43</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.17</v>
+        <v>4.86</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>56.5</v>
+        <v>52.71</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AP13" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ13" t="n">
-        <v>14.17</v>
+        <v>13.71</v>
       </c>
       <c r="AR13" t="n">
-        <v>14.33</v>
+        <v>14.14</v>
       </c>
       <c r="AS13" t="n">
-        <v>6</v>
+        <v>6.14</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>62.5</v>
+        <v>60.43</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA13" t="n">
-        <v>14.17</v>
+        <v>12.57</v>
       </c>
       <c r="BB13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.17</v>
+        <v>4.57</v>
       </c>
       <c r="BD13" t="n">
-        <v>22.5</v>
+        <v>22.57</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="BH13" t="n">
-        <v>7.85</v>
+        <v>8</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.15</v>
+        <v>4.07</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3.54</v>
+        <v>3.79</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT13" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BU13" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV13" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY13" t="n">
         <v>1.9</v>
@@ -6043,64 +6043,64 @@
         <v>2.12</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.46</v>
+        <v>4.4</v>
       </c>
       <c r="CC13" t="n">
-        <v>1.55</v>
+        <v>1.84</v>
       </c>
       <c r="CD13" t="n">
-        <v>1.58</v>
+        <v>2</v>
       </c>
       <c r="CE13" t="n">
         <v>1.38</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="CM13" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.19</v>
+        <v>3.25</v>
       </c>
       <c r="CR13" t="n">
         <v>1.39</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="CU13" t="n">
         <v>1.43</v>
@@ -6124,88 +6124,88 @@
         <v>1.59</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.37</v>
+        <v>3.41</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF13" t="n">
         <v>1.92</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="DH13" t="n">
-        <v>102.23</v>
+        <v>100.57</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="DK13" t="n">
-        <v>5</v>
+        <v>4.86</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DM13" t="n">
-        <v>53.92</v>
+        <v>52.21</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.38</v>
+        <v>2.21</v>
       </c>
       <c r="DP13" t="n">
-        <v>15.62</v>
+        <v>15.28</v>
       </c>
       <c r="DQ13" t="n">
-        <v>15.23</v>
+        <v>15.07</v>
       </c>
       <c r="DR13" t="n">
-        <v>5.54</v>
+        <v>5.64</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>55.54</v>
+        <v>55</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX13" t="n">
-        <v>13.38</v>
+        <v>12.64</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.92</v>
+        <v>8.43</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.46</v>
+        <v>4.22</v>
       </c>
       <c r="EA13" t="n">
         <v>23</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="14">
@@ -6215,10 +6215,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
         <v>7</v>
@@ -6227,49 +6227,49 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>84.29000000000001</v>
+        <v>85.12</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="L14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="M14" t="n">
-        <v>34.14</v>
+        <v>35.75</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="O14" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="P14" t="n">
-        <v>16.57</v>
+        <v>16.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="R14" t="n">
-        <v>6.86</v>
+        <v>7.38</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
       </c>
       <c r="T14" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6281,28 +6281,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>45.86</v>
+        <v>44.75</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.14</v>
+        <v>0.38</v>
       </c>
       <c r="Z14" t="n">
-        <v>11.14</v>
+        <v>10.75</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.859999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>21.57</v>
+        <v>20.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6386,70 +6386,70 @@
         <v>3</v>
       </c>
       <c r="BG14" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="BH14" t="n">
         <v>9.07</v>
       </c>
       <c r="BI14" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.07</v>
+        <v>4.2</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.93</v>
+        <v>4.8</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT14" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BU14" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV14" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW14" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX14" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BY14" t="n">
-        <v>4.6</v>
+        <v>4.74</v>
       </c>
       <c r="BZ14" t="n">
-        <v>5.23</v>
+        <v>5.36</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.37</v>
+        <v>4.34</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.97</v>
+        <v>4.92</v>
       </c>
       <c r="CC14" t="n">
         <v>8.5</v>
@@ -6461,19 +6461,19 @@
         <v>1.37</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CK14" t="n">
         <v>1.82</v>
@@ -6527,55 +6527,55 @@
         <v>1.58</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="DG14" t="n">
         <v>1.07</v>
       </c>
       <c r="DH14" t="n">
-        <v>70.86</v>
+        <v>72.2</v>
       </c>
       <c r="DI14" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.22</v>
+        <v>3.27</v>
       </c>
       <c r="DK14" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DM14" t="n">
-        <v>27</v>
+        <v>28.33</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="DO14" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="DP14" t="n">
-        <v>15.07</v>
+        <v>15</v>
       </c>
       <c r="DQ14" t="n">
-        <v>11.93</v>
+        <v>11.8</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.279999999999999</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="DS14" t="n">
         <v>0.07000000000000001</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>39.29</v>
+        <v>39.13</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.22</v>
+        <v>0.34</v>
       </c>
       <c r="DX14" t="n">
-        <v>8.779999999999999</v>
+        <v>8.73</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.21</v>
+        <v>7.2</v>
       </c>
       <c r="DZ14" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="EA14" t="n">
-        <v>18</v>
+        <v>17.8</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.78</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="15">

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -1794,7 +1794,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
         <v>3.86</v>
@@ -1806,7 +1806,7 @@
         <v>0.14</v>
       </c>
       <c r="J3" t="n">
-        <v>2.86</v>
+        <v>2.71</v>
       </c>
       <c r="K3" t="n">
         <v>5.43</v>
@@ -1869,7 +1869,7 @@
         <v>1.59</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.29</v>
+        <v>2.14</v>
       </c>
       <c r="AF3" t="n">
         <v>0.12</v>
@@ -2106,7 +2106,7 @@
         <v>0.06</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="DG3" t="n">
         <v>3.53</v>
@@ -2118,7 +2118,7 @@
         <v>0.13</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="DK3" t="n">
         <v>4.93</v>
@@ -2175,7 +2175,7 @@
         <v>1.37</v>
       </c>
       <c r="EC3" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="4">
@@ -2227,7 +2227,7 @@
         <v>2.29</v>
       </c>
       <c r="P4" t="n">
-        <v>12.43</v>
+        <v>12.57</v>
       </c>
       <c r="Q4" t="n">
         <v>14.57</v>
@@ -2539,7 +2539,7 @@
         <v>1.8</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.67</v>
+        <v>13.73</v>
       </c>
       <c r="DQ4" t="n">
         <v>15.87</v>
@@ -2600,7 +2600,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="G5" t="n">
         <v>2.29</v>
@@ -2612,7 +2612,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.14</v>
+        <v>2.29</v>
       </c>
       <c r="K5" t="n">
         <v>3.86</v>
@@ -2675,7 +2675,7 @@
         <v>1.35</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.14</v>
+        <v>2.29</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2912,7 +2912,7 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="DG5" t="n">
         <v>1.74</v>
@@ -2924,7 +2924,7 @@
         <v>0.06</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="DK5" t="n">
         <v>3.6</v>
@@ -2981,7 +2981,7 @@
         <v>1.07</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="6">
@@ -5824,7 +5824,7 @@
         <v>0.29</v>
       </c>
       <c r="F13" t="n">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="G13" t="n">
         <v>2.14</v>
@@ -5836,7 +5836,7 @@
         <v>0.14</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>2.57</v>
       </c>
       <c r="K13" t="n">
         <v>4.86</v>
@@ -5848,7 +5848,7 @@
         <v>51.71</v>
       </c>
       <c r="N13" t="n">
-        <v>0.86</v>
+        <v>0.71</v>
       </c>
       <c r="O13" t="n">
         <v>2.71</v>
@@ -5899,7 +5899,7 @@
         <v>1.45</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.86</v>
+        <v>2.43</v>
       </c>
       <c r="AF13" t="n">
         <v>0.14</v>
@@ -6136,7 +6136,7 @@
         <v>0.22</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="DG13" t="n">
         <v>2.5</v>
@@ -6148,7 +6148,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.78</v>
+        <v>2.57</v>
       </c>
       <c r="DK13" t="n">
         <v>4.86</v>
@@ -6160,7 +6160,7 @@
         <v>52.21</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="DO13" t="n">
         <v>2.21</v>
@@ -6205,7 +6205,7 @@
         <v>1.48</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.64</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="14">
@@ -6723,7 +6723,7 @@
         <v>0.12</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="AL15" t="n">
         <v>2.5</v>
@@ -6735,7 +6735,7 @@
         <v>31.62</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AP15" t="n">
         <v>1.38</v>
@@ -6786,7 +6786,7 @@
         <v>1.12</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="BG15" t="n">
         <v>2.4</v>
@@ -6954,7 +6954,7 @@
         <v>0.13</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.33</v>
+        <v>3.27</v>
       </c>
       <c r="DK15" t="n">
         <v>3.73</v>
@@ -6966,7 +6966,7 @@
         <v>30.86</v>
       </c>
       <c r="DN15" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="DO15" t="n">
         <v>1.94</v>
@@ -7011,7 +7011,7 @@
         <v>1.13</v>
       </c>
       <c r="EC15" t="n">
-        <v>3.33</v>
+        <v>3.27</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F6" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="G6" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="H6" t="n">
-        <v>75.70999999999999</v>
+        <v>81</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>4.14</v>
+        <v>4.12</v>
       </c>
       <c r="K6" t="n">
-        <v>3.71</v>
+        <v>3.75</v>
       </c>
       <c r="L6" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="M6" t="n">
-        <v>39.57</v>
+        <v>42.38</v>
       </c>
       <c r="N6" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="P6" t="n">
-        <v>16.29</v>
+        <v>16.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>15.43</v>
+        <v>15.25</v>
       </c>
       <c r="R6" t="n">
-        <v>7.86</v>
+        <v>7.62</v>
       </c>
       <c r="S6" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="T6" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3057,28 +3057,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>41</v>
+        <v>43.75</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>13.29</v>
+        <v>14.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.29</v>
+        <v>4.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>15.29</v>
+        <v>15.75</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AE6" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,70 +3162,70 @@
         <v>4.62</v>
       </c>
       <c r="BG6" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.27</v>
+        <v>10.12</v>
       </c>
       <c r="BI6" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BP6" t="n">
-        <v>5.73</v>
+        <v>5.56</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.47</v>
+        <v>4.5</v>
       </c>
       <c r="BR6" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS6" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT6" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BU6" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BV6" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BY6" t="n">
-        <v>4.85</v>
+        <v>4.44</v>
       </c>
       <c r="BZ6" t="n">
-        <v>4.94</v>
+        <v>4.56</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.03</v>
+        <v>4</v>
       </c>
       <c r="CC6" t="n">
         <v>5.64</v>
@@ -3234,13 +3234,13 @@
         <v>5.36</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CH6" t="n">
         <v>1.4</v>
@@ -3249,40 +3249,40 @@
         <v>1.79</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CM6" t="n">
         <v>1.75</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CO6" t="n">
         <v>1.31</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.51</v>
+        <v>3.52</v>
       </c>
       <c r="CR6" t="n">
         <v>1.45</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CV6" t="n">
         <v>1.84</v>
@@ -3291,16 +3291,16 @@
         <v>2.01</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="CZ6" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="DB6" t="n">
         <v>1.34</v>
@@ -3312,46 +3312,46 @@
         <v>3.68</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="DH6" t="n">
-        <v>75.2</v>
+        <v>77.88</v>
       </c>
       <c r="DI6" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ6" t="n">
-        <v>4.53</v>
+        <v>4.5</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.46</v>
+        <v>4.44</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DM6" t="n">
-        <v>36.8</v>
+        <v>38.38</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="DP6" t="n">
-        <v>17.53</v>
+        <v>17.56</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.66</v>
+        <v>13.68</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.67</v>
+        <v>8.5</v>
       </c>
       <c r="DS6" t="n">
         <v>0.06</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>43.4</v>
+        <v>44.62</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DX6" t="n">
-        <v>14.2</v>
+        <v>14.75</v>
       </c>
       <c r="DY6" t="n">
-        <v>9.130000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.07</v>
+        <v>5.12</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.14</v>
+        <v>16.31</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="EC6" t="n">
-        <v>3.93</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
         <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3487,136 +3487,136 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AI7" t="n">
-        <v>83.70999999999999</v>
+        <v>84</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.86</v>
+        <v>3.88</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN7" t="n">
-        <v>31</v>
+        <v>30.5</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AQ7" t="n">
-        <v>16.14</v>
+        <v>15.88</v>
       </c>
       <c r="AR7" t="n">
-        <v>11.71</v>
+        <v>12.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>40</v>
+        <v>39.62</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.859999999999999</v>
+        <v>10.25</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.86</v>
+        <v>6.75</v>
       </c>
       <c r="BC7" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.43</v>
+        <v>3.38</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.4</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.93</v>
+        <v>3.88</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.33</v>
+        <v>4.38</v>
       </c>
       <c r="BR7" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS7" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT7" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BU7" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV7" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW7" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX7" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BY7" t="n">
         <v>5.46</v>
@@ -3625,37 +3625,37 @@
         <v>5.71</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.94</v>
+        <v>3.91</v>
       </c>
       <c r="CC7" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="CD7" t="n">
-        <v>5.94</v>
+        <v>5.76</v>
       </c>
       <c r="CE7" t="n">
         <v>1.42</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CG7" t="n">
         <v>2.73</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CL7" t="n">
         <v>2.53</v>
@@ -3670,7 +3670,7 @@
         <v>1.33</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="CQ7" t="n">
         <v>3.63</v>
@@ -3679,16 +3679,16 @@
         <v>1.44</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CU7" t="n">
         <v>1.41</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CW7" t="n">
         <v>2.06</v>
@@ -3697,10 +3697,10 @@
         <v>1.93</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CZ7" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="DA7" t="n">
         <v>1.53</v>
@@ -3718,76 +3718,76 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="DG7" t="n">
         <v>2</v>
       </c>
       <c r="DH7" t="n">
-        <v>83.06</v>
+        <v>83.25</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.67</v>
+        <v>3.69</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM7" t="n">
-        <v>31.47</v>
+        <v>31.19</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="DP7" t="n">
-        <v>15.73</v>
+        <v>15.63</v>
       </c>
       <c r="DQ7" t="n">
-        <v>13.6</v>
+        <v>13.88</v>
       </c>
       <c r="DR7" t="n">
-        <v>8</v>
+        <v>8.81</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>41.93</v>
+        <v>41.62</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="DX7" t="n">
-        <v>10.94</v>
+        <v>11.07</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.47</v>
+        <v>7.38</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.47</v>
+        <v>3.69</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.07</v>
+        <v>17.25</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.47</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="8">

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1469,139 +1469,139 @@
         <v>2.75</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.14</v>
+        <v>1.75</v>
       </c>
       <c r="AI2" t="n">
-        <v>89.14</v>
+        <v>87.12</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AK2" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AL2" t="n">
-        <v>4.57</v>
+        <v>4.5</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.57</v>
+        <v>0.38</v>
       </c>
       <c r="AN2" t="n">
-        <v>53.86</v>
+        <v>50.38</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.43</v>
+        <v>2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>17.43</v>
+        <v>16.88</v>
       </c>
       <c r="AR2" t="n">
-        <v>13.71</v>
+        <v>13.75</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.71</v>
+        <v>7</v>
       </c>
       <c r="AT2" t="n">
         <v>1</v>
       </c>
       <c r="AU2" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>56.57</v>
+        <v>57.12</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BA2" t="n">
-        <v>14.43</v>
+        <v>13.88</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.43</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BC2" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="BD2" t="n">
-        <v>20.86</v>
+        <v>20.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="BH2" t="n">
-        <v>7.87</v>
+        <v>8.06</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.73</v>
+        <v>3.44</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.13</v>
+        <v>3.81</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BT2" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BU2" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV2" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BY2" t="n">
         <v>1.38</v>
@@ -1610,55 +1610,55 @@
         <v>1.38</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.84</v>
+        <v>4.76</v>
       </c>
       <c r="CB2" t="n">
-        <v>5.26</v>
+        <v>5.14</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CE2" t="n">
         <v>1.35</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="CH2" t="n">
         <v>1.45</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CL2" t="n">
         <v>2.4</v>
       </c>
       <c r="CM2" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CN2" t="n">
         <v>1.6</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="CR2" t="n">
         <v>1.37</v>
@@ -1673,106 +1673,106 @@
         <v>1.48</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="DB2" t="n">
         <v>1.27</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.09</v>
+        <v>3.15</v>
       </c>
       <c r="DE2" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="DH2" t="n">
-        <v>96.8</v>
+        <v>95.31</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.4</v>
+        <v>5.31</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="DM2" t="n">
-        <v>60.73</v>
+        <v>58.56</v>
       </c>
       <c r="DN2" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="DP2" t="n">
-        <v>16.46</v>
+        <v>16.25</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.27</v>
+        <v>13.32</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.2</v>
+        <v>5.94</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>58.93</v>
+        <v>59.06</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DX2" t="n">
-        <v>16.33</v>
+        <v>15.94</v>
       </c>
       <c r="DY2" t="n">
-        <v>11.13</v>
+        <v>10.87</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.2</v>
+        <v>5.06</v>
       </c>
       <c r="EA2" t="n">
-        <v>21.47</v>
+        <v>21.25</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
         <v>8</v>
@@ -1797,46 +1797,46 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>3.86</v>
+        <v>3.25</v>
       </c>
       <c r="H3" t="n">
-        <v>104.29</v>
+        <v>98.25</v>
       </c>
       <c r="I3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J3" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="K3" t="n">
-        <v>5.43</v>
+        <v>5.62</v>
       </c>
       <c r="L3" t="n">
-        <v>0.57</v>
+        <v>0.38</v>
       </c>
       <c r="M3" t="n">
-        <v>47.71</v>
+        <v>46.75</v>
       </c>
       <c r="N3" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="P3" t="n">
-        <v>13.14</v>
+        <v>13.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>16.14</v>
+        <v>15.75</v>
       </c>
       <c r="R3" t="n">
-        <v>7.14</v>
+        <v>7</v>
       </c>
       <c r="S3" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="T3" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>57.29</v>
+        <v>55</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>15</v>
+        <v>14.38</v>
       </c>
       <c r="AA3" t="n">
-        <v>10.86</v>
+        <v>10.25</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.14</v>
+        <v>4.12</v>
       </c>
       <c r="AC3" t="n">
-        <v>23.14</v>
+        <v>22.12</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AF3" t="n">
         <v>0.12</v>
@@ -1953,49 +1953,49 @@
         <v>1.75</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.07</v>
+        <v>9.19</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BP3" t="n">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.6</v>
+        <v>6.12</v>
       </c>
       <c r="BR3" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS3" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BT3" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BU3" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BV3" t="n">
         <v>0</v>
@@ -2004,19 +2004,19 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.38</v>
+        <v>2.64</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.51</v>
+        <v>2.72</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.74</v>
+        <v>3.73</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.96</v>
+        <v>3.92</v>
       </c>
       <c r="CC3" t="n">
         <v>4.26</v>
@@ -2028,16 +2028,16 @@
         <v>1.42</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CH3" t="n">
         <v>1.36</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CJ3" t="n">
         <v>2.02</v>
@@ -2046,7 +2046,7 @@
         <v>1.85</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CM3" t="n">
         <v>1.86</v>
@@ -2061,7 +2061,7 @@
         <v>2.06</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.69</v>
+        <v>3.7</v>
       </c>
       <c r="CR3" t="n">
         <v>1.43</v>
@@ -2079,13 +2079,13 @@
         <v>1.78</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CZ3" t="n">
         <v>1.92</v>
@@ -2097,52 +2097,52 @@
         <v>1.36</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.83</v>
+        <v>3.85</v>
       </c>
       <c r="DE3" t="n">
         <v>0.06</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.53</v>
+        <v>3.25</v>
       </c>
       <c r="DH3" t="n">
-        <v>92.67</v>
+        <v>90.38</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.93</v>
+        <v>5.06</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.47</v>
+        <v>0.38</v>
       </c>
       <c r="DM3" t="n">
-        <v>42.06</v>
+        <v>41.94</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="DP3" t="n">
-        <v>14.6</v>
+        <v>14.57</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.53</v>
+        <v>14.43</v>
       </c>
       <c r="DR3" t="n">
-        <v>7</v>
+        <v>6.94</v>
       </c>
       <c r="DS3" t="n">
         <v>0.06</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>51.07</v>
+        <v>50.31</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DX3" t="n">
-        <v>12.6</v>
+        <v>12.44</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.8</v>
+        <v>3.81</v>
       </c>
       <c r="EA3" t="n">
-        <v>21.26</v>
+        <v>20.87</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="n">
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
         <v>0.29</v>
@@ -2278,136 +2278,136 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="AI4" t="n">
-        <v>79.5</v>
+        <v>80.11</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="AL4" t="n">
-        <v>4</v>
+        <v>4.22</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN4" t="n">
-        <v>31.12</v>
+        <v>32.89</v>
       </c>
       <c r="AO4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>43.56</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>17.78</v>
+      </c>
+      <c r="BE4" t="n">
         <v>1</v>
       </c>
-      <c r="AP4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>14.75</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>8.619999999999999</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AU4" t="n">
+      <c r="BF4" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>9.31</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="BK4" t="n">
         <v>0.38</v>
       </c>
-      <c r="AV4" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>42.75</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>18.25</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.4</v>
-      </c>
       <c r="BL4" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.4</v>
+        <v>4.56</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="BR4" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS4" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BT4" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BU4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BV4" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX4" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BY4" t="n">
         <v>2.67</v>
@@ -2416,22 +2416,22 @@
         <v>2.97</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.71</v>
+        <v>3.66</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.89</v>
+        <v>3.83</v>
       </c>
       <c r="CC4" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="CD4" t="n">
         <v>7</v>
-      </c>
-      <c r="CD4" t="n">
-        <v>7.49</v>
       </c>
       <c r="CE4" t="n">
         <v>1.43</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="CG4" t="n">
         <v>2.72</v>
@@ -2440,37 +2440,37 @@
         <v>1.36</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CL4" t="n">
         <v>2.55</v>
       </c>
       <c r="CM4" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CO4" t="n">
         <v>1.33</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.6</v>
+        <v>3.61</v>
       </c>
       <c r="CR4" t="n">
         <v>1.43</v>
       </c>
       <c r="CS4" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CT4" t="n">
         <v>2.85</v>
@@ -2479,73 +2479,73 @@
         <v>1.39</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CX4" t="n">
         <v>1.86</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CZ4" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="DA4" t="n">
         <v>1.56</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.73</v>
+        <v>3.77</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="DH4" t="n">
-        <v>76.8</v>
+        <v>77.31</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.67</v>
+        <v>3.75</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.33</v>
+        <v>4.43</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="DM4" t="n">
-        <v>34.73</v>
+        <v>35.5</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.73</v>
+        <v>13.69</v>
       </c>
       <c r="DQ4" t="n">
-        <v>15.87</v>
+        <v>15.81</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.470000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="DS4" t="n">
         <v>0.06</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>44.07</v>
+        <v>44.44</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="DX4" t="n">
-        <v>8.529999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="DY4" t="n">
-        <v>4.86</v>
+        <v>5.31</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.67</v>
+        <v>3.63</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.07</v>
+        <v>19.69</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="EC4" t="n">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="5">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
         <v>8</v>
@@ -2600,82 +2600,82 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="G5" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="H5" t="n">
-        <v>86.14</v>
+        <v>85.62</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="K5" t="n">
-        <v>3.86</v>
+        <v>3.62</v>
       </c>
       <c r="L5" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="M5" t="n">
-        <v>45</v>
+        <v>41.88</v>
       </c>
       <c r="N5" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="O5" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="P5" t="n">
-        <v>14.29</v>
+        <v>14.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>15.14</v>
+        <v>15.12</v>
       </c>
       <c r="R5" t="n">
-        <v>5.71</v>
+        <v>5.62</v>
       </c>
       <c r="S5" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="U5" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V5" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>54</v>
+        <v>53.62</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>12.71</v>
+        <v>11.62</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.57</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="AC5" t="n">
-        <v>23.14</v>
+        <v>24.38</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,70 +2759,70 @@
         <v>3.12</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.4</v>
+        <v>8.31</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BO5" t="n">
         <v>1</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.4</v>
+        <v>4.19</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="BR5" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS5" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BT5" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BU5" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV5" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.11</v>
+        <v>3.94</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3.43</v>
+        <v>4.41</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.67</v>
+        <v>3.75</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.95</v>
+        <v>4.06</v>
       </c>
       <c r="CC5" t="n">
         <v>6.33</v>
@@ -2834,19 +2834,19 @@
         <v>1.42</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="CH5" t="n">
         <v>1.38</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CJ5" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CK5" t="n">
         <v>1.88</v>
@@ -2861,31 +2861,31 @@
         <v>1.49</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.67</v>
+        <v>3.63</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="CU5" t="n">
         <v>1.41</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CW5" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="CX5" t="n">
         <v>1.95</v>
@@ -2912,76 +2912,76 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DH5" t="n">
-        <v>77.27</v>
+        <v>77.56</v>
       </c>
       <c r="DI5" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DM5" t="n">
-        <v>37.06</v>
+        <v>36</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="DP5" t="n">
-        <v>15.6</v>
+        <v>15.62</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.67</v>
+        <v>14.68</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.66</v>
+        <v>8.44</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>49.53</v>
+        <v>49.62</v>
       </c>
       <c r="DW5" t="n">
         <v>0.06</v>
       </c>
       <c r="DX5" t="n">
-        <v>9.93</v>
+        <v>9.56</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.53</v>
+        <v>7.18</v>
       </c>
       <c r="DZ5" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="EA5" t="n">
-        <v>22</v>
+        <v>22.69</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="6">
@@ -3797,91 +3797,91 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="F8" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="H8" t="n">
-        <v>108.75</v>
+        <v>105.56</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="K8" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="L8" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="M8" t="n">
-        <v>46.25</v>
+        <v>44.78</v>
       </c>
       <c r="N8" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="O8" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="P8" t="n">
-        <v>11.75</v>
+        <v>11.67</v>
       </c>
       <c r="Q8" t="n">
-        <v>16.25</v>
+        <v>16.22</v>
       </c>
       <c r="R8" t="n">
-        <v>5.88</v>
+        <v>6.11</v>
       </c>
       <c r="S8" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="T8" t="n">
         <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>63.5</v>
+        <v>61.89</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z8" t="n">
-        <v>15.38</v>
+        <v>15.22</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.25</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.12</v>
+        <v>6.11</v>
       </c>
       <c r="AC8" t="n">
-        <v>23</v>
+        <v>23.44</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -3968,70 +3968,70 @@
         <v>2.14</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.53</v>
+        <v>3.56</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.67</v>
+        <v>9.31</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.53</v>
+        <v>3.56</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL8" t="n">
         <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.87</v>
+        <v>4.56</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
       </c>
       <c r="BS8" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BT8" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BV8" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BW8" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BX8" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.79</v>
+        <v>3.8</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="CC8" t="n">
         <v>4.77</v>
@@ -4043,7 +4043,7 @@
         <v>1.38</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CG8" t="n">
         <v>2.84</v>
@@ -4064,7 +4064,7 @@
         <v>2.4</v>
       </c>
       <c r="CM8" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CN8" t="n">
         <v>1.54</v>
@@ -4073,19 +4073,19 @@
         <v>1.3</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="CR8" t="n">
         <v>1.4</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="CU8" t="n">
         <v>1.4</v>
@@ -4100,10 +4100,10 @@
         <v>1.86</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CZ8" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DA8" t="n">
         <v>1.56</v>
@@ -4112,85 +4112,85 @@
         <v>1.32</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="DF8" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.86</v>
+        <v>2.69</v>
       </c>
       <c r="DH8" t="n">
-        <v>101</v>
+        <v>99.69</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.6</v>
+        <v>5.31</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="DM8" t="n">
-        <v>44.13</v>
+        <v>43.44</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.93</v>
+        <v>11.88</v>
       </c>
       <c r="DQ8" t="n">
-        <v>15.73</v>
+        <v>15.75</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.27</v>
+        <v>6.37</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>60</v>
+        <v>59.31</v>
       </c>
       <c r="DW8" t="n">
         <v>0.06</v>
       </c>
       <c r="DX8" t="n">
-        <v>13.34</v>
+        <v>13.37</v>
       </c>
       <c r="DY8" t="n">
         <v>8.06</v>
       </c>
       <c r="DZ8" t="n">
-        <v>5.27</v>
+        <v>5.31</v>
       </c>
       <c r="EA8" t="n">
-        <v>22.27</v>
+        <v>22.56</v>
       </c>
       <c r="EB8" t="n">
         <v>1.53</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="9">
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
         <v>7</v>
@@ -4212,82 +4212,82 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="G9" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>71.29000000000001</v>
+        <v>74.12</v>
       </c>
       <c r="I9" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="J9" t="n">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="K9" t="n">
-        <v>3.29</v>
+        <v>3.12</v>
       </c>
       <c r="L9" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="M9" t="n">
-        <v>26.29</v>
+        <v>26.75</v>
       </c>
       <c r="N9" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="P9" t="n">
-        <v>15.71</v>
+        <v>15.62</v>
       </c>
       <c r="Q9" t="n">
-        <v>17.57</v>
+        <v>16.88</v>
       </c>
       <c r="R9" t="n">
-        <v>10.86</v>
+        <v>10.88</v>
       </c>
       <c r="S9" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="T9" t="n">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="U9" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="V9" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>43.71</v>
+        <v>44.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.43</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.86</v>
+        <v>6.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.57</v>
+        <v>3.12</v>
       </c>
       <c r="AC9" t="n">
-        <v>18.86</v>
+        <v>18.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.91</v>
+        <v>1.02</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="AF9" t="n">
         <v>0.29</v>
@@ -4371,70 +4371,70 @@
         <v>2.71</v>
       </c>
       <c r="BG9" t="n">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.93</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.86</v>
+        <v>5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.07</v>
+        <v>3.87</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT9" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BU9" t="n">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="BV9" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW9" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX9" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.73</v>
+        <v>3.61</v>
       </c>
       <c r="BZ9" t="n">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.26</v>
+        <v>4.16</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.62</v>
+        <v>4.51</v>
       </c>
       <c r="CC9" t="n">
         <v>8.23</v>
@@ -4443,16 +4443,16 @@
         <v>9.609999999999999</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.68</v>
+        <v>2.73</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CI9" t="n">
         <v>1.91</v>
@@ -4461,10 +4461,10 @@
         <v>1.84</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CM9" t="n">
         <v>2.02</v>
@@ -4473,13 +4473,13 @@
         <v>1.62</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.12</v>
+        <v>3.16</v>
       </c>
       <c r="CR9" t="n">
         <v>1.4</v>
@@ -4500,100 +4500,100 @@
         <v>1.93</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CY9" t="n">
         <v>2.2</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DA9" t="n">
         <v>1.66</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.23</v>
+        <v>3.3</v>
       </c>
       <c r="DE9" t="n">
         <v>0.14</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="DH9" t="n">
-        <v>67.22</v>
+        <v>69</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.22</v>
+        <v>0.27</v>
       </c>
       <c r="DM9" t="n">
-        <v>25.29</v>
+        <v>25.6</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.07</v>
+        <v>14.13</v>
       </c>
       <c r="DQ9" t="n">
-        <v>16.86</v>
+        <v>16.53</v>
       </c>
       <c r="DR9" t="n">
-        <v>10</v>
+        <v>10.07</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>42.71</v>
+        <v>43.2</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.640000000000001</v>
+        <v>9.27</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.64</v>
+        <v>6</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3</v>
+        <v>3.26</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.86</v>
+        <v>16.8</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
         <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4693,139 +4693,139 @@
         <v>0.88</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.57</v>
+        <v>3.62</v>
       </c>
       <c r="AI10" t="n">
-        <v>111.86</v>
+        <v>110.75</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AL10" t="n">
-        <v>6.43</v>
+        <v>6.25</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="AN10" t="n">
-        <v>57.86</v>
+        <v>60.12</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14.86</v>
+        <v>14.88</v>
       </c>
       <c r="AR10" t="n">
-        <v>11.86</v>
+        <v>12.38</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.86</v>
+        <v>4.75</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>59.29</v>
+        <v>58</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA10" t="n">
-        <v>14.71</v>
+        <v>14</v>
       </c>
       <c r="BB10" t="n">
-        <v>9.710000000000001</v>
+        <v>9</v>
       </c>
       <c r="BC10" t="n">
         <v>5</v>
       </c>
       <c r="BD10" t="n">
-        <v>25.14</v>
+        <v>26.12</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.13</v>
+        <v>9.94</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BP10" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.07</v>
+        <v>5.12</v>
       </c>
       <c r="BR10" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS10" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT10" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BU10" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV10" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BY10" t="n">
         <v>1.25</v>
@@ -4834,16 +4834,16 @@
         <v>1.25</v>
       </c>
       <c r="CA10" t="n">
-        <v>5.5</v>
+        <v>5.46</v>
       </c>
       <c r="CB10" t="n">
-        <v>6.15</v>
+        <v>6.13</v>
       </c>
       <c r="CC10" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="CD10" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="CE10" t="n">
         <v>1.33</v>
@@ -4861,10 +4861,10 @@
         <v>1.6</v>
       </c>
       <c r="CJ10" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CL10" t="n">
         <v>2.55</v>
@@ -4885,34 +4885,34 @@
         <v>2.92</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CS10" t="n">
         <v>2.63</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CW10" t="n">
         <v>2.3</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="DB10" t="n">
         <v>1.26</v>
@@ -4924,79 +4924,79 @@
         <v>3.02</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.53</v>
+        <v>0.62</v>
       </c>
       <c r="DG10" t="n">
-        <v>3.53</v>
+        <v>3.56</v>
       </c>
       <c r="DH10" t="n">
-        <v>120.73</v>
+        <v>119.62</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="DK10" t="n">
-        <v>7.93</v>
+        <v>7.75</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="DM10" t="n">
-        <v>67.59999999999999</v>
+        <v>68.12</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="DO10" t="n">
-        <v>4.33</v>
+        <v>4.12</v>
       </c>
       <c r="DP10" t="n">
-        <v>12.53</v>
+        <v>12.69</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.47</v>
+        <v>12.69</v>
       </c>
       <c r="DR10" t="n">
-        <v>4.6</v>
+        <v>4.56</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>61.67</v>
+        <v>60.88</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX10" t="n">
-        <v>18.93</v>
+        <v>18.31</v>
       </c>
       <c r="DY10" t="n">
-        <v>12.93</v>
+        <v>12.38</v>
       </c>
       <c r="DZ10" t="n">
-        <v>6</v>
+        <v>5.94</v>
       </c>
       <c r="EA10" t="n">
-        <v>25.6</v>
+        <v>26.06</v>
       </c>
       <c r="EB10" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
         <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -5096,139 +5096,139 @@
         <v>1.62</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="AI11" t="n">
-        <v>107.71</v>
+        <v>107.5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="AK11" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.57</v>
+        <v>5</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.14</v>
+        <v>0.5</v>
       </c>
       <c r="AN11" t="n">
-        <v>54</v>
+        <v>54.88</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12.86</v>
+        <v>12.88</v>
       </c>
       <c r="AR11" t="n">
-        <v>13.14</v>
+        <v>13.25</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.14</v>
+        <v>4.88</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>61</v>
+        <v>61.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA11" t="n">
-        <v>12.29</v>
+        <v>13.62</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.140000000000001</v>
+        <v>9</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.14</v>
+        <v>4.62</v>
       </c>
       <c r="BD11" t="n">
-        <v>24.57</v>
+        <v>23.38</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.529999999999999</v>
+        <v>8.81</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BL11" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.73</v>
+        <v>4.12</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.8</v>
+        <v>4.69</v>
       </c>
       <c r="BR11" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS11" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT11" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV11" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW11" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX11" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BY11" t="n">
         <v>1.55</v>
@@ -5237,43 +5237,43 @@
         <v>1.57</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.48</v>
+        <v>4.5</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.94</v>
+        <v>4.98</v>
       </c>
       <c r="CC11" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="CD11" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="CE11" t="n">
         <v>1.34</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="CH11" t="n">
         <v>1.45</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CK11" t="n">
         <v>1.77</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="CM11" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CN11" t="n">
         <v>1.57</v>
@@ -5282,19 +5282,19 @@
         <v>1.26</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="CR11" t="n">
         <v>1.37</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="CU11" t="n">
         <v>1.48</v>
@@ -5315,91 +5315,91 @@
         <v>2.01</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="DB11" t="n">
         <v>1.26</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.11</v>
+        <v>3.08</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="DH11" t="n">
-        <v>112.33</v>
+        <v>111.94</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>6</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>59.44</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>62.88</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>15.62</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>24.19</v>
+      </c>
+      <c r="EB11" t="n">
         <v>1.8</v>
       </c>
-      <c r="DK11" t="n">
-        <v>5.87</v>
-      </c>
-      <c r="DL11" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="DM11" t="n">
-        <v>59.33</v>
-      </c>
-      <c r="DN11" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="DO11" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="DP11" t="n">
-        <v>11.73</v>
-      </c>
-      <c r="DQ11" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="DR11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="DS11" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="DT11" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="DU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV11" t="n">
-        <v>62.73</v>
-      </c>
-      <c r="DW11" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="DX11" t="n">
-        <v>15.13</v>
-      </c>
-      <c r="DY11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="DZ11" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="EA11" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="EB11" t="n">
-        <v>1.76</v>
-      </c>
       <c r="EC11" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="12">
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
         <v>8</v>
@@ -5421,82 +5421,82 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="G12" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="H12" t="n">
-        <v>77.56999999999999</v>
+        <v>76.62</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="J12" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="K12" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>31.57</v>
+        <v>31.38</v>
       </c>
       <c r="N12" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="O12" t="n">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="P12" t="n">
-        <v>11.43</v>
+        <v>11.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>12</v>
+        <v>12.12</v>
       </c>
       <c r="R12" t="n">
-        <v>9.859999999999999</v>
+        <v>10</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="T12" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="U12" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="V12" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>46.14</v>
+        <v>44.75</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z12" t="n">
-        <v>8</v>
+        <v>7.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>6</v>
+        <v>5.38</v>
       </c>
       <c r="AB12" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AC12" t="n">
-        <v>17.14</v>
+        <v>16.75</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5580,70 +5580,70 @@
         <v>2.75</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.33</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.47</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.07</v>
+        <v>4.44</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.27</v>
+        <v>4.19</v>
       </c>
       <c r="BR12" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS12" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BT12" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BU12" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV12" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW12" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BX12" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BY12" t="n">
-        <v>5.41</v>
+        <v>5.92</v>
       </c>
       <c r="BZ12" t="n">
-        <v>5.5</v>
+        <v>6.13</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.18</v>
+        <v>4.28</v>
       </c>
       <c r="CC12" t="n">
         <v>6.67</v>
@@ -5655,13 +5655,13 @@
         <v>1.43</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CI12" t="n">
         <v>1.69</v>
@@ -5673,7 +5673,7 @@
         <v>1.88</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CM12" t="n">
         <v>1.85</v>
@@ -5685,22 +5685,22 @@
         <v>1.34</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.77</v>
+        <v>3.71</v>
       </c>
       <c r="CR12" t="n">
         <v>1.42</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.97</v>
+        <v>2.93</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CV12" t="n">
         <v>1.77</v>
@@ -5712,97 +5712,97 @@
         <v>1.91</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CZ12" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="DH12" t="n">
-        <v>73.73999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="DI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="DK12" t="n">
-        <v>3.07</v>
+        <v>3.19</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DM12" t="n">
-        <v>31.2</v>
+        <v>31.13</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.93</v>
+        <v>13</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.53</v>
+        <v>12.56</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>42.66</v>
+        <v>42.18</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DX12" t="n">
-        <v>8.199999999999999</v>
+        <v>7.82</v>
       </c>
       <c r="DY12" t="n">
-        <v>5.87</v>
+        <v>5.56</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="EA12" t="n">
-        <v>16.6</v>
+        <v>16.44</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="13">
@@ -5812,94 +5812,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
         <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="F13" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="G13" t="n">
-        <v>2.14</v>
+        <v>2.62</v>
       </c>
       <c r="H13" t="n">
-        <v>98.70999999999999</v>
+        <v>94.25</v>
       </c>
       <c r="I13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J13" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="K13" t="n">
-        <v>4.86</v>
+        <v>5.5</v>
       </c>
       <c r="L13" t="n">
-        <v>0.29</v>
+        <v>0.5</v>
       </c>
       <c r="M13" t="n">
-        <v>51.71</v>
+        <v>54.62</v>
       </c>
       <c r="N13" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="O13" t="n">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="P13" t="n">
-        <v>16.86</v>
+        <v>16.38</v>
       </c>
       <c r="Q13" t="n">
-        <v>16</v>
+        <v>15.25</v>
       </c>
       <c r="R13" t="n">
-        <v>5.14</v>
+        <v>5.12</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="T13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>51.62</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.57</v>
       </c>
-      <c r="U13" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>49.57</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>12.71</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>8.859999999999999</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>23.43</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AE13" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AF13" t="n">
         <v>0.14</v>
@@ -5983,70 +5983,70 @@
         <v>2.43</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="BH13" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.07</v>
+        <v>4.13</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3.79</v>
+        <v>3.93</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT13" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BU13" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV13" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.1</v>
+        <v>4.26</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="CC13" t="n">
         <v>1.84</v>
@@ -6055,73 +6055,73 @@
         <v>2</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="CM13" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="CR13" t="n">
         <v>1.39</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="CT13" t="n">
         <v>2.97</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="CZ13" t="n">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="DB13" t="n">
         <v>1.31</v>
@@ -6133,79 +6133,79 @@
         <v>3.41</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.22</v>
+        <v>0.27</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="DH13" t="n">
-        <v>100.57</v>
+        <v>98.06999999999999</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.57</v>
+        <v>2.47</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.86</v>
+        <v>5.2</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.14</v>
+        <v>0.27</v>
       </c>
       <c r="DM13" t="n">
-        <v>52.21</v>
+        <v>53.73</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.78</v>
+        <v>0.73</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.21</v>
+        <v>2.33</v>
       </c>
       <c r="DP13" t="n">
-        <v>15.28</v>
+        <v>15.13</v>
       </c>
       <c r="DQ13" t="n">
-        <v>15.07</v>
+        <v>14.73</v>
       </c>
       <c r="DR13" t="n">
-        <v>5.64</v>
+        <v>5.6</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.29</v>
+        <v>0.34</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.29</v>
+        <v>0.34</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>55</v>
+        <v>55.73</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.64</v>
+        <v>13.07</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.43</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.22</v>
+        <v>4.6</v>
       </c>
       <c r="EA13" t="n">
-        <v>23</v>
+        <v>22.53</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C14" t="n">
         <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6308,136 +6308,136 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AI14" t="n">
-        <v>57.43</v>
+        <v>54.62</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.57</v>
+        <v>3.75</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AN14" t="n">
-        <v>19.86</v>
+        <v>22.75</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ14" t="n">
-        <v>13.57</v>
+        <v>13.38</v>
       </c>
       <c r="AR14" t="n">
-        <v>9.859999999999999</v>
+        <v>10.25</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.710000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="AT14" t="n">
         <v>3</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>32.71</v>
+        <v>32.88</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="BA14" t="n">
-        <v>6.43</v>
+        <v>6.12</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.57</v>
+        <v>4.25</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="BD14" t="n">
-        <v>14.43</v>
+        <v>15.12</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="BF14" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.07</v>
+        <v>9.19</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.8</v>
+        <v>4.88</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT14" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BU14" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV14" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW14" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX14" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BY14" t="n">
         <v>4.74</v>
@@ -6446,85 +6446,85 @@
         <v>5.36</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.34</v>
+        <v>4.46</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.92</v>
+        <v>5.17</v>
       </c>
       <c r="CC14" t="n">
-        <v>8.5</v>
+        <v>9.31</v>
       </c>
       <c r="CD14" t="n">
-        <v>12.58</v>
+        <v>13.27</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CI14" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>2</v>
+      </c>
+      <c r="CK14" t="n">
         <v>1.8</v>
       </c>
-      <c r="CJ14" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="CK14" t="n">
-        <v>1.82</v>
-      </c>
       <c r="CL14" t="n">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="CM14" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="CO14" t="n">
         <v>1.25</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="CR14" t="n">
         <v>1.38</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="CT14" t="n">
         <v>3.03</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="CZ14" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="DB14" t="n">
         <v>1.29</v>
@@ -6539,76 +6539,76 @@
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="DG14" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="DH14" t="n">
-        <v>72.2</v>
+        <v>69.87</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.27</v>
+        <v>3.38</v>
       </c>
       <c r="DK14" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DM14" t="n">
-        <v>28.33</v>
+        <v>29.25</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="DO14" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="DP14" t="n">
-        <v>15</v>
+        <v>14.82</v>
       </c>
       <c r="DQ14" t="n">
-        <v>11.8</v>
+        <v>11.88</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.470000000000001</v>
+        <v>8.56</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>39.13</v>
+        <v>38.82</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.34</v>
+        <v>0.38</v>
       </c>
       <c r="DX14" t="n">
-        <v>8.73</v>
+        <v>8.44</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.2</v>
+        <v>6.88</v>
       </c>
       <c r="DZ14" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.8</v>
+        <v>17.93</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C15" t="n">
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
         <v>0.14</v>
@@ -6708,139 +6708,139 @@
         <v>2.86</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AI15" t="n">
-        <v>80.12</v>
+        <v>82.89</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.62</v>
+        <v>3.56</v>
       </c>
       <c r="AL15" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>35.22</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>15.11</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>46.44</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>20.22</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="BG15" t="n">
         <v>2.5</v>
       </c>
-      <c r="AM15" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>31.62</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>17.12</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>15.62</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>45.88</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>19</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>2.4</v>
-      </c>
       <c r="BH15" t="n">
-        <v>9.199999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.73</v>
+        <v>3.75</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.4</v>
+        <v>5.06</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BT15" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BU15" t="n">
-        <v>6.67</v>
+        <v>12.5</v>
       </c>
       <c r="BV15" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW15" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX15" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BY15" t="n">
         <v>4.2</v>
@@ -6849,16 +6849,16 @@
         <v>4.37</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.89</v>
+        <v>3.91</v>
       </c>
       <c r="CC15" t="n">
-        <v>5.82</v>
+        <v>5.73</v>
       </c>
       <c r="CD15" t="n">
-        <v>5.97</v>
+        <v>6.04</v>
       </c>
       <c r="CE15" t="n">
         <v>1.4</v>
@@ -6873,19 +6873,19 @@
         <v>1.38</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.99</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CM15" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="CN15" t="n">
         <v>1.52</v>
@@ -6894,124 +6894,124 @@
         <v>1.31</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="CR15" t="n">
         <v>1.42</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CW15" t="n">
         <v>2.03</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CZ15" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="DB15" t="n">
         <v>1.33</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF15" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="DH15" t="n">
-        <v>72.8</v>
+        <v>74.81</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.73</v>
+        <v>3.69</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DM15" t="n">
-        <v>30.86</v>
+        <v>32.94</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="DP15" t="n">
-        <v>15.6</v>
+        <v>15.63</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.86</v>
+        <v>15.56</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.87</v>
+        <v>7.75</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>47</v>
+        <v>47.25</v>
       </c>
       <c r="DW15" t="n">
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>11.53</v>
+        <v>11.63</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.34</v>
+        <v>7.56</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.2</v>
+        <v>4.06</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.33</v>
+        <v>20</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="EC15" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -1487,7 +1487,7 @@
         <v>2.88</v>
       </c>
       <c r="AL2" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="AM2" t="n">
         <v>0.38</v>
@@ -1502,10 +1502,10 @@
         <v>2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>16.88</v>
+        <v>17</v>
       </c>
       <c r="AR2" t="n">
-        <v>13.75</v>
+        <v>14.25</v>
       </c>
       <c r="AS2" t="n">
         <v>7</v>
@@ -1526,25 +1526,25 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>57.12</v>
+        <v>57.38</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.25</v>
       </c>
       <c r="BA2" t="n">
-        <v>13.88</v>
+        <v>14</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.119999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="BC2" t="n">
         <v>4.75</v>
       </c>
       <c r="BD2" t="n">
-        <v>20.5</v>
+        <v>20.62</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="BF2" t="n">
         <v>2.5</v>
@@ -1553,7 +1553,7 @@
         <v>2.44</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.06</v>
+        <v>8.19</v>
       </c>
       <c r="BI2" t="n">
         <v>2.44</v>
@@ -1718,7 +1718,7 @@
         <v>2.94</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.31</v>
+        <v>5.44</v>
       </c>
       <c r="DL2" t="n">
         <v>0.5</v>
@@ -1733,10 +1733,10 @@
         <v>2.5</v>
       </c>
       <c r="DP2" t="n">
-        <v>16.25</v>
+        <v>16.31</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.32</v>
+        <v>13.57</v>
       </c>
       <c r="DR2" t="n">
         <v>5.94</v>
@@ -1751,22 +1751,22 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>59.06</v>
+        <v>59.19</v>
       </c>
       <c r="DW2" t="n">
         <v>0.18</v>
       </c>
       <c r="DX2" t="n">
-        <v>15.94</v>
+        <v>16</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.87</v>
+        <v>10.93</v>
       </c>
       <c r="DZ2" t="n">
         <v>5.06</v>
       </c>
       <c r="EA2" t="n">
-        <v>21.25</v>
+        <v>21.31</v>
       </c>
       <c r="EB2" t="n">
         <v>1.78</v>
@@ -1824,13 +1824,13 @@
         <v>1.25</v>
       </c>
       <c r="P3" t="n">
-        <v>13.25</v>
+        <v>13.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>15.75</v>
+        <v>15.88</v>
       </c>
       <c r="R3" t="n">
-        <v>7</v>
+        <v>7.25</v>
       </c>
       <c r="S3" t="n">
         <v>0.75</v>
@@ -1848,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>55</v>
+        <v>54.75</v>
       </c>
       <c r="Y3" t="n">
         <v>0.25</v>
@@ -1956,7 +1956,7 @@
         <v>1.94</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.19</v>
+        <v>9.31</v>
       </c>
       <c r="BI3" t="n">
         <v>1.94</v>
@@ -2136,13 +2136,13 @@
         <v>1.25</v>
       </c>
       <c r="DP3" t="n">
-        <v>14.57</v>
+        <v>14.82</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.43</v>
+        <v>14.5</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.94</v>
+        <v>7.06</v>
       </c>
       <c r="DS3" t="n">
         <v>0.06</v>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>50.31</v>
+        <v>50.18</v>
       </c>
       <c r="DW3" t="n">
         <v>0.12</v>
@@ -3878,7 +3878,7 @@
         <v>6.11</v>
       </c>
       <c r="AC8" t="n">
-        <v>23.44</v>
+        <v>23.56</v>
       </c>
       <c r="AD8" t="n">
         <v>1.71</v>
@@ -4184,7 +4184,7 @@
         <v>5.31</v>
       </c>
       <c r="EA8" t="n">
-        <v>22.56</v>
+        <v>22.63</v>
       </c>
       <c r="EB8" t="n">
         <v>1.53</v>
@@ -6780,7 +6780,7 @@
         <v>3.89</v>
       </c>
       <c r="BD15" t="n">
-        <v>20.22</v>
+        <v>20.11</v>
       </c>
       <c r="BE15" t="n">
         <v>1.16</v>
@@ -7005,7 +7005,7 @@
         <v>4.06</v>
       </c>
       <c r="EA15" t="n">
-        <v>20</v>
+        <v>19.94</v>
       </c>
       <c r="EB15" t="n">
         <v>1.15</v>

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
         <v>8</v>
@@ -1391,82 +1391,82 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="G2" t="n">
-        <v>3.12</v>
+        <v>2.78</v>
       </c>
       <c r="H2" t="n">
-        <v>103.5</v>
+        <v>100.56</v>
       </c>
       <c r="I2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="K2" t="n">
-        <v>6.12</v>
+        <v>5.67</v>
       </c>
       <c r="L2" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="M2" t="n">
-        <v>66.75</v>
+        <v>62.33</v>
       </c>
       <c r="N2" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="O2" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="P2" t="n">
-        <v>15.62</v>
+        <v>15.78</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.88</v>
+        <v>12.89</v>
       </c>
       <c r="R2" t="n">
-        <v>4.88</v>
+        <v>5</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="U2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>61</v>
+        <v>59.56</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z2" t="n">
-        <v>18</v>
+        <v>17.33</v>
       </c>
       <c r="AA2" t="n">
-        <v>12.62</v>
+        <v>12</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.38</v>
+        <v>5.33</v>
       </c>
       <c r="AC2" t="n">
-        <v>22</v>
+        <v>21.22</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AF2" t="n">
         <v>0.12</v>
@@ -1550,70 +1550,70 @@
         <v>2.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.19</v>
+        <v>8</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="BO2" t="n">
         <v>1</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="BQ2" t="n">
-        <v>3.81</v>
+        <v>3.71</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BU2" t="n">
-        <v>25</v>
+        <v>29.41</v>
       </c>
       <c r="BV2" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.76</v>
+        <v>4.67</v>
       </c>
       <c r="CB2" t="n">
-        <v>5.14</v>
+        <v>5.04</v>
       </c>
       <c r="CC2" t="n">
         <v>1.98</v>
@@ -1622,157 +1622,157 @@
         <v>2.14</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CI2" t="n">
         <v>1.68</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CK2" t="n">
         <v>1.77</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CM2" t="n">
         <v>1.96</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CO2" t="n">
         <v>1.26</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CX2" t="n">
         <v>1.81</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DA2" t="n">
         <v>1.62</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.15</v>
+        <v>3.21</v>
       </c>
       <c r="DE2" t="n">
         <v>0.06</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="DH2" t="n">
-        <v>95.31</v>
+        <v>94.23999999999999</v>
       </c>
       <c r="DI2" t="n">
         <v>0.18</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.94</v>
+        <v>2.83</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.44</v>
+        <v>5.24</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DM2" t="n">
-        <v>58.56</v>
+        <v>56.71</v>
       </c>
       <c r="DN2" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="DP2" t="n">
-        <v>16.31</v>
+        <v>16.35</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.57</v>
+        <v>13.53</v>
       </c>
       <c r="DR2" t="n">
         <v>5.94</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>59.19</v>
+        <v>58.53</v>
       </c>
       <c r="DW2" t="n">
         <v>0.18</v>
       </c>
       <c r="DX2" t="n">
-        <v>16</v>
+        <v>15.76</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.93</v>
+        <v>10.71</v>
       </c>
       <c r="DZ2" t="n">
         <v>5.06</v>
       </c>
       <c r="EA2" t="n">
-        <v>21.31</v>
+        <v>20.94</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="n">
         <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1872,130 +1872,130 @@
         <v>2.25</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="AI3" t="n">
-        <v>82.5</v>
+        <v>83.11</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.5</v>
+        <v>4.67</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AN3" t="n">
-        <v>37.12</v>
+        <v>36.56</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15.88</v>
+        <v>16.44</v>
       </c>
       <c r="AR3" t="n">
-        <v>13.12</v>
+        <v>14.56</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.88</v>
+        <v>6.67</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>45.62</v>
+        <v>48.78</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.5</v>
+        <v>10.11</v>
       </c>
       <c r="BB3" t="n">
-        <v>7</v>
+        <v>6.89</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="BD3" t="n">
-        <v>19.62</v>
+        <v>19</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.31</v>
+        <v>9.35</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BP3" t="n">
-        <v>2.25</v>
+        <v>2.41</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.12</v>
+        <v>6.06</v>
       </c>
       <c r="BR3" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS3" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT3" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BU3" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BV3" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BY3" t="n">
         <v>2.64</v>
@@ -2013,25 +2013,25 @@
         <v>2.72</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.73</v>
+        <v>3.71</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.92</v>
+        <v>3.88</v>
       </c>
       <c r="CC3" t="n">
-        <v>4.26</v>
+        <v>3.98</v>
       </c>
       <c r="CD3" t="n">
-        <v>5.35</v>
+        <v>4.98</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="CH3" t="n">
         <v>1.36</v>
@@ -2040,13 +2040,13 @@
         <v>1.72</v>
       </c>
       <c r="CJ3" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="CM3" t="n">
         <v>1.86</v>
@@ -2058,10 +2058,10 @@
         <v>1.34</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="CR3" t="n">
         <v>1.43</v>
@@ -2085,64 +2085,64 @@
         <v>1.89</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CZ3" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="DA3" t="n">
         <v>1.55</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.85</v>
+        <v>3.91</v>
       </c>
       <c r="DE3" t="n">
         <v>0.06</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.25</v>
+        <v>3.29</v>
       </c>
       <c r="DH3" t="n">
-        <v>90.38</v>
+        <v>90.23</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.06</v>
+        <v>5.12</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DM3" t="n">
-        <v>41.94</v>
+        <v>41.36</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="DP3" t="n">
-        <v>14.82</v>
+        <v>15.17</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.5</v>
+        <v>15.18</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.06</v>
+        <v>6.94</v>
       </c>
       <c r="DS3" t="n">
         <v>0.06</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>50.18</v>
+        <v>51.59</v>
       </c>
       <c r="DW3" t="n">
         <v>0.12</v>
       </c>
       <c r="DX3" t="n">
-        <v>12.44</v>
+        <v>12.12</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.619999999999999</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.81</v>
+        <v>3.64</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.87</v>
+        <v>20.47</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="EC3" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="4">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="n">
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
         <v>0.12</v>
@@ -3084,82 +3084,82 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AI6" t="n">
-        <v>74.75</v>
+        <v>77.33</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK6" t="n">
-        <v>4.88</v>
+        <v>4.56</v>
       </c>
       <c r="AL6" t="n">
-        <v>5.12</v>
+        <v>4.89</v>
       </c>
       <c r="AM6" t="n">
         <v>1</v>
       </c>
       <c r="AN6" t="n">
-        <v>34.38</v>
+        <v>35.22</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="AQ6" t="n">
-        <v>18.62</v>
+        <v>18.44</v>
       </c>
       <c r="AR6" t="n">
-        <v>12.12</v>
+        <v>13.22</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.380000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>45.5</v>
+        <v>47.67</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA6" t="n">
-        <v>15</v>
+        <v>14.22</v>
       </c>
       <c r="BB6" t="n">
-        <v>9.25</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.75</v>
+        <v>5.44</v>
       </c>
       <c r="BD6" t="n">
-        <v>16.88</v>
+        <v>17.67</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.62</v>
+        <v>4.33</v>
       </c>
       <c r="BG6" t="n">
         <v>2.94</v>
@@ -3171,49 +3171,49 @@
         <v>2.94</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BP6" t="n">
-        <v>5.56</v>
+        <v>5.59</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.5</v>
+        <v>4.47</v>
       </c>
       <c r="BR6" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS6" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BU6" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BV6" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BY6" t="n">
         <v>4.44</v>
@@ -3222,22 +3222,22 @@
         <v>4.56</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.98</v>
+        <v>3.95</v>
       </c>
       <c r="CB6" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="CC6" t="n">
-        <v>5.64</v>
+        <v>5.25</v>
       </c>
       <c r="CD6" t="n">
-        <v>5.36</v>
+        <v>4.99</v>
       </c>
       <c r="CE6" t="n">
         <v>1.4</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="CG6" t="n">
         <v>2.78</v>
@@ -3246,37 +3246,37 @@
         <v>1.4</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CK6" t="n">
         <v>1.77</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CM6" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CO6" t="n">
         <v>1.31</v>
       </c>
       <c r="CP6" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="CR6" t="n">
         <v>1.45</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="CT6" t="n">
         <v>2.78</v>
@@ -3291,13 +3291,13 @@
         <v>2.01</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CZ6" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DA6" t="n">
         <v>1.55</v>
@@ -3306,52 +3306,52 @@
         <v>1.34</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.68</v>
+        <v>3.71</v>
       </c>
       <c r="DE6" t="n">
         <v>0.06</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="DH6" t="n">
-        <v>77.88</v>
+        <v>79.06</v>
       </c>
       <c r="DI6" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ6" t="n">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.44</v>
+        <v>4.35</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="DM6" t="n">
-        <v>38.38</v>
+        <v>38.59</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="DP6" t="n">
-        <v>17.56</v>
+        <v>17.53</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.68</v>
+        <v>14.18</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.5</v>
+        <v>8.18</v>
       </c>
       <c r="DS6" t="n">
         <v>0.06</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>44.62</v>
+        <v>45.83</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DX6" t="n">
-        <v>14.75</v>
+        <v>14.35</v>
       </c>
       <c r="DY6" t="n">
-        <v>9.619999999999999</v>
+        <v>9.35</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.12</v>
+        <v>5</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.31</v>
+        <v>16.77</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="EC6" t="n">
-        <v>3.94</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="7">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="F7" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="G7" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="H7" t="n">
-        <v>82.5</v>
+        <v>80.56</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="K7" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="M7" t="n">
-        <v>31.88</v>
+        <v>30.33</v>
       </c>
       <c r="N7" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="O7" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="P7" t="n">
-        <v>15.38</v>
+        <v>16.56</v>
       </c>
       <c r="Q7" t="n">
-        <v>15.25</v>
+        <v>15.89</v>
       </c>
       <c r="R7" t="n">
-        <v>7.12</v>
+        <v>6.78</v>
       </c>
       <c r="S7" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="T7" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="U7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>43.62</v>
+        <v>41.67</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>11.88</v>
+        <v>11.89</v>
       </c>
       <c r="AA7" t="n">
-        <v>8</v>
+        <v>7.89</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="AC7" t="n">
-        <v>18</v>
+        <v>17.67</v>
       </c>
       <c r="AD7" t="n">
         <v>1.25</v>
       </c>
       <c r="AE7" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,70 +3565,70 @@
         <v>3.38</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.380000000000001</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.88</v>
+        <v>3.94</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.38</v>
+        <v>4.41</v>
       </c>
       <c r="BR7" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS7" t="n">
-        <v>87.5</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BU7" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV7" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW7" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX7" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BY7" t="n">
-        <v>5.46</v>
+        <v>5.38</v>
       </c>
       <c r="BZ7" t="n">
-        <v>5.71</v>
+        <v>5.55</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.91</v>
+        <v>3.86</v>
       </c>
       <c r="CC7" t="n">
         <v>5.6</v>
@@ -3637,16 +3637,16 @@
         <v>5.76</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CI7" t="n">
         <v>1.77</v>
@@ -3658,7 +3658,7 @@
         <v>1.89</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="CM7" t="n">
         <v>1.84</v>
@@ -3670,10 +3670,10 @@
         <v>1.33</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.63</v>
+        <v>3.69</v>
       </c>
       <c r="CR7" t="n">
         <v>1.44</v>
@@ -3688,7 +3688,7 @@
         <v>1.41</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CW7" t="n">
         <v>2.06</v>
@@ -3709,85 +3709,85 @@
         <v>1.36</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.8</v>
+        <v>3.86</v>
       </c>
       <c r="DE7" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DG7" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DH7" t="n">
-        <v>83.25</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="DI7" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.69</v>
+        <v>3.77</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.25</v>
+        <v>3.29</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DM7" t="n">
-        <v>31.19</v>
+        <v>30.41</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="DP7" t="n">
-        <v>15.63</v>
+        <v>16.24</v>
       </c>
       <c r="DQ7" t="n">
-        <v>13.88</v>
+        <v>14.29</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.81</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>41.62</v>
+        <v>40.71</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.07</v>
+        <v>11.12</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.38</v>
+        <v>7.35</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.69</v>
+        <v>3.76</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.25</v>
+        <v>17.12</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.44</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="8">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4290,139 +4290,139 @@
         <v>2.38</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AI9" t="n">
-        <v>63.14</v>
+        <v>65.25</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.43</v>
+        <v>3.38</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.29</v>
+        <v>2.88</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN9" t="n">
-        <v>24.29</v>
+        <v>24.12</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12.43</v>
+        <v>11.88</v>
       </c>
       <c r="AR9" t="n">
-        <v>16.14</v>
+        <v>15.88</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.140000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>41.71</v>
+        <v>41.75</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.859999999999999</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.43</v>
+        <v>5</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.43</v>
+        <v>3.12</v>
       </c>
       <c r="BD9" t="n">
-        <v>14.86</v>
+        <v>14.62</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.98</v>
+        <v>0.91</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.869999999999999</v>
+        <v>8.69</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="BP9" t="n">
-        <v>5</v>
+        <v>4.81</v>
       </c>
       <c r="BQ9" t="n">
-        <v>3.87</v>
+        <v>3.88</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT9" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BU9" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BV9" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW9" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX9" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BY9" t="n">
         <v>3.61</v>
@@ -4431,169 +4431,169 @@
         <v>3.83</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.16</v>
+        <v>4.39</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.51</v>
+        <v>4.73</v>
       </c>
       <c r="CC9" t="n">
-        <v>8.23</v>
+        <v>8.57</v>
       </c>
       <c r="CD9" t="n">
-        <v>9.609999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.03</v>
+        <v>3.1</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CJ9" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="CP9" t="n">
         <v>1.84</v>
       </c>
-      <c r="CK9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="CL9" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="CM9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="CN9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="CO9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="CP9" t="n">
-        <v>1.88</v>
-      </c>
       <c r="CQ9" t="n">
-        <v>3.16</v>
+        <v>3.08</v>
       </c>
       <c r="CR9" t="n">
         <v>1.4</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="CT9" t="n">
         <v>2.96</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="CV9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="CW9" t="n">
         <v>1.95</v>
       </c>
-      <c r="CW9" t="n">
-        <v>1.93</v>
-      </c>
       <c r="CX9" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="DH9" t="n">
-        <v>69</v>
+        <v>69.68000000000001</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DJ9" t="n">
         <v>3</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DM9" t="n">
-        <v>25.6</v>
+        <v>25.44</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.13</v>
+        <v>13.75</v>
       </c>
       <c r="DQ9" t="n">
-        <v>16.53</v>
+        <v>16.38</v>
       </c>
       <c r="DR9" t="n">
-        <v>10.07</v>
+        <v>9.94</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>43.2</v>
+        <v>43.12</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.27</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="DY9" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.26</v>
+        <v>3.12</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.8</v>
+        <v>16.56</v>
       </c>
       <c r="EB9" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="10">
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
         <v>8</v>
@@ -5018,82 +5018,82 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="G11" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="H11" t="n">
-        <v>116.38</v>
+        <v>114.56</v>
       </c>
       <c r="I11" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="J11" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="K11" t="n">
-        <v>7</v>
+        <v>6.89</v>
       </c>
       <c r="L11" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="M11" t="n">
-        <v>64</v>
+        <v>61.22</v>
       </c>
       <c r="N11" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="O11" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>10.75</v>
+        <v>11.11</v>
       </c>
       <c r="Q11" t="n">
-        <v>14</v>
+        <v>13.33</v>
       </c>
       <c r="R11" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="S11" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="T11" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V11" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>64.25</v>
+        <v>63.56</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>17.62</v>
+        <v>17</v>
       </c>
       <c r="AA11" t="n">
-        <v>11.25</v>
+        <v>10.78</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.38</v>
+        <v>6.22</v>
       </c>
       <c r="AC11" t="n">
-        <v>25</v>
+        <v>24.22</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AF11" t="n">
         <v>0.25</v>
@@ -5180,67 +5180,67 @@
         <v>2.88</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.81</v>
+        <v>8.65</v>
       </c>
       <c r="BI11" t="n">
         <v>2.88</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.62</v>
+        <v>0.76</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.69</v>
+        <v>4.65</v>
       </c>
       <c r="BR11" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS11" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT11" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU11" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV11" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW11" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX11" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.98</v>
+        <v>5.17</v>
       </c>
       <c r="CC11" t="n">
         <v>1.84</v>
@@ -5249,157 +5249,157 @@
         <v>1.8</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.09</v>
+        <v>3.15</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="CI11" t="n">
         <v>1.78</v>
       </c>
       <c r="CJ11" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="CM11" t="n">
         <v>1.98</v>
       </c>
-      <c r="CK11" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="CL11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="CM11" t="n">
-        <v>1.96</v>
-      </c>
       <c r="CN11" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.03</v>
+        <v>2.97</v>
       </c>
       <c r="CR11" t="n">
         <v>1.37</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="CT11" t="n">
         <v>3.1</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="DE11" t="n">
         <v>0.12</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="DH11" t="n">
-        <v>111.94</v>
+        <v>111.24</v>
       </c>
       <c r="DI11" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="DK11" t="n">
         <v>6</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="DM11" t="n">
-        <v>59.44</v>
+        <v>58.24</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.82</v>
+        <v>11.94</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13.62</v>
+        <v>13.29</v>
       </c>
       <c r="DR11" t="n">
-        <v>4.31</v>
+        <v>4.3</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>62.88</v>
+        <v>62.59</v>
       </c>
       <c r="DW11" t="n">
         <v>0.06</v>
       </c>
       <c r="DX11" t="n">
-        <v>15.62</v>
+        <v>15.41</v>
       </c>
       <c r="DY11" t="n">
-        <v>10.12</v>
+        <v>9.94</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.5</v>
+        <v>5.47</v>
       </c>
       <c r="EA11" t="n">
-        <v>24.19</v>
+        <v>23.82</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="12">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
         <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
         <v>0.38</v>
@@ -5902,139 +5902,139 @@
         <v>2.25</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="AI13" t="n">
-        <v>102.43</v>
+        <v>104.12</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="AL13" t="n">
-        <v>4.86</v>
+        <v>4.62</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>52.71</v>
+        <v>52</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AQ13" t="n">
-        <v>13.71</v>
+        <v>13.62</v>
       </c>
       <c r="AR13" t="n">
-        <v>14.14</v>
+        <v>14.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.14</v>
+        <v>6.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>60.43</v>
+        <v>59.38</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA13" t="n">
-        <v>12.57</v>
+        <v>12.5</v>
       </c>
       <c r="BB13" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="BH13" t="n">
         <v>8</v>
       </c>
-      <c r="BC13" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>22.57</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BI13" t="n">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.13</v>
+        <v>4.06</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3.93</v>
+        <v>3.81</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT13" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BU13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BV13" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BY13" t="n">
         <v>1.81</v>
@@ -6043,25 +6043,25 @@
         <v>2</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.26</v>
+        <v>4.19</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.7</v>
+        <v>4.62</v>
       </c>
       <c r="CC13" t="n">
-        <v>1.84</v>
+        <v>2.16</v>
       </c>
       <c r="CD13" t="n">
-        <v>2</v>
+        <v>2.31</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="CH13" t="n">
         <v>1.43</v>
@@ -6070,10 +6070,10 @@
         <v>1.78</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CL13" t="n">
         <v>2.26</v>
@@ -6082,43 +6082,43 @@
         <v>1.89</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CO13" t="n">
         <v>1.28</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CV13" t="n">
         <v>1.79</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CX13" t="n">
         <v>1.8</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="DA13" t="n">
         <v>1.62</v>
@@ -6127,85 +6127,85 @@
         <v>1.31</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.41</v>
+        <v>3.46</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
       <c r="DH13" t="n">
-        <v>98.06999999999999</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="DI13" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.2</v>
+        <v>5.06</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DM13" t="n">
-        <v>53.73</v>
+        <v>53.31</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="DP13" t="n">
-        <v>15.13</v>
+        <v>15</v>
       </c>
       <c r="DQ13" t="n">
-        <v>14.73</v>
+        <v>14.88</v>
       </c>
       <c r="DR13" t="n">
-        <v>5.6</v>
+        <v>5.81</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>55.73</v>
+        <v>55.5</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX13" t="n">
-        <v>13.07</v>
+        <v>13</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.470000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="EA13" t="n">
-        <v>22.53</v>
+        <v>22.5</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="14">
@@ -6215,10 +6215,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
         <v>8</v>
@@ -6227,49 +6227,49 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="G14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H14" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="M14" t="n">
+        <v>35.56</v>
+      </c>
+      <c r="N14" t="n">
         <v>1</v>
       </c>
-      <c r="H14" t="n">
-        <v>85.12</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3</v>
-      </c>
-      <c r="K14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="M14" t="n">
-        <v>35.75</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1.12</v>
-      </c>
       <c r="O14" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="P14" t="n">
-        <v>16.25</v>
+        <v>16.89</v>
       </c>
       <c r="Q14" t="n">
-        <v>13.5</v>
+        <v>13.89</v>
       </c>
       <c r="R14" t="n">
-        <v>7.38</v>
+        <v>6.89</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="T14" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6281,28 +6281,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>44.75</v>
+        <v>43.67</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>10.75</v>
+        <v>11.33</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.5</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.25</v>
+        <v>2.44</v>
       </c>
       <c r="AC14" t="n">
-        <v>20.75</v>
+        <v>20.78</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6389,67 +6389,67 @@
         <v>2.94</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.19</v>
+        <v>9.24</v>
       </c>
       <c r="BI14" t="n">
         <v>2.94</v>
       </c>
       <c r="BJ14" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="BL14" t="n">
         <v>0.88</v>
       </c>
-      <c r="BK14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>0.8100000000000001</v>
-      </c>
       <c r="BM14" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.25</v>
+        <v>4.35</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.88</v>
+        <v>4.82</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BU14" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV14" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW14" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX14" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BY14" t="n">
-        <v>4.74</v>
+        <v>4.57</v>
       </c>
       <c r="BZ14" t="n">
-        <v>5.36</v>
+        <v>5.19</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.46</v>
+        <v>4.4</v>
       </c>
       <c r="CB14" t="n">
-        <v>5.17</v>
+        <v>5.07</v>
       </c>
       <c r="CC14" t="n">
         <v>9.31</v>
@@ -6461,28 +6461,28 @@
         <v>1.36</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="CH14" t="n">
         <v>1.44</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CK14" t="n">
         <v>1.8</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="CM14" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CN14" t="n">
         <v>1.58</v>
@@ -6491,22 +6491,22 @@
         <v>1.25</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.03</v>
+        <v>2.99</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CV14" t="n">
         <v>1.81</v>
@@ -6530,52 +6530,52 @@
         <v>1.29</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="DG14" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="DH14" t="n">
-        <v>69.87</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="DI14" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.38</v>
+        <v>3.29</v>
       </c>
       <c r="DK14" t="n">
-        <v>2.25</v>
+        <v>2.53</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="DM14" t="n">
-        <v>29.25</v>
+        <v>29.53</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="DO14" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="DP14" t="n">
-        <v>14.82</v>
+        <v>15.24</v>
       </c>
       <c r="DQ14" t="n">
-        <v>11.88</v>
+        <v>12.18</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.56</v>
+        <v>8.24</v>
       </c>
       <c r="DS14" t="n">
         <v>0.06</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>38.82</v>
+        <v>38.59</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DX14" t="n">
-        <v>8.44</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="DY14" t="n">
-        <v>6.88</v>
+        <v>6.71</v>
       </c>
       <c r="DZ14" t="n">
-        <v>1.56</v>
+        <v>2.18</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.93</v>
+        <v>18.12</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="15">

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2678,52 +2678,52 @@
         <v>2.38</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="AG5" t="n">
         <v>2</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AI5" t="n">
-        <v>69.5</v>
+        <v>72</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AN5" t="n">
-        <v>30.12</v>
+        <v>30.89</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>16.75</v>
+        <v>16.89</v>
       </c>
       <c r="AR5" t="n">
-        <v>14.25</v>
+        <v>14.33</v>
       </c>
       <c r="AS5" t="n">
-        <v>11.25</v>
+        <v>10.56</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -2735,82 +2735,82 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>45.62</v>
+        <v>45.22</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.5</v>
+        <v>8.33</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.75</v>
+        <v>5.78</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.75</v>
+        <v>2.56</v>
       </c>
       <c r="BD5" t="n">
-        <v>21</v>
+        <v>20.67</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.82</v>
+        <v>0.93</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.31</v>
+        <v>8.24</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BO5" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.19</v>
+        <v>4.06</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.12</v>
+        <v>4.18</v>
       </c>
       <c r="BR5" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS5" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT5" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BU5" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV5" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BY5" t="n">
         <v>3.94</v>
@@ -2819,40 +2819,40 @@
         <v>4.41</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="CC5" t="n">
-        <v>6.33</v>
+        <v>6.03</v>
       </c>
       <c r="CD5" t="n">
-        <v>7.65</v>
+        <v>7.23</v>
       </c>
       <c r="CE5" t="n">
         <v>1.42</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="CH5" t="n">
         <v>1.38</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CJ5" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="CM5" t="n">
         <v>1.84</v>
@@ -2861,22 +2861,22 @@
         <v>1.49</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.63</v>
+        <v>3.66</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CU5" t="n">
         <v>1.41</v>
@@ -2900,25 +2900,25 @@
         <v>1.52</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
       <c r="DE5" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="DH5" t="n">
-        <v>77.56</v>
+        <v>78.41</v>
       </c>
       <c r="DI5" t="n">
         <v>0.06</v>
@@ -2927,28 +2927,28 @@
         <v>2.82</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="DM5" t="n">
-        <v>36</v>
+        <v>36.06</v>
       </c>
       <c r="DN5" t="n">
         <v>1</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="DP5" t="n">
-        <v>15.62</v>
+        <v>15.77</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.68</v>
+        <v>14.7</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.44</v>
+        <v>8.24</v>
       </c>
       <c r="DS5" t="n">
         <v>0.12</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>49.62</v>
+        <v>49.17</v>
       </c>
       <c r="DW5" t="n">
         <v>0.06</v>
       </c>
       <c r="DX5" t="n">
-        <v>9.56</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.18</v>
+        <v>7.12</v>
       </c>
       <c r="DZ5" t="n">
-        <v>2.38</v>
+        <v>2.77</v>
       </c>
       <c r="EA5" t="n">
-        <v>22.69</v>
+        <v>22.42</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="6">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
         <v>0.44</v>
@@ -3887,64 +3887,64 @@
         <v>1</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>92.14</v>
+        <v>90.62</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AL8" t="n">
-        <v>5.71</v>
+        <v>5.62</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.29</v>
+        <v>0.62</v>
       </c>
       <c r="AN8" t="n">
-        <v>41.71</v>
+        <v>41.25</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AP8" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12.14</v>
+        <v>12.25</v>
       </c>
       <c r="AR8" t="n">
-        <v>15.14</v>
+        <v>15</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.71</v>
+        <v>7.12</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>56</v>
+        <v>54.88</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
@@ -3953,73 +3953,73 @@
         <v>11</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.71</v>
+        <v>6.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.29</v>
+        <v>4.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>21.43</v>
+        <v>21.25</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.56</v>
+        <v>3.59</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.31</v>
+        <v>9.41</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.56</v>
+        <v>3.59</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="BL8" t="n">
         <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.75</v>
+        <v>4.82</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.56</v>
+        <v>4.59</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
       </c>
       <c r="BS8" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BT8" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU8" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BV8" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BW8" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX8" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY8" t="n">
         <v>2.38</v>
@@ -4028,28 +4028,28 @@
         <v>2.39</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="CB8" t="n">
-        <v>4</v>
+        <v>3.99</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.77</v>
+        <v>4.38</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.67</v>
+        <v>4.3</v>
       </c>
       <c r="CE8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="CH8" t="n">
         <v>1.38</v>
-      </c>
-      <c r="CF8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="CG8" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="CH8" t="n">
-        <v>1.39</v>
       </c>
       <c r="CI8" t="n">
         <v>1.8</v>
@@ -4058,25 +4058,25 @@
         <v>1.93</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CM8" t="n">
         <v>1.89</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CO8" t="n">
         <v>1.3</v>
       </c>
       <c r="CP8" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="CR8" t="n">
         <v>1.4</v>
@@ -4097,7 +4097,7 @@
         <v>1.98</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CY8" t="n">
         <v>2.37</v>
@@ -4109,88 +4109,88 @@
         <v>1.56</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.53</v>
+        <v>3.54</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="DH8" t="n">
-        <v>99.69</v>
+        <v>98.53</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.31</v>
+        <v>5.29</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="DM8" t="n">
-        <v>43.44</v>
+        <v>43.12</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.88</v>
+        <v>11.94</v>
       </c>
       <c r="DQ8" t="n">
-        <v>15.75</v>
+        <v>15.65</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.37</v>
+        <v>6.59</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>59.31</v>
+        <v>58.59</v>
       </c>
       <c r="DW8" t="n">
         <v>0.06</v>
       </c>
       <c r="DX8" t="n">
-        <v>13.37</v>
+        <v>13.23</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.06</v>
+        <v>7.88</v>
       </c>
       <c r="DZ8" t="n">
-        <v>5.31</v>
+        <v>5.35</v>
       </c>
       <c r="EA8" t="n">
-        <v>22.63</v>
+        <v>22.47</v>
       </c>
       <c r="EB8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="EC8" t="n">
         <v>1.53</v>
-      </c>
-      <c r="EC8" t="n">
-        <v>1.5</v>
       </c>
     </row>
     <row r="9">
@@ -4347,7 +4347,7 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>41.75</v>
+        <v>41.62</v>
       </c>
       <c r="AZ9" t="n">
         <v>0.5</v>
@@ -4572,7 +4572,7 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>43.12</v>
+        <v>43.06</v>
       </c>
       <c r="DW9" t="n">
         <v>0.31</v>
@@ -5072,25 +5072,25 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>63.56</v>
+        <v>63.67</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>17</v>
+        <v>17.11</v>
       </c>
       <c r="AA11" t="n">
         <v>10.78</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.22</v>
+        <v>6.33</v>
       </c>
       <c r="AC11" t="n">
         <v>24.22</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AE11" t="n">
         <v>1.56</v>
@@ -5378,25 +5378,25 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>62.59</v>
+        <v>62.65</v>
       </c>
       <c r="DW11" t="n">
         <v>0.06</v>
       </c>
       <c r="DX11" t="n">
-        <v>15.41</v>
+        <v>15.47</v>
       </c>
       <c r="DY11" t="n">
         <v>9.94</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.47</v>
+        <v>5.53</v>
       </c>
       <c r="EA11" t="n">
         <v>23.82</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="EC11" t="n">
         <v>1.59</v>
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
         <v>8</v>
@@ -5421,82 +5421,82 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="G12" t="n">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="H12" t="n">
-        <v>76.62</v>
+        <v>79.67</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="J12" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="K12" t="n">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>31.38</v>
+        <v>35.89</v>
       </c>
       <c r="N12" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="P12" t="n">
-        <v>11.75</v>
+        <v>12</v>
       </c>
       <c r="Q12" t="n">
-        <v>12.12</v>
+        <v>12.22</v>
       </c>
       <c r="R12" t="n">
-        <v>10</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="T12" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="V12" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>44.75</v>
+        <v>45.67</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z12" t="n">
-        <v>7.25</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.38</v>
+        <v>6.22</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AC12" t="n">
-        <v>16.75</v>
+        <v>17.22</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.82</v>
+        <v>0.93</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5580,70 +5580,70 @@
         <v>2.75</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.619999999999999</v>
+        <v>8.76</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.44</v>
+        <v>4.53</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.19</v>
+        <v>4.24</v>
       </c>
       <c r="BR12" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS12" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT12" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BU12" t="n">
-        <v>18.75</v>
+        <v>23.53</v>
       </c>
       <c r="BV12" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW12" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX12" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BY12" t="n">
-        <v>5.92</v>
+        <v>5.82</v>
       </c>
       <c r="BZ12" t="n">
-        <v>6.13</v>
+        <v>6.01</v>
       </c>
       <c r="CA12" t="n">
-        <v>4</v>
+        <v>3.97</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.28</v>
+        <v>4.25</v>
       </c>
       <c r="CC12" t="n">
         <v>6.67</v>
@@ -5658,7 +5658,7 @@
         <v>2.99</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CH12" t="n">
         <v>1.36</v>
@@ -5670,7 +5670,7 @@
         <v>2.1</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CL12" t="n">
         <v>2.59</v>
@@ -5679,7 +5679,7 @@
         <v>1.85</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CO12" t="n">
         <v>1.34</v>
@@ -5688,7 +5688,7 @@
         <v>2.08</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="CR12" t="n">
         <v>1.42</v>
@@ -5706,13 +5706,13 @@
         <v>1.77</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CX12" t="n">
         <v>1.91</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CZ12" t="n">
         <v>1.91</v>
@@ -5733,76 +5733,76 @@
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="DH12" t="n">
-        <v>73.5</v>
+        <v>75.3</v>
       </c>
       <c r="DI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="DK12" t="n">
-        <v>3.19</v>
+        <v>3.36</v>
       </c>
       <c r="DL12" t="n">
         <v>0.12</v>
       </c>
       <c r="DM12" t="n">
-        <v>31.13</v>
+        <v>33.53</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="DP12" t="n">
-        <v>13</v>
+        <v>13.06</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.56</v>
+        <v>12.59</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.5</v>
+        <v>9.06</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>42.18</v>
+        <v>42.82</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DX12" t="n">
-        <v>7.82</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="DY12" t="n">
-        <v>5.56</v>
+        <v>6</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="EA12" t="n">
-        <v>16.44</v>
+        <v>16.7</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.88</v>
+        <v>0.93</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="13">
@@ -6618,94 +6618,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
         <v>9</v>
       </c>
       <c r="E15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F15" t="n">
-        <v>2.29</v>
+        <v>2.62</v>
       </c>
       <c r="G15" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="H15" t="n">
-        <v>64.43000000000001</v>
+        <v>69.25</v>
       </c>
       <c r="I15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J15" t="n">
-        <v>2.86</v>
+        <v>3.25</v>
       </c>
       <c r="K15" t="n">
-        <v>5.14</v>
+        <v>4.88</v>
       </c>
       <c r="L15" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="M15" t="n">
-        <v>30</v>
+        <v>30.38</v>
       </c>
       <c r="N15" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="O15" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="P15" t="n">
-        <v>13.86</v>
+        <v>14</v>
       </c>
       <c r="Q15" t="n">
-        <v>16.14</v>
+        <v>16.38</v>
       </c>
       <c r="R15" t="n">
-        <v>8.289999999999999</v>
+        <v>8</v>
       </c>
       <c r="S15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T15" t="n">
         <v>1</v>
       </c>
-      <c r="T15" t="n">
-        <v>1.14</v>
-      </c>
       <c r="U15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>48.29</v>
+        <v>49.5</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>13.86</v>
+        <v>13</v>
       </c>
       <c r="AA15" t="n">
-        <v>9.57</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.29</v>
+        <v>3.88</v>
       </c>
       <c r="AC15" t="n">
-        <v>19.71</v>
+        <v>20.75</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.86</v>
+        <v>3.25</v>
       </c>
       <c r="AF15" t="n">
         <v>0.11</v>
@@ -6789,34 +6789,34 @@
         <v>3.56</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="BH15" t="n">
-        <v>8.880000000000001</v>
+        <v>8.76</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BQ15" t="n">
         <v>5.06</v>
@@ -6825,34 +6825,34 @@
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT15" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BU15" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BV15" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW15" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX15" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BY15" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="BZ15" t="n">
-        <v>4.37</v>
+        <v>4.1</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.76</v>
+        <v>3.71</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.91</v>
+        <v>3.86</v>
       </c>
       <c r="CC15" t="n">
         <v>5.73</v>
@@ -6864,25 +6864,25 @@
         <v>1.4</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="CH15" t="n">
         <v>1.38</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CM15" t="n">
         <v>1.88</v>
@@ -6894,73 +6894,73 @@
         <v>1.31</v>
       </c>
       <c r="CP15" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.48</v>
+        <v>3.52</v>
       </c>
       <c r="CR15" t="n">
         <v>1.42</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.97</v>
+        <v>3.01</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CV15" t="n">
         <v>1.85</v>
       </c>
       <c r="CW15" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CX15" t="n">
         <v>1.88</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CZ15" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.59</v>
+        <v>3.64</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF15" t="n">
-        <v>2.31</v>
+        <v>2.47</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="DH15" t="n">
-        <v>74.81</v>
+        <v>76.47</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.69</v>
+        <v>3.65</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="DM15" t="n">
         <v>32.94</v>
@@ -6969,16 +6969,16 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="DO15" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="DP15" t="n">
-        <v>15.63</v>
+        <v>15.59</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.56</v>
+        <v>15.71</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.75</v>
+        <v>7.65</v>
       </c>
       <c r="DS15" t="n">
         <v>0.06</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>47.25</v>
+        <v>47.88</v>
       </c>
       <c r="DW15" t="n">
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>11.63</v>
+        <v>11.35</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.56</v>
+        <v>7.47</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.06</v>
+        <v>3.89</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.94</v>
+        <v>20.41</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="EC15" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1469,139 +1469,139 @@
         <v>2.56</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AI2" t="n">
-        <v>87.12</v>
+        <v>87</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AL2" t="n">
-        <v>4.75</v>
+        <v>5.11</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="AN2" t="n">
-        <v>50.38</v>
+        <v>48.89</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AP2" t="n">
-        <v>2</v>
+        <v>2.56</v>
       </c>
       <c r="AQ2" t="n">
-        <v>17</v>
+        <v>17.11</v>
       </c>
       <c r="AR2" t="n">
-        <v>14.25</v>
+        <v>13.56</v>
       </c>
       <c r="AS2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT2" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>57.38</v>
+        <v>56.33</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA2" t="n">
-        <v>14</v>
+        <v>13.44</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.25</v>
+        <v>9</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.75</v>
+        <v>4.44</v>
       </c>
       <c r="BD2" t="n">
-        <v>20.62</v>
+        <v>20</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="BH2" t="n">
-        <v>8</v>
+        <v>8.56</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="BO2" t="n">
         <v>1</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.41</v>
+        <v>3.94</v>
       </c>
       <c r="BQ2" t="n">
-        <v>3.71</v>
+        <v>3.78</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BT2" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BU2" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV2" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BY2" t="n">
         <v>1.44</v>
@@ -1610,22 +1610,22 @@
         <v>1.44</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.67</v>
+        <v>4.61</v>
       </c>
       <c r="CB2" t="n">
-        <v>5.04</v>
+        <v>5.02</v>
       </c>
       <c r="CC2" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="CE2" t="n">
         <v>1.36</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CG2" t="n">
         <v>2.94</v>
@@ -1637,13 +1637,13 @@
         <v>1.68</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CK2" t="n">
         <v>1.77</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CM2" t="n">
         <v>1.96</v>
@@ -1652,13 +1652,13 @@
         <v>1.59</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CR2" t="n">
         <v>1.38</v>
@@ -1667,7 +1667,7 @@
         <v>2.74</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CU2" t="n">
         <v>1.47</v>
@@ -1676,7 +1676,7 @@
         <v>1.75</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CX2" t="n">
         <v>1.81</v>
@@ -1697,82 +1697,82 @@
         <v>1.88</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="DE2" t="n">
         <v>0.06</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="DH2" t="n">
-        <v>94.23999999999999</v>
+        <v>93.78</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.24</v>
+        <v>5.39</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.53</v>
+        <v>0.67</v>
       </c>
       <c r="DM2" t="n">
-        <v>56.71</v>
+        <v>55.61</v>
       </c>
       <c r="DN2" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.47</v>
+        <v>2.72</v>
       </c>
       <c r="DP2" t="n">
-        <v>16.35</v>
+        <v>16.44</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.53</v>
+        <v>13.23</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.94</v>
+        <v>6.5</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>58.53</v>
+        <v>57.94</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DX2" t="n">
-        <v>15.76</v>
+        <v>15.38</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.71</v>
+        <v>10.5</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.06</v>
+        <v>4.89</v>
       </c>
       <c r="EA2" t="n">
-        <v>20.94</v>
+        <v>20.61</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
@@ -1794,49 +1794,49 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="G3" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="H3" t="n">
-        <v>98.25</v>
+        <v>97.44</v>
       </c>
       <c r="I3" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="J3" t="n">
-        <v>2.75</v>
+        <v>3.11</v>
       </c>
       <c r="K3" t="n">
-        <v>5.62</v>
+        <v>5.78</v>
       </c>
       <c r="L3" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>46.75</v>
+        <v>46.22</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="O3" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="P3" t="n">
-        <v>13.75</v>
+        <v>14.11</v>
       </c>
       <c r="Q3" t="n">
-        <v>15.88</v>
+        <v>15.78</v>
       </c>
       <c r="R3" t="n">
-        <v>7.25</v>
+        <v>7</v>
       </c>
       <c r="S3" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="T3" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>54.75</v>
+        <v>53.67</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z3" t="n">
-        <v>14.38</v>
+        <v>14.89</v>
       </c>
       <c r="AA3" t="n">
-        <v>10.25</v>
+        <v>10.56</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.12</v>
+        <v>4.33</v>
       </c>
       <c r="AC3" t="n">
-        <v>22.12</v>
+        <v>20.89</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.25</v>
+        <v>2.67</v>
       </c>
       <c r="AF3" t="n">
         <v>0.11</v>
@@ -1953,49 +1953,49 @@
         <v>2</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.35</v>
+        <v>9.56</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.41</v>
+        <v>0.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BP3" t="n">
-        <v>2.41</v>
+        <v>2.78</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.06</v>
+        <v>5.94</v>
       </c>
       <c r="BR3" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS3" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT3" t="n">
-        <v>29.41</v>
+        <v>33.33</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.88</v>
+        <v>11.11</v>
       </c>
       <c r="BV3" t="n">
         <v>0</v>
@@ -2004,19 +2004,19 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BY3" t="n">
         <v>2.64</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.71</v>
+        <v>3.66</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.88</v>
+        <v>3.83</v>
       </c>
       <c r="CC3" t="n">
         <v>3.98</v>
@@ -2028,25 +2028,25 @@
         <v>1.43</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CJ3" t="n">
         <v>2.01</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CM3" t="n">
         <v>1.86</v>
@@ -2058,22 +2058,22 @@
         <v>1.34</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.74</v>
+        <v>3.76</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CV3" t="n">
         <v>1.78</v>
@@ -2085,10 +2085,10 @@
         <v>1.89</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CZ3" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DA3" t="n">
         <v>1.55</v>
@@ -2097,52 +2097,52 @@
         <v>1.37</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.91</v>
+        <v>3.94</v>
       </c>
       <c r="DE3" t="n">
         <v>0.06</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.29</v>
+        <v>3.22</v>
       </c>
       <c r="DH3" t="n">
-        <v>90.23</v>
+        <v>90.28</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.12</v>
+        <v>5.22</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="DM3" t="n">
-        <v>41.36</v>
+        <v>41.39</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.65</v>
+        <v>0.78</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="DP3" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="DQ3" t="n">
         <v>15.17</v>
       </c>
-      <c r="DQ3" t="n">
-        <v>15.18</v>
-      </c>
       <c r="DR3" t="n">
-        <v>6.94</v>
+        <v>6.84</v>
       </c>
       <c r="DS3" t="n">
         <v>0.06</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>51.59</v>
+        <v>51.22</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX3" t="n">
-        <v>12.12</v>
+        <v>12.5</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.470000000000001</v>
+        <v>8.73</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.64</v>
+        <v>3.78</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.47</v>
+        <v>19.94</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="4">
@@ -2185,61 +2185,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
         <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F4" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="G4" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="H4" t="n">
-        <v>73.70999999999999</v>
+        <v>78.12</v>
       </c>
       <c r="I4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J4" t="n">
-        <v>4.14</v>
+        <v>3.88</v>
       </c>
       <c r="K4" t="n">
-        <v>4.71</v>
+        <v>5.38</v>
       </c>
       <c r="L4" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="M4" t="n">
-        <v>38.86</v>
+        <v>43.12</v>
       </c>
       <c r="N4" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="O4" t="n">
-        <v>2.29</v>
+        <v>2.75</v>
       </c>
       <c r="P4" t="n">
-        <v>12.57</v>
+        <v>12</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.57</v>
+        <v>15</v>
       </c>
       <c r="R4" t="n">
-        <v>8.289999999999999</v>
+        <v>7.75</v>
       </c>
       <c r="S4" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="T4" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2251,28 +2251,28 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>45.57</v>
+        <v>46.38</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.43</v>
+        <v>10.12</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.14</v>
+        <v>6.12</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.29</v>
+        <v>4</v>
       </c>
       <c r="AC4" t="n">
-        <v>22.14</v>
+        <v>22.12</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AE4" t="n">
-        <v>3.86</v>
+        <v>3.62</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,70 +2356,70 @@
         <v>3.22</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.31</v>
+        <v>9.82</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.56</v>
+        <v>5.06</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.75</v>
+        <v>4.76</v>
       </c>
       <c r="BR4" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BU4" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV4" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX4" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.67</v>
+        <v>3.12</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.97</v>
+        <v>3.61</v>
       </c>
       <c r="CA4" t="n">
         <v>3.66</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.83</v>
+        <v>3.88</v>
       </c>
       <c r="CC4" t="n">
         <v>6.52</v>
@@ -2431,16 +2431,16 @@
         <v>1.43</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.99</v>
@@ -2449,7 +2449,7 @@
         <v>1.83</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="CM4" t="n">
         <v>1.93</v>
@@ -2458,22 +2458,22 @@
         <v>1.54</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.61</v>
+        <v>3.57</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="CU4" t="n">
         <v>1.39</v>
@@ -2488,7 +2488,7 @@
         <v>1.86</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CZ4" t="n">
         <v>1.96</v>
@@ -2497,55 +2497,55 @@
         <v>1.56</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.77</v>
+        <v>3.73</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="DH4" t="n">
-        <v>77.31</v>
+        <v>79.17</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.43</v>
+        <v>4.77</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DM4" t="n">
-        <v>35.5</v>
+        <v>37.7</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DO4" t="n">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.69</v>
+        <v>13.36</v>
       </c>
       <c r="DQ4" t="n">
-        <v>15.81</v>
+        <v>15.94</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.44</v>
+        <v>8.18</v>
       </c>
       <c r="DS4" t="n">
         <v>0.06</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>44.44</v>
+        <v>44.89</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX4" t="n">
-        <v>8.94</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="DY4" t="n">
-        <v>5.31</v>
+        <v>5.76</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.63</v>
+        <v>3.53</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.69</v>
+        <v>19.82</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="EC4" t="n">
-        <v>3.5</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="5">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
@@ -2600,82 +2600,82 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="G5" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="H5" t="n">
-        <v>85.62</v>
+        <v>85.33</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="K5" t="n">
-        <v>3.62</v>
+        <v>3.33</v>
       </c>
       <c r="L5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="M5" t="n">
-        <v>41.88</v>
+        <v>41.33</v>
       </c>
       <c r="N5" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="O5" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="P5" t="n">
-        <v>14.5</v>
+        <v>14.67</v>
       </c>
       <c r="Q5" t="n">
-        <v>15.12</v>
+        <v>15.22</v>
       </c>
       <c r="R5" t="n">
-        <v>5.62</v>
+        <v>5.78</v>
       </c>
       <c r="S5" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="T5" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="U5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>53.62</v>
+        <v>52.22</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.62</v>
+        <v>11.56</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.619999999999999</v>
+        <v>8.44</v>
       </c>
       <c r="AB5" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="AC5" t="n">
-        <v>24.38</v>
+        <v>23.44</v>
       </c>
       <c r="AD5" t="n">
         <v>1.25</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AF5" t="n">
         <v>0.22</v>
@@ -2759,70 +2759,70 @@
         <v>3.11</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.29</v>
+        <v>2.17</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.24</v>
+        <v>7.94</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.29</v>
+        <v>2.17</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BP5" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="BQ5" t="n">
         <v>4.06</v>
       </c>
-      <c r="BQ5" t="n">
-        <v>4.18</v>
-      </c>
       <c r="BR5" t="n">
-        <v>94.12</v>
+        <v>88.89</v>
       </c>
       <c r="BS5" t="n">
-        <v>70.59</v>
+        <v>66.67</v>
       </c>
       <c r="BT5" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BU5" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV5" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="BZ5" t="n">
-        <v>4.41</v>
+        <v>4.39</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.7</v>
+        <v>3.69</v>
       </c>
       <c r="CB5" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="CC5" t="n">
         <v>6.03</v>
@@ -2849,19 +2849,19 @@
         <v>2</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CM5" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CN5" t="n">
         <v>1.49</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CP5" t="n">
         <v>2.07</v>
@@ -2873,115 +2873,115 @@
         <v>1.43</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CW5" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CY5" t="n">
         <v>2.46</v>
       </c>
       <c r="CZ5" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="DA5" t="n">
         <v>1.52</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.82</v>
+        <v>3.87</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="DH5" t="n">
-        <v>78.41</v>
+        <v>78.67</v>
       </c>
       <c r="DI5" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.52</v>
+        <v>3.38</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DM5" t="n">
-        <v>36.06</v>
+        <v>36.11</v>
       </c>
       <c r="DN5" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="DP5" t="n">
-        <v>15.77</v>
+        <v>15.78</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.7</v>
+        <v>14.78</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.24</v>
+        <v>8.17</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>49.17</v>
+        <v>48.72</v>
       </c>
       <c r="DW5" t="n">
         <v>0.06</v>
       </c>
       <c r="DX5" t="n">
-        <v>9.880000000000001</v>
+        <v>9.94</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.12</v>
+        <v>7.11</v>
       </c>
       <c r="DZ5" t="n">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="EA5" t="n">
-        <v>22.42</v>
+        <v>22.06</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="6">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F7" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="H7" t="n">
-        <v>80.56</v>
+        <v>84</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>3.67</v>
+        <v>3.8</v>
       </c>
       <c r="K7" t="n">
-        <v>3.89</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="M7" t="n">
-        <v>30.33</v>
+        <v>33.5</v>
       </c>
       <c r="N7" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="O7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P7" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.33</v>
       </c>
-      <c r="P7" t="n">
-        <v>16.56</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>15.89</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6.78</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>41.67</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>11.89</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>7.89</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>17.67</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AE7" t="n">
-        <v>3.67</v>
+        <v>3.8</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,70 +3565,70 @@
         <v>3.38</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.470000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.41</v>
+        <v>4.22</v>
       </c>
       <c r="BR7" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS7" t="n">
-        <v>82.34999999999999</v>
+        <v>77.78</v>
       </c>
       <c r="BT7" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BU7" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV7" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW7" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX7" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BY7" t="n">
-        <v>5.38</v>
+        <v>5.02</v>
       </c>
       <c r="BZ7" t="n">
-        <v>5.55</v>
+        <v>5.18</v>
       </c>
       <c r="CA7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="CB7" t="n">
         <v>3.82</v>
-      </c>
-      <c r="CB7" t="n">
-        <v>3.86</v>
       </c>
       <c r="CC7" t="n">
         <v>5.6</v>
@@ -3640,25 +3640,25 @@
         <v>1.43</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="CG7" t="n">
         <v>2.7</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CM7" t="n">
         <v>1.84</v>
@@ -3667,31 +3667,31 @@
         <v>1.5</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CP7" t="n">
         <v>2.07</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.69</v>
+        <v>3.74</v>
       </c>
       <c r="CR7" t="n">
         <v>1.44</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CX7" t="n">
         <v>1.93</v>
@@ -3706,88 +3706,88 @@
         <v>1.53</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.86</v>
+        <v>3.91</v>
       </c>
       <c r="DE7" t="n">
         <v>0.06</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="DH7" t="n">
-        <v>82.18000000000001</v>
+        <v>84</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.77</v>
+        <v>3.84</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.29</v>
+        <v>3.39</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="DM7" t="n">
-        <v>30.41</v>
+        <v>32.17</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="DP7" t="n">
-        <v>16.24</v>
+        <v>16.34</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.29</v>
+        <v>14.22</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.529999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>40.71</v>
+        <v>41.39</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.12</v>
+        <v>11.39</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.35</v>
+        <v>7.39</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.76</v>
+        <v>4</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.12</v>
+        <v>17.33</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.53</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
         <v>0.44</v>
@@ -3887,139 +3887,139 @@
         <v>1</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AI8" t="n">
-        <v>90.62</v>
+        <v>90.11</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="AL8" t="n">
-        <v>5.62</v>
+        <v>5.67</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="AN8" t="n">
-        <v>41.25</v>
+        <v>40.89</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.12</v>
+        <v>3.22</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12.25</v>
+        <v>12.56</v>
       </c>
       <c r="AR8" t="n">
-        <v>15</v>
+        <v>15.22</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.12</v>
+        <v>7.11</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>54.88</v>
+        <v>54.89</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>11</v>
+        <v>10.67</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.5</v>
+        <v>6.44</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.5</v>
+        <v>4.22</v>
       </c>
       <c r="BD8" t="n">
-        <v>21.25</v>
+        <v>21.11</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.59</v>
+        <v>3.61</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.41</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.59</v>
+        <v>3.61</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BL8" t="n">
         <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.82</v>
+        <v>5.06</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.59</v>
+        <v>4.56</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
       </c>
       <c r="BS8" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BT8" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BU8" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BV8" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BW8" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX8" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY8" t="n">
         <v>2.38</v>
@@ -4028,25 +4028,25 @@
         <v>2.39</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.78</v>
+        <v>3.73</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.99</v>
+        <v>3.93</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.38</v>
+        <v>4.2</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.3</v>
+        <v>4.16</v>
       </c>
       <c r="CE8" t="n">
         <v>1.39</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="CH8" t="n">
         <v>1.38</v>
@@ -4061,7 +4061,7 @@
         <v>1.84</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="CM8" t="n">
         <v>1.89</v>
@@ -4070,34 +4070,34 @@
         <v>1.53</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CW8" t="n">
         <v>1.98</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CY8" t="n">
         <v>2.37</v>
@@ -4112,85 +4112,85 @@
         <v>1.33</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.54</v>
+        <v>3.59</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DF8" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="DH8" t="n">
-        <v>98.53</v>
+        <v>97.84</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.29</v>
+        <v>5.34</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.65</v>
+        <v>0.73</v>
       </c>
       <c r="DM8" t="n">
-        <v>43.12</v>
+        <v>42.84</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.94</v>
+        <v>12.12</v>
       </c>
       <c r="DQ8" t="n">
-        <v>15.65</v>
+        <v>15.72</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.59</v>
+        <v>6.61</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>58.59</v>
+        <v>58.39</v>
       </c>
       <c r="DW8" t="n">
         <v>0.06</v>
       </c>
       <c r="DX8" t="n">
-        <v>13.23</v>
+        <v>12.94</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.88</v>
+        <v>7.78</v>
       </c>
       <c r="DZ8" t="n">
-        <v>5.35</v>
+        <v>5.16</v>
       </c>
       <c r="EA8" t="n">
-        <v>22.47</v>
+        <v>22.33</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="9">
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
@@ -4212,82 +4212,82 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="G9" t="n">
         <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>74.12</v>
+        <v>77.89</v>
       </c>
       <c r="I9" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="J9" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="K9" t="n">
-        <v>3.12</v>
+        <v>3.22</v>
       </c>
       <c r="L9" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="M9" t="n">
-        <v>26.75</v>
+        <v>27.67</v>
       </c>
       <c r="N9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="O9" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="P9" t="n">
-        <v>15.62</v>
+        <v>15.67</v>
       </c>
       <c r="Q9" t="n">
-        <v>16.88</v>
+        <v>16.33</v>
       </c>
       <c r="R9" t="n">
-        <v>10.88</v>
+        <v>10.44</v>
       </c>
       <c r="S9" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="T9" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="U9" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="V9" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>44.5</v>
+        <v>45.11</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.619999999999999</v>
+        <v>10.11</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.5</v>
+        <v>6.78</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.12</v>
+        <v>3.33</v>
       </c>
       <c r="AC9" t="n">
-        <v>18.5</v>
+        <v>17.78</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AF9" t="n">
         <v>0.25</v>
@@ -4371,70 +4371,70 @@
         <v>2.75</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.06</v>
+        <v>2.94</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.69</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.06</v>
+        <v>2.94</v>
       </c>
       <c r="BJ9" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.81</v>
+        <v>4.71</v>
       </c>
       <c r="BQ9" t="n">
-        <v>3.88</v>
+        <v>3.94</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>81.25</v>
+        <v>76.47</v>
       </c>
       <c r="BT9" t="n">
-        <v>81.25</v>
+        <v>76.47</v>
       </c>
       <c r="BU9" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV9" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW9" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX9" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BY9" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="BZ9" t="n">
         <v>3.61</v>
       </c>
-      <c r="BZ9" t="n">
-        <v>3.83</v>
-      </c>
       <c r="CA9" t="n">
-        <v>4.39</v>
+        <v>4.34</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.73</v>
+        <v>4.66</v>
       </c>
       <c r="CC9" t="n">
         <v>8.57</v>
@@ -4446,25 +4446,25 @@
         <v>1.36</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CI9" t="n">
         <v>1.9</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CM9" t="n">
         <v>2.03</v>
@@ -4476,22 +4476,22 @@
         <v>1.25</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CR9" t="n">
         <v>1.4</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CV9" t="n">
         <v>1.93</v>
@@ -4509,91 +4509,91 @@
         <v>2.1</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="DB9" t="n">
         <v>1.28</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="DE9" t="n">
         <v>0.12</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="DH9" t="n">
-        <v>69.68000000000001</v>
+        <v>71.94</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="DK9" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DM9" t="n">
-        <v>25.44</v>
+        <v>26</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.75</v>
+        <v>13.89</v>
       </c>
       <c r="DQ9" t="n">
-        <v>16.38</v>
+        <v>16.12</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.94</v>
+        <v>9.76</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>43.06</v>
+        <v>43.47</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.869999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.75</v>
+        <v>5.94</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.12</v>
+        <v>3.23</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.56</v>
+        <v>16.29</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="10">
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
         <v>8</v>
@@ -4615,82 +4615,82 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="G10" t="n">
-        <v>3.5</v>
+        <v>3.89</v>
       </c>
       <c r="H10" t="n">
-        <v>128.5</v>
+        <v>130.22</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="J10" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>9.25</v>
+        <v>9.67</v>
       </c>
       <c r="L10" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="M10" t="n">
-        <v>76.12</v>
+        <v>74.78</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="O10" t="n">
-        <v>5.62</v>
+        <v>5.67</v>
       </c>
       <c r="P10" t="n">
-        <v>10.5</v>
+        <v>10.56</v>
       </c>
       <c r="Q10" t="n">
-        <v>13</v>
+        <v>12.67</v>
       </c>
       <c r="R10" t="n">
-        <v>4.38</v>
+        <v>4.22</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="T10" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="U10" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="V10" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>63.75</v>
+        <v>63.67</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z10" t="n">
-        <v>22.62</v>
+        <v>22</v>
       </c>
       <c r="AA10" t="n">
-        <v>15.75</v>
+        <v>15.44</v>
       </c>
       <c r="AB10" t="n">
-        <v>6.88</v>
+        <v>6.56</v>
       </c>
       <c r="AC10" t="n">
-        <v>26</v>
+        <v>26.33</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AF10" t="n">
         <v>0.12</v>
@@ -4774,70 +4774,70 @@
         <v>1.62</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.94</v>
+        <v>10.29</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.75</v>
+        <v>4.82</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.12</v>
+        <v>5.41</v>
       </c>
       <c r="BR10" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS10" t="n">
-        <v>87.5</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BU10" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV10" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="CA10" t="n">
-        <v>5.46</v>
+        <v>5.52</v>
       </c>
       <c r="CB10" t="n">
-        <v>6.13</v>
+        <v>6.2</v>
       </c>
       <c r="CC10" t="n">
         <v>1.61</v>
@@ -4846,28 +4846,28 @@
         <v>1.63</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CI10" t="n">
         <v>1.6</v>
       </c>
       <c r="CJ10" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CK10" t="n">
         <v>1.82</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CM10" t="n">
         <v>1.89</v>
@@ -4879,10 +4879,10 @@
         <v>1.21</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="CR10" t="n">
         <v>1.37</v>
@@ -4897,10 +4897,10 @@
         <v>1.51</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="CX10" t="n">
         <v>1.84</v>
@@ -4915,88 +4915,88 @@
         <v>1.59</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="DC10" t="n">
         <v>1.8</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="DE10" t="n">
         <v>0.06</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="DG10" t="n">
-        <v>3.56</v>
+        <v>3.76</v>
       </c>
       <c r="DH10" t="n">
-        <v>119.62</v>
+        <v>121.06</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.06</v>
+        <v>-0.11</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="DK10" t="n">
-        <v>7.75</v>
+        <v>8.06</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="DM10" t="n">
-        <v>68.12</v>
+        <v>67.88</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="DO10" t="n">
-        <v>4.12</v>
+        <v>4.23</v>
       </c>
       <c r="DP10" t="n">
-        <v>12.69</v>
+        <v>12.59</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.69</v>
+        <v>12.53</v>
       </c>
       <c r="DR10" t="n">
-        <v>4.56</v>
+        <v>4.47</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>60.88</v>
+        <v>61</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX10" t="n">
-        <v>18.31</v>
+        <v>18.24</v>
       </c>
       <c r="DY10" t="n">
-        <v>12.38</v>
+        <v>12.41</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.94</v>
+        <v>5.83</v>
       </c>
       <c r="EA10" t="n">
-        <v>26.06</v>
+        <v>26.23</v>
       </c>
       <c r="EB10" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="11">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5502,49 +5502,49 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AI12" t="n">
-        <v>70.38</v>
+        <v>71.56</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.88</v>
+        <v>3.11</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN12" t="n">
-        <v>30.88</v>
+        <v>32.22</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14.25</v>
+        <v>14.11</v>
       </c>
       <c r="AR12" t="n">
-        <v>13</v>
+        <v>13.33</v>
       </c>
       <c r="AS12" t="n">
         <v>9</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,82 +5556,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>39.62</v>
+        <v>40.78</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="BA12" t="n">
-        <v>8.380000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.75</v>
+        <v>5.78</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.62</v>
+        <v>2.89</v>
       </c>
       <c r="BD12" t="n">
-        <v>16.12</v>
+        <v>16.78</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.76</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.53</v>
+        <v>4.44</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.24</v>
+        <v>4.28</v>
       </c>
       <c r="BR12" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS12" t="n">
-        <v>70.59</v>
+        <v>66.67</v>
       </c>
       <c r="BT12" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BU12" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV12" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW12" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX12" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BY12" t="n">
         <v>5.82</v>
@@ -5640,16 +5640,16 @@
         <v>6.01</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.97</v>
+        <v>3.94</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.25</v>
+        <v>4.21</v>
       </c>
       <c r="CC12" t="n">
-        <v>6.67</v>
+        <v>6.41</v>
       </c>
       <c r="CD12" t="n">
-        <v>8.41</v>
+        <v>7.99</v>
       </c>
       <c r="CE12" t="n">
         <v>1.43</v>
@@ -5658,28 +5658,28 @@
         <v>2.99</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="CH12" t="n">
         <v>1.36</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CJ12" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CL12" t="n">
         <v>2.59</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CO12" t="n">
         <v>1.34</v>
@@ -5688,13 +5688,13 @@
         <v>2.08</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="CR12" t="n">
         <v>1.42</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CT12" t="n">
         <v>2.89</v>
@@ -5703,16 +5703,16 @@
         <v>1.41</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="CZ12" t="n">
         <v>1.91</v>
@@ -5727,82 +5727,82 @@
         <v>2.1</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="DH12" t="n">
-        <v>75.3</v>
+        <v>75.61</v>
       </c>
       <c r="DI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="DK12" t="n">
-        <v>3.36</v>
+        <v>3.44</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DM12" t="n">
-        <v>33.53</v>
+        <v>34.06</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="DP12" t="n">
         <v>13.06</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.59</v>
+        <v>12.77</v>
       </c>
       <c r="DR12" t="n">
         <v>9.06</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>42.82</v>
+        <v>43.22</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="DX12" t="n">
-        <v>8.300000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="DY12" t="n">
         <v>6</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="EA12" t="n">
-        <v>16.7</v>
+        <v>17</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
         <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
         <v>0.38</v>
@@ -5902,139 +5902,139 @@
         <v>2.25</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AI13" t="n">
-        <v>104.12</v>
+        <v>105.22</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AL13" t="n">
-        <v>4.62</v>
+        <v>4.33</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>52</v>
+        <v>52.22</v>
       </c>
       <c r="AO13" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>14.67</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>59.33</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>23.44</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BJ13" t="n">
         <v>0.88</v>
       </c>
-      <c r="AP13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>13.62</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>59.38</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>8.119999999999999</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>8</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>0.9399999999999999</v>
-      </c>
       <c r="BK13" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.06</v>
+        <v>3.88</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3.81</v>
+        <v>3.71</v>
       </c>
       <c r="BR13" t="n">
-        <v>100</v>
+        <v>94.12</v>
       </c>
       <c r="BS13" t="n">
-        <v>87.5</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT13" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BU13" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV13" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BY13" t="n">
         <v>1.81</v>
@@ -6043,28 +6043,28 @@
         <v>2</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.19</v>
+        <v>4.14</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.62</v>
+        <v>4.53</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="CE13" t="n">
         <v>1.38</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CI13" t="n">
         <v>1.78</v>
@@ -6073,7 +6073,7 @@
         <v>1.96</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="CL13" t="n">
         <v>2.26</v>
@@ -6082,25 +6082,25 @@
         <v>1.89</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CO13" t="n">
         <v>1.28</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="CU13" t="n">
         <v>1.43</v>
@@ -6109,103 +6109,103 @@
         <v>1.79</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="CY13" t="n">
         <v>2.27</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="DA13" t="n">
         <v>1.62</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.46</v>
+        <v>3.54</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.68</v>
+        <v>2.59</v>
       </c>
       <c r="DH13" t="n">
-        <v>99.18000000000001</v>
+        <v>100.06</v>
       </c>
       <c r="DI13" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.06</v>
+        <v>4.88</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DM13" t="n">
-        <v>53.31</v>
+        <v>53.35</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="DP13" t="n">
-        <v>15</v>
+        <v>15.12</v>
       </c>
       <c r="DQ13" t="n">
-        <v>14.88</v>
+        <v>14.94</v>
       </c>
       <c r="DR13" t="n">
-        <v>5.81</v>
+        <v>5.76</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>55.5</v>
+        <v>55.7</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX13" t="n">
-        <v>13</v>
+        <v>12.76</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.5</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.5</v>
+        <v>4.41</v>
       </c>
       <c r="EA13" t="n">
-        <v>22.5</v>
+        <v>23</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" t="n">
         <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6308,136 +6308,136 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AH14" t="n">
         <v>1</v>
       </c>
       <c r="AI14" t="n">
-        <v>54.62</v>
+        <v>55.67</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AM14" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>22.22</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>34.44</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>9.06</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="BK14" t="n">
         <v>0.5</v>
       </c>
-      <c r="AN14" t="n">
-        <v>22.75</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>13.38</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>32.88</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>6.12</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>15.12</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>9.24</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>0.53</v>
-      </c>
       <c r="BL14" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.35</v>
+        <v>4.39</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.82</v>
+        <v>4.61</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>88.23999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT14" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BU14" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV14" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX14" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BY14" t="n">
         <v>4.57</v>
@@ -6446,40 +6446,40 @@
         <v>5.19</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="CB14" t="n">
-        <v>5.07</v>
+        <v>4.95</v>
       </c>
       <c r="CC14" t="n">
-        <v>9.31</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="CD14" t="n">
-        <v>13.27</v>
+        <v>12.4</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CK14" t="n">
         <v>1.8</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CM14" t="n">
         <v>1.95</v>
@@ -6488,31 +6488,31 @@
         <v>1.58</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.15</v>
+        <v>3.23</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.99</v>
+        <v>2.93</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="CV14" t="n">
         <v>1.81</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CX14" t="n">
         <v>1.83</v>
@@ -6527,55 +6527,55 @@
         <v>1.6</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.28</v>
+        <v>3.37</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="DG14" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="DH14" t="n">
-        <v>69.81999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.29</v>
+        <v>3.44</v>
       </c>
       <c r="DK14" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM14" t="n">
-        <v>29.53</v>
+        <v>28.89</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="DO14" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="DP14" t="n">
-        <v>15.24</v>
+        <v>15.11</v>
       </c>
       <c r="DQ14" t="n">
-        <v>12.18</v>
+        <v>12.5</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.24</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="DS14" t="n">
         <v>0.06</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>38.59</v>
+        <v>39.06</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="DX14" t="n">
-        <v>8.880000000000001</v>
+        <v>8.56</v>
       </c>
       <c r="DY14" t="n">
-        <v>6.71</v>
+        <v>6.44</v>
       </c>
       <c r="DZ14" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="EA14" t="n">
-        <v>18.12</v>
+        <v>18.11</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" t="n">
         <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
         <v>0.12</v>
@@ -6708,139 +6708,139 @@
         <v>3.25</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AH15" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AI15" t="n">
-        <v>82.89</v>
+        <v>80</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.56</v>
+        <v>3.2</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN15" t="n">
-        <v>35.22</v>
+        <v>34.5</v>
       </c>
       <c r="AO15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="BN15" t="n">
         <v>1.22</v>
       </c>
-      <c r="AP15" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>15.11</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AU15" t="n">
+      <c r="BO15" t="n">
         <v>1.22</v>
       </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>46.44</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>9.890000000000001</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>20.11</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>8.76</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>1.24</v>
-      </c>
       <c r="BP15" t="n">
-        <v>3.65</v>
+        <v>3.78</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.06</v>
+        <v>5.33</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>70.59</v>
+        <v>66.67</v>
       </c>
       <c r="BT15" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BU15" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BV15" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX15" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BY15" t="n">
         <v>3.95</v>
@@ -6849,73 +6849,73 @@
         <v>4.1</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.71</v>
+        <v>3.87</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.86</v>
+        <v>4.05</v>
       </c>
       <c r="CC15" t="n">
-        <v>5.73</v>
+        <v>6.76</v>
       </c>
       <c r="CD15" t="n">
-        <v>6.04</v>
+        <v>7.12</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.74</v>
+        <v>2.81</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="CM15" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CN15" t="n">
         <v>1.52</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="CR15" t="n">
         <v>1.42</v>
       </c>
       <c r="CS15" t="n">
-        <v>3.01</v>
+        <v>2.97</v>
       </c>
       <c r="CT15" t="n">
         <v>2.88</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="CW15" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="CX15" t="n">
         <v>1.88</v>
@@ -6924,94 +6924,94 @@
         <v>2.35</v>
       </c>
       <c r="CZ15" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DA15" t="n">
         <v>1.57</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
       <c r="DE15" t="n">
         <v>0.11</v>
       </c>
       <c r="DF15" t="n">
-        <v>2.47</v>
+        <v>2.33</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="DH15" t="n">
-        <v>76.47</v>
+        <v>75.22</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.41</v>
+        <v>3.22</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.65</v>
+        <v>3.61</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DM15" t="n">
-        <v>32.94</v>
+        <v>32.67</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="DP15" t="n">
-        <v>15.59</v>
+        <v>15.28</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.71</v>
+        <v>15.45</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.65</v>
+        <v>8.06</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>47.88</v>
+        <v>47.28</v>
       </c>
       <c r="DW15" t="n">
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>11.35</v>
+        <v>11.06</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.47</v>
+        <v>7.22</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.89</v>
+        <v>3.84</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.41</v>
+        <v>20.67</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="EC15" t="n">
-        <v>3.41</v>
+        <v>3.22</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>56.33</v>
+        <v>56.44</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.22</v>
@@ -1751,7 +1751,7 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>57.94</v>
+        <v>58</v>
       </c>
       <c r="DW2" t="n">
         <v>0.16</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>46.38</v>
+        <v>46.25</v>
       </c>
       <c r="Y4" t="n">
         <v>0.25</v>
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>44.89</v>
+        <v>44.83</v>
       </c>
       <c r="DW4" t="n">
         <v>0.18</v>

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
         <v>9</v>
@@ -1391,82 +1391,82 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="H2" t="n">
-        <v>100.56</v>
+        <v>97</v>
       </c>
       <c r="I2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J2" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="K2" t="n">
-        <v>5.67</v>
+        <v>5.4</v>
       </c>
       <c r="L2" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="M2" t="n">
-        <v>62.33</v>
+        <v>59.5</v>
       </c>
       <c r="N2" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="O2" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="P2" t="n">
-        <v>15.78</v>
+        <v>15.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.89</v>
+        <v>13.7</v>
       </c>
       <c r="R2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="T2" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="U2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>59.56</v>
+        <v>57.9</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z2" t="n">
-        <v>17.33</v>
+        <v>16.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>12</v>
+        <v>11.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.33</v>
+        <v>5.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>21.22</v>
+        <v>21.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AF2" t="n">
         <v>0.11</v>
@@ -1550,70 +1550,70 @@
         <v>2.67</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.56</v>
+        <v>8.32</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="BO2" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.94</v>
+        <v>3.89</v>
       </c>
       <c r="BQ2" t="n">
-        <v>3.78</v>
+        <v>3.63</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BT2" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BU2" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV2" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.61</v>
+        <v>4.53</v>
       </c>
       <c r="CB2" t="n">
-        <v>5.02</v>
+        <v>4.92</v>
       </c>
       <c r="CC2" t="n">
         <v>1.93</v>
@@ -1625,19 +1625,19 @@
         <v>1.36</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="CH2" t="n">
         <v>1.44</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CK2" t="n">
         <v>1.77</v>
@@ -1649,34 +1649,34 @@
         <v>1.96</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CO2" t="n">
         <v>1.27</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="CR2" t="n">
         <v>1.38</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="CX2" t="n">
         <v>1.81</v>
@@ -1694,22 +1694,22 @@
         <v>1.28</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="DH2" t="n">
-        <v>93.78</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="DI2" t="n">
         <v>0.16</v>
@@ -1718,61 +1718,61 @@
         <v>2.89</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.39</v>
+        <v>5.26</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DM2" t="n">
-        <v>55.61</v>
+        <v>54.47</v>
       </c>
       <c r="DN2" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="DP2" t="n">
-        <v>16.44</v>
+        <v>16.32</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.23</v>
+        <v>13.63</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.5</v>
+        <v>6.47</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>58</v>
+        <v>57.21</v>
       </c>
       <c r="DW2" t="n">
         <v>0.16</v>
       </c>
       <c r="DX2" t="n">
-        <v>15.38</v>
+        <v>15.05</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.5</v>
+        <v>10.21</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.89</v>
+        <v>4.84</v>
       </c>
       <c r="EA2" t="n">
-        <v>20.61</v>
+        <v>20.58</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="n">
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1872,130 +1872,130 @@
         <v>2.67</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
       <c r="AI3" t="n">
-        <v>83.11</v>
+        <v>86</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK3" t="n">
         <v>2</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN3" t="n">
-        <v>36.56</v>
+        <v>40</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>16.44</v>
+        <v>16.7</v>
       </c>
       <c r="AR3" t="n">
-        <v>14.56</v>
+        <v>14.3</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.67</v>
+        <v>6.3</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>48.78</v>
+        <v>50.4</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.11</v>
+        <v>11.3</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.89</v>
+        <v>7.7</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="BF3" t="n">
         <v>2</v>
       </c>
       <c r="BG3" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.56</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="BI3" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BP3" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.94</v>
+        <v>5.89</v>
       </c>
       <c r="BR3" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS3" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BT3" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BU3" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BV3" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BY3" t="n">
         <v>2.64</v>
@@ -2013,40 +2013,40 @@
         <v>2.71</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="CC3" t="n">
-        <v>3.98</v>
+        <v>3.77</v>
       </c>
       <c r="CD3" t="n">
-        <v>4.98</v>
+        <v>4.66</v>
       </c>
       <c r="CE3" t="n">
         <v>1.43</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="CH3" t="n">
         <v>1.35</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CJ3" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CK3" t="n">
         <v>1.85</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="CM3" t="n">
         <v>1.86</v>
@@ -2055,13 +2055,13 @@
         <v>1.52</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.76</v>
+        <v>3.82</v>
       </c>
       <c r="CR3" t="n">
         <v>1.44</v>
@@ -2079,13 +2079,13 @@
         <v>1.78</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CX3" t="n">
         <v>1.89</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CZ3" t="n">
         <v>1.92</v>
@@ -2094,88 +2094,88 @@
         <v>1.55</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.94</v>
+        <v>3.99</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="DH3" t="n">
-        <v>90.28</v>
+        <v>91.42</v>
       </c>
       <c r="DI3" t="n">
         <v>0.16</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.22</v>
+        <v>5.21</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DM3" t="n">
-        <v>41.39</v>
+        <v>42.95</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="DP3" t="n">
-        <v>15.27</v>
+        <v>15.47</v>
       </c>
       <c r="DQ3" t="n">
-        <v>15.17</v>
+        <v>15</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.84</v>
+        <v>6.63</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>51.22</v>
+        <v>51.95</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.73</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.78</v>
+        <v>3.95</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.94</v>
+        <v>19.79</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="n">
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
         <v>0.25</v>
@@ -2278,136 +2278,136 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>80.11</v>
+        <v>78.8</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.22</v>
+        <v>4.4</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>32.89</v>
+        <v>32.9</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14.56</v>
+        <v>15.3</v>
       </c>
       <c r="AR4" t="n">
-        <v>16.78</v>
+        <v>16.9</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.56</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>43.56</v>
+        <v>44.3</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.56</v>
+        <v>9.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.44</v>
+        <v>6.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.11</v>
+        <v>3.3</v>
       </c>
       <c r="BD4" t="n">
-        <v>17.78</v>
+        <v>18.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.82</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.71</v>
+        <v>0.78</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.06</v>
+        <v>5.11</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.76</v>
+        <v>4.67</v>
       </c>
       <c r="BR4" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS4" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT4" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BU4" t="n">
-        <v>23.53</v>
+        <v>27.78</v>
       </c>
       <c r="BV4" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW4" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX4" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BY4" t="n">
         <v>3.12</v>
@@ -2416,22 +2416,22 @@
         <v>3.61</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="CC4" t="n">
-        <v>6.52</v>
+        <v>6.35</v>
       </c>
       <c r="CD4" t="n">
-        <v>7</v>
+        <v>6.79</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CG4" t="n">
         <v>2.73</v>
@@ -2449,7 +2449,7 @@
         <v>1.83</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CM4" t="n">
         <v>1.93</v>
@@ -2461,31 +2461,31 @@
         <v>1.32</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="CR4" t="n">
         <v>1.42</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="CU4" t="n">
         <v>1.39</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CW4" t="n">
         <v>2.03</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CY4" t="n">
         <v>2.37</v>
@@ -2494,58 +2494,58 @@
         <v>1.96</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="DB4" t="n">
         <v>1.34</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="DH4" t="n">
-        <v>79.17</v>
+        <v>78.5</v>
       </c>
       <c r="DI4" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.65</v>
+        <v>3.67</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.77</v>
+        <v>4.84</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="DM4" t="n">
-        <v>37.7</v>
+        <v>37.44</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.36</v>
+        <v>13.83</v>
       </c>
       <c r="DQ4" t="n">
-        <v>15.94</v>
+        <v>16.06</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.18</v>
+        <v>8</v>
       </c>
       <c r="DS4" t="n">
         <v>0.06</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>44.83</v>
+        <v>45.17</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX4" t="n">
-        <v>9.289999999999999</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="DY4" t="n">
-        <v>5.76</v>
+        <v>6.16</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.53</v>
+        <v>3.61</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.82</v>
+        <v>20.28</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="EC4" t="n">
-        <v>3.41</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="5">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
@@ -2600,82 +2600,82 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="G5" t="n">
-        <v>2.11</v>
+        <v>2.6</v>
       </c>
       <c r="H5" t="n">
-        <v>85.33</v>
+        <v>89.3</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.33</v>
+        <v>3.8</v>
       </c>
       <c r="L5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="M5" t="n">
-        <v>41.33</v>
+        <v>44.2</v>
       </c>
       <c r="N5" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="O5" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="P5" t="n">
-        <v>14.67</v>
+        <v>14.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>15.22</v>
+        <v>15.1</v>
       </c>
       <c r="R5" t="n">
-        <v>5.78</v>
+        <v>5.5</v>
       </c>
       <c r="S5" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T5" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="U5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>52.22</v>
+        <v>53.7</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.56</v>
+        <v>11.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.44</v>
+        <v>9</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.11</v>
+        <v>2.9</v>
       </c>
       <c r="AC5" t="n">
-        <v>23.44</v>
+        <v>24.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AF5" t="n">
         <v>0.22</v>
@@ -2759,70 +2759,70 @@
         <v>3.11</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="BH5" t="n">
-        <v>7.94</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BO5" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.89</v>
+        <v>3.84</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.06</v>
+        <v>4.21</v>
       </c>
       <c r="BR5" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS5" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT5" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BU5" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BV5" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.95</v>
+        <v>3.76</v>
       </c>
       <c r="BZ5" t="n">
-        <v>4.39</v>
+        <v>4.13</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.69</v>
+        <v>3.65</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.96</v>
+        <v>3.93</v>
       </c>
       <c r="CC5" t="n">
         <v>6.03</v>
@@ -2834,28 +2834,28 @@
         <v>1.42</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CJ5" t="n">
         <v>2</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CM5" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CN5" t="n">
         <v>1.49</v>
@@ -2867,7 +2867,7 @@
         <v>2.07</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.66</v>
+        <v>3.67</v>
       </c>
       <c r="CR5" t="n">
         <v>1.43</v>
@@ -2900,55 +2900,55 @@
         <v>1.52</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="DC5" t="n">
         <v>2.15</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.87</v>
+        <v>3.86</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="DH5" t="n">
-        <v>78.67</v>
+        <v>81.11</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.38</v>
+        <v>3.63</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="DM5" t="n">
-        <v>36.11</v>
+        <v>37.9</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="DP5" t="n">
-        <v>15.78</v>
+        <v>15.68</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.78</v>
+        <v>14.74</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.17</v>
+        <v>7.9</v>
       </c>
       <c r="DS5" t="n">
         <v>0.11</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>48.72</v>
+        <v>49.68</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX5" t="n">
-        <v>9.94</v>
+        <v>10.21</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.11</v>
+        <v>7.47</v>
       </c>
       <c r="DZ5" t="n">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="EA5" t="n">
-        <v>22.06</v>
+        <v>22.74</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
         <v>0.12</v>
@@ -3084,136 +3084,136 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.11</v>
+        <v>3.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AI6" t="n">
-        <v>77.33</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK6" t="n">
-        <v>4.56</v>
+        <v>4.8</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.89</v>
+        <v>4.9</v>
       </c>
       <c r="AM6" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AN6" t="n">
-        <v>35.22</v>
+        <v>39.6</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>18.44</v>
+        <v>19</v>
       </c>
       <c r="AR6" t="n">
-        <v>13.22</v>
+        <v>13.3</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.67</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>47.67</v>
+        <v>47.4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="BA6" t="n">
-        <v>14.22</v>
+        <v>13.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.779999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.44</v>
+        <v>5.3</v>
       </c>
       <c r="BD6" t="n">
-        <v>17.67</v>
+        <v>17.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="BG6" t="n">
         <v>2.94</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.12</v>
+        <v>10.06</v>
       </c>
       <c r="BI6" t="n">
         <v>2.94</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BP6" t="n">
-        <v>5.59</v>
+        <v>5.67</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.47</v>
+        <v>4.33</v>
       </c>
       <c r="BR6" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS6" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BT6" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BU6" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BV6" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>76.47</v>
+        <v>72.22</v>
       </c>
       <c r="BY6" t="n">
         <v>4.44</v>
@@ -3222,55 +3222,55 @@
         <v>4.56</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.96</v>
+        <v>3.98</v>
       </c>
       <c r="CC6" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="CD6" t="n">
         <v>5.25</v>
-      </c>
-      <c r="CD6" t="n">
-        <v>4.99</v>
       </c>
       <c r="CE6" t="n">
         <v>1.4</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CH6" t="n">
         <v>1.4</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="CM6" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CO6" t="n">
         <v>1.31</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="CR6" t="n">
         <v>1.45</v>
@@ -3285,73 +3285,73 @@
         <v>1.41</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="CZ6" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="DC6" t="n">
         <v>2.09</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.71</v>
+        <v>3.73</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.71</v>
+        <v>2.83</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="DH6" t="n">
-        <v>79.06</v>
+        <v>79.39</v>
       </c>
       <c r="DI6" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ6" t="n">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.35</v>
+        <v>4.39</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.65</v>
+        <v>0.78</v>
       </c>
       <c r="DM6" t="n">
-        <v>38.59</v>
+        <v>40.84</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.71</v>
+        <v>2.78</v>
       </c>
       <c r="DP6" t="n">
-        <v>17.53</v>
+        <v>17.89</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14.18</v>
+        <v>14.17</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.18</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DS6" t="n">
         <v>0.06</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>45.83</v>
+        <v>45.78</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="DX6" t="n">
-        <v>14.35</v>
+        <v>13.94</v>
       </c>
       <c r="DY6" t="n">
-        <v>9.35</v>
+        <v>9</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5</v>
+        <v>4.94</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.77</v>
+        <v>16.78</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="EC6" t="n">
-        <v>3.82</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="n">
         <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
         <v>0.1</v>
@@ -3487,136 +3487,136 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AI7" t="n">
-        <v>84</v>
+        <v>84.67</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.88</v>
+        <v>3.44</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN7" t="n">
-        <v>30.5</v>
+        <v>31.22</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AQ7" t="n">
-        <v>15.88</v>
+        <v>16.56</v>
       </c>
       <c r="AR7" t="n">
-        <v>12.5</v>
+        <v>12.67</v>
       </c>
       <c r="AS7" t="n">
-        <v>10.5</v>
+        <v>10.22</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>39.62</v>
+        <v>40.33</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BA7" t="n">
-        <v>10.25</v>
+        <v>11.11</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.75</v>
+        <v>7.22</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.5</v>
+        <v>3.89</v>
       </c>
       <c r="BD7" t="n">
-        <v>16.5</v>
+        <v>17.56</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.38</v>
+        <v>3</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.33</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BP7" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.22</v>
+        <v>4.47</v>
       </c>
       <c r="BR7" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS7" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT7" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BU7" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BV7" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW7" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX7" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BY7" t="n">
         <v>5.02</v>
@@ -3625,25 +3625,25 @@
         <v>5.18</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="CC7" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="CD7" t="n">
-        <v>5.76</v>
+        <v>5.53</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF7" t="n">
         <v>2.96</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="CH7" t="n">
         <v>1.36</v>
@@ -3655,10 +3655,10 @@
         <v>1.97</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="CM7" t="n">
         <v>1.84</v>
@@ -3670,22 +3670,22 @@
         <v>1.34</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CV7" t="n">
         <v>1.8</v>
@@ -3706,88 +3706,88 @@
         <v>1.53</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.91</v>
+        <v>3.96</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DH7" t="n">
-        <v>84</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="DI7" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.84</v>
+        <v>3.63</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.39</v>
+        <v>3.42</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="DM7" t="n">
-        <v>32.17</v>
+        <v>32.42</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="DP7" t="n">
-        <v>16.34</v>
+        <v>16.63</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.22</v>
+        <v>14.21</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.33</v>
+        <v>8.31</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>41.39</v>
+        <v>41.63</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.39</v>
+        <v>11.74</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.39</v>
+        <v>7.58</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4</v>
+        <v>4.16</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.33</v>
+        <v>17.79</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.61</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="8">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
         <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="F8" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="G8" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="H8" t="n">
-        <v>105.56</v>
+        <v>98.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L8" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="M8" t="n">
-        <v>44.78</v>
+        <v>42.2</v>
       </c>
       <c r="N8" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="O8" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="P8" t="n">
-        <v>11.67</v>
+        <v>12.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>16.22</v>
+        <v>16.8</v>
       </c>
       <c r="R8" t="n">
-        <v>6.11</v>
+        <v>6.7</v>
       </c>
       <c r="S8" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="T8" t="n">
         <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>61.89</v>
+        <v>60.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z8" t="n">
-        <v>15.22</v>
+        <v>14.7</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.109999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.11</v>
+        <v>5.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>23.56</v>
+        <v>23.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AE8" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AF8" t="n">
         <v>0.22</v>
@@ -3968,70 +3968,70 @@
         <v>2.44</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.61</v>
+        <v>3.63</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.609999999999999</v>
+        <v>9.58</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.61</v>
+        <v>3.63</v>
       </c>
       <c r="BJ8" t="n">
         <v>1.11</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BL8" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BM8" t="n">
         <v>0.89</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="BP8" t="n">
-        <v>5.06</v>
+        <v>5.11</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.56</v>
+        <v>4.47</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
       </c>
       <c r="BS8" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BU8" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BV8" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BW8" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX8" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.93</v>
+        <v>3.91</v>
       </c>
       <c r="CC8" t="n">
         <v>4.2</v>
@@ -4061,31 +4061,31 @@
         <v>1.84</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CM8" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CN8" t="n">
         <v>1.53</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="CR8" t="n">
         <v>1.41</v>
       </c>
       <c r="CS8" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CU8" t="n">
         <v>1.39</v>
@@ -4094,7 +4094,7 @@
         <v>1.87</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CX8" t="n">
         <v>1.86</v>
@@ -4109,88 +4109,88 @@
         <v>1.56</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.59</v>
+        <v>3.61</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="DH8" t="n">
-        <v>97.84</v>
+        <v>94.53</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.34</v>
+        <v>5.21</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="DM8" t="n">
-        <v>42.84</v>
+        <v>41.58</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="DP8" t="n">
-        <v>12.12</v>
+        <v>12.42</v>
       </c>
       <c r="DQ8" t="n">
-        <v>15.72</v>
+        <v>16.05</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.61</v>
+        <v>6.89</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>58.39</v>
+        <v>57.9</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.94</v>
+        <v>12.79</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.78</v>
+        <v>7.68</v>
       </c>
       <c r="DZ8" t="n">
-        <v>5.16</v>
+        <v>5.1</v>
       </c>
       <c r="EA8" t="n">
-        <v>22.33</v>
+        <v>22.16</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
         <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4290,91 +4290,91 @@
         <v>2.22</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AI9" t="n">
-        <v>65.25</v>
+        <v>65.11</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.38</v>
+        <v>3.33</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.25</v>
+        <v>0.44</v>
       </c>
       <c r="AN9" t="n">
-        <v>24.12</v>
+        <v>24.44</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AQ9" t="n">
-        <v>11.88</v>
+        <v>12.11</v>
       </c>
       <c r="AR9" t="n">
-        <v>15.88</v>
+        <v>15.67</v>
       </c>
       <c r="AS9" t="n">
         <v>9</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>41.62</v>
+        <v>40.67</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.119999999999999</v>
+        <v>7.89</v>
       </c>
       <c r="BB9" t="n">
-        <v>5</v>
+        <v>4.67</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.12</v>
+        <v>3.22</v>
       </c>
       <c r="BD9" t="n">
-        <v>14.62</v>
+        <v>14.33</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="BG9" t="n">
         <v>2.94</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.710000000000001</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="BI9" t="n">
         <v>2.94</v>
@@ -4383,46 +4383,46 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.71</v>
+        <v>4.61</v>
       </c>
       <c r="BQ9" t="n">
-        <v>3.94</v>
+        <v>4.11</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT9" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BU9" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV9" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX9" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BY9" t="n">
         <v>3.41</v>
@@ -4431,40 +4431,40 @@
         <v>3.61</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.34</v>
+        <v>4.26</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.66</v>
+        <v>4.58</v>
       </c>
       <c r="CC9" t="n">
-        <v>8.57</v>
+        <v>8.02</v>
       </c>
       <c r="CD9" t="n">
-        <v>10.2</v>
+        <v>9.68</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.09</v>
+        <v>3.06</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CI9" t="n">
         <v>1.9</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CK9" t="n">
         <v>1.73</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="CM9" t="n">
         <v>2.03</v>
@@ -4473,13 +4473,13 @@
         <v>1.63</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.09</v>
+        <v>3.13</v>
       </c>
       <c r="CR9" t="n">
         <v>1.4</v>
@@ -4512,88 +4512,88 @@
         <v>1.67</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="DH9" t="n">
-        <v>71.94</v>
+        <v>71.5</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DJ9" t="n">
         <v>2.88</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.23</v>
+        <v>0.33</v>
       </c>
       <c r="DM9" t="n">
-        <v>26</v>
+        <v>26.06</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="DP9" t="n">
         <v>13.89</v>
       </c>
       <c r="DQ9" t="n">
-        <v>16.12</v>
+        <v>16</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.76</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>43.47</v>
+        <v>42.89</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.17</v>
+        <v>9</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.94</v>
+        <v>5.72</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.23</v>
+        <v>3.28</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.29</v>
+        <v>16.06</v>
       </c>
       <c r="EB9" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4693,139 +4693,139 @@
         <v>0.78</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.75</v>
+        <v>1.11</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.62</v>
+        <v>3.22</v>
       </c>
       <c r="AI10" t="n">
-        <v>110.75</v>
+        <v>114.33</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="AL10" t="n">
-        <v>6.25</v>
+        <v>5.67</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AN10" t="n">
-        <v>60.12</v>
+        <v>60</v>
       </c>
       <c r="AO10" t="n">
         <v>1</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14.88</v>
+        <v>15.56</v>
       </c>
       <c r="AR10" t="n">
-        <v>12.38</v>
+        <v>12.44</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.75</v>
+        <v>4.78</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>58</v>
+        <v>57.89</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA10" t="n">
-        <v>14</v>
+        <v>13.67</v>
       </c>
       <c r="BB10" t="n">
-        <v>9</v>
+        <v>8.56</v>
       </c>
       <c r="BC10" t="n">
-        <v>5</v>
+        <v>5.11</v>
       </c>
       <c r="BD10" t="n">
-        <v>26.12</v>
+        <v>25.89</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.29</v>
+        <v>9.94</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.82</v>
+        <v>4.72</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.41</v>
+        <v>5.17</v>
       </c>
       <c r="BR10" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS10" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT10" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BU10" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV10" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BY10" t="n">
         <v>1.24</v>
@@ -4834,73 +4834,73 @@
         <v>1.24</v>
       </c>
       <c r="CA10" t="n">
-        <v>5.52</v>
+        <v>5.38</v>
       </c>
       <c r="CB10" t="n">
-        <v>6.2</v>
+        <v>6.03</v>
       </c>
       <c r="CC10" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="CD10" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="CH10" t="n">
         <v>1.5</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="CJ10" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="CK10" t="n">
         <v>1.82</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CM10" t="n">
         <v>1.89</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CO10" t="n">
         <v>1.21</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CX10" t="n">
         <v>1.84</v>
@@ -4915,88 +4915,88 @@
         <v>1.59</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="DD10" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="DE10" t="n">
         <v>0.06</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.59</v>
+        <v>0.77</v>
       </c>
       <c r="DG10" t="n">
-        <v>3.76</v>
+        <v>3.56</v>
       </c>
       <c r="DH10" t="n">
-        <v>121.06</v>
+        <v>122.28</v>
       </c>
       <c r="DI10" t="n">
         <v>-0.11</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="DK10" t="n">
-        <v>8.06</v>
+        <v>7.67</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="DM10" t="n">
-        <v>67.88</v>
+        <v>67.39</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="DO10" t="n">
-        <v>4.23</v>
+        <v>4.06</v>
       </c>
       <c r="DP10" t="n">
-        <v>12.59</v>
+        <v>13.06</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.53</v>
+        <v>12.56</v>
       </c>
       <c r="DR10" t="n">
-        <v>4.47</v>
+        <v>4.5</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>61</v>
+        <v>60.78</v>
       </c>
       <c r="DW10" t="n">
         <v>0.11</v>
       </c>
       <c r="DX10" t="n">
-        <v>18.24</v>
+        <v>17.83</v>
       </c>
       <c r="DY10" t="n">
-        <v>12.41</v>
+        <v>12</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.83</v>
+        <v>5.84</v>
       </c>
       <c r="EA10" t="n">
-        <v>26.23</v>
+        <v>26.11</v>
       </c>
       <c r="EB10" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="11">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
         <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F11" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="G11" t="n">
-        <v>3.89</v>
+        <v>3.7</v>
       </c>
       <c r="H11" t="n">
-        <v>114.56</v>
+        <v>112.6</v>
       </c>
       <c r="I11" t="n">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="J11" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="K11" t="n">
-        <v>6.89</v>
+        <v>6.8</v>
       </c>
       <c r="L11" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="M11" t="n">
-        <v>61.22</v>
+        <v>63.2</v>
       </c>
       <c r="N11" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>11.11</v>
+        <v>10.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>13.33</v>
+        <v>12.8</v>
       </c>
       <c r="R11" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="S11" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="U11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>63.67</v>
+        <v>63.7</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>17.11</v>
+        <v>16.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>10.78</v>
+        <v>10.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.33</v>
+        <v>6.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>24.22</v>
+        <v>24.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AF11" t="n">
         <v>0.25</v>
@@ -5177,70 +5177,70 @@
         <v>1.62</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.65</v>
+        <v>8.56</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.76</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="BP11" t="n">
         <v>4</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.65</v>
+        <v>4.56</v>
       </c>
       <c r="BR11" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS11" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT11" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BU11" t="n">
-        <v>23.53</v>
+        <v>27.78</v>
       </c>
       <c r="BV11" t="n">
-        <v>17.65</v>
+        <v>22.22</v>
       </c>
       <c r="BW11" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX11" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.7</v>
+        <v>4.91</v>
       </c>
       <c r="CB11" t="n">
-        <v>5.17</v>
+        <v>5.49</v>
       </c>
       <c r="CC11" t="n">
         <v>1.84</v>
@@ -5249,43 +5249,43 @@
         <v>1.8</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="CM11" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.97</v>
+        <v>2.91</v>
       </c>
       <c r="CR11" t="n">
         <v>1.37</v>
@@ -5300,106 +5300,106 @@
         <v>1.5</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="DB11" t="n">
         <v>1.25</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.02</v>
+        <v>2.96</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="DH11" t="n">
-        <v>111.24</v>
+        <v>110.33</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="DK11" t="n">
         <v>6</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DM11" t="n">
-        <v>58.24</v>
+        <v>59.5</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.94</v>
+        <v>11.67</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13.29</v>
+        <v>13</v>
       </c>
       <c r="DR11" t="n">
-        <v>4.3</v>
+        <v>4.22</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>62.65</v>
+        <v>62.72</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX11" t="n">
-        <v>15.47</v>
+        <v>15.33</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.94</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.53</v>
+        <v>5.55</v>
       </c>
       <c r="EA11" t="n">
-        <v>23.82</v>
+        <v>23.95</v>
       </c>
       <c r="EB11" t="n">
         <v>1.79</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="12">
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
         <v>9</v>
@@ -5421,82 +5421,82 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="G12" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="H12" t="n">
-        <v>79.67</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="J12" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="K12" t="n">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>35.89</v>
+        <v>35.4</v>
       </c>
       <c r="N12" t="n">
         <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="P12" t="n">
         <v>12</v>
       </c>
       <c r="Q12" t="n">
-        <v>12.22</v>
+        <v>12.9</v>
       </c>
       <c r="R12" t="n">
-        <v>9.109999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="S12" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="T12" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="V12" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>45.67</v>
+        <v>44.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>8.220000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>6.22</v>
+        <v>5.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>17.22</v>
+        <v>17.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5580,70 +5580,70 @@
         <v>2.78</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.779999999999999</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.44</v>
+        <v>4.26</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.28</v>
+        <v>4.32</v>
       </c>
       <c r="BR12" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS12" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BT12" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BU12" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV12" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW12" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX12" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BY12" t="n">
-        <v>5.82</v>
+        <v>5.67</v>
       </c>
       <c r="BZ12" t="n">
-        <v>6.01</v>
+        <v>5.97</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.94</v>
+        <v>3.9</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.21</v>
+        <v>4.17</v>
       </c>
       <c r="CC12" t="n">
         <v>6.41</v>
@@ -5655,28 +5655,28 @@
         <v>1.43</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CI12" t="n">
         <v>1.7</v>
       </c>
       <c r="CJ12" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CK12" t="n">
         <v>1.88</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CN12" t="n">
         <v>1.51</v>
@@ -5685,10 +5685,10 @@
         <v>1.34</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.67</v>
+        <v>3.74</v>
       </c>
       <c r="CR12" t="n">
         <v>1.42</v>
@@ -5703,19 +5703,19 @@
         <v>1.41</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CY12" t="n">
         <v>2.37</v>
       </c>
       <c r="CZ12" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DA12" t="n">
         <v>1.56</v>
@@ -5724,85 +5724,85 @@
         <v>1.35</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.74</v>
+        <v>3.79</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="DH12" t="n">
-        <v>75.61</v>
+        <v>75.95</v>
       </c>
       <c r="DI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="DK12" t="n">
-        <v>3.44</v>
+        <v>3.32</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DM12" t="n">
-        <v>34.06</v>
+        <v>33.89</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.06</v>
+        <v>13</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.77</v>
+        <v>13.1</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.06</v>
+        <v>9.26</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>43.22</v>
+        <v>42.79</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="DX12" t="n">
-        <v>8.44</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="DY12" t="n">
-        <v>6</v>
+        <v>5.69</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="EA12" t="n">
-        <v>17</v>
+        <v>17.32</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="13">
@@ -5812,94 +5812,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
         <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="F13" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="G13" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="H13" t="n">
-        <v>94.25</v>
+        <v>94.67</v>
       </c>
       <c r="I13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J13" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="K13" t="n">
-        <v>5.5</v>
+        <v>5.33</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="M13" t="n">
-        <v>54.62</v>
+        <v>62.33</v>
       </c>
       <c r="N13" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="P13" t="n">
-        <v>16.38</v>
+        <v>16.11</v>
       </c>
       <c r="Q13" t="n">
-        <v>15.25</v>
+        <v>16.22</v>
       </c>
       <c r="R13" t="n">
-        <v>5.12</v>
+        <v>4.89</v>
       </c>
       <c r="S13" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="T13" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="U13" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="V13" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>51.62</v>
+        <v>52</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z13" t="n">
-        <v>13.5</v>
+        <v>13.56</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.880000000000001</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.62</v>
+        <v>4.78</v>
       </c>
       <c r="AC13" t="n">
-        <v>22.5</v>
+        <v>22.44</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AF13" t="n">
         <v>0.11</v>
@@ -5983,70 +5983,70 @@
         <v>2.22</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="BH13" t="n">
-        <v>7.71</v>
+        <v>7.78</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.88</v>
+        <v>4.06</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3.71</v>
+        <v>3.61</v>
       </c>
       <c r="BR13" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS13" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT13" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BU13" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV13" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.14</v>
+        <v>4.19</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.53</v>
+        <v>4.52</v>
       </c>
       <c r="CC13" t="n">
         <v>2.12</v>
@@ -6061,28 +6061,28 @@
         <v>2.75</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="CH13" t="n">
         <v>1.42</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CK13" t="n">
         <v>1.66</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="CM13" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CO13" t="n">
         <v>1.28</v>
@@ -6106,106 +6106,106 @@
         <v>1.43</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="DB13" t="n">
         <v>1.33</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.54</v>
+        <v>3.57</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="DH13" t="n">
-        <v>100.06</v>
+        <v>99.94</v>
       </c>
       <c r="DI13" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.88</v>
+        <v>4.83</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DM13" t="n">
-        <v>53.35</v>
+        <v>57.28</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="DP13" t="n">
-        <v>15.12</v>
+        <v>15.06</v>
       </c>
       <c r="DQ13" t="n">
-        <v>14.94</v>
+        <v>15.44</v>
       </c>
       <c r="DR13" t="n">
-        <v>5.76</v>
+        <v>5.61</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>55.7</v>
+        <v>55.66</v>
       </c>
       <c r="DW13" t="n">
         <v>0.11</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.76</v>
+        <v>12.84</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.359999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.41</v>
+        <v>4.5</v>
       </c>
       <c r="EA13" t="n">
-        <v>23</v>
+        <v>22.94</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C14" t="n">
         <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6308,136 +6308,136 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AH14" t="n">
         <v>1</v>
       </c>
       <c r="AI14" t="n">
-        <v>55.67</v>
+        <v>54</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="AK14" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AN14" t="n">
-        <v>22.22</v>
+        <v>24.1</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AQ14" t="n">
-        <v>13.33</v>
+        <v>12.8</v>
       </c>
       <c r="AR14" t="n">
-        <v>11.11</v>
+        <v>10.7</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.67</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>34.44</v>
+        <v>34.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.78</v>
+        <v>5.7</v>
       </c>
       <c r="BB14" t="n">
         <v>4</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="BD14" t="n">
-        <v>15.44</v>
+        <v>16.1</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.22</v>
+        <v>2.9</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.06</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.78</v>
+        <v>0.95</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.39</v>
+        <v>4.37</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.61</v>
+        <v>4.53</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BU14" t="n">
-        <v>16.67</v>
+        <v>21.05</v>
       </c>
       <c r="BV14" t="n">
-        <v>16.67</v>
+        <v>21.05</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX14" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="BY14" t="n">
         <v>4.57</v>
@@ -6446,55 +6446,55 @@
         <v>5.19</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.35</v>
+        <v>4.57</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.95</v>
+        <v>5.27</v>
       </c>
       <c r="CC14" t="n">
-        <v>8.789999999999999</v>
+        <v>10.81</v>
       </c>
       <c r="CD14" t="n">
-        <v>12.4</v>
+        <v>13.7</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.98</v>
+        <v>3.04</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CI14" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="CK14" t="n">
         <v>1.78</v>
       </c>
-      <c r="CJ14" t="n">
-        <v>2</v>
-      </c>
-      <c r="CK14" t="n">
-        <v>1.8</v>
-      </c>
       <c r="CL14" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CM14" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.23</v>
+        <v>3.17</v>
       </c>
       <c r="CR14" t="n">
         <v>1.41</v>
@@ -6509,106 +6509,106 @@
         <v>1.48</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="CZ14" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.37</v>
+        <v>3.3</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="DG14" t="n">
         <v>1.16</v>
       </c>
       <c r="DH14" t="n">
-        <v>69.5</v>
+        <v>67.89</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.44</v>
+        <v>3.26</v>
       </c>
       <c r="DK14" t="n">
-        <v>2.44</v>
+        <v>2.37</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DM14" t="n">
-        <v>28.89</v>
+        <v>29.53</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="DO14" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="DP14" t="n">
-        <v>15.11</v>
+        <v>14.74</v>
       </c>
       <c r="DQ14" t="n">
-        <v>12.5</v>
+        <v>12.21</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.279999999999999</v>
+        <v>8.42</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>39.06</v>
+        <v>38.9</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="DX14" t="n">
-        <v>8.56</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="DY14" t="n">
-        <v>6.44</v>
+        <v>6.32</v>
       </c>
       <c r="DZ14" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="EA14" t="n">
-        <v>18.11</v>
+        <v>18.32</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.78</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="15">
@@ -6618,94 +6618,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
         <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F15" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="G15" t="n">
-        <v>2.38</v>
+        <v>2.89</v>
       </c>
       <c r="H15" t="n">
-        <v>69.25</v>
+        <v>69.78</v>
       </c>
       <c r="I15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J15" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="K15" t="n">
-        <v>4.88</v>
+        <v>5.11</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="M15" t="n">
-        <v>30.38</v>
+        <v>30.11</v>
       </c>
       <c r="N15" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="O15" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="P15" t="n">
-        <v>14</v>
+        <v>14.11</v>
       </c>
       <c r="Q15" t="n">
-        <v>16.38</v>
+        <v>17</v>
       </c>
       <c r="R15" t="n">
-        <v>8</v>
+        <v>8.56</v>
       </c>
       <c r="S15" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="U15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>49.5</v>
+        <v>50</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="Z15" t="n">
-        <v>13</v>
+        <v>12.89</v>
       </c>
       <c r="AA15" t="n">
-        <v>9.119999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.88</v>
+        <v>3.67</v>
       </c>
       <c r="AC15" t="n">
-        <v>20.75</v>
+        <v>21.22</v>
       </c>
       <c r="AD15" t="n">
         <v>1.1</v>
       </c>
       <c r="AE15" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AF15" t="n">
         <v>0.1</v>
@@ -6789,70 +6789,70 @@
         <v>3.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.17</v>
+        <v>9.26</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.78</v>
+        <v>3.68</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.33</v>
+        <v>5.53</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT15" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BU15" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BV15" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX15" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BY15" t="n">
-        <v>3.95</v>
+        <v>3.73</v>
       </c>
       <c r="BZ15" t="n">
-        <v>4.1</v>
+        <v>3.89</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.87</v>
+        <v>3.82</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="CC15" t="n">
         <v>6.76</v>
@@ -6861,55 +6861,55 @@
         <v>7.12</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="CH15" t="n">
         <v>1.39</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CJ15" t="n">
         <v>2.01</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="CM15" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CN15" t="n">
         <v>1.52</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.45</v>
+        <v>3.48</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CV15" t="n">
         <v>1.83</v>
@@ -6918,67 +6918,67 @@
         <v>2.06</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CY15" t="n">
         <v>2.35</v>
       </c>
       <c r="CZ15" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="DA15" t="n">
         <v>1.57</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF15" t="n">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="DH15" t="n">
-        <v>75.22</v>
+        <v>75.16</v>
       </c>
       <c r="DI15" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.61</v>
+        <v>3.79</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="DM15" t="n">
-        <v>32.67</v>
+        <v>32.42</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="DP15" t="n">
-        <v>15.28</v>
+        <v>15.26</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.45</v>
+        <v>15.79</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.06</v>
+        <v>8.32</v>
       </c>
       <c r="DS15" t="n">
         <v>0.05</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>47.28</v>
+        <v>47.63</v>
       </c>
       <c r="DW15" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DX15" t="n">
-        <v>11.06</v>
+        <v>11.11</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.22</v>
+        <v>7.37</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.84</v>
+        <v>3.74</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.67</v>
+        <v>20.89</v>
       </c>
       <c r="EB15" t="n">
         <v>1.11</v>
       </c>
       <c r="EC15" t="n">
-        <v>3.22</v>
+        <v>3.11</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -2185,61 +2185,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
         <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F4" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="G4" t="n">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="H4" t="n">
-        <v>78.12</v>
+        <v>75.33</v>
       </c>
       <c r="I4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J4" t="n">
-        <v>3.88</v>
+        <v>3.56</v>
       </c>
       <c r="K4" t="n">
-        <v>5.38</v>
+        <v>4.78</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="M4" t="n">
-        <v>43.12</v>
+        <v>39.89</v>
       </c>
       <c r="N4" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="O4" t="n">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="P4" t="n">
-        <v>12</v>
+        <v>12.22</v>
       </c>
       <c r="Q4" t="n">
-        <v>15</v>
+        <v>15.44</v>
       </c>
       <c r="R4" t="n">
-        <v>7.75</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2251,28 +2251,28 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>46.25</v>
+        <v>45.22</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z4" t="n">
-        <v>10.12</v>
+        <v>9.33</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.12</v>
+        <v>5.56</v>
       </c>
       <c r="AB4" t="n">
-        <v>4</v>
+        <v>3.78</v>
       </c>
       <c r="AC4" t="n">
-        <v>22.12</v>
+        <v>22.67</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AE4" t="n">
-        <v>3.62</v>
+        <v>3.33</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,70 +2356,70 @@
         <v>3.3</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.779999999999999</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.39</v>
+        <v>0.47</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.11</v>
+        <v>4.95</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.67</v>
+        <v>4.68</v>
       </c>
       <c r="BR4" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS4" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT4" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BU4" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV4" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW4" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX4" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.12</v>
+        <v>3.99</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.61</v>
+        <v>4.83</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.65</v>
+        <v>3.71</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.86</v>
+        <v>3.97</v>
       </c>
       <c r="CC4" t="n">
         <v>6.35</v>
@@ -2431,25 +2431,25 @@
         <v>1.42</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="CH4" t="n">
         <v>1.37</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="CM4" t="n">
         <v>1.93</v>
@@ -2461,10 +2461,10 @@
         <v>1.32</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.56</v>
+        <v>3.53</v>
       </c>
       <c r="CR4" t="n">
         <v>1.42</v>
@@ -2473,22 +2473,22 @@
         <v>2.99</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="CU4" t="n">
         <v>1.39</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="CX4" t="n">
         <v>1.85</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CZ4" t="n">
         <v>1.96</v>
@@ -2500,85 +2500,85 @@
         <v>1.34</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.74</v>
+        <v>3.73</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="DH4" t="n">
-        <v>78.5</v>
+        <v>77.16</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.67</v>
+        <v>3.53</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.84</v>
+        <v>4.58</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="DM4" t="n">
-        <v>37.44</v>
+        <v>36.21</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.83</v>
+        <v>13.84</v>
       </c>
       <c r="DQ4" t="n">
-        <v>16.06</v>
+        <v>16.21</v>
       </c>
       <c r="DR4" t="n">
-        <v>8</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>45.17</v>
+        <v>44.74</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX4" t="n">
-        <v>9.779999999999999</v>
+        <v>9.42</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.16</v>
+        <v>5.9</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.61</v>
+        <v>3.53</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.28</v>
+        <v>20.63</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="EC4" t="n">
-        <v>3.44</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="5">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4693,139 +4693,139 @@
         <v>0.78</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="AI10" t="n">
-        <v>114.33</v>
+        <v>116.9</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AL10" t="n">
-        <v>5.67</v>
+        <v>5.8</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AN10" t="n">
-        <v>60</v>
+        <v>60.2</v>
       </c>
       <c r="AO10" t="n">
         <v>1</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>15.56</v>
+        <v>15.8</v>
       </c>
       <c r="AR10" t="n">
-        <v>12.44</v>
+        <v>12.7</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.78</v>
+        <v>4.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>57.89</v>
+        <v>58.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA10" t="n">
-        <v>13.67</v>
+        <v>14.3</v>
       </c>
       <c r="BB10" t="n">
-        <v>8.56</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.11</v>
+        <v>5.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>25.89</v>
+        <v>26.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="BF10" t="n">
         <v>2</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.94</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.33</v>
+        <v>0.42</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.72</v>
+        <v>4.58</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.17</v>
+        <v>5.16</v>
       </c>
       <c r="BR10" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS10" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BU10" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BV10" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BY10" t="n">
         <v>1.24</v>
@@ -4834,40 +4834,40 @@
         <v>1.24</v>
       </c>
       <c r="CA10" t="n">
-        <v>5.38</v>
+        <v>5.35</v>
       </c>
       <c r="CB10" t="n">
         <v>6.03</v>
       </c>
       <c r="CC10" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="CD10" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="CE10" t="n">
         <v>1.33</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CJ10" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="CM10" t="n">
         <v>1.89</v>
@@ -4888,7 +4888,7 @@
         <v>1.38</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CT10" t="n">
         <v>3.02</v>
@@ -4897,10 +4897,10 @@
         <v>1.5</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="CX10" t="n">
         <v>1.84</v>
@@ -4918,85 +4918,85 @@
         <v>1.26</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.04</v>
+        <v>3.07</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="DG10" t="n">
-        <v>3.56</v>
+        <v>3.63</v>
       </c>
       <c r="DH10" t="n">
-        <v>122.28</v>
+        <v>123.21</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="DK10" t="n">
-        <v>7.67</v>
+        <v>7.63</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="DM10" t="n">
-        <v>67.39</v>
+        <v>67.11</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="DO10" t="n">
-        <v>4.06</v>
+        <v>3.95</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.06</v>
+        <v>13.32</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.56</v>
+        <v>12.69</v>
       </c>
       <c r="DR10" t="n">
-        <v>4.5</v>
+        <v>4.42</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>60.78</v>
+        <v>60.9</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX10" t="n">
-        <v>17.83</v>
+        <v>17.95</v>
       </c>
       <c r="DY10" t="n">
-        <v>12</v>
+        <v>11.95</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.84</v>
+        <v>6</v>
       </c>
       <c r="EA10" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
       <c r="EB10" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="11">
@@ -5051,7 +5051,7 @@
         <v>10.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="R11" t="n">
         <v>3.7</v>
@@ -5363,7 +5363,7 @@
         <v>11.67</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13</v>
+        <v>13.06</v>
       </c>
       <c r="DR11" t="n">
         <v>4.22</v>
@@ -6338,7 +6338,7 @@
         <v>1</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="AR14" t="n">
         <v>10.7</v>
@@ -6569,7 +6569,7 @@
         <v>1.21</v>
       </c>
       <c r="DP14" t="n">
-        <v>14.74</v>
+        <v>14.79</v>
       </c>
       <c r="DQ14" t="n">
         <v>12.21</v>

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
         <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F4" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="G4" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="H4" t="n">
-        <v>75.33</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J4" t="n">
-        <v>3.56</v>
+        <v>3.3</v>
       </c>
       <c r="K4" t="n">
-        <v>4.78</v>
+        <v>5.4</v>
       </c>
       <c r="L4" t="n">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="M4" t="n">
-        <v>39.89</v>
+        <v>42</v>
       </c>
       <c r="N4" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="O4" t="n">
-        <v>2.44</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>12.22</v>
+        <v>12</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.44</v>
+        <v>15.7</v>
       </c>
       <c r="R4" t="n">
-        <v>8.220000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>45.22</v>
+        <v>45.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.33</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.56</v>
+        <v>5.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>22.67</v>
+        <v>23.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE4" t="n">
-        <v>3.33</v>
+        <v>3.1</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,70 +2356,70 @@
         <v>3.3</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.630000000000001</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.95</v>
+        <v>5.15</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.68</v>
+        <v>4.8</v>
       </c>
       <c r="BR4" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS4" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT4" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BU4" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BV4" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW4" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX4" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.99</v>
+        <v>3.75</v>
       </c>
       <c r="BZ4" t="n">
-        <v>4.83</v>
+        <v>4.53</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.97</v>
+        <v>3.95</v>
       </c>
       <c r="CC4" t="n">
         <v>6.35</v>
@@ -2431,10 +2431,10 @@
         <v>1.42</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CH4" t="n">
         <v>1.37</v>
@@ -2449,28 +2449,28 @@
         <v>1.84</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CM4" t="n">
         <v>1.93</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CO4" t="n">
         <v>1.32</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.53</v>
+        <v>3.54</v>
       </c>
       <c r="CR4" t="n">
         <v>1.42</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="CT4" t="n">
         <v>2.87</v>
@@ -2482,7 +2482,7 @@
         <v>1.82</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CX4" t="n">
         <v>1.85</v>
@@ -2500,85 +2500,85 @@
         <v>1.34</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="DE4" t="n">
         <v>0.1</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="DH4" t="n">
-        <v>77.16</v>
+        <v>78.84999999999999</v>
       </c>
       <c r="DI4" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.53</v>
+        <v>3.4</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.58</v>
+        <v>4.9</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.37</v>
+        <v>0.55</v>
       </c>
       <c r="DM4" t="n">
-        <v>36.21</v>
+        <v>37.45</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.84</v>
+        <v>13.65</v>
       </c>
       <c r="DQ4" t="n">
-        <v>16.21</v>
+        <v>16.3</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.210000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>44.74</v>
+        <v>44.85</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX4" t="n">
-        <v>9.42</v>
+        <v>9.4</v>
       </c>
       <c r="DY4" t="n">
-        <v>5.9</v>
+        <v>5.95</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.53</v>
+        <v>3.45</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.63</v>
+        <v>20.95</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="EC4" t="n">
-        <v>3.31</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
         <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2678,52 +2678,52 @@
         <v>2.3</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG5" t="n">
         <v>2</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AI5" t="n">
-        <v>72</v>
+        <v>73.7</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="AN5" t="n">
-        <v>30.89</v>
+        <v>31.4</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AP5" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>16.89</v>
+        <v>16.9</v>
       </c>
       <c r="AR5" t="n">
-        <v>14.33</v>
+        <v>14.1</v>
       </c>
       <c r="AS5" t="n">
-        <v>10.56</v>
+        <v>10.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -2735,82 +2735,82 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>45.22</v>
+        <v>45.7</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.33</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.78</v>
+        <v>5.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="BD5" t="n">
-        <v>20.67</v>
+        <v>20.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="BH5" t="n">
         <v>8.050000000000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.21</v>
+        <v>4.2</v>
       </c>
       <c r="BR5" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS5" t="n">
-        <v>68.42</v>
+        <v>65</v>
       </c>
       <c r="BT5" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BU5" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BV5" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BY5" t="n">
         <v>3.76</v>
@@ -2819,25 +2819,25 @@
         <v>4.13</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.93</v>
+        <v>3.88</v>
       </c>
       <c r="CC5" t="n">
-        <v>6.03</v>
+        <v>5.71</v>
       </c>
       <c r="CD5" t="n">
-        <v>7.23</v>
+        <v>6.78</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="CH5" t="n">
         <v>1.37</v>
@@ -2846,10 +2846,10 @@
         <v>1.75</v>
       </c>
       <c r="CJ5" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CL5" t="n">
         <v>2.59</v>
@@ -2861,13 +2861,13 @@
         <v>1.49</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="CR5" t="n">
         <v>1.43</v>
@@ -2882,16 +2882,16 @@
         <v>1.4</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CW5" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CZ5" t="n">
         <v>1.85</v>
@@ -2900,88 +2900,88 @@
         <v>1.52</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.86</v>
+        <v>3.89</v>
       </c>
       <c r="DE5" t="n">
         <v>0.1</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="DH5" t="n">
-        <v>81.11</v>
+        <v>81.5</v>
       </c>
       <c r="DI5" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.63</v>
+        <v>3.65</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.37</v>
+        <v>0.45</v>
       </c>
       <c r="DM5" t="n">
-        <v>37.9</v>
+        <v>37.8</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="DP5" t="n">
-        <v>15.68</v>
+        <v>15.75</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.74</v>
+        <v>14.6</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>49.68</v>
+        <v>49.7</v>
       </c>
       <c r="DW5" t="n">
         <v>0.05</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.21</v>
+        <v>10.05</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.47</v>
+        <v>7.25</v>
       </c>
       <c r="DZ5" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="EA5" t="n">
-        <v>22.74</v>
+        <v>22.6</v>
       </c>
       <c r="EB5" t="n">
         <v>1.11</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="6">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
         <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F6" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="H6" t="n">
-        <v>81</v>
+        <v>81.44</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>4.12</v>
+        <v>3.67</v>
       </c>
       <c r="K6" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="L6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="M6" t="n">
-        <v>42.38</v>
+        <v>42.78</v>
       </c>
       <c r="N6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P6" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>14.11</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="AD6" t="n">
         <v>1.5</v>
       </c>
-      <c r="O6" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="P6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>15.25</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7.62</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>43.75</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>15.75</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AE6" t="n">
-        <v>3.25</v>
+        <v>2.89</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,70 +3162,70 @@
         <v>4.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.06</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BL6" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="BP6" t="n">
-        <v>5.67</v>
+        <v>5.58</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="BR6" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>88.89</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BU6" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BV6" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>72.22</v>
+        <v>68.42</v>
       </c>
       <c r="BY6" t="n">
-        <v>4.44</v>
+        <v>4.23</v>
       </c>
       <c r="BZ6" t="n">
-        <v>4.56</v>
+        <v>4.38</v>
       </c>
       <c r="CA6" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.98</v>
+        <v>3.93</v>
       </c>
       <c r="CC6" t="n">
         <v>5.62</v>
@@ -3234,16 +3234,16 @@
         <v>5.25</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CI6" t="n">
         <v>1.79</v>
@@ -3252,25 +3252,25 @@
         <v>1.95</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CM6" t="n">
         <v>1.79</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CO6" t="n">
         <v>1.31</v>
       </c>
       <c r="CP6" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.52</v>
+        <v>3.57</v>
       </c>
       <c r="CR6" t="n">
         <v>1.45</v>
@@ -3288,103 +3288,103 @@
         <v>1.83</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CX6" t="n">
         <v>1.89</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CZ6" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="DB6" t="n">
         <v>1.35</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.73</v>
+        <v>3.76</v>
       </c>
       <c r="DE6" t="n">
         <v>0.05</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.83</v>
+        <v>2.68</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="DH6" t="n">
-        <v>79.39</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ6" t="n">
-        <v>4.5</v>
+        <v>4.26</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.39</v>
+        <v>4.37</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="DM6" t="n">
-        <v>40.84</v>
+        <v>41.11</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.78</v>
+        <v>2.63</v>
       </c>
       <c r="DP6" t="n">
-        <v>17.89</v>
+        <v>17.58</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14.17</v>
+        <v>14.31</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.220000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>45.78</v>
+        <v>46</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.94</v>
+        <v>13.79</v>
       </c>
       <c r="DY6" t="n">
         <v>9</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.94</v>
+        <v>4.79</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.78</v>
+        <v>17.16</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="EC6" t="n">
-        <v>3.94</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="7">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
         <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="G7" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="H7" t="n">
-        <v>84</v>
+        <v>86.09</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>4.09</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="M7" t="n">
-        <v>33.5</v>
+        <v>34</v>
       </c>
       <c r="N7" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="O7" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="P7" t="n">
-        <v>16.7</v>
+        <v>16.64</v>
       </c>
       <c r="Q7" t="n">
-        <v>15.6</v>
+        <v>15.91</v>
       </c>
       <c r="R7" t="n">
-        <v>6.6</v>
+        <v>6.36</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>42.8</v>
+        <v>45.18</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>12.3</v>
+        <v>12.18</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.4</v>
+        <v>4.18</v>
       </c>
       <c r="AC7" t="n">
         <v>18</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE7" t="n">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,70 +3565,70 @@
         <v>3</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.470000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.63</v>
+        <v>0.75</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.47</v>
+        <v>4.5</v>
       </c>
       <c r="BR7" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS7" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT7" t="n">
-        <v>36.84</v>
+        <v>40</v>
       </c>
       <c r="BU7" t="n">
-        <v>15.79</v>
+        <v>20</v>
       </c>
       <c r="BV7" t="n">
-        <v>5.26</v>
+        <v>10</v>
       </c>
       <c r="BW7" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX7" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BY7" t="n">
-        <v>5.02</v>
+        <v>4.71</v>
       </c>
       <c r="BZ7" t="n">
-        <v>5.18</v>
+        <v>4.88</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="CC7" t="n">
         <v>5.4</v>
@@ -3640,19 +3640,19 @@
         <v>1.44</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CK7" t="n">
         <v>1.89</v>
@@ -3670,10 +3670,10 @@
         <v>1.34</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="CR7" t="n">
         <v>1.45</v>
@@ -3688,10 +3688,10 @@
         <v>1.39</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CX7" t="n">
         <v>1.93</v>
@@ -3709,85 +3709,85 @@
         <v>1.38</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.96</v>
+        <v>4.01</v>
       </c>
       <c r="DE7" t="n">
         <v>0.05</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="DH7" t="n">
-        <v>84.31999999999999</v>
+        <v>85.45</v>
       </c>
       <c r="DI7" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.63</v>
+        <v>3.55</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DM7" t="n">
-        <v>32.42</v>
+        <v>32.75</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="DP7" t="n">
-        <v>16.63</v>
+        <v>16.6</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.21</v>
+        <v>14.45</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.31</v>
+        <v>8.1</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>41.63</v>
+        <v>43</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.74</v>
+        <v>11.7</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.58</v>
+        <v>7.65</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.16</v>
+        <v>4.05</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.79</v>
+        <v>17.8</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="8">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
         <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5499,52 +5499,52 @@
         <v>2.1</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AG12" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AI12" t="n">
-        <v>71.56</v>
+        <v>70.5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN12" t="n">
-        <v>32.22</v>
+        <v>30.7</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14.11</v>
+        <v>14.3</v>
       </c>
       <c r="AR12" t="n">
-        <v>13.33</v>
+        <v>13.7</v>
       </c>
       <c r="AS12" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,82 +5556,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>40.78</v>
+        <v>39.8</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="BA12" t="n">
-        <v>8.67</v>
+        <v>8.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.78</v>
+        <v>5.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="BD12" t="n">
-        <v>16.78</v>
+        <v>16.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.630000000000001</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.63</v>
+        <v>0.75</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.26</v>
+        <v>4.15</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.32</v>
+        <v>4.35</v>
       </c>
       <c r="BR12" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS12" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BT12" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BU12" t="n">
-        <v>21.05</v>
+        <v>25</v>
       </c>
       <c r="BV12" t="n">
-        <v>15.79</v>
+        <v>20</v>
       </c>
       <c r="BW12" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX12" t="n">
-        <v>31.58</v>
+        <v>35</v>
       </c>
       <c r="BY12" t="n">
         <v>5.67</v>
@@ -5640,31 +5640,31 @@
         <v>5.97</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.17</v>
+        <v>4.13</v>
       </c>
       <c r="CC12" t="n">
-        <v>6.41</v>
+        <v>6.27</v>
       </c>
       <c r="CD12" t="n">
-        <v>7.99</v>
+        <v>7.68</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="CH12" t="n">
         <v>1.35</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CJ12" t="n">
         <v>2.09</v>
@@ -5685,10 +5685,10 @@
         <v>1.34</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="CR12" t="n">
         <v>1.42</v>
@@ -5706,7 +5706,7 @@
         <v>1.77</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CX12" t="n">
         <v>1.89</v>
@@ -5721,88 +5721,88 @@
         <v>1.56</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.79</v>
+        <v>3.85</v>
       </c>
       <c r="DE12" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="DH12" t="n">
-        <v>75.95</v>
+        <v>75.2</v>
       </c>
       <c r="DI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="DK12" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="DL12" t="n">
         <v>0.1</v>
       </c>
       <c r="DM12" t="n">
-        <v>33.89</v>
+        <v>33.05</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="DP12" t="n">
-        <v>13</v>
+        <v>13.15</v>
       </c>
       <c r="DQ12" t="n">
-        <v>13.1</v>
+        <v>13.3</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.26</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>42.79</v>
+        <v>42.2</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DX12" t="n">
         <v>8.050000000000001</v>
       </c>
       <c r="DY12" t="n">
-        <v>5.69</v>
+        <v>5.55</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="EA12" t="n">
-        <v>17.32</v>
+        <v>17.2</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="13">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C15" t="n">
         <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
         <v>0.11</v>
@@ -6708,52 +6708,52 @@
         <v>3</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="AI15" t="n">
-        <v>80</v>
+        <v>79.73</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AN15" t="n">
-        <v>34.5</v>
+        <v>34.64</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ15" t="n">
-        <v>16.3</v>
+        <v>16.55</v>
       </c>
       <c r="AR15" t="n">
-        <v>14.7</v>
+        <v>14.27</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.1</v>
+        <v>8.27</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6765,82 +6765,82 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>45.5</v>
+        <v>46.18</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.5</v>
+        <v>9.73</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.7</v>
+        <v>6.18</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="BD15" t="n">
-        <v>20.6</v>
+        <v>21.18</v>
       </c>
       <c r="BE15" t="n">
         <v>1.12</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.26</v>
+        <v>9.6</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.68</v>
+        <v>3.95</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.53</v>
+        <v>5.6</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT15" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BU15" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BV15" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX15" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BY15" t="n">
         <v>3.73</v>
@@ -6849,28 +6849,28 @@
         <v>3.89</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="CB15" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="CC15" t="n">
-        <v>6.76</v>
+        <v>6.64</v>
       </c>
       <c r="CD15" t="n">
-        <v>7.12</v>
+        <v>6.96</v>
       </c>
       <c r="CE15" t="n">
         <v>1.4</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CI15" t="n">
         <v>1.79</v>
@@ -6882,7 +6882,7 @@
         <v>1.86</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CM15" t="n">
         <v>1.88</v>
@@ -6894,16 +6894,16 @@
         <v>1.31</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="CR15" t="n">
         <v>1.43</v>
       </c>
       <c r="CS15" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="CT15" t="n">
         <v>2.85</v>
@@ -6933,52 +6933,52 @@
         <v>1.34</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.65</v>
+        <v>3.67</v>
       </c>
       <c r="DE15" t="n">
         <v>0.1</v>
       </c>
       <c r="DF15" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DG15" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="DH15" t="n">
-        <v>75.16</v>
+        <v>75.25</v>
       </c>
       <c r="DI15" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.79</v>
+        <v>3.85</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DM15" t="n">
-        <v>32.42</v>
+        <v>32.6</v>
       </c>
       <c r="DN15" t="n">
         <v>0.9</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="DP15" t="n">
-        <v>15.26</v>
+        <v>15.45</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.79</v>
+        <v>15.5</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.32</v>
+        <v>8.4</v>
       </c>
       <c r="DS15" t="n">
         <v>0.05</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>47.63</v>
+        <v>47.9</v>
       </c>
       <c r="DW15" t="n">
         <v>0.05</v>
       </c>
       <c r="DX15" t="n">
-        <v>11.11</v>
+        <v>11.15</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.37</v>
+        <v>7.55</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.89</v>
+        <v>21.2</v>
       </c>
       <c r="EB15" t="n">
         <v>1.11</v>
       </c>
       <c r="EC15" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="n">
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1469,139 +1469,139 @@
         <v>2.6</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AI2" t="n">
-        <v>87</v>
+        <v>90.7</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AK2" t="n">
         <v>3</v>
       </c>
       <c r="AL2" t="n">
-        <v>5.11</v>
+        <v>5.5</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AN2" t="n">
-        <v>48.89</v>
+        <v>53.2</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="AQ2" t="n">
-        <v>17.11</v>
+        <v>16</v>
       </c>
       <c r="AR2" t="n">
-        <v>13.56</v>
+        <v>13.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>56.44</v>
+        <v>58.8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA2" t="n">
-        <v>13.44</v>
+        <v>14.1</v>
       </c>
       <c r="BB2" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.44</v>
+        <v>4.6</v>
       </c>
       <c r="BD2" t="n">
         <v>20</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.32</v>
+        <v>8.35</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.63</v>
+        <v>0.8</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.89</v>
+        <v>4</v>
       </c>
       <c r="BQ2" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BT2" t="n">
-        <v>31.58</v>
+        <v>35</v>
       </c>
       <c r="BU2" t="n">
-        <v>26.32</v>
+        <v>30</v>
       </c>
       <c r="BV2" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BY2" t="n">
         <v>1.54</v>
@@ -1610,40 +1610,40 @@
         <v>1.55</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.53</v>
+        <v>4.59</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.92</v>
+        <v>5</v>
       </c>
       <c r="CC2" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="CH2" t="n">
         <v>1.44</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CM2" t="n">
         <v>1.96</v>
@@ -1652,19 +1652,19 @@
         <v>1.58</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="CR2" t="n">
         <v>1.38</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CT2" t="n">
         <v>3.04</v>
@@ -1676,7 +1676,7 @@
         <v>1.76</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="CX2" t="n">
         <v>1.81</v>
@@ -1688,91 +1688,91 @@
         <v>2.01</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="DB2" t="n">
         <v>1.28</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="DE2" t="n">
         <v>0.05</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="DH2" t="n">
-        <v>92.26000000000001</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.26</v>
+        <v>5.45</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="DM2" t="n">
-        <v>54.47</v>
+        <v>56.35</v>
       </c>
       <c r="DN2" t="n">
         <v>1</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.69</v>
+        <v>2.85</v>
       </c>
       <c r="DP2" t="n">
-        <v>16.32</v>
+        <v>15.8</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.63</v>
+        <v>13.45</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.47</v>
+        <v>6.2</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>57.21</v>
+        <v>58.35</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX2" t="n">
-        <v>15.05</v>
+        <v>15.3</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.21</v>
+        <v>10.4</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.84</v>
+        <v>4.9</v>
       </c>
       <c r="EA2" t="n">
-        <v>20.58</v>
+        <v>20.55</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
         <v>10</v>
@@ -1794,49 +1794,49 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="G3" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="H3" t="n">
-        <v>97.44</v>
+        <v>95.5</v>
       </c>
       <c r="I3" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="J3" t="n">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>5.78</v>
+        <v>5.6</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="M3" t="n">
-        <v>46.22</v>
+        <v>46.8</v>
       </c>
       <c r="N3" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="O3" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="P3" t="n">
-        <v>14.11</v>
+        <v>13.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>15.78</v>
+        <v>15.2</v>
       </c>
       <c r="R3" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="S3" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>53.67</v>
+        <v>52.2</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>14.89</v>
+        <v>14.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>10.56</v>
+        <v>10.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>20.89</v>
+        <v>20.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="AF3" t="n">
         <v>0.1</v>
@@ -1953,49 +1953,49 @@
         <v>2</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.369999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BP3" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.89</v>
+        <v>5.9</v>
       </c>
       <c r="BR3" t="n">
-        <v>89.47</v>
+        <v>85</v>
       </c>
       <c r="BS3" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BT3" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BU3" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BV3" t="n">
         <v>0</v>
@@ -2004,19 +2004,19 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.64</v>
+        <v>2.81</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.71</v>
+        <v>2.86</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.64</v>
+        <v>3.61</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.82</v>
+        <v>3.79</v>
       </c>
       <c r="CC3" t="n">
         <v>3.77</v>
@@ -2025,13 +2025,13 @@
         <v>4.66</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF3" t="n">
         <v>3</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CH3" t="n">
         <v>1.35</v>
@@ -2043,16 +2043,16 @@
         <v>2.02</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CO3" t="n">
         <v>1.35</v>
@@ -2067,13 +2067,13 @@
         <v>1.44</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.04</v>
+        <v>3.07</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CV3" t="n">
         <v>1.78</v>
@@ -2082,7 +2082,7 @@
         <v>2.1</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CY3" t="n">
         <v>2.39</v>
@@ -2097,52 +2097,52 @@
         <v>1.38</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.99</v>
+        <v>4.01</v>
       </c>
       <c r="DE3" t="n">
         <v>0.05</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="DH3" t="n">
-        <v>91.42</v>
+        <v>90.75</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.21</v>
+        <v>5.15</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DM3" t="n">
-        <v>42.95</v>
+        <v>43.4</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="DP3" t="n">
-        <v>15.47</v>
+        <v>15.3</v>
       </c>
       <c r="DQ3" t="n">
-        <v>15</v>
+        <v>14.75</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.63</v>
+        <v>6.95</v>
       </c>
       <c r="DS3" t="n">
         <v>0.05</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>51.95</v>
+        <v>51.3</v>
       </c>
       <c r="DW3" t="n">
         <v>0.1</v>
       </c>
       <c r="DX3" t="n">
-        <v>13</v>
+        <v>12.75</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.050000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.79</v>
+        <v>19.85</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="4">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
         <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
         <v>0.4</v>
@@ -3887,139 +3887,139 @@
         <v>1.2</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>90.11</v>
+        <v>92.8</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="AL8" t="n">
-        <v>5.67</v>
+        <v>5.7</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AN8" t="n">
-        <v>40.89</v>
+        <v>42.3</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12.56</v>
+        <v>12.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>15.22</v>
+        <v>15.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.11</v>
+        <v>6.9</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>54.89</v>
+        <v>55.8</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>10.67</v>
+        <v>10.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.44</v>
+        <v>6.3</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="BD8" t="n">
-        <v>21.11</v>
+        <v>20.5</v>
       </c>
       <c r="BE8" t="n">
         <v>1.27</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.63</v>
+        <v>3.7</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.58</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.63</v>
+        <v>3.7</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BL8" t="n">
         <v>1.05</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BN8" t="n">
         <v>1.95</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="BP8" t="n">
-        <v>5.11</v>
+        <v>5.15</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.47</v>
+        <v>4.4</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
       </c>
       <c r="BS8" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BT8" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BU8" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BV8" t="n">
-        <v>26.32</v>
+        <v>30</v>
       </c>
       <c r="BW8" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX8" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BY8" t="n">
         <v>2.31</v>
@@ -4028,16 +4028,16 @@
         <v>2.33</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.72</v>
+        <v>3.68</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.91</v>
+        <v>3.87</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.2</v>
+        <v>4.02</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.16</v>
+        <v>3.99</v>
       </c>
       <c r="CE8" t="n">
         <v>1.39</v>
@@ -4046,7 +4046,7 @@
         <v>2.91</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="CH8" t="n">
         <v>1.38</v>
@@ -4055,19 +4055,19 @@
         <v>1.8</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CM8" t="n">
         <v>1.9</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CO8" t="n">
         <v>1.3</v>
@@ -4082,31 +4082,31 @@
         <v>1.41</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CU8" t="n">
         <v>1.39</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CX8" t="n">
         <v>1.86</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CZ8" t="n">
         <v>1.95</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="DB8" t="n">
         <v>1.34</v>
@@ -4115,82 +4115,82 @@
         <v>2.06</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.61</v>
+        <v>3.62</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="DH8" t="n">
-        <v>94.53</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.21</v>
+        <v>5.25</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="DM8" t="n">
-        <v>41.58</v>
+        <v>42.25</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="DP8" t="n">
-        <v>12.42</v>
+        <v>12.35</v>
       </c>
       <c r="DQ8" t="n">
-        <v>16.05</v>
+        <v>16.1</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.89</v>
+        <v>6.8</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>57.9</v>
+        <v>58.2</v>
       </c>
       <c r="DW8" t="n">
         <v>0.05</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.79</v>
+        <v>12.6</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.68</v>
+        <v>7.55</v>
       </c>
       <c r="DZ8" t="n">
-        <v>5.1</v>
+        <v>5.05</v>
       </c>
       <c r="EA8" t="n">
-        <v>22.16</v>
+        <v>21.8</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9">
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
         <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F9" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="H9" t="n">
-        <v>77.89</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="J9" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="K9" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="L9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="M9" t="n">
-        <v>27.67</v>
+        <v>27.8</v>
       </c>
       <c r="N9" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="O9" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="P9" t="n">
-        <v>15.67</v>
+        <v>15.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>16.33</v>
+        <v>16.1</v>
       </c>
       <c r="R9" t="n">
-        <v>10.44</v>
+        <v>10.1</v>
       </c>
       <c r="S9" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="T9" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="U9" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="V9" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>45.11</v>
+        <v>44.2</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.11</v>
+        <v>10.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.78</v>
+        <v>6.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>17.78</v>
+        <v>17.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AF9" t="n">
         <v>0.22</v>
@@ -4371,70 +4371,70 @@
         <v>2.78</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.779999999999999</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BL9" t="n">
         <v>1</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.61</v>
+        <v>4.68</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.11</v>
+        <v>4.05</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT9" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BU9" t="n">
-        <v>27.78</v>
+        <v>31.58</v>
       </c>
       <c r="BV9" t="n">
-        <v>5.56</v>
+        <v>10.53</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX9" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.61</v>
+        <v>3.58</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.26</v>
+        <v>4.19</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.58</v>
+        <v>4.5</v>
       </c>
       <c r="CC9" t="n">
         <v>8.02</v>
@@ -4446,10 +4446,10 @@
         <v>1.37</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.06</v>
+        <v>3.03</v>
       </c>
       <c r="CH9" t="n">
         <v>1.44</v>
@@ -4458,13 +4458,13 @@
         <v>1.9</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CK9" t="n">
         <v>1.73</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CM9" t="n">
         <v>2.03</v>
@@ -4476,34 +4476,34 @@
         <v>1.26</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="CR9" t="n">
         <v>1.4</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CV9" t="n">
         <v>1.93</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.1</v>
@@ -4515,85 +4515,85 @@
         <v>1.29</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.28</v>
+        <v>3.31</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="DH9" t="n">
-        <v>71.5</v>
+        <v>71.84</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="DK9" t="n">
         <v>3</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DM9" t="n">
-        <v>26.06</v>
+        <v>26.21</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.89</v>
+        <v>14.1</v>
       </c>
       <c r="DQ9" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.720000000000001</v>
+        <v>9.58</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>42.89</v>
+        <v>42.53</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DX9" t="n">
-        <v>9</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.72</v>
+        <v>5.74</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.28</v>
+        <v>3.37</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.06</v>
+        <v>16.05</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.99</v>
+        <v>1.01</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="10">
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
         <v>10</v>
@@ -4615,82 +4615,82 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="G10" t="n">
-        <v>3.89</v>
+        <v>3.6</v>
       </c>
       <c r="H10" t="n">
-        <v>130.22</v>
+        <v>133.1</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>9.67</v>
+        <v>9</v>
       </c>
       <c r="L10" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="M10" t="n">
-        <v>74.78</v>
+        <v>75.2</v>
       </c>
       <c r="N10" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="O10" t="n">
-        <v>5.67</v>
+        <v>5.3</v>
       </c>
       <c r="P10" t="n">
-        <v>10.56</v>
+        <v>11</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.67</v>
+        <v>12.8</v>
       </c>
       <c r="R10" t="n">
-        <v>4.22</v>
+        <v>4.5</v>
       </c>
       <c r="S10" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="T10" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="U10" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="V10" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>63.67</v>
+        <v>64.3</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>22</v>
+        <v>21.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>15.44</v>
+        <v>15.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>6.56</v>
+        <v>6.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>26.33</v>
+        <v>26.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AF10" t="n">
         <v>0.2</v>
@@ -4774,70 +4774,70 @@
         <v>2</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.789999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.58</v>
+        <v>4.45</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.16</v>
+        <v>5.1</v>
       </c>
       <c r="BR10" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS10" t="n">
-        <v>84.20999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT10" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BU10" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BV10" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="CA10" t="n">
-        <v>5.35</v>
+        <v>5.27</v>
       </c>
       <c r="CB10" t="n">
-        <v>6.03</v>
+        <v>5.94</v>
       </c>
       <c r="CC10" t="n">
         <v>1.7</v>
@@ -4846,16 +4846,16 @@
         <v>1.72</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CI10" t="n">
         <v>1.61</v>
@@ -4870,19 +4870,19 @@
         <v>2.55</v>
       </c>
       <c r="CM10" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.93</v>
+        <v>2.97</v>
       </c>
       <c r="CR10" t="n">
         <v>1.38</v>
@@ -4897,10 +4897,10 @@
         <v>1.5</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CX10" t="n">
         <v>1.84</v>
@@ -4915,88 +4915,88 @@
         <v>1.59</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.07</v>
+        <v>3.13</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="DG10" t="n">
-        <v>3.63</v>
+        <v>3.5</v>
       </c>
       <c r="DH10" t="n">
-        <v>123.21</v>
+        <v>125</v>
       </c>
       <c r="DI10" t="n">
         <v>-0.1</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="DK10" t="n">
-        <v>7.63</v>
+        <v>7.4</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="DM10" t="n">
-        <v>67.11</v>
+        <v>67.7</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="DO10" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.32</v>
+        <v>13.4</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.69</v>
+        <v>12.75</v>
       </c>
       <c r="DR10" t="n">
-        <v>4.42</v>
+        <v>4.55</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>60.9</v>
+        <v>61.35</v>
       </c>
       <c r="DW10" t="n">
         <v>0.1</v>
       </c>
       <c r="DX10" t="n">
-        <v>17.95</v>
+        <v>17.8</v>
       </c>
       <c r="DY10" t="n">
         <v>11.95</v>
       </c>
       <c r="DZ10" t="n">
-        <v>6</v>
+        <v>5.85</v>
       </c>
       <c r="EA10" t="n">
-        <v>26.37</v>
+        <v>26.4</v>
       </c>
       <c r="EB10" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" t="n">
         <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
         <v>0.2</v>
@@ -5096,139 +5096,139 @@
         <v>1.4</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AI11" t="n">
-        <v>107.5</v>
+        <v>106.56</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AL11" t="n">
-        <v>5</v>
+        <v>4.89</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AN11" t="n">
-        <v>54.88</v>
+        <v>56</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12.88</v>
+        <v>12.56</v>
       </c>
       <c r="AR11" t="n">
-        <v>13.25</v>
+        <v>13.11</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.88</v>
+        <v>5.11</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>61.5</v>
+        <v>61.44</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA11" t="n">
-        <v>13.62</v>
+        <v>13.56</v>
       </c>
       <c r="BB11" t="n">
         <v>9</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.62</v>
+        <v>4.56</v>
       </c>
       <c r="BD11" t="n">
-        <v>23.38</v>
+        <v>23.22</v>
       </c>
       <c r="BE11" t="n">
         <v>1.58</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="BG11" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.56</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="BI11" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="BP11" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.56</v>
+        <v>4.63</v>
       </c>
       <c r="BR11" t="n">
-        <v>94.44</v>
+        <v>89.47</v>
       </c>
       <c r="BS11" t="n">
-        <v>83.33</v>
+        <v>78.95</v>
       </c>
       <c r="BT11" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BU11" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV11" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW11" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX11" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BY11" t="n">
         <v>1.46</v>
@@ -5237,34 +5237,34 @@
         <v>1.49</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.91</v>
+        <v>4.82</v>
       </c>
       <c r="CB11" t="n">
-        <v>5.49</v>
+        <v>5.38</v>
       </c>
       <c r="CC11" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CD11" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CI11" t="n">
         <v>1.76</v>
       </c>
       <c r="CJ11" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CK11" t="n">
         <v>1.75</v>
@@ -5273,34 +5273,34 @@
         <v>2.34</v>
       </c>
       <c r="CM11" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CN11" t="n">
         <v>1.59</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CW11" t="n">
         <v>2.14</v>
@@ -5312,94 +5312,94 @@
         <v>2.24</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DA11" t="n">
         <v>1.64</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.96</v>
+        <v>3.04</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="DH11" t="n">
-        <v>110.33</v>
+        <v>109.74</v>
       </c>
       <c r="DI11" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="DK11" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM11" t="n">
-        <v>59.5</v>
+        <v>59.79</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.44</v>
+        <v>0.53</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.67</v>
+        <v>11.58</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13.06</v>
+        <v>13</v>
       </c>
       <c r="DR11" t="n">
-        <v>4.22</v>
+        <v>4.37</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>62.72</v>
+        <v>62.63</v>
       </c>
       <c r="DW11" t="n">
         <v>0.05</v>
       </c>
       <c r="DX11" t="n">
-        <v>15.33</v>
+        <v>15.21</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.779999999999999</v>
+        <v>9.74</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.55</v>
+        <v>5.48</v>
       </c>
       <c r="EA11" t="n">
-        <v>23.95</v>
+        <v>23.84</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="12">
@@ -5535,7 +5535,7 @@
         <v>14.3</v>
       </c>
       <c r="AR12" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="AS12" t="n">
         <v>8.9</v>
@@ -5766,7 +5766,7 @@
         <v>13.15</v>
       </c>
       <c r="DQ12" t="n">
-        <v>13.3</v>
+        <v>13.25</v>
       </c>
       <c r="DR12" t="n">
         <v>9.199999999999999</v>
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
         <v>0.33</v>
@@ -5902,139 +5902,139 @@
         <v>2.22</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AI13" t="n">
-        <v>105.22</v>
+        <v>103.3</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AL13" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>52.22</v>
+        <v>49.9</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ13" t="n">
         <v>14</v>
       </c>
       <c r="AR13" t="n">
-        <v>14.67</v>
+        <v>14.7</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.33</v>
+        <v>6.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>59.33</v>
+        <v>56.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA13" t="n">
-        <v>12.11</v>
+        <v>11.7</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.89</v>
+        <v>7.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="BD13" t="n">
-        <v>23.44</v>
+        <v>23.3</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.67</v>
+        <v>2.58</v>
       </c>
       <c r="BH13" t="n">
-        <v>7.78</v>
+        <v>7.68</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.67</v>
+        <v>2.58</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.06</v>
+        <v>3.95</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3.61</v>
+        <v>3.63</v>
       </c>
       <c r="BR13" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS13" t="n">
-        <v>83.33</v>
+        <v>78.95</v>
       </c>
       <c r="BT13" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BU13" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV13" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BY13" t="n">
         <v>1.75</v>
@@ -6043,55 +6043,55 @@
         <v>1.94</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.19</v>
+        <v>4.17</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.52</v>
+        <v>4.51</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.12</v>
+        <v>2.49</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.28</v>
+        <v>2.98</v>
       </c>
       <c r="CE13" t="n">
         <v>1.38</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="CH13" t="n">
         <v>1.42</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="CM13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="CP13" t="n">
         <v>1.9</v>
       </c>
-      <c r="CN13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="CO13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="CP13" t="n">
-        <v>1.89</v>
-      </c>
       <c r="CQ13" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="CR13" t="n">
         <v>1.41</v>
@@ -6106,10 +6106,10 @@
         <v>1.43</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CX13" t="n">
         <v>1.81</v>
@@ -6127,85 +6127,85 @@
         <v>1.33</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.57</v>
+        <v>3.6</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="DH13" t="n">
-        <v>99.94</v>
+        <v>99.20999999999999</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.83</v>
+        <v>4.74</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DM13" t="n">
-        <v>57.28</v>
+        <v>55.79</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.22</v>
+        <v>2.11</v>
       </c>
       <c r="DP13" t="n">
-        <v>15.06</v>
+        <v>15</v>
       </c>
       <c r="DQ13" t="n">
-        <v>15.44</v>
+        <v>15.42</v>
       </c>
       <c r="DR13" t="n">
-        <v>5.61</v>
+        <v>5.74</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>55.66</v>
+        <v>54.32</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.84</v>
+        <v>12.58</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.33</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.5</v>
+        <v>4.47</v>
       </c>
       <c r="EA13" t="n">
-        <v>22.94</v>
+        <v>22.89</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="14">
@@ -6215,10 +6215,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
         <v>10</v>
@@ -6227,49 +6227,49 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="G14" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="H14" t="n">
-        <v>83.33</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="L14" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="M14" t="n">
-        <v>35.56</v>
+        <v>32.9</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="P14" t="n">
-        <v>16.89</v>
+        <v>15.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>13.89</v>
+        <v>13.6</v>
       </c>
       <c r="R14" t="n">
-        <v>6.89</v>
+        <v>7</v>
       </c>
       <c r="S14" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6281,28 +6281,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>43.67</v>
+        <v>41.3</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>11.33</v>
+        <v>10.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.890000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AC14" t="n">
-        <v>20.78</v>
+        <v>19.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6386,70 +6386,70 @@
         <v>2.9</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="BH14" t="n">
         <v>8.949999999999999</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.63</v>
+        <v>0.8</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.37</v>
+        <v>4.45</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.53</v>
+        <v>4.45</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BT14" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BU14" t="n">
-        <v>21.05</v>
+        <v>25</v>
       </c>
       <c r="BV14" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX14" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BY14" t="n">
-        <v>4.57</v>
+        <v>5.41</v>
       </c>
       <c r="BZ14" t="n">
-        <v>5.19</v>
+        <v>5.99</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.57</v>
+        <v>4.63</v>
       </c>
       <c r="CB14" t="n">
-        <v>5.27</v>
+        <v>5.33</v>
       </c>
       <c r="CC14" t="n">
         <v>10.81</v>
@@ -6461,25 +6461,25 @@
         <v>1.36</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="CK14" t="n">
         <v>1.78</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CM14" t="n">
         <v>1.98</v>
@@ -6491,16 +6491,16 @@
         <v>1.25</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="CR14" t="n">
         <v>1.41</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CT14" t="n">
         <v>2.93</v>
@@ -6509,10 +6509,10 @@
         <v>1.48</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CX14" t="n">
         <v>1.82</v>
@@ -6527,55 +6527,55 @@
         <v>1.62</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="DG14" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="DH14" t="n">
-        <v>67.89</v>
+        <v>65.8</v>
       </c>
       <c r="DI14" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="DK14" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DM14" t="n">
-        <v>29.53</v>
+        <v>28.5</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="DO14" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="DP14" t="n">
-        <v>14.79</v>
+        <v>14.35</v>
       </c>
       <c r="DQ14" t="n">
-        <v>12.21</v>
+        <v>12.15</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.42</v>
+        <v>8.4</v>
       </c>
       <c r="DS14" t="n">
         <v>0.05</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>38.9</v>
+        <v>37.95</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="DX14" t="n">
-        <v>8.369999999999999</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="DY14" t="n">
-        <v>6.32</v>
+        <v>6.05</v>
       </c>
       <c r="DZ14" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="EA14" t="n">
-        <v>18.32</v>
+        <v>17.8</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="15">

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="n">
         <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1872,130 +1872,130 @@
         <v>2.8</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="AI3" t="n">
-        <v>86</v>
+        <v>86.27</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK3" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.7</v>
+        <v>4.36</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AN3" t="n">
-        <v>40</v>
+        <v>37.18</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ3" t="n">
-        <v>16.7</v>
+        <v>16.36</v>
       </c>
       <c r="AR3" t="n">
-        <v>14.3</v>
+        <v>14.27</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.3</v>
+        <v>6.82</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>50.4</v>
+        <v>49.55</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="BA3" t="n">
-        <v>11.3</v>
+        <v>10.64</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.7</v>
+        <v>7.27</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="BD3" t="n">
-        <v>18.8</v>
+        <v>19.36</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="BF3" t="n">
         <v>2</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BN3" t="n">
         <v>1.1</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BP3" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.9</v>
+        <v>5.76</v>
       </c>
       <c r="BR3" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS3" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BT3" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BU3" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BV3" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BY3" t="n">
         <v>2.81</v>
@@ -2013,28 +2013,28 @@
         <v>2.86</v>
       </c>
       <c r="CA3" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="CC3" t="n">
         <v>3.61</v>
       </c>
-      <c r="CB3" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="CC3" t="n">
-        <v>3.77</v>
-      </c>
       <c r="CD3" t="n">
-        <v>4.66</v>
+        <v>4.44</v>
       </c>
       <c r="CE3" t="n">
         <v>1.44</v>
       </c>
       <c r="CF3" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CI3" t="n">
         <v>1.72</v>
@@ -2043,10 +2043,10 @@
         <v>2.02</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CM3" t="n">
         <v>1.87</v>
@@ -2055,28 +2055,28 @@
         <v>1.53</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.82</v>
+        <v>3.85</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="CU3" t="n">
         <v>1.37</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CW3" t="n">
         <v>2.1</v>
@@ -2094,55 +2094,55 @@
         <v>1.55</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.01</v>
+        <v>4.06</v>
       </c>
       <c r="DE3" t="n">
         <v>0.05</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="DH3" t="n">
-        <v>90.75</v>
+        <v>90.67</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.15</v>
+        <v>4.95</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM3" t="n">
-        <v>43.4</v>
+        <v>41.76</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="DP3" t="n">
-        <v>15.3</v>
+        <v>15.19</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.75</v>
+        <v>14.71</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.95</v>
+        <v>7.19</v>
       </c>
       <c r="DS3" t="n">
         <v>0.05</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>51.3</v>
+        <v>50.81</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DX3" t="n">
-        <v>12.75</v>
+        <v>12.34</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.9</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.85</v>
+        <v>3.71</v>
       </c>
       <c r="EA3" t="n">
-        <v>19.85</v>
+        <v>20.09</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="n">
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
         <v>0.2</v>
@@ -2278,136 +2278,136 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AI4" t="n">
-        <v>78.8</v>
+        <v>76.81999999999999</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.4</v>
+        <v>4.18</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AN4" t="n">
-        <v>32.9</v>
+        <v>32.82</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ4" t="n">
-        <v>15.3</v>
+        <v>14.91</v>
       </c>
       <c r="AR4" t="n">
-        <v>16.9</v>
+        <v>16.18</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.18</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>44.3</v>
+        <v>44.73</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA4" t="n">
-        <v>9.5</v>
+        <v>9.27</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="BD4" t="n">
-        <v>18.8</v>
+        <v>18.64</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.949999999999999</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.15</v>
+        <v>5.1</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.8</v>
+        <v>4.76</v>
       </c>
       <c r="BR4" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS4" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT4" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BU4" t="n">
-        <v>25</v>
+        <v>28.57</v>
       </c>
       <c r="BV4" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW4" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX4" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BY4" t="n">
         <v>3.75</v>
@@ -2416,28 +2416,28 @@
         <v>4.53</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.95</v>
+        <v>3.91</v>
       </c>
       <c r="CC4" t="n">
-        <v>6.35</v>
+        <v>6</v>
       </c>
       <c r="CD4" t="n">
-        <v>6.79</v>
+        <v>6.42</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CI4" t="n">
         <v>1.76</v>
@@ -2449,22 +2449,22 @@
         <v>1.84</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CM4" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.54</v>
+        <v>3.57</v>
       </c>
       <c r="CR4" t="n">
         <v>1.42</v>
@@ -2497,88 +2497,88 @@
         <v>1.57</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.74</v>
+        <v>3.79</v>
       </c>
       <c r="DE4" t="n">
         <v>0.1</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="DH4" t="n">
-        <v>78.84999999999999</v>
+        <v>77.81</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.9</v>
+        <v>4.76</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="DM4" t="n">
-        <v>37.45</v>
+        <v>37.19</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.65</v>
+        <v>13.52</v>
       </c>
       <c r="DQ4" t="n">
-        <v>16.3</v>
+        <v>15.95</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.19</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>44.85</v>
+        <v>45.05</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX4" t="n">
-        <v>9.4</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="DY4" t="n">
-        <v>5.95</v>
+        <v>5.86</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.95</v>
+        <v>20.76</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="EC4" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="5">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
         <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="H8" t="n">
-        <v>98.5</v>
+        <v>95</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="K8" t="n">
-        <v>4.8</v>
+        <v>4.55</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="M8" t="n">
-        <v>42.2</v>
+        <v>40.18</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="O8" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="P8" t="n">
-        <v>12.3</v>
+        <v>12</v>
       </c>
       <c r="Q8" t="n">
-        <v>16.8</v>
+        <v>16.73</v>
       </c>
       <c r="R8" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="S8" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>60.6</v>
+        <v>58.27</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>14.7</v>
+        <v>13.64</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.09</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.9</v>
+        <v>5.55</v>
       </c>
       <c r="AC8" t="n">
-        <v>23.1</v>
+        <v>23.64</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AF8" t="n">
         <v>0.3</v>
@@ -3968,70 +3968,70 @@
         <v>2.4</v>
       </c>
       <c r="BG8" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>95.23999999999999</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>90.48</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="CA8" t="n">
         <v>3.7</v>
       </c>
-      <c r="BH8" t="n">
-        <v>9.550000000000001</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>100</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>95</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>70</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>60</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>30</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>10</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>70</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>3.68</v>
-      </c>
       <c r="CB8" t="n">
-        <v>3.87</v>
+        <v>3.88</v>
       </c>
       <c r="CC8" t="n">
         <v>4.02</v>
@@ -4043,7 +4043,7 @@
         <v>1.39</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="CG8" t="n">
         <v>2.78</v>
@@ -4061,7 +4061,7 @@
         <v>1.83</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="CM8" t="n">
         <v>1.9</v>
@@ -4091,10 +4091,10 @@
         <v>1.39</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CX8" t="n">
         <v>1.86</v>
@@ -4115,82 +4115,82 @@
         <v>2.06</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.62</v>
+        <v>3.63</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="DH8" t="n">
-        <v>95.65000000000001</v>
+        <v>93.95</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="DM8" t="n">
-        <v>42.25</v>
+        <v>41.19</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.7</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="DP8" t="n">
-        <v>12.35</v>
+        <v>12.19</v>
       </c>
       <c r="DQ8" t="n">
         <v>16.1</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.8</v>
+        <v>6.95</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>58.2</v>
+        <v>57.09</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.6</v>
+        <v>12.14</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.55</v>
+        <v>7.24</v>
       </c>
       <c r="DZ8" t="n">
-        <v>5.05</v>
+        <v>4.91</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.8</v>
+        <v>22.14</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="9">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4693,139 +4693,139 @@
         <v>0.8</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="AI10" t="n">
-        <v>116.9</v>
+        <v>119.36</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AL10" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AN10" t="n">
-        <v>60.2</v>
+        <v>63.73</v>
       </c>
       <c r="AO10" t="n">
         <v>1</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ10" t="n">
-        <v>15.8</v>
+        <v>15.64</v>
       </c>
       <c r="AR10" t="n">
-        <v>12.7</v>
+        <v>12.36</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>58.4</v>
+        <v>59</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA10" t="n">
-        <v>14.3</v>
+        <v>15.09</v>
       </c>
       <c r="BB10" t="n">
-        <v>8.800000000000001</v>
+        <v>9.82</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.5</v>
+        <v>5.27</v>
       </c>
       <c r="BD10" t="n">
-        <v>26.4</v>
+        <v>26.91</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="BF10" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.6</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL10" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.45</v>
+        <v>4.48</v>
       </c>
       <c r="BQ10" t="n">
         <v>5.1</v>
       </c>
       <c r="BR10" t="n">
-        <v>95</v>
+        <v>90.48</v>
       </c>
       <c r="BS10" t="n">
-        <v>80</v>
+        <v>76.19</v>
       </c>
       <c r="BT10" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BU10" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BV10" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BY10" t="n">
         <v>1.27</v>
@@ -4834,40 +4834,40 @@
         <v>1.26</v>
       </c>
       <c r="CA10" t="n">
-        <v>5.27</v>
+        <v>5.22</v>
       </c>
       <c r="CB10" t="n">
-        <v>5.94</v>
+        <v>5.86</v>
       </c>
       <c r="CC10" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="CD10" t="n">
         <v>1.7</v>
-      </c>
-      <c r="CD10" t="n">
-        <v>1.72</v>
       </c>
       <c r="CE10" t="n">
         <v>1.34</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="CH10" t="n">
         <v>1.48</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CJ10" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CK10" t="n">
         <v>1.83</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="CM10" t="n">
         <v>1.88</v>
@@ -4879,10 +4879,10 @@
         <v>1.22</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="CR10" t="n">
         <v>1.38</v>
@@ -4897,10 +4897,10 @@
         <v>1.5</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CX10" t="n">
         <v>1.84</v>
@@ -4915,88 +4915,88 @@
         <v>1.59</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.13</v>
+        <v>3.16</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="DG10" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="DH10" t="n">
-        <v>125</v>
+        <v>125.9</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="DK10" t="n">
-        <v>7.4</v>
+        <v>7.43</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="DM10" t="n">
-        <v>67.7</v>
+        <v>69.19</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="DO10" t="n">
-        <v>3.85</v>
+        <v>3.81</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.4</v>
+        <v>13.43</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.75</v>
+        <v>12.57</v>
       </c>
       <c r="DR10" t="n">
-        <v>4.55</v>
+        <v>4.53</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>61.35</v>
+        <v>61.52</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX10" t="n">
-        <v>17.8</v>
+        <v>18.05</v>
       </c>
       <c r="DY10" t="n">
-        <v>11.95</v>
+        <v>12.33</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.85</v>
+        <v>5.71</v>
       </c>
       <c r="EA10" t="n">
-        <v>26.4</v>
+        <v>26.67</v>
       </c>
       <c r="EB10" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="11">
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
         <v>10</v>
@@ -5421,82 +5421,82 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="G12" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="H12" t="n">
-        <v>79.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="J12" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="K12" t="n">
-        <v>3.5</v>
+        <v>3.73</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>35.4</v>
+        <v>35.64</v>
       </c>
       <c r="N12" t="n">
         <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="P12" t="n">
-        <v>12</v>
+        <v>11.73</v>
       </c>
       <c r="Q12" t="n">
-        <v>12.9</v>
+        <v>12.64</v>
       </c>
       <c r="R12" t="n">
-        <v>9.5</v>
+        <v>9.09</v>
       </c>
       <c r="S12" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>44.6</v>
+        <v>45.18</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>7.5</v>
+        <v>8.27</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.6</v>
+        <v>6.18</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="AC12" t="n">
-        <v>17.8</v>
+        <v>17.82</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.87</v>
+        <v>0.93</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AF12" t="n">
         <v>0.1</v>
@@ -5580,70 +5580,70 @@
         <v>2.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.550000000000001</v>
+        <v>8.52</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.15</v>
+        <v>4.14</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="BR12" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS12" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BT12" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BU12" t="n">
-        <v>25</v>
+        <v>28.57</v>
       </c>
       <c r="BV12" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW12" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX12" t="n">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="BY12" t="n">
-        <v>5.67</v>
+        <v>5.44</v>
       </c>
       <c r="BZ12" t="n">
-        <v>5.97</v>
+        <v>5.7</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.88</v>
+        <v>3.83</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.13</v>
+        <v>4.08</v>
       </c>
       <c r="CC12" t="n">
         <v>6.27</v>
@@ -5652,28 +5652,28 @@
         <v>7.68</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CI12" t="n">
         <v>1.69</v>
       </c>
       <c r="CJ12" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CK12" t="n">
         <v>1.88</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CM12" t="n">
         <v>1.87</v>
@@ -5682,13 +5682,13 @@
         <v>1.51</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.78</v>
+        <v>3.79</v>
       </c>
       <c r="CR12" t="n">
         <v>1.42</v>
@@ -5706,7 +5706,7 @@
         <v>1.77</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CX12" t="n">
         <v>1.89</v>
@@ -5721,88 +5721,88 @@
         <v>1.56</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.85</v>
+        <v>3.89</v>
       </c>
       <c r="DE12" t="n">
         <v>0.05</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="DH12" t="n">
-        <v>75.2</v>
+        <v>76.52</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="DK12" t="n">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="DL12" t="n">
         <v>0.1</v>
       </c>
       <c r="DM12" t="n">
-        <v>33.05</v>
+        <v>33.29</v>
       </c>
       <c r="DN12" t="n">
         <v>1.05</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.15</v>
+        <v>12.95</v>
       </c>
       <c r="DQ12" t="n">
-        <v>13.25</v>
+        <v>13.1</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>42.2</v>
+        <v>42.62</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DX12" t="n">
-        <v>8.050000000000001</v>
+        <v>8.43</v>
       </c>
       <c r="DY12" t="n">
-        <v>5.55</v>
+        <v>5.86</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="EA12" t="n">
-        <v>17.2</v>
+        <v>17.24</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="13">
@@ -6618,94 +6618,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
         <v>11</v>
       </c>
       <c r="E15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F15" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="G15" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="H15" t="n">
-        <v>69.78</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J15" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="K15" t="n">
-        <v>5.11</v>
+        <v>5</v>
       </c>
       <c r="L15" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="M15" t="n">
-        <v>30.11</v>
+        <v>33.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="O15" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="P15" t="n">
-        <v>14.11</v>
+        <v>14.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="R15" t="n">
-        <v>8.56</v>
+        <v>8</v>
       </c>
       <c r="S15" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T15" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="U15" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="V15" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>50</v>
+        <v>50.9</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>12.89</v>
+        <v>13.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>9.220000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.67</v>
+        <v>3.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>21.22</v>
+        <v>21.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AE15" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AF15" t="n">
         <v>0.09</v>
@@ -6789,70 +6789,70 @@
         <v>3.18</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.6</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.95</v>
+        <v>3.86</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.6</v>
+        <v>5.48</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT15" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BU15" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BV15" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW15" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX15" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BY15" t="n">
-        <v>3.73</v>
+        <v>3.77</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.89</v>
+        <v>3.88</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.81</v>
+        <v>3.77</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.98</v>
+        <v>3.93</v>
       </c>
       <c r="CC15" t="n">
         <v>6.64</v>
@@ -6864,16 +6864,16 @@
         <v>1.4</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CH15" t="n">
         <v>1.38</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CJ15" t="n">
         <v>2.01</v>
@@ -6882,7 +6882,7 @@
         <v>1.86</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CM15" t="n">
         <v>1.88</v>
@@ -6891,25 +6891,25 @@
         <v>1.52</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CS15" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CV15" t="n">
         <v>1.83</v>
@@ -6930,88 +6930,88 @@
         <v>1.57</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.67</v>
+        <v>3.74</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF15" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DH15" t="n">
-        <v>75.25</v>
+        <v>76.48</v>
       </c>
       <c r="DI15" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="DM15" t="n">
-        <v>32.6</v>
+        <v>34.1</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="DP15" t="n">
-        <v>15.45</v>
+        <v>15.38</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.5</v>
+        <v>15.33</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.4</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>47.9</v>
+        <v>48.43</v>
       </c>
       <c r="DW15" t="n">
         <v>0.05</v>
       </c>
       <c r="DX15" t="n">
-        <v>11.15</v>
+        <v>11.38</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.55</v>
+        <v>7.76</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="EA15" t="n">
-        <v>21.2</v>
+        <v>21.43</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="EC15" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1469,139 +1469,139 @@
         <v>2.6</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.8</v>
+        <v>2.09</v>
       </c>
       <c r="AI2" t="n">
-        <v>90.7</v>
+        <v>90.27</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AK2" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="AL2" t="n">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AN2" t="n">
-        <v>53.2</v>
+        <v>52.09</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="AQ2" t="n">
-        <v>16</v>
+        <v>15.55</v>
       </c>
       <c r="AR2" t="n">
-        <v>13.2</v>
+        <v>13.09</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.3</v>
+        <v>7.27</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AU2" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>58.8</v>
+        <v>57.82</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA2" t="n">
-        <v>14.1</v>
+        <v>13.91</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.5</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.6</v>
+        <v>4.27</v>
       </c>
       <c r="BD2" t="n">
-        <v>20</v>
+        <v>20.55</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.35</v>
+        <v>8.52</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BP2" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BQ2" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="BR2" t="n">
-        <v>100</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS2" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BT2" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BU2" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV2" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BY2" t="n">
         <v>1.54</v>
@@ -1610,37 +1610,37 @@
         <v>1.55</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.59</v>
+        <v>4.52</v>
       </c>
       <c r="CB2" t="n">
-        <v>5</v>
+        <v>4.91</v>
       </c>
       <c r="CC2" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="CD2" t="n">
-        <v>1.97</v>
+        <v>2.12</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="CH2" t="n">
         <v>1.44</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CL2" t="n">
         <v>2.39</v>
@@ -1655,19 +1655,19 @@
         <v>1.26</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="CU2" t="n">
         <v>1.46</v>
@@ -1676,103 +1676,103 @@
         <v>1.76</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="DA2" t="n">
         <v>1.61</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.21</v>
+        <v>3.27</v>
       </c>
       <c r="DE2" t="n">
         <v>0.05</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="DH2" t="n">
-        <v>93.84999999999999</v>
+        <v>93.47</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.45</v>
+        <v>5.43</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="DM2" t="n">
-        <v>56.35</v>
+        <v>55.62</v>
       </c>
       <c r="DN2" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.85</v>
+        <v>2.72</v>
       </c>
       <c r="DP2" t="n">
-        <v>15.8</v>
+        <v>15.57</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.45</v>
+        <v>13.38</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.2</v>
+        <v>6.24</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>58.35</v>
+        <v>57.86</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX2" t="n">
-        <v>15.3</v>
+        <v>15.14</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.4</v>
+        <v>10.43</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.9</v>
+        <v>4.71</v>
       </c>
       <c r="EA2" t="n">
-        <v>20.55</v>
+        <v>20.81</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="3">
@@ -2332,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>44.73</v>
+        <v>44.64</v>
       </c>
       <c r="AZ4" t="n">
         <v>0.09</v>
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>45.05</v>
+        <v>45</v>
       </c>
       <c r="DW4" t="n">
         <v>0.14</v>
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
         <v>10</v>
@@ -2600,82 +2600,82 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="H5" t="n">
-        <v>89.3</v>
+        <v>94</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="K5" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="M5" t="n">
-        <v>44.2</v>
+        <v>46.27</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="O5" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="P5" t="n">
-        <v>14.6</v>
+        <v>14.82</v>
       </c>
       <c r="Q5" t="n">
-        <v>15.1</v>
+        <v>15.27</v>
       </c>
       <c r="R5" t="n">
-        <v>5.5</v>
+        <v>5.27</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>53.7</v>
+        <v>55.27</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.9</v>
+        <v>12.18</v>
       </c>
       <c r="AA5" t="n">
-        <v>9</v>
+        <v>9.18</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AC5" t="n">
-        <v>24.6</v>
+        <v>24.27</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AF5" t="n">
         <v>0.2</v>
@@ -2759,70 +2759,70 @@
         <v>3</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.050000000000001</v>
+        <v>8</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="BO5" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.85</v>
+        <v>3.71</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.2</v>
+        <v>4.29</v>
       </c>
       <c r="BR5" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS5" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BT5" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BU5" t="n">
-        <v>15</v>
+        <v>19.05</v>
       </c>
       <c r="BV5" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.76</v>
+        <v>3.54</v>
       </c>
       <c r="BZ5" t="n">
-        <v>4.13</v>
+        <v>3.88</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.62</v>
+        <v>3.66</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.88</v>
+        <v>3.92</v>
       </c>
       <c r="CC5" t="n">
         <v>5.71</v>
@@ -2837,19 +2837,19 @@
         <v>2.98</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CH5" t="n">
         <v>1.37</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CL5" t="n">
         <v>2.59</v>
@@ -2861,7 +2861,7 @@
         <v>1.49</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CP5" t="n">
         <v>2.09</v>
@@ -2873,7 +2873,7 @@
         <v>1.43</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="CT5" t="n">
         <v>2.85</v>
@@ -2882,10 +2882,10 @@
         <v>1.4</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="CW5" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="CX5" t="n">
         <v>1.97</v>
@@ -2906,82 +2906,82 @@
         <v>2.16</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
       <c r="DE5" t="n">
         <v>0.1</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="DH5" t="n">
-        <v>81.5</v>
+        <v>84.33</v>
       </c>
       <c r="DI5" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.65</v>
+        <v>3.67</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="DM5" t="n">
-        <v>37.8</v>
+        <v>39.19</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="DP5" t="n">
-        <v>15.75</v>
+        <v>15.81</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.6</v>
+        <v>14.71</v>
       </c>
       <c r="DR5" t="n">
-        <v>8</v>
+        <v>7.76</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>49.7</v>
+        <v>50.71</v>
       </c>
       <c r="DW5" t="n">
         <v>0.05</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.05</v>
+        <v>10.28</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.25</v>
+        <v>7.43</v>
       </c>
       <c r="DZ5" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="EA5" t="n">
-        <v>22.6</v>
+        <v>22.52</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="6">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
         <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>81.44</v>
+        <v>84.8</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3.67</v>
+        <v>3.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="L6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="M6" t="n">
-        <v>42.78</v>
+        <v>43.9</v>
       </c>
       <c r="N6" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="P6" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>15.44</v>
+        <v>15.8</v>
       </c>
       <c r="R6" t="n">
-        <v>7.44</v>
+        <v>7.2</v>
       </c>
       <c r="S6" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T6" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3057,28 +3057,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>44.44</v>
+        <v>45.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>14.11</v>
+        <v>15.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.890000000000001</v>
+        <v>10.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.22</v>
+        <v>4.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>16.67</v>
+        <v>17.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,70 +3162,70 @@
         <v>4.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.949999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="BL6" t="n">
         <v>0.95</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="BP6" t="n">
-        <v>5.58</v>
+        <v>5.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.32</v>
+        <v>4.2</v>
       </c>
       <c r="BR6" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS6" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BT6" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BU6" t="n">
-        <v>31.58</v>
+        <v>35</v>
       </c>
       <c r="BV6" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BY6" t="n">
-        <v>4.23</v>
+        <v>4.03</v>
       </c>
       <c r="BZ6" t="n">
-        <v>4.38</v>
+        <v>4.15</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.96</v>
+        <v>3.92</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.93</v>
+        <v>3.9</v>
       </c>
       <c r="CC6" t="n">
         <v>5.62</v>
@@ -3234,124 +3234,124 @@
         <v>5.25</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CF6" t="n">
         <v>2.87</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CH6" t="n">
         <v>1.39</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CK6" t="n">
         <v>1.77</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CM6" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CO6" t="n">
         <v>1.31</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CS6" t="n">
         <v>2.99</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="CU6" t="n">
         <v>1.41</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CX6" t="n">
         <v>1.89</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CZ6" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="DB6" t="n">
         <v>1.35</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="DE6" t="n">
         <v>0.05</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="DH6" t="n">
-        <v>79.68000000000001</v>
+        <v>81.45</v>
       </c>
       <c r="DI6" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ6" t="n">
-        <v>4.26</v>
+        <v>4.2</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.37</v>
+        <v>4.35</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="DM6" t="n">
-        <v>41.11</v>
+        <v>41.75</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="DP6" t="n">
-        <v>17.58</v>
+        <v>17.55</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14.31</v>
+        <v>14.55</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.1</v>
+        <v>7.95</v>
       </c>
       <c r="DS6" t="n">
         <v>0.05</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>46</v>
+        <v>46.5</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.79</v>
+        <v>14.35</v>
       </c>
       <c r="DY6" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.79</v>
+        <v>5.05</v>
       </c>
       <c r="EA6" t="n">
-        <v>17.16</v>
+        <v>17.45</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="EC6" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" t="n">
         <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
         <v>0.09</v>
@@ -3487,136 +3487,136 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AI7" t="n">
-        <v>84.67</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN7" t="n">
-        <v>31.22</v>
+        <v>29.9</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ7" t="n">
-        <v>16.56</v>
+        <v>16.3</v>
       </c>
       <c r="AR7" t="n">
-        <v>12.67</v>
+        <v>13.3</v>
       </c>
       <c r="AS7" t="n">
-        <v>10.22</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AU7" t="n">
         <v>1</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>40.33</v>
+        <v>39.3</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BA7" t="n">
-        <v>11.11</v>
+        <v>10.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.22</v>
+        <v>7</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>17.56</v>
+        <v>17.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BF7" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.4</v>
+        <v>8.24</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.8</v>
+        <v>3.62</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.5</v>
+        <v>4.52</v>
       </c>
       <c r="BR7" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS7" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT7" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BU7" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BV7" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW7" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX7" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BY7" t="n">
         <v>4.71</v>
@@ -3625,16 +3625,16 @@
         <v>4.88</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.74</v>
+        <v>3.79</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.75</v>
+        <v>3.77</v>
       </c>
       <c r="CC7" t="n">
-        <v>5.4</v>
+        <v>5.85</v>
       </c>
       <c r="CD7" t="n">
-        <v>5.53</v>
+        <v>5.84</v>
       </c>
       <c r="CE7" t="n">
         <v>1.44</v>
@@ -3649,19 +3649,19 @@
         <v>1.35</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CL7" t="n">
         <v>2.59</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CN7" t="n">
         <v>1.5</v>
@@ -3670,16 +3670,16 @@
         <v>1.34</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="CR7" t="n">
         <v>1.45</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CT7" t="n">
         <v>2.79</v>
@@ -3688,16 +3688,16 @@
         <v>1.39</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CX7" t="n">
         <v>1.93</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CZ7" t="n">
         <v>1.88</v>
@@ -3706,7 +3706,7 @@
         <v>1.53</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="DC7" t="n">
         <v>2.22</v>
@@ -3718,76 +3718,76 @@
         <v>0.05</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="DH7" t="n">
-        <v>85.45</v>
+        <v>84.09</v>
       </c>
       <c r="DI7" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.55</v>
+        <v>3.48</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM7" t="n">
-        <v>32.75</v>
+        <v>32.05</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="DP7" t="n">
-        <v>16.6</v>
+        <v>16.48</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.45</v>
+        <v>14.67</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>43</v>
+        <v>42.38</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.7</v>
+        <v>11.52</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.65</v>
+        <v>7.52</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.8</v>
+        <v>17.67</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.35</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="8">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
         <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
         <v>0.1</v>
@@ -4290,139 +4290,139 @@
         <v>2.1</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AI9" t="n">
-        <v>65.11</v>
+        <v>64</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.33</v>
+        <v>3.2</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AN9" t="n">
-        <v>24.44</v>
+        <v>24</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12.11</v>
+        <v>12.7</v>
       </c>
       <c r="AR9" t="n">
-        <v>15.67</v>
+        <v>16</v>
       </c>
       <c r="AS9" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AU9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>41</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="BE9" t="n">
         <v>0.89</v>
       </c>
-      <c r="AV9" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>40.67</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>7.89</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>14.33</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>0.9</v>
-      </c>
       <c r="BF9" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.789999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ9" t="n">
         <v>1</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.47</v>
+        <v>0.55</v>
       </c>
       <c r="BL9" t="n">
         <v>1</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.68</v>
+        <v>4.65</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT9" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BU9" t="n">
-        <v>31.58</v>
+        <v>35</v>
       </c>
       <c r="BV9" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX9" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BY9" t="n">
         <v>3.39</v>
@@ -4431,16 +4431,16 @@
         <v>3.58</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.19</v>
+        <v>4.15</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.5</v>
+        <v>4.44</v>
       </c>
       <c r="CC9" t="n">
-        <v>8.02</v>
+        <v>7.56</v>
       </c>
       <c r="CD9" t="n">
-        <v>9.68</v>
+        <v>9.09</v>
       </c>
       <c r="CE9" t="n">
         <v>1.37</v>
@@ -4449,22 +4449,22 @@
         <v>2.75</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CI9" t="n">
         <v>1.9</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CK9" t="n">
         <v>1.73</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CM9" t="n">
         <v>2.03</v>
@@ -4479,22 +4479,22 @@
         <v>1.88</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CR9" t="n">
         <v>1.4</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CT9" t="n">
         <v>2.94</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CW9" t="n">
         <v>1.94</v>
@@ -4506,7 +4506,7 @@
         <v>2.19</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DA9" t="n">
         <v>1.67</v>
@@ -4521,79 +4521,79 @@
         <v>3.31</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.16</v>
+        <v>0.25</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="DH9" t="n">
-        <v>71.84</v>
+        <v>70.95</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="DK9" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DM9" t="n">
-        <v>26.21</v>
+        <v>25.9</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.1</v>
+        <v>14.3</v>
       </c>
       <c r="DQ9" t="n">
-        <v>15.9</v>
+        <v>16.05</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.58</v>
+        <v>9.85</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>42.53</v>
+        <v>42.6</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.109999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.74</v>
+        <v>5.6</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.05</v>
+        <v>15.6</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.01</v>
+        <v>0.99</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="10">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
         <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="G11" t="n">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="H11" t="n">
-        <v>112.6</v>
+        <v>109.45</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J11" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="K11" t="n">
-        <v>6.8</v>
+        <v>6.82</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="M11" t="n">
-        <v>63.2</v>
+        <v>62</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>10.7</v>
+        <v>10.82</v>
       </c>
       <c r="Q11" t="n">
-        <v>12.9</v>
+        <v>12.73</v>
       </c>
       <c r="R11" t="n">
-        <v>3.7</v>
+        <v>4.36</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="T11" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>63.7</v>
+        <v>62.64</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>16.7</v>
+        <v>15.91</v>
       </c>
       <c r="AA11" t="n">
-        <v>10.4</v>
+        <v>10.09</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.3</v>
+        <v>5.82</v>
       </c>
       <c r="AC11" t="n">
-        <v>24.4</v>
+        <v>24.45</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="AF11" t="n">
         <v>0.22</v>
@@ -5177,70 +5177,70 @@
         <v>1.78</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.529999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.63</v>
+        <v>4.9</v>
       </c>
       <c r="BR11" t="n">
-        <v>89.47</v>
+        <v>85</v>
       </c>
       <c r="BS11" t="n">
-        <v>78.95</v>
+        <v>75</v>
       </c>
       <c r="BT11" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BU11" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BV11" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>35</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="CB11" t="n">
         <v>5.26</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>36.84</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="BZ11" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="CA11" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="CB11" t="n">
-        <v>5.38</v>
       </c>
       <c r="CC11" t="n">
         <v>1.85</v>
@@ -5249,13 +5249,13 @@
         <v>1.82</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.17</v>
+        <v>3.12</v>
       </c>
       <c r="CH11" t="n">
         <v>1.48</v>
@@ -5264,7 +5264,7 @@
         <v>1.76</v>
       </c>
       <c r="CJ11" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CK11" t="n">
         <v>1.75</v>
@@ -5282,124 +5282,124 @@
         <v>1.25</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.06</v>
+        <v>3.02</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.04</v>
+        <v>3.11</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.26</v>
+        <v>3.35</v>
       </c>
       <c r="DH11" t="n">
-        <v>109.74</v>
+        <v>108.15</v>
       </c>
       <c r="DI11" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.9</v>
+        <v>5.95</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.47</v>
+        <v>0.55</v>
       </c>
       <c r="DM11" t="n">
-        <v>59.79</v>
+        <v>59.3</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.58</v>
+        <v>11.6</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="DR11" t="n">
-        <v>4.37</v>
+        <v>4.7</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>62.63</v>
+        <v>62.1</v>
       </c>
       <c r="DW11" t="n">
         <v>0.05</v>
       </c>
       <c r="DX11" t="n">
-        <v>15.21</v>
+        <v>14.85</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.74</v>
+        <v>9.6</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.48</v>
+        <v>5.25</v>
       </c>
       <c r="EA11" t="n">
-        <v>23.84</v>
+        <v>23.9</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="12">
@@ -5475,7 +5475,7 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>45.18</v>
+        <v>45.27</v>
       </c>
       <c r="Y12" t="n">
         <v>0.18</v>
@@ -5781,7 +5781,7 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>42.62</v>
+        <v>42.67</v>
       </c>
       <c r="DW12" t="n">
         <v>0.28</v>
@@ -5812,94 +5812,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
         <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="F13" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="G13" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="H13" t="n">
-        <v>94.67</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J13" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="K13" t="n">
-        <v>5.33</v>
+        <v>5.2</v>
       </c>
       <c r="L13" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="M13" t="n">
-        <v>62.33</v>
+        <v>64.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="O13" t="n">
-        <v>2.89</v>
+        <v>2.6</v>
       </c>
       <c r="P13" t="n">
-        <v>16.11</v>
+        <v>16.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>16.22</v>
+        <v>16.1</v>
       </c>
       <c r="R13" t="n">
-        <v>4.89</v>
+        <v>4.8</v>
       </c>
       <c r="S13" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="T13" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="U13" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="V13" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>52</v>
+        <v>53.8</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z13" t="n">
-        <v>13.56</v>
+        <v>13.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.779999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.78</v>
+        <v>4.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>22.44</v>
+        <v>22.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AF13" t="n">
         <v>0.2</v>
@@ -5983,70 +5983,70 @@
         <v>2.3</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="BH13" t="n">
-        <v>7.68</v>
+        <v>7.55</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3.63</v>
+        <v>3.7</v>
       </c>
       <c r="BR13" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS13" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT13" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BU13" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BV13" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.17</v>
+        <v>4.19</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.51</v>
+        <v>4.49</v>
       </c>
       <c r="CC13" t="n">
         <v>2.49</v>
@@ -6058,28 +6058,28 @@
         <v>1.38</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CK13" t="n">
         <v>1.67</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="CM13" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CN13" t="n">
         <v>1.6</v>
@@ -6088,28 +6088,28 @@
         <v>1.29</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="CR13" t="n">
         <v>1.41</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="CX13" t="n">
         <v>1.81</v>
@@ -6124,88 +6124,88 @@
         <v>1.63</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="DH13" t="n">
-        <v>99.20999999999999</v>
+        <v>101.45</v>
       </c>
       <c r="DI13" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.74</v>
+        <v>4.7</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DM13" t="n">
-        <v>55.79</v>
+        <v>57.1</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="DP13" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="DQ13" t="n">
-        <v>15.42</v>
+        <v>15.4</v>
       </c>
       <c r="DR13" t="n">
-        <v>5.74</v>
+        <v>5.65</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>54.32</v>
+        <v>55.1</v>
       </c>
       <c r="DW13" t="n">
         <v>0.1</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.58</v>
+        <v>12.75</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.109999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.47</v>
+        <v>4.45</v>
       </c>
       <c r="EA13" t="n">
-        <v>22.89</v>
+        <v>23.05</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" t="n">
         <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6308,136 +6308,136 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AH14" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AI14" t="n">
-        <v>54</v>
+        <v>54.45</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AL14" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AN14" t="n">
-        <v>24.1</v>
+        <v>25.36</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AP14" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12.9</v>
+        <v>13.36</v>
       </c>
       <c r="AR14" t="n">
-        <v>10.7</v>
+        <v>11.18</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>34.6</v>
+        <v>34.09</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.7</v>
+        <v>5.73</v>
       </c>
       <c r="BB14" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="BD14" t="n">
-        <v>16.1</v>
+        <v>16.27</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="BG14" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.949999999999999</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="BI14" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ14" t="n">
         <v>0.9</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.45</v>
+        <v>4.29</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.45</v>
+        <v>4.52</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BU14" t="n">
-        <v>25</v>
+        <v>28.57</v>
       </c>
       <c r="BV14" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW14" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX14" t="n">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="BY14" t="n">
         <v>5.41</v>
@@ -6446,43 +6446,43 @@
         <v>5.99</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.63</v>
+        <v>4.62</v>
       </c>
       <c r="CB14" t="n">
-        <v>5.33</v>
+        <v>5.3</v>
       </c>
       <c r="CC14" t="n">
-        <v>10.81</v>
+        <v>10.46</v>
       </c>
       <c r="CD14" t="n">
-        <v>13.7</v>
+        <v>13.39</v>
       </c>
       <c r="CE14" t="n">
         <v>1.36</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="CK14" t="n">
         <v>1.78</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CM14" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CN14" t="n">
         <v>1.59</v>
@@ -6491,16 +6491,16 @@
         <v>1.25</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="CR14" t="n">
         <v>1.41</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="CT14" t="n">
         <v>2.93</v>
@@ -6509,10 +6509,10 @@
         <v>1.48</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="CX14" t="n">
         <v>1.82</v>
@@ -6527,55 +6527,55 @@
         <v>1.62</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="DG14" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="DH14" t="n">
-        <v>65.8</v>
+        <v>65.47</v>
       </c>
       <c r="DI14" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="DK14" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DM14" t="n">
-        <v>28.5</v>
+        <v>28.95</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="DO14" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="DP14" t="n">
-        <v>14.35</v>
+        <v>14.52</v>
       </c>
       <c r="DQ14" t="n">
-        <v>12.15</v>
+        <v>12.33</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.4</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DS14" t="n">
         <v>0.05</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>37.95</v>
+        <v>37.52</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="DX14" t="n">
-        <v>8.050000000000001</v>
+        <v>7.95</v>
       </c>
       <c r="DY14" t="n">
-        <v>6.05</v>
+        <v>5.86</v>
       </c>
       <c r="DZ14" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.8</v>
+        <v>17.81</v>
       </c>
       <c r="EB14" t="n">
         <v>0.82</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="15">

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -2633,7 +2633,7 @@
         <v>14.82</v>
       </c>
       <c r="Q5" t="n">
-        <v>15.27</v>
+        <v>15.36</v>
       </c>
       <c r="R5" t="n">
         <v>5.27</v>
@@ -2654,7 +2654,7 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>55.27</v>
+        <v>55.18</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -2945,7 +2945,7 @@
         <v>15.81</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.71</v>
+        <v>14.76</v>
       </c>
       <c r="DR5" t="n">
         <v>7.76</v>
@@ -2960,7 +2960,7 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>50.71</v>
+        <v>50.67</v>
       </c>
       <c r="DW5" t="n">
         <v>0.05</v>
@@ -6362,7 +6362,7 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>34.09</v>
+        <v>34.18</v>
       </c>
       <c r="AZ14" t="n">
         <v>0.45</v>
@@ -6587,7 +6587,7 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>37.52</v>
+        <v>37.57</v>
       </c>
       <c r="DW14" t="n">
         <v>0.43</v>
@@ -6690,10 +6690,10 @@
         <v>0.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="AB15" t="n">
         <v>3.7</v>
@@ -6702,7 +6702,7 @@
         <v>21.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE15" t="n">
         <v>2.9</v>
@@ -6996,10 +6996,10 @@
         <v>0.05</v>
       </c>
       <c r="DX15" t="n">
-        <v>11.38</v>
+        <v>11.43</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.76</v>
+        <v>7.81</v>
       </c>
       <c r="DZ15" t="n">
         <v>3.62</v>

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
         <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="H2" t="n">
-        <v>97</v>
+        <v>97.27</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K2" t="n">
-        <v>5.4</v>
+        <v>5.18</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="M2" t="n">
-        <v>59.5</v>
+        <v>57.27</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="O2" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="P2" t="n">
-        <v>15.6</v>
+        <v>16</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.7</v>
+        <v>14</v>
       </c>
       <c r="R2" t="n">
-        <v>5.1</v>
+        <v>5.18</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>57.9</v>
+        <v>57.18</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z2" t="n">
-        <v>16.5</v>
+        <v>16.36</v>
       </c>
       <c r="AA2" t="n">
-        <v>11.3</v>
+        <v>11.18</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.2</v>
+        <v>5.18</v>
       </c>
       <c r="AC2" t="n">
-        <v>21.1</v>
+        <v>20.91</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AF2" t="n">
         <v>0.09</v>
@@ -1550,70 +1550,70 @@
         <v>2.82</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.52</v>
+        <v>8.41</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.76</v>
+        <v>0.86</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="BO2" t="n">
         <v>0.86</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="BQ2" t="n">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="BR2" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS2" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BT2" t="n">
-        <v>33.33</v>
+        <v>36.36</v>
       </c>
       <c r="BU2" t="n">
-        <v>28.57</v>
+        <v>31.82</v>
       </c>
       <c r="BV2" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>33.33</v>
+        <v>31.82</v>
       </c>
       <c r="BY2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BZ2" t="n">
         <v>1.54</v>
       </c>
-      <c r="BZ2" t="n">
-        <v>1.55</v>
-      </c>
       <c r="CA2" t="n">
-        <v>4.52</v>
+        <v>4.51</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.91</v>
+        <v>4.89</v>
       </c>
       <c r="CC2" t="n">
         <v>2</v>
@@ -1628,7 +1628,7 @@
         <v>2.69</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CH2" t="n">
         <v>1.44</v>
@@ -1643,7 +1643,7 @@
         <v>1.77</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CM2" t="n">
         <v>1.96</v>
@@ -1655,7 +1655,7 @@
         <v>1.26</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CQ2" t="n">
         <v>3.11</v>
@@ -1664,7 +1664,7 @@
         <v>1.39</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CT2" t="n">
         <v>3.01</v>
@@ -1697,82 +1697,82 @@
         <v>1.91</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="DH2" t="n">
-        <v>93.47</v>
+        <v>93.77</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ2" t="n">
         <v>2.95</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.43</v>
+        <v>5.32</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="DM2" t="n">
-        <v>55.62</v>
+        <v>54.68</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="DP2" t="n">
-        <v>15.57</v>
+        <v>15.78</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.38</v>
+        <v>13.54</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.24</v>
+        <v>6.22</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>57.86</v>
+        <v>57.5</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX2" t="n">
-        <v>15.14</v>
+        <v>15.13</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.43</v>
+        <v>10.41</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.71</v>
+        <v>4.72</v>
       </c>
       <c r="EA2" t="n">
-        <v>20.81</v>
+        <v>20.73</v>
       </c>
       <c r="EB2" t="n">
         <v>1.68</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
         <v>11</v>
@@ -1794,49 +1794,49 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="G3" t="n">
-        <v>3.1</v>
+        <v>3.36</v>
       </c>
       <c r="H3" t="n">
-        <v>95.5</v>
+        <v>95.18000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="K3" t="n">
-        <v>5.6</v>
+        <v>5.91</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="M3" t="n">
-        <v>46.8</v>
+        <v>47.82</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="O3" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="P3" t="n">
-        <v>13.9</v>
+        <v>14.18</v>
       </c>
       <c r="Q3" t="n">
-        <v>15.2</v>
+        <v>15.55</v>
       </c>
       <c r="R3" t="n">
-        <v>7.6</v>
+        <v>7.55</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>52.2</v>
+        <v>52.91</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z3" t="n">
-        <v>14.2</v>
+        <v>15.09</v>
       </c>
       <c r="AA3" t="n">
-        <v>10.1</v>
+        <v>10.91</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.1</v>
+        <v>4.18</v>
       </c>
       <c r="AC3" t="n">
-        <v>20.9</v>
+        <v>21.27</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AF3" t="n">
         <v>0.09</v>
@@ -1956,46 +1956,46 @@
         <v>1.86</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.1</v>
+        <v>9.23</v>
       </c>
       <c r="BI3" t="n">
         <v>1.86</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="BP3" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.76</v>
+        <v>5.91</v>
       </c>
       <c r="BR3" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BS3" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BT3" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BU3" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BV3" t="n">
         <v>0</v>
@@ -2004,19 +2004,19 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.81</v>
+        <v>2.72</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.86</v>
+        <v>2.77</v>
       </c>
       <c r="CA3" t="n">
         <v>3.59</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="CC3" t="n">
         <v>3.61</v>
@@ -2028,10 +2028,10 @@
         <v>1.44</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="CH3" t="n">
         <v>1.34</v>
@@ -2049,7 +2049,7 @@
         <v>2.52</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CN3" t="n">
         <v>1.53</v>
@@ -2061,13 +2061,13 @@
         <v>2.12</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.85</v>
+        <v>3.87</v>
       </c>
       <c r="CR3" t="n">
         <v>1.45</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CT3" t="n">
         <v>2.78</v>
@@ -2076,22 +2076,22 @@
         <v>1.37</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CW3" t="n">
         <v>2.1</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CZ3" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="DB3" t="n">
         <v>1.39</v>
@@ -2103,79 +2103,79 @@
         <v>4.06</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.14</v>
+        <v>3.27</v>
       </c>
       <c r="DH3" t="n">
-        <v>90.67</v>
+        <v>90.72</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.95</v>
+        <v>5.14</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="DM3" t="n">
-        <v>41.76</v>
+        <v>42.5</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="DO3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="DP3" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="DQ3" t="n">
+        <v>14.91</v>
+      </c>
+      <c r="DR3" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="DS3" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="DT3" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="DU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV3" t="n">
+        <v>51.23</v>
+      </c>
+      <c r="DW3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DX3" t="n">
+        <v>12.87</v>
+      </c>
+      <c r="DY3" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="DZ3" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="EA3" t="n">
+        <v>20.31</v>
+      </c>
+      <c r="EB3" t="n">
         <v>1.38</v>
       </c>
-      <c r="DP3" t="n">
-        <v>15.19</v>
-      </c>
-      <c r="DQ3" t="n">
-        <v>14.71</v>
-      </c>
-      <c r="DR3" t="n">
-        <v>7.19</v>
-      </c>
-      <c r="DS3" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="DT3" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="DU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV3" t="n">
-        <v>50.81</v>
-      </c>
-      <c r="DW3" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="DX3" t="n">
-        <v>12.34</v>
-      </c>
-      <c r="DY3" t="n">
-        <v>8.619999999999999</v>
-      </c>
-      <c r="DZ3" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="EA3" t="n">
-        <v>20.09</v>
-      </c>
-      <c r="EB3" t="n">
-        <v>1.34</v>
-      </c>
       <c r="EC3" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
         <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="H4" t="n">
-        <v>78.90000000000001</v>
+        <v>81.55</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="K4" t="n">
-        <v>5.4</v>
+        <v>5.45</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="M4" t="n">
-        <v>42</v>
+        <v>45.09</v>
       </c>
       <c r="N4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="P4" t="n">
+        <v>12.73</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>46.45</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>22.91</v>
+      </c>
+      <c r="AD4" t="n">
         <v>1.2</v>
       </c>
-      <c r="O4" t="n">
+      <c r="AE4" t="n">
         <v>3</v>
-      </c>
-      <c r="P4" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="R4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>45.4</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>3.1</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,70 +2356,70 @@
         <v>3.18</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.859999999999999</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.48</v>
+        <v>0.55</v>
       </c>
       <c r="BL4" t="n">
         <v>0.86</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.1</v>
+        <v>5.09</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.76</v>
+        <v>4.86</v>
       </c>
       <c r="BR4" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS4" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BT4" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BU4" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BV4" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX4" t="n">
-        <v>42.86</v>
+        <v>45.45</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.75</v>
+        <v>3.63</v>
       </c>
       <c r="BZ4" t="n">
-        <v>4.53</v>
+        <v>4.37</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.67</v>
+        <v>3.64</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.91</v>
+        <v>3.87</v>
       </c>
       <c r="CC4" t="n">
         <v>6</v>
@@ -2431,10 +2431,10 @@
         <v>1.43</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CH4" t="n">
         <v>1.36</v>
@@ -2449,7 +2449,7 @@
         <v>1.84</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CM4" t="n">
         <v>1.92</v>
@@ -2461,19 +2461,19 @@
         <v>1.33</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.57</v>
+        <v>3.6</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CS4" t="n">
         <v>3</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="CU4" t="n">
         <v>1.39</v>
@@ -2485,7 +2485,7 @@
         <v>2.07</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CY4" t="n">
         <v>2.36</v>
@@ -2494,91 +2494,91 @@
         <v>1.96</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF4" t="n">
         <v>2.09</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="DH4" t="n">
-        <v>77.81</v>
+        <v>79.18000000000001</v>
       </c>
       <c r="DI4" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.33</v>
+        <v>3.27</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.76</v>
+        <v>4.82</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DM4" t="n">
-        <v>37.19</v>
+        <v>38.96</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.52</v>
+        <v>13.82</v>
       </c>
       <c r="DQ4" t="n">
-        <v>15.95</v>
+        <v>15.77</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.19</v>
+        <v>8</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>45</v>
+        <v>45.54</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX4" t="n">
-        <v>9.279999999999999</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="DY4" t="n">
-        <v>5.86</v>
+        <v>6.09</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.43</v>
+        <v>3.45</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.76</v>
+        <v>20.78</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="EC4" t="n">
-        <v>3.14</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n">
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2678,52 +2678,52 @@
         <v>2.36</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG5" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AI5" t="n">
-        <v>73.7</v>
+        <v>73.27</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.5</v>
+        <v>3.73</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AN5" t="n">
-        <v>31.4</v>
+        <v>30.73</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="AQ5" t="n">
-        <v>16.9</v>
+        <v>16.36</v>
       </c>
       <c r="AR5" t="n">
-        <v>14.1</v>
+        <v>14.64</v>
       </c>
       <c r="AS5" t="n">
-        <v>10.5</v>
+        <v>10.27</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -2735,82 +2735,82 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>45.7</v>
+        <v>45.45</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.18</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="BD5" t="n">
-        <v>20.6</v>
+        <v>20</v>
       </c>
       <c r="BE5" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BF5" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="BH5" t="n">
-        <v>8</v>
+        <v>8.18</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.71</v>
+        <v>3.77</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.29</v>
+        <v>4.41</v>
       </c>
       <c r="BR5" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS5" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT5" t="n">
-        <v>42.86</v>
+        <v>45.45</v>
       </c>
       <c r="BU5" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BV5" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>42.86</v>
+        <v>45.45</v>
       </c>
       <c r="BY5" t="n">
         <v>3.54</v>
@@ -2819,40 +2819,40 @@
         <v>3.88</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.66</v>
+        <v>3.63</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.92</v>
+        <v>3.88</v>
       </c>
       <c r="CC5" t="n">
-        <v>5.71</v>
+        <v>5.45</v>
       </c>
       <c r="CD5" t="n">
-        <v>6.78</v>
+        <v>6.42</v>
       </c>
       <c r="CE5" t="n">
         <v>1.43</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CI5" t="n">
         <v>1.74</v>
       </c>
       <c r="CJ5" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CK5" t="n">
         <v>1.89</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="CM5" t="n">
         <v>1.84</v>
@@ -2861,22 +2861,22 @@
         <v>1.49</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.71</v>
+        <v>3.74</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CS5" t="n">
         <v>3</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="CU5" t="n">
         <v>1.4</v>
@@ -2888,7 +2888,7 @@
         <v>2.07</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CY5" t="n">
         <v>2.47</v>
@@ -2903,52 +2903,52 @@
         <v>1.37</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="DG5" t="n">
         <v>2</v>
       </c>
       <c r="DH5" t="n">
-        <v>84.33</v>
+        <v>83.64</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.67</v>
+        <v>3.78</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="DM5" t="n">
-        <v>39.19</v>
+        <v>38.5</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="DP5" t="n">
-        <v>15.81</v>
+        <v>15.59</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.76</v>
+        <v>15</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.76</v>
+        <v>7.77</v>
       </c>
       <c r="DS5" t="n">
         <v>0.14</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>50.67</v>
+        <v>50.32</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.28</v>
+        <v>10.18</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.43</v>
+        <v>7.32</v>
       </c>
       <c r="DZ5" t="n">
         <v>2.86</v>
       </c>
       <c r="EA5" t="n">
-        <v>22.52</v>
+        <v>22.14</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" t="n">
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
         <v>0.1</v>
@@ -3084,136 +3084,136 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AI6" t="n">
-        <v>78.09999999999999</v>
+        <v>79.18000000000001</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK6" t="n">
-        <v>4.8</v>
+        <v>4.64</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.9</v>
+        <v>4.73</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AN6" t="n">
-        <v>39.6</v>
+        <v>38.27</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="AQ6" t="n">
-        <v>19</v>
+        <v>18.82</v>
       </c>
       <c r="AR6" t="n">
-        <v>13.3</v>
+        <v>13.64</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.699999999999999</v>
+        <v>8.73</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>47.4</v>
+        <v>46.73</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BA6" t="n">
-        <v>13.5</v>
+        <v>13.55</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.3</v>
+        <v>5.18</v>
       </c>
       <c r="BD6" t="n">
-        <v>17.6</v>
+        <v>17.64</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.5</v>
+        <v>4.36</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.75</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BP6" t="n">
-        <v>5.5</v>
+        <v>5.33</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.2</v>
+        <v>4.43</v>
       </c>
       <c r="BR6" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BU6" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BV6" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY6" t="n">
         <v>4.03</v>
@@ -3222,43 +3222,43 @@
         <v>4.15</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.92</v>
+        <v>3.91</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.9</v>
+        <v>3.87</v>
       </c>
       <c r="CC6" t="n">
-        <v>5.62</v>
+        <v>5.54</v>
       </c>
       <c r="CD6" t="n">
-        <v>5.25</v>
+        <v>5.23</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CH6" t="n">
         <v>1.39</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CL6" t="n">
         <v>2.45</v>
       </c>
       <c r="CM6" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CN6" t="n">
         <v>1.55</v>
@@ -3267,34 +3267,34 @@
         <v>1.31</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.55</v>
+        <v>3.59</v>
       </c>
       <c r="CR6" t="n">
         <v>1.44</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CW6" t="n">
         <v>2.01</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CZ6" t="n">
         <v>1.94</v>
@@ -3306,52 +3306,52 @@
         <v>1.35</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.74</v>
+        <v>3.76</v>
       </c>
       <c r="DE6" t="n">
         <v>0.05</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="DH6" t="n">
-        <v>81.45</v>
+        <v>81.86</v>
       </c>
       <c r="DI6" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ6" t="n">
-        <v>4.2</v>
+        <v>4.14</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.35</v>
+        <v>4.29</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="DM6" t="n">
-        <v>41.75</v>
+        <v>40.95</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.65</v>
+        <v>2.52</v>
       </c>
       <c r="DP6" t="n">
-        <v>17.55</v>
+        <v>17.52</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14.55</v>
+        <v>14.67</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.95</v>
+        <v>8</v>
       </c>
       <c r="DS6" t="n">
         <v>0.05</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>46.5</v>
+        <v>46.19</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DX6" t="n">
-        <v>14.35</v>
+        <v>14.34</v>
       </c>
       <c r="DY6" t="n">
-        <v>9.300000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="EA6" t="n">
-        <v>17.45</v>
+        <v>17.48</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="EC6" t="n">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="7">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
         <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="H7" t="n">
-        <v>86.09</v>
+        <v>84.58</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>3.64</v>
+        <v>3.75</v>
       </c>
       <c r="K7" t="n">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
       <c r="L7" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="M7" t="n">
-        <v>34</v>
+        <v>34.33</v>
       </c>
       <c r="N7" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="P7" t="n">
-        <v>16.64</v>
+        <v>16.42</v>
       </c>
       <c r="Q7" t="n">
-        <v>15.91</v>
+        <v>15.58</v>
       </c>
       <c r="R7" t="n">
-        <v>6.36</v>
+        <v>6.83</v>
       </c>
       <c r="S7" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="T7" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="U7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>45.18</v>
+        <v>44.75</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>12.18</v>
+        <v>11.67</v>
       </c>
       <c r="AA7" t="n">
-        <v>8</v>
+        <v>7.67</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.18</v>
+        <v>4</v>
       </c>
       <c r="AC7" t="n">
-        <v>18</v>
+        <v>17.58</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AE7" t="n">
-        <v>3.64</v>
+        <v>3.75</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,70 +3565,70 @@
         <v>2.9</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.24</v>
+        <v>8.27</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.62</v>
+        <v>3.64</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.52</v>
+        <v>4.55</v>
       </c>
       <c r="BR7" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS7" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BU7" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BV7" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW7" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX7" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BY7" t="n">
-        <v>4.71</v>
+        <v>4.95</v>
       </c>
       <c r="BZ7" t="n">
-        <v>4.88</v>
+        <v>5.13</v>
       </c>
       <c r="CA7" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="CB7" t="n">
         <v>3.79</v>
-      </c>
-      <c r="CB7" t="n">
-        <v>3.77</v>
       </c>
       <c r="CC7" t="n">
         <v>5.85</v>
@@ -3640,25 +3640,25 @@
         <v>1.44</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CI7" t="n">
         <v>1.74</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CK7" t="n">
         <v>1.88</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CM7" t="n">
         <v>1.85</v>
@@ -3670,16 +3670,16 @@
         <v>1.34</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="CR7" t="n">
         <v>1.45</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="CT7" t="n">
         <v>2.79</v>
@@ -3688,10 +3688,10 @@
         <v>1.39</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CX7" t="n">
         <v>1.93</v>
@@ -3712,82 +3712,82 @@
         <v>2.22</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.01</v>
+        <v>4.02</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF7" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DH7" t="n">
-        <v>84.09</v>
+        <v>83.36</v>
       </c>
       <c r="DI7" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.48</v>
+        <v>3.55</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.38</v>
+        <v>3.41</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DM7" t="n">
-        <v>32.05</v>
+        <v>32.32</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="DP7" t="n">
-        <v>16.48</v>
+        <v>16.37</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.67</v>
+        <v>14.54</v>
       </c>
       <c r="DR7" t="n">
-        <v>8</v>
+        <v>8.18</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>42.38</v>
+        <v>42.27</v>
       </c>
       <c r="DW7" t="n">
         <v>0.14</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.52</v>
+        <v>11.27</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.52</v>
+        <v>7.37</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4</v>
+        <v>3.91</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.67</v>
+        <v>17.45</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.29</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
         <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
         <v>0.36</v>
@@ -3887,139 +3887,139 @@
         <v>1.27</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AI8" t="n">
-        <v>92.8</v>
+        <v>91.91</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AL8" t="n">
-        <v>5.7</v>
+        <v>5.45</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AN8" t="n">
-        <v>42.3</v>
+        <v>41.64</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12.4</v>
+        <v>12.82</v>
       </c>
       <c r="AR8" t="n">
-        <v>15.4</v>
+        <v>15.82</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.9</v>
+        <v>6.82</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>55.8</v>
+        <v>55.27</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>10.5</v>
+        <v>10.09</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.3</v>
+        <v>6.18</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.2</v>
+        <v>3.91</v>
       </c>
       <c r="BD8" t="n">
-        <v>20.5</v>
+        <v>20.18</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.52</v>
+        <v>3.55</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.57</v>
+        <v>9.41</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.52</v>
+        <v>3.55</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BL8" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="BP8" t="n">
-        <v>5.14</v>
+        <v>5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.43</v>
+        <v>4.41</v>
       </c>
       <c r="BR8" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS8" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BT8" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BU8" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BV8" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX8" t="n">
-        <v>66.67</v>
+        <v>63.64</v>
       </c>
       <c r="BY8" t="n">
         <v>2.7</v>
@@ -4028,25 +4028,25 @@
         <v>2.76</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.7</v>
+        <v>3.73</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.88</v>
+        <v>3.91</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.02</v>
+        <v>4.33</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.99</v>
+        <v>4.3</v>
       </c>
       <c r="CE8" t="n">
         <v>1.39</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CH8" t="n">
         <v>1.38</v>
@@ -4055,13 +4055,13 @@
         <v>1.8</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CK8" t="n">
         <v>1.83</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CM8" t="n">
         <v>1.9</v>
@@ -4073,19 +4073,19 @@
         <v>1.3</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="CR8" t="n">
         <v>1.41</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CU8" t="n">
         <v>1.39</v>
@@ -4109,25 +4109,25 @@
         <v>1.57</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="DC8" t="n">
         <v>2.06</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.63</v>
+        <v>3.62</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="DH8" t="n">
-        <v>93.95</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
@@ -4136,61 +4136,61 @@
         <v>1.95</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="DM8" t="n">
-        <v>41.19</v>
+        <v>40.91</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="DP8" t="n">
-        <v>12.19</v>
+        <v>12.41</v>
       </c>
       <c r="DQ8" t="n">
-        <v>16.1</v>
+        <v>16.28</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.95</v>
+        <v>6.91</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>57.09</v>
+        <v>56.77</v>
       </c>
       <c r="DW8" t="n">
         <v>0.09</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.14</v>
+        <v>11.87</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.24</v>
+        <v>7.13</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.91</v>
+        <v>4.73</v>
       </c>
       <c r="EA8" t="n">
-        <v>22.14</v>
+        <v>21.91</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="9">
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
         <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="G9" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="H9" t="n">
-        <v>77.90000000000001</v>
+        <v>78.45</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J9" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="K9" t="n">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="M9" t="n">
-        <v>27.8</v>
+        <v>26.55</v>
       </c>
       <c r="N9" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="O9" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="P9" t="n">
-        <v>15.9</v>
+        <v>15.82</v>
       </c>
       <c r="Q9" t="n">
-        <v>16.1</v>
+        <v>16.45</v>
       </c>
       <c r="R9" t="n">
-        <v>10.1</v>
+        <v>9.82</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="T9" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>44.2</v>
+        <v>45.09</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.2</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.7</v>
+        <v>6.18</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AC9" t="n">
-        <v>17.6</v>
+        <v>18.18</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AF9" t="n">
         <v>0.4</v>
@@ -4371,34 +4371,34 @@
         <v>2.7</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.65</v>
+        <v>8.67</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BL9" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.65</v>
+        <v>4.67</v>
       </c>
       <c r="BQ9" t="n">
         <v>3.95</v>
@@ -4407,34 +4407,34 @@
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT9" t="n">
-        <v>80</v>
+        <v>76.19</v>
       </c>
       <c r="BU9" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BV9" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW9" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX9" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.39</v>
+        <v>3.44</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.15</v>
+        <v>4.11</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.44</v>
+        <v>4.4</v>
       </c>
       <c r="CC9" t="n">
         <v>7.56</v>
@@ -4443,13 +4443,13 @@
         <v>9.09</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="CG9" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="CH9" t="n">
         <v>1.43</v>
@@ -4458,13 +4458,13 @@
         <v>1.9</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CK9" t="n">
         <v>1.73</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CM9" t="n">
         <v>2.03</v>
@@ -4479,22 +4479,22 @@
         <v>1.88</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="CR9" t="n">
         <v>1.4</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CW9" t="n">
         <v>1.94</v>
@@ -4503,7 +4503,7 @@
         <v>1.74</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.09</v>
@@ -4515,85 +4515,85 @@
         <v>1.29</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.31</v>
+        <v>3.34</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="DH9" t="n">
-        <v>70.95</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="DK9" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DM9" t="n">
-        <v>25.9</v>
+        <v>25.34</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.3</v>
+        <v>14.33</v>
       </c>
       <c r="DQ9" t="n">
-        <v>16.05</v>
+        <v>16.24</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.85</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>42.6</v>
+        <v>43.14</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.949999999999999</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.6</v>
+        <v>5.38</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="EA9" t="n">
-        <v>15.6</v>
+        <v>16</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="10">
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
         <v>11</v>
@@ -4615,82 +4615,82 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="G10" t="n">
-        <v>3.6</v>
+        <v>3.91</v>
       </c>
       <c r="H10" t="n">
-        <v>133.1</v>
+        <v>133.64</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>9</v>
+        <v>9.27</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="M10" t="n">
-        <v>75.2</v>
+        <v>74.64</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="O10" t="n">
-        <v>5.3</v>
+        <v>5.27</v>
       </c>
       <c r="P10" t="n">
-        <v>11</v>
+        <v>10.91</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.8</v>
+        <v>12.82</v>
       </c>
       <c r="R10" t="n">
-        <v>4.5</v>
+        <v>4.27</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="T10" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>64.3</v>
+        <v>65</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z10" t="n">
-        <v>21.3</v>
+        <v>21.82</v>
       </c>
       <c r="AA10" t="n">
-        <v>15.1</v>
+        <v>15.36</v>
       </c>
       <c r="AB10" t="n">
-        <v>6.2</v>
+        <v>6.45</v>
       </c>
       <c r="AC10" t="n">
-        <v>26.4</v>
+        <v>27.27</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AF10" t="n">
         <v>0.18</v>
@@ -4774,70 +4774,70 @@
         <v>1.91</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.619999999999999</v>
+        <v>9.91</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BL10" t="n">
         <v>0.95</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.48</v>
+        <v>4.59</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.1</v>
+        <v>5.27</v>
       </c>
       <c r="BR10" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS10" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT10" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BU10" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BV10" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>33.33</v>
+        <v>31.82</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CA10" t="n">
-        <v>5.22</v>
+        <v>5.35</v>
       </c>
       <c r="CB10" t="n">
-        <v>5.86</v>
+        <v>5.99</v>
       </c>
       <c r="CC10" t="n">
         <v>1.68</v>
@@ -4846,43 +4846,43 @@
         <v>1.7</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.13</v>
+        <v>3.16</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CJ10" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="CM10" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CO10" t="n">
         <v>1.22</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="CR10" t="n">
         <v>1.38</v>
@@ -4903,100 +4903,100 @@
         <v>2.33</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="CZ10" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DC10" t="n">
         <v>1.86</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="DE10" t="n">
         <v>0.09</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="DG10" t="n">
-        <v>3.57</v>
+        <v>3.73</v>
       </c>
       <c r="DH10" t="n">
-        <v>125.9</v>
+        <v>126.5</v>
       </c>
       <c r="DI10" t="n">
         <v>-0.09</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="DK10" t="n">
-        <v>7.43</v>
+        <v>7.64</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="DM10" t="n">
-        <v>69.19</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="DO10" t="n">
-        <v>3.81</v>
+        <v>3.86</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.43</v>
+        <v>13.28</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.57</v>
+        <v>12.59</v>
       </c>
       <c r="DR10" t="n">
-        <v>4.53</v>
+        <v>4.41</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>61.52</v>
+        <v>62</v>
       </c>
       <c r="DW10" t="n">
         <v>0.09</v>
       </c>
       <c r="DX10" t="n">
-        <v>18.05</v>
+        <v>18.45</v>
       </c>
       <c r="DY10" t="n">
-        <v>12.33</v>
+        <v>12.59</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.71</v>
+        <v>5.86</v>
       </c>
       <c r="EA10" t="n">
-        <v>26.67</v>
+        <v>27.09</v>
       </c>
       <c r="EB10" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" t="n">
         <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
         <v>0.18</v>
@@ -5096,139 +5096,139 @@
         <v>1.64</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AI11" t="n">
-        <v>106.56</v>
+        <v>107.6</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.89</v>
+        <v>4.9</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AN11" t="n">
         <v>56</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12.56</v>
+        <v>12.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>13.11</v>
+        <v>13.1</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.11</v>
+        <v>5.2</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>61.44</v>
+        <v>61.3</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA11" t="n">
-        <v>13.56</v>
+        <v>13.2</v>
       </c>
       <c r="BB11" t="n">
         <v>9</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.56</v>
+        <v>4.2</v>
       </c>
       <c r="BD11" t="n">
-        <v>23.22</v>
+        <v>23.3</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.699999999999999</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.8</v>
+        <v>3.81</v>
       </c>
       <c r="BQ11" t="n">
         <v>4.9</v>
       </c>
       <c r="BR11" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS11" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BT11" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BU11" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV11" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW11" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX11" t="n">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="BY11" t="n">
         <v>1.53</v>
@@ -5240,13 +5240,13 @@
         <v>4.73</v>
       </c>
       <c r="CB11" t="n">
-        <v>5.26</v>
+        <v>5.2</v>
       </c>
       <c r="CC11" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="CD11" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="CE11" t="n">
         <v>1.34</v>
@@ -5258,19 +5258,19 @@
         <v>3.12</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CI11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="CK11" t="n">
         <v>1.76</v>
       </c>
-      <c r="CJ11" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="CK11" t="n">
-        <v>1.75</v>
-      </c>
       <c r="CL11" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="CM11" t="n">
         <v>1.99</v>
@@ -5282,7 +5282,7 @@
         <v>1.25</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CQ11" t="n">
         <v>2.98</v>
@@ -5291,19 +5291,19 @@
         <v>1.39</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CX11" t="n">
         <v>1.78</v>
@@ -5318,88 +5318,88 @@
         <v>1.63</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.11</v>
+        <v>3.17</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="DH11" t="n">
-        <v>108.15</v>
+        <v>108.57</v>
       </c>
       <c r="DI11" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.95</v>
+        <v>5.91</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="DM11" t="n">
-        <v>59.3</v>
+        <v>59.14</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.6</v>
+        <v>11.62</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.9</v>
+        <v>12.91</v>
       </c>
       <c r="DR11" t="n">
-        <v>4.7</v>
+        <v>4.76</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>62.1</v>
+        <v>62</v>
       </c>
       <c r="DW11" t="n">
         <v>0.05</v>
       </c>
       <c r="DX11" t="n">
-        <v>14.85</v>
+        <v>14.62</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.6</v>
+        <v>9.57</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.25</v>
+        <v>5.05</v>
       </c>
       <c r="EA11" t="n">
         <v>23.9</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
         <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5499,52 +5499,52 @@
         <v>2.09</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AI12" t="n">
-        <v>70.5</v>
+        <v>70.09</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AL12" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AN12" t="n">
-        <v>30.7</v>
+        <v>29.82</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14.3</v>
+        <v>14.27</v>
       </c>
       <c r="AR12" t="n">
-        <v>13.6</v>
+        <v>13.45</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.9</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,82 +5556,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>39.8</v>
+        <v>38.73</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BA12" t="n">
-        <v>8.6</v>
+        <v>8.27</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.5</v>
+        <v>5.36</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="BD12" t="n">
-        <v>16.6</v>
+        <v>16.18</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.52</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.14</v>
+        <v>4.27</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.33</v>
+        <v>4.55</v>
       </c>
       <c r="BR12" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS12" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="BU12" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BV12" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BW12" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX12" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BY12" t="n">
         <v>5.44</v>
@@ -5640,55 +5640,55 @@
         <v>5.7</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.83</v>
+        <v>4.03</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.08</v>
+        <v>4.28</v>
       </c>
       <c r="CC12" t="n">
-        <v>6.27</v>
+        <v>7.34</v>
       </c>
       <c r="CD12" t="n">
-        <v>7.68</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="CH12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="CO12" t="n">
         <v>1.34</v>
       </c>
-      <c r="CI12" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="CJ12" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="CK12" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="CL12" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="CM12" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="CN12" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="CO12" t="n">
-        <v>1.35</v>
-      </c>
       <c r="CP12" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.79</v>
+        <v>3.74</v>
       </c>
       <c r="CR12" t="n">
         <v>1.42</v>
@@ -5709,100 +5709,100 @@
         <v>2.15</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="CZ12" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.89</v>
+        <v>3.84</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="DG12" t="n">
         <v>1.86</v>
       </c>
       <c r="DH12" t="n">
-        <v>76.52</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="DK12" t="n">
-        <v>3.38</v>
+        <v>3.41</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DM12" t="n">
-        <v>33.29</v>
+        <v>32.73</v>
       </c>
       <c r="DN12" t="n">
         <v>1.05</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.95</v>
+        <v>13</v>
       </c>
       <c r="DQ12" t="n">
-        <v>13.1</v>
+        <v>13.04</v>
       </c>
       <c r="DR12" t="n">
-        <v>9</v>
+        <v>9.27</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>42.67</v>
+        <v>42</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DX12" t="n">
-        <v>8.43</v>
+        <v>8.27</v>
       </c>
       <c r="DY12" t="n">
-        <v>5.86</v>
+        <v>5.77</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="EA12" t="n">
-        <v>17.24</v>
+        <v>17</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
         <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
         <v>0.3</v>
@@ -5902,139 +5902,139 @@
         <v>2.3</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AI13" t="n">
-        <v>103.3</v>
+        <v>102.18</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AL13" t="n">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>49.9</v>
+        <v>49.18</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="AQ13" t="n">
-        <v>14</v>
+        <v>14.55</v>
       </c>
       <c r="AR13" t="n">
-        <v>14.7</v>
+        <v>14.73</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.5</v>
+        <v>6.18</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>56.4</v>
+        <v>55.45</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA13" t="n">
-        <v>11.7</v>
+        <v>11.73</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.5</v>
+        <v>7.55</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
       <c r="BD13" t="n">
-        <v>23.3</v>
+        <v>22.27</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="BH13" t="n">
-        <v>7.55</v>
+        <v>7.62</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.75</v>
+        <v>3.81</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
       <c r="BR13" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS13" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT13" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BU13" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BV13" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BY13" t="n">
         <v>1.71</v>
@@ -6043,25 +6043,25 @@
         <v>1.89</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.19</v>
+        <v>4.15</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.49</v>
+        <v>4.45</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="CE13" t="n">
         <v>1.38</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CH13" t="n">
         <v>1.41</v>
@@ -6070,19 +6070,19 @@
         <v>1.75</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CK13" t="n">
         <v>1.67</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CM13" t="n">
         <v>1.9</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CO13" t="n">
         <v>1.29</v>
@@ -6091,16 +6091,16 @@
         <v>1.91</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="CR13" t="n">
         <v>1.41</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CU13" t="n">
         <v>1.42</v>
@@ -6109,7 +6109,7 @@
         <v>1.76</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CX13" t="n">
         <v>1.81</v>
@@ -6118,10 +6118,10 @@
         <v>2.26</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="DB13" t="n">
         <v>1.34</v>
@@ -6130,82 +6130,82 @@
         <v>2.05</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.62</v>
+        <v>3.63</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="DH13" t="n">
-        <v>101.45</v>
+        <v>100.95</v>
       </c>
       <c r="DI13" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.7</v>
+        <v>4.81</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DM13" t="n">
-        <v>57.1</v>
+        <v>56.38</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="DO13" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="DP13" t="n">
-        <v>15.1</v>
+        <v>15.34</v>
       </c>
       <c r="DQ13" t="n">
-        <v>15.4</v>
+        <v>15.38</v>
       </c>
       <c r="DR13" t="n">
-        <v>5.65</v>
+        <v>5.52</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>55.1</v>
+        <v>54.66</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.75</v>
+        <v>12.72</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.300000000000001</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.45</v>
+        <v>4.43</v>
       </c>
       <c r="EA13" t="n">
-        <v>23.05</v>
+        <v>22.52</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="14">
@@ -6215,10 +6215,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
         <v>11</v>
@@ -6227,49 +6227,49 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="G14" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="H14" t="n">
-        <v>77.59999999999999</v>
+        <v>75.45</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="K14" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="M14" t="n">
-        <v>32.9</v>
+        <v>35.45</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="O14" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="P14" t="n">
-        <v>15.8</v>
+        <v>15.64</v>
       </c>
       <c r="Q14" t="n">
-        <v>13.6</v>
+        <v>13.91</v>
       </c>
       <c r="R14" t="n">
-        <v>7</v>
+        <v>7.45</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6281,28 +6281,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>41.3</v>
+        <v>40.18</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="Z14" t="n">
-        <v>10.4</v>
+        <v>10.09</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.1</v>
+        <v>7.82</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AC14" t="n">
-        <v>19.5</v>
+        <v>20.09</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6389,67 +6389,67 @@
         <v>3.05</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.859999999999999</v>
+        <v>8.68</v>
       </c>
       <c r="BI14" t="n">
         <v>3.05</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.29</v>
+        <v>4.18</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.52</v>
+        <v>4.45</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BT14" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BU14" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BV14" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BW14" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX14" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BY14" t="n">
-        <v>5.41</v>
+        <v>5.33</v>
       </c>
       <c r="BZ14" t="n">
-        <v>5.99</v>
+        <v>5.82</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.62</v>
+        <v>4.56</v>
       </c>
       <c r="CB14" t="n">
-        <v>5.3</v>
+        <v>5.21</v>
       </c>
       <c r="CC14" t="n">
         <v>10.46</v>
@@ -6461,10 +6461,10 @@
         <v>1.36</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="CH14" t="n">
         <v>1.44</v>
@@ -6473,28 +6473,28 @@
         <v>1.74</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CM14" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="CR14" t="n">
         <v>1.41</v>
@@ -6509,106 +6509,106 @@
         <v>1.48</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CW14" t="n">
         <v>2.16</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.32</v>
+        <v>3.39</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="DG14" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="DH14" t="n">
-        <v>65.47</v>
+        <v>64.95</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.29</v>
+        <v>3.18</v>
       </c>
       <c r="DK14" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DM14" t="n">
-        <v>28.95</v>
+        <v>30.41</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="DO14" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="DP14" t="n">
-        <v>14.52</v>
+        <v>14.5</v>
       </c>
       <c r="DQ14" t="n">
-        <v>12.33</v>
+        <v>12.54</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.380000000000001</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>37.57</v>
+        <v>37.18</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DX14" t="n">
-        <v>7.95</v>
+        <v>7.91</v>
       </c>
       <c r="DY14" t="n">
-        <v>5.86</v>
+        <v>5.82</v>
       </c>
       <c r="DZ14" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.81</v>
+        <v>18.18</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" t="n">
         <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
         <v>0.1</v>
@@ -6708,49 +6708,49 @@
         <v>2.9</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AI15" t="n">
-        <v>79.73</v>
+        <v>83.42</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AN15" t="n">
-        <v>34.64</v>
+        <v>42.17</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AQ15" t="n">
-        <v>16.55</v>
+        <v>16.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>14.27</v>
+        <v>14.42</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.27</v>
+        <v>8</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AU15" t="n">
         <v>1</v>
@@ -6765,82 +6765,82 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>46.18</v>
+        <v>48.25</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.73</v>
+        <v>9.92</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.18</v>
+        <v>6.42</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>21.18</v>
+        <v>21.83</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.380000000000001</v>
+        <v>9.18</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.86</v>
+        <v>3.77</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.48</v>
+        <v>5.36</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BT15" t="n">
-        <v>42.86</v>
+        <v>45.45</v>
       </c>
       <c r="BU15" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BV15" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW15" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX15" t="n">
-        <v>42.86</v>
+        <v>45.45</v>
       </c>
       <c r="BY15" t="n">
         <v>3.77</v>
@@ -6849,28 +6849,28 @@
         <v>3.88</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.77</v>
+        <v>3.75</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.93</v>
+        <v>3.9</v>
       </c>
       <c r="CC15" t="n">
-        <v>6.64</v>
+        <v>6.24</v>
       </c>
       <c r="CD15" t="n">
-        <v>6.96</v>
+        <v>6.55</v>
       </c>
       <c r="CE15" t="n">
         <v>1.4</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CI15" t="n">
         <v>1.78</v>
@@ -6879,16 +6879,16 @@
         <v>2.01</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CL15" t="n">
         <v>2.6</v>
       </c>
       <c r="CM15" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CO15" t="n">
         <v>1.32</v>
@@ -6897,7 +6897,7 @@
         <v>2.04</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.54</v>
+        <v>3.57</v>
       </c>
       <c r="CR15" t="n">
         <v>1.44</v>
@@ -6912,43 +6912,43 @@
         <v>1.38</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CW15" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CZ15" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="DA15" t="n">
         <v>1.57</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.74</v>
+        <v>3.79</v>
       </c>
       <c r="DE15" t="n">
         <v>0.09</v>
       </c>
       <c r="DF15" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="DH15" t="n">
-        <v>76.48</v>
+        <v>78.64</v>
       </c>
       <c r="DI15" t="n">
         <v>0.05</v>
@@ -6957,58 +6957,58 @@
         <v>3.14</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.86</v>
+        <v>3.82</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DM15" t="n">
-        <v>34.1</v>
+        <v>38.23</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="DP15" t="n">
-        <v>15.38</v>
+        <v>15.41</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.33</v>
+        <v>15.37</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.140000000000001</v>
+        <v>8</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>48.43</v>
+        <v>49.45</v>
       </c>
       <c r="DW15" t="n">
         <v>0.05</v>
       </c>
       <c r="DX15" t="n">
-        <v>11.43</v>
+        <v>11.46</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.81</v>
+        <v>7.87</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.62</v>
+        <v>3.59</v>
       </c>
       <c r="EA15" t="n">
-        <v>21.43</v>
+        <v>21.77</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="EC15" t="n">
         <v>3.05</v>

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -3466,10 +3466,10 @@
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>11.67</v>
+        <v>11.75</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.67</v>
+        <v>7.75</v>
       </c>
       <c r="AB7" t="n">
         <v>4</v>
@@ -3772,10 +3772,10 @@
         <v>0.14</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.27</v>
+        <v>11.32</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.37</v>
+        <v>7.41</v>
       </c>
       <c r="DZ7" t="n">
         <v>3.91</v>

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
         <v>11</v>
@@ -2600,82 +2600,82 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="G5" t="n">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="H5" t="n">
-        <v>94</v>
+        <v>93.08</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="K5" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="L5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="M5" t="n">
-        <v>46.27</v>
+        <v>45.92</v>
       </c>
       <c r="N5" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="O5" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="P5" t="n">
-        <v>14.82</v>
+        <v>14.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>15.36</v>
+        <v>15.75</v>
       </c>
       <c r="R5" t="n">
-        <v>5.27</v>
+        <v>5</v>
       </c>
       <c r="S5" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T5" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="U5" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="V5" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>55.18</v>
+        <v>55.08</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>12.18</v>
+        <v>11.92</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.18</v>
+        <v>8.92</v>
       </c>
       <c r="AB5" t="n">
         <v>3</v>
       </c>
       <c r="AC5" t="n">
-        <v>24.27</v>
+        <v>24.33</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="AF5" t="n">
         <v>0.18</v>
@@ -2759,70 +2759,70 @@
         <v>2.82</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.18</v>
+        <v>8</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BO5" t="n">
         <v>1.09</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.77</v>
+        <v>3.78</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.41</v>
+        <v>4.22</v>
       </c>
       <c r="BR5" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS5" t="n">
-        <v>68.18000000000001</v>
+        <v>65.22</v>
       </c>
       <c r="BT5" t="n">
-        <v>45.45</v>
+        <v>43.48</v>
       </c>
       <c r="BU5" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BV5" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>45.45</v>
+        <v>43.48</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.54</v>
+        <v>3.39</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3.88</v>
+        <v>3.7</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.63</v>
+        <v>3.61</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="CC5" t="n">
         <v>5.45</v>
@@ -2834,7 +2834,7 @@
         <v>1.43</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CG5" t="n">
         <v>2.69</v>
@@ -2849,10 +2849,10 @@
         <v>2.01</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CM5" t="n">
         <v>1.84</v>
@@ -2864,7 +2864,7 @@
         <v>1.34</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CQ5" t="n">
         <v>3.74</v>
@@ -2873,7 +2873,7 @@
         <v>1.44</v>
       </c>
       <c r="CS5" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="CT5" t="n">
         <v>2.83</v>
@@ -2891,7 +2891,7 @@
         <v>1.96</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CZ5" t="n">
         <v>1.85</v>
@@ -2912,76 +2912,76 @@
         <v>0.09</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="DG5" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DH5" t="n">
-        <v>83.64</v>
+        <v>83.61</v>
       </c>
       <c r="DI5" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="DK5" t="n">
         <v>3.78</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="DM5" t="n">
-        <v>38.5</v>
+        <v>38.66</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="DP5" t="n">
-        <v>15.59</v>
+        <v>15.39</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15</v>
+        <v>15.22</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.77</v>
+        <v>7.52</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>50.32</v>
+        <v>50.47</v>
       </c>
       <c r="DW5" t="n">
         <v>0.04</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.18</v>
+        <v>10.13</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.32</v>
+        <v>7.26</v>
       </c>
       <c r="DZ5" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="EA5" t="n">
-        <v>22.14</v>
+        <v>22.26</v>
       </c>
       <c r="EB5" t="n">
         <v>1.13</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="6">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
         <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>84.8</v>
+        <v>84.73</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="K6" t="n">
-        <v>3.8</v>
+        <v>3.73</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="M6" t="n">
-        <v>43.9</v>
+        <v>43.64</v>
       </c>
       <c r="N6" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="O6" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="P6" t="n">
-        <v>16.1</v>
+        <v>16.73</v>
       </c>
       <c r="Q6" t="n">
-        <v>15.8</v>
+        <v>15.82</v>
       </c>
       <c r="R6" t="n">
-        <v>7.2</v>
+        <v>7.27</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="T6" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3057,28 +3057,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>45.6</v>
+        <v>44.55</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>15.2</v>
+        <v>14.64</v>
       </c>
       <c r="AA6" t="n">
-        <v>10.4</v>
+        <v>10.09</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.8</v>
+        <v>4.55</v>
       </c>
       <c r="AC6" t="n">
-        <v>17.3</v>
+        <v>17.82</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.9</v>
+        <v>3.18</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,70 +3162,70 @@
         <v>4.36</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.86</v>
+        <v>2.77</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.859999999999999</v>
+        <v>9.77</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.86</v>
+        <v>2.77</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BP6" t="n">
-        <v>5.33</v>
+        <v>5.27</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.43</v>
+        <v>4.41</v>
       </c>
       <c r="BR6" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS6" t="n">
-        <v>85.70999999999999</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BU6" t="n">
-        <v>33.33</v>
+        <v>31.82</v>
       </c>
       <c r="BV6" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>71.43000000000001</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BY6" t="n">
-        <v>4.03</v>
+        <v>3.9</v>
       </c>
       <c r="BZ6" t="n">
-        <v>4.15</v>
+        <v>4.01</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.91</v>
+        <v>3.87</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.87</v>
+        <v>3.85</v>
       </c>
       <c r="CC6" t="n">
         <v>5.54</v>
@@ -3246,31 +3246,31 @@
         <v>1.39</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="CM6" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CN6" t="n">
         <v>1.55</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CP6" t="n">
         <v>2.02</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="CR6" t="n">
         <v>1.44</v>
@@ -3285,7 +3285,7 @@
         <v>1.4</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CW6" t="n">
         <v>2.01</v>
@@ -3309,82 +3309,82 @@
         <v>2.11</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.76</v>
+        <v>3.77</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="DH6" t="n">
-        <v>81.86</v>
+        <v>81.95999999999999</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ6" t="n">
-        <v>4.14</v>
+        <v>4.23</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.29</v>
+        <v>4.23</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="DM6" t="n">
-        <v>40.95</v>
+        <v>40.96</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="DP6" t="n">
-        <v>17.52</v>
+        <v>17.78</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14.67</v>
+        <v>14.73</v>
       </c>
       <c r="DR6" t="n">
         <v>8</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>46.19</v>
+        <v>45.64</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DX6" t="n">
-        <v>14.34</v>
+        <v>14.1</v>
       </c>
       <c r="DY6" t="n">
-        <v>9.33</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5</v>
+        <v>4.86</v>
       </c>
       <c r="EA6" t="n">
-        <v>17.48</v>
+        <v>17.73</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="EC6" t="n">
-        <v>3.66</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" t="n">
         <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
         <v>0.08</v>
@@ -3487,136 +3487,136 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.3</v>
+        <v>1.64</v>
       </c>
       <c r="AI7" t="n">
-        <v>81.90000000000001</v>
+        <v>82.27</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AN7" t="n">
-        <v>29.9</v>
+        <v>32.18</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AQ7" t="n">
-        <v>16.3</v>
+        <v>16.64</v>
       </c>
       <c r="AR7" t="n">
-        <v>13.3</v>
+        <v>13.27</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AU7" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>39.3</v>
+        <v>40.09</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BA7" t="n">
-        <v>10.8</v>
+        <v>10.73</v>
       </c>
       <c r="BB7" t="n">
-        <v>7</v>
+        <v>6.91</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="BD7" t="n">
-        <v>17.3</v>
+        <v>17.18</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.27</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.64</v>
+        <v>3.7</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.55</v>
+        <v>4.61</v>
       </c>
       <c r="BR7" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS7" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT7" t="n">
-        <v>36.36</v>
+        <v>39.13</v>
       </c>
       <c r="BU7" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BV7" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW7" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX7" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BY7" t="n">
         <v>4.95</v>
@@ -3625,34 +3625,34 @@
         <v>5.13</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.79</v>
+        <v>3.76</v>
       </c>
       <c r="CC7" t="n">
-        <v>5.85</v>
+        <v>5.58</v>
       </c>
       <c r="CD7" t="n">
-        <v>5.84</v>
+        <v>5.64</v>
       </c>
       <c r="CE7" t="n">
         <v>1.44</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CI7" t="n">
         <v>1.74</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CK7" t="n">
         <v>1.88</v>
@@ -3670,34 +3670,34 @@
         <v>1.34</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="CR7" t="n">
         <v>1.45</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CX7" t="n">
         <v>1.93</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CZ7" t="n">
         <v>1.88</v>
@@ -3709,85 +3709,85 @@
         <v>1.39</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.02</v>
+        <v>4.03</v>
       </c>
       <c r="DE7" t="n">
         <v>0.04</v>
       </c>
       <c r="DF7" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="DG7" t="n">
         <v>2.05</v>
       </c>
-      <c r="DG7" t="n">
-        <v>1.91</v>
-      </c>
       <c r="DH7" t="n">
-        <v>83.36</v>
+        <v>83.48</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.41</v>
+        <v>3.56</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="DM7" t="n">
-        <v>32.32</v>
+        <v>33.3</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="DP7" t="n">
-        <v>16.37</v>
+        <v>16.53</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.54</v>
+        <v>14.48</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.18</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>42.27</v>
+        <v>42.52</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.32</v>
+        <v>11.26</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.41</v>
+        <v>7.35</v>
       </c>
       <c r="DZ7" t="n">
         <v>3.91</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.45</v>
+        <v>17.39</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.36</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
         <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E8" t="n">
         <v>0.36</v>
@@ -3887,139 +3887,139 @@
         <v>1.27</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>91.91</v>
+        <v>93.83</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AL8" t="n">
-        <v>5.45</v>
+        <v>5.42</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AN8" t="n">
-        <v>41.64</v>
+        <v>43.58</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12.82</v>
+        <v>13.17</v>
       </c>
       <c r="AR8" t="n">
-        <v>15.82</v>
+        <v>16.25</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.82</v>
+        <v>6.67</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>55.27</v>
+        <v>56.17</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>10.09</v>
+        <v>9.92</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.18</v>
+        <v>6.25</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.91</v>
+        <v>3.67</v>
       </c>
       <c r="BD8" t="n">
-        <v>20.18</v>
+        <v>21.08</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.55</v>
+        <v>3.43</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.41</v>
+        <v>9.35</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.55</v>
+        <v>3.43</v>
       </c>
       <c r="BJ8" t="n">
         <v>1.09</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="BP8" t="n">
-        <v>5</v>
+        <v>4.96</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.41</v>
+        <v>4.39</v>
       </c>
       <c r="BR8" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS8" t="n">
-        <v>90.91</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>68.18000000000001</v>
+        <v>65.22</v>
       </c>
       <c r="BU8" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BV8" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX8" t="n">
-        <v>63.64</v>
+        <v>60.87</v>
       </c>
       <c r="BY8" t="n">
         <v>2.7</v>
@@ -4028,16 +4028,16 @@
         <v>2.76</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.73</v>
+        <v>3.7</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.91</v>
+        <v>3.88</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.33</v>
+        <v>4.17</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.3</v>
+        <v>4.19</v>
       </c>
       <c r="CE8" t="n">
         <v>1.39</v>
@@ -4046,7 +4046,7 @@
         <v>2.91</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CH8" t="n">
         <v>1.38</v>
@@ -4055,16 +4055,16 @@
         <v>1.8</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CK8" t="n">
         <v>1.83</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CM8" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CN8" t="n">
         <v>1.54</v>
@@ -4109,88 +4109,88 @@
         <v>1.57</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="DC8" t="n">
         <v>2.06</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.62</v>
+        <v>3.63</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="DH8" t="n">
-        <v>93.45999999999999</v>
+        <v>94.39</v>
       </c>
       <c r="DI8" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="DK8" t="n">
         <v>5</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="DM8" t="n">
-        <v>40.91</v>
+        <v>41.95</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="DP8" t="n">
-        <v>12.41</v>
+        <v>12.61</v>
       </c>
       <c r="DQ8" t="n">
-        <v>16.28</v>
+        <v>16.48</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.91</v>
+        <v>6.83</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>56.77</v>
+        <v>57.17</v>
       </c>
       <c r="DW8" t="n">
         <v>0.09</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.87</v>
+        <v>11.7</v>
       </c>
       <c r="DY8" t="n">
         <v>7.13</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.73</v>
+        <v>4.57</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.91</v>
+        <v>22.3</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="9">
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
         <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>0.09</v>
+        <v>0.25</v>
       </c>
       <c r="F9" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="H9" t="n">
-        <v>78.45</v>
+        <v>77.75</v>
       </c>
       <c r="I9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="J9" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="L9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="M9" t="n">
-        <v>26.55</v>
+        <v>27.92</v>
       </c>
       <c r="N9" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="P9" t="n">
-        <v>15.82</v>
+        <v>15.58</v>
       </c>
       <c r="Q9" t="n">
-        <v>16.45</v>
+        <v>16.75</v>
       </c>
       <c r="R9" t="n">
-        <v>9.82</v>
+        <v>9.5</v>
       </c>
       <c r="S9" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="T9" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="U9" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="V9" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>45.09</v>
+        <v>45.67</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.640000000000001</v>
+        <v>9.58</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.18</v>
+        <v>6.08</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>18.18</v>
+        <v>18.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AE9" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AF9" t="n">
         <v>0.4</v>
@@ -4374,67 +4374,67 @@
         <v>3.05</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.67</v>
+        <v>8.77</v>
       </c>
       <c r="BI9" t="n">
         <v>3.05</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BL9" t="n">
         <v>0.95</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.67</v>
+        <v>4.68</v>
       </c>
       <c r="BQ9" t="n">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT9" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BU9" t="n">
-        <v>33.33</v>
+        <v>31.82</v>
       </c>
       <c r="BV9" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX9" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.44</v>
+        <v>3.37</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.65</v>
+        <v>3.54</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.11</v>
+        <v>4.05</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.4</v>
+        <v>4.34</v>
       </c>
       <c r="CC9" t="n">
         <v>7.56</v>
@@ -4446,52 +4446,52 @@
         <v>1.38</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CI9" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="CP9" t="n">
         <v>1.9</v>
       </c>
-      <c r="CJ9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="CK9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="CL9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="CM9" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="CN9" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="CO9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="CP9" t="n">
-        <v>1.88</v>
-      </c>
       <c r="CQ9" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CV9" t="n">
         <v>1.93</v>
@@ -4500,100 +4500,100 @@
         <v>1.94</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.24</v>
+        <v>0.32</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="DH9" t="n">
-        <v>71.56999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.71</v>
+        <v>2.59</v>
       </c>
       <c r="DK9" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DM9" t="n">
-        <v>25.34</v>
+        <v>26.14</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.33</v>
+        <v>14.27</v>
       </c>
       <c r="DQ9" t="n">
-        <v>16.24</v>
+        <v>16.41</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.720000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>43.14</v>
+        <v>43.55</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.720000000000001</v>
+        <v>8.73</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.38</v>
+        <v>5.36</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.33</v>
+        <v>3.36</v>
       </c>
       <c r="EA9" t="n">
-        <v>16</v>
+        <v>16.27</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="10">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C12" t="n">
         <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5499,52 +5499,52 @@
         <v>2.09</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AI12" t="n">
-        <v>70.09</v>
+        <v>72.58</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK12" t="n">
         <v>3</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.09</v>
+        <v>2.83</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AN12" t="n">
-        <v>29.82</v>
+        <v>30.08</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14.27</v>
+        <v>14.75</v>
       </c>
       <c r="AR12" t="n">
-        <v>13.45</v>
+        <v>13.42</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.449999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,82 +5556,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>38.73</v>
+        <v>39.33</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BA12" t="n">
-        <v>8.27</v>
+        <v>8.08</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.36</v>
+        <v>5.08</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="BD12" t="n">
-        <v>16.18</v>
+        <v>16.83</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.859999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.27</v>
+        <v>4.26</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BR12" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS12" t="n">
-        <v>68.18000000000001</v>
+        <v>65.22</v>
       </c>
       <c r="BT12" t="n">
-        <v>45.45</v>
+        <v>43.48</v>
       </c>
       <c r="BU12" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV12" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BW12" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX12" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BY12" t="n">
         <v>5.44</v>
@@ -5640,22 +5640,22 @@
         <v>5.7</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.03</v>
+        <v>3.98</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.28</v>
+        <v>4.25</v>
       </c>
       <c r="CC12" t="n">
-        <v>7.34</v>
+        <v>7.11</v>
       </c>
       <c r="CD12" t="n">
-        <v>8.789999999999999</v>
+        <v>8.52</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CG12" t="n">
         <v>2.7</v>
@@ -5667,10 +5667,10 @@
         <v>1.68</v>
       </c>
       <c r="CJ12" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CL12" t="n">
         <v>2.53</v>
@@ -5694,13 +5694,13 @@
         <v>1.42</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CV12" t="n">
         <v>1.77</v>
@@ -5712,19 +5712,19 @@
         <v>1.88</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CZ12" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="DB12" t="n">
         <v>1.36</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="DD12" t="n">
         <v>3.84</v>
@@ -5733,76 +5733,76 @@
         <v>0.04</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="DH12" t="n">
-        <v>76.04000000000001</v>
+        <v>77.09</v>
       </c>
       <c r="DI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="DK12" t="n">
-        <v>3.41</v>
+        <v>3.26</v>
       </c>
       <c r="DL12" t="n">
         <v>0.09</v>
       </c>
       <c r="DM12" t="n">
-        <v>32.73</v>
+        <v>32.74</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="DP12" t="n">
-        <v>13</v>
+        <v>13.31</v>
       </c>
       <c r="DQ12" t="n">
-        <v>13.04</v>
+        <v>13.05</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.27</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>42</v>
+        <v>42.17</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DX12" t="n">
-        <v>8.27</v>
+        <v>8.17</v>
       </c>
       <c r="DY12" t="n">
-        <v>5.77</v>
+        <v>5.61</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="EA12" t="n">
-        <v>17</v>
+        <v>17.3</v>
       </c>
       <c r="EB12" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="13">

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="n">
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
         <v>0.09</v>
@@ -1469,139 +1469,139 @@
         <v>2.64</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AI2" t="n">
-        <v>90.27</v>
+        <v>92.92</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK2" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="AL2" t="n">
-        <v>5.45</v>
+        <v>5.58</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AN2" t="n">
-        <v>52.09</v>
+        <v>53.67</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="AQ2" t="n">
-        <v>15.55</v>
+        <v>15.83</v>
       </c>
       <c r="AR2" t="n">
-        <v>13.09</v>
+        <v>13.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.27</v>
+        <v>6.92</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>57.82</v>
+        <v>59.42</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA2" t="n">
-        <v>13.91</v>
+        <v>14.17</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.640000000000001</v>
+        <v>9.83</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.27</v>
+        <v>4.33</v>
       </c>
       <c r="BD2" t="n">
-        <v>20.55</v>
+        <v>20.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.41</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="BQ2" t="n">
         <v>3.91</v>
       </c>
       <c r="BR2" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS2" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BT2" t="n">
-        <v>36.36</v>
+        <v>39.13</v>
       </c>
       <c r="BU2" t="n">
-        <v>31.82</v>
+        <v>34.78</v>
       </c>
       <c r="BV2" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>31.82</v>
+        <v>34.78</v>
       </c>
       <c r="BY2" t="n">
         <v>1.53</v>
@@ -1610,25 +1610,25 @@
         <v>1.54</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.51</v>
+        <v>4.54</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.89</v>
+        <v>4.93</v>
       </c>
       <c r="CC2" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="CE2" t="n">
         <v>1.36</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CH2" t="n">
         <v>1.44</v>
@@ -1643,7 +1643,7 @@
         <v>1.77</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CM2" t="n">
         <v>1.96</v>
@@ -1658,7 +1658,7 @@
         <v>1.86</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CR2" t="n">
         <v>1.39</v>
@@ -1679,13 +1679,13 @@
         <v>2.14</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CY2" t="n">
         <v>2.29</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="DA2" t="n">
         <v>1.61</v>
@@ -1694,85 +1694,85 @@
         <v>1.29</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="DH2" t="n">
-        <v>93.77</v>
+        <v>95</v>
       </c>
       <c r="DI2" t="n">
         <v>0.13</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.32</v>
+        <v>5.39</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="DM2" t="n">
-        <v>54.68</v>
+        <v>55.39</v>
       </c>
       <c r="DN2" t="n">
         <v>1</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.69</v>
+        <v>2.74</v>
       </c>
       <c r="DP2" t="n">
-        <v>15.78</v>
+        <v>15.91</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.54</v>
+        <v>13.74</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.22</v>
+        <v>6.09</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>57.5</v>
+        <v>58.35</v>
       </c>
       <c r="DW2" t="n">
         <v>0.13</v>
       </c>
       <c r="DX2" t="n">
-        <v>15.13</v>
+        <v>15.22</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.41</v>
+        <v>10.48</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.72</v>
+        <v>4.74</v>
       </c>
       <c r="EA2" t="n">
-        <v>20.73</v>
+        <v>20.7</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" t="n">
         <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1872,130 +1872,130 @@
         <v>2.82</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="AI3" t="n">
-        <v>86.27</v>
+        <v>88.25</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.36</v>
+        <v>4.42</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AN3" t="n">
-        <v>37.18</v>
+        <v>37.33</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AQ3" t="n">
-        <v>16.36</v>
+        <v>16.17</v>
       </c>
       <c r="AR3" t="n">
-        <v>14.27</v>
+        <v>14.08</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.82</v>
+        <v>6.75</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>49.55</v>
+        <v>50.25</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.64</v>
+        <v>10.83</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.27</v>
+        <v>7.67</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.36</v>
+        <v>3.17</v>
       </c>
       <c r="BD3" t="n">
-        <v>19.36</v>
+        <v>19.17</v>
       </c>
       <c r="BE3" t="n">
         <v>1.18</v>
       </c>
       <c r="BF3" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.23</v>
+        <v>9.09</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BP3" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.91</v>
+        <v>5.78</v>
       </c>
       <c r="BR3" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BS3" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BT3" t="n">
-        <v>27.27</v>
+        <v>30.43</v>
       </c>
       <c r="BU3" t="n">
-        <v>9.09</v>
+        <v>13.04</v>
       </c>
       <c r="BV3" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BY3" t="n">
         <v>2.72</v>
@@ -2016,52 +2016,52 @@
         <v>3.59</v>
       </c>
       <c r="CB3" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="CC3" t="n">
         <v>3.73</v>
       </c>
-      <c r="CC3" t="n">
-        <v>3.61</v>
-      </c>
       <c r="CD3" t="n">
-        <v>4.44</v>
+        <v>4.53</v>
       </c>
       <c r="CE3" t="n">
         <v>1.44</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CH3" t="n">
         <v>1.34</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CJ3" t="n">
         <v>2.02</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CM3" t="n">
         <v>1.88</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CO3" t="n">
         <v>1.36</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.87</v>
+        <v>3.92</v>
       </c>
       <c r="CR3" t="n">
         <v>1.45</v>
@@ -2076,10 +2076,10 @@
         <v>1.37</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CX3" t="n">
         <v>1.87</v>
@@ -2097,52 +2097,52 @@
         <v>1.39</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.06</v>
+        <v>4.12</v>
       </c>
       <c r="DE3" t="n">
         <v>0.04</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="DH3" t="n">
-        <v>90.72</v>
+        <v>91.56</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.14</v>
+        <v>5.13</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DM3" t="n">
-        <v>42.5</v>
+        <v>42.35</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="DP3" t="n">
-        <v>15.27</v>
+        <v>15.22</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.91</v>
+        <v>14.78</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.18</v>
+        <v>7.13</v>
       </c>
       <c r="DS3" t="n">
         <v>0.04</v>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>51.23</v>
+        <v>51.52</v>
       </c>
       <c r="DW3" t="n">
         <v>0.13</v>
@@ -2163,19 +2163,19 @@
         <v>12.87</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.09</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.77</v>
+        <v>3.65</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.31</v>
+        <v>20.17</v>
       </c>
       <c r="EB3" t="n">
         <v>1.38</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="n">
         <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
         <v>0.18</v>
@@ -2278,136 +2278,136 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AI4" t="n">
-        <v>76.81999999999999</v>
+        <v>75.42</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.18</v>
+        <v>3.92</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AN4" t="n">
-        <v>32.82</v>
+        <v>31.58</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14.91</v>
+        <v>15.08</v>
       </c>
       <c r="AR4" t="n">
-        <v>16.18</v>
+        <v>15.75</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.18</v>
+        <v>8.25</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>44.64</v>
+        <v>43.92</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA4" t="n">
-        <v>9.27</v>
+        <v>8.75</v>
       </c>
       <c r="BB4" t="n">
-        <v>6</v>
+        <v>5.67</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.27</v>
+        <v>3.08</v>
       </c>
       <c r="BD4" t="n">
-        <v>18.64</v>
+        <v>18.42</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.949999999999999</v>
+        <v>9.83</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.09</v>
+        <v>5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.86</v>
+        <v>4.83</v>
       </c>
       <c r="BR4" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS4" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BT4" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BU4" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV4" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX4" t="n">
-        <v>45.45</v>
+        <v>43.48</v>
       </c>
       <c r="BY4" t="n">
         <v>3.63</v>
@@ -2416,43 +2416,43 @@
         <v>4.37</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.64</v>
+        <v>3.74</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.87</v>
+        <v>3.97</v>
       </c>
       <c r="CC4" t="n">
-        <v>6</v>
+        <v>6.71</v>
       </c>
       <c r="CD4" t="n">
-        <v>6.42</v>
+        <v>6.78</v>
       </c>
       <c r="CE4" t="n">
         <v>1.43</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="CH4" t="n">
         <v>1.36</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CM4" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CN4" t="n">
         <v>1.54</v>
@@ -2461,91 +2461,91 @@
         <v>1.33</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CS4" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="CU4" t="n">
         <v>1.39</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CZ4" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="DE4" t="n">
         <v>0.09</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="DH4" t="n">
-        <v>79.18000000000001</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.27</v>
+        <v>3.22</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.82</v>
+        <v>4.65</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DM4" t="n">
-        <v>38.96</v>
+        <v>38.04</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.82</v>
+        <v>13.96</v>
       </c>
       <c r="DQ4" t="n">
-        <v>15.77</v>
+        <v>15.56</v>
       </c>
       <c r="DR4" t="n">
-        <v>8</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="DS4" t="n">
         <v>0.13</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>45.54</v>
+        <v>45.13</v>
       </c>
       <c r="DW4" t="n">
         <v>0.13</v>
       </c>
       <c r="DX4" t="n">
-        <v>9.539999999999999</v>
+        <v>9.26</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.09</v>
+        <v>5.91</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.78</v>
+        <v>20.57</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="EC4" t="n">
-        <v>3.09</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="5">
@@ -3953,16 +3953,16 @@
         <v>9.92</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.25</v>
+        <v>6.17</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.67</v>
+        <v>3.75</v>
       </c>
       <c r="BD8" t="n">
         <v>21.08</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="BF8" t="n">
         <v>2.25</v>
@@ -4178,16 +4178,16 @@
         <v>11.7</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.13</v>
+        <v>7.09</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.57</v>
+        <v>4.61</v>
       </c>
       <c r="EA8" t="n">
         <v>22.3</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="EC8" t="n">
         <v>1.78</v>
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" t="n">
         <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4693,139 +4693,139 @@
         <v>0.82</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG10" t="n">
         <v>1</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="AI10" t="n">
-        <v>119.36</v>
+        <v>125.5</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="AK10" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AL10" t="n">
-        <v>6</v>
+        <v>5.92</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AN10" t="n">
-        <v>63.73</v>
+        <v>65.75</v>
       </c>
       <c r="AO10" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>15.64</v>
+        <v>15.33</v>
       </c>
       <c r="AR10" t="n">
-        <v>12.36</v>
+        <v>12</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.55</v>
+        <v>4.42</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>59</v>
+        <v>60.42</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA10" t="n">
-        <v>15.09</v>
+        <v>15.58</v>
       </c>
       <c r="BB10" t="n">
-        <v>9.82</v>
+        <v>9.92</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.27</v>
+        <v>5.67</v>
       </c>
       <c r="BD10" t="n">
-        <v>26.91</v>
+        <v>26.67</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.91</v>
+        <v>9.74</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.55</v>
+        <v>0.61</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.59</v>
+        <v>4.52</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.27</v>
+        <v>5.17</v>
       </c>
       <c r="BR10" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS10" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT10" t="n">
-        <v>36.36</v>
+        <v>39.13</v>
       </c>
       <c r="BU10" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BV10" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>31.82</v>
+        <v>34.78</v>
       </c>
       <c r="BY10" t="n">
         <v>1.25</v>
@@ -4834,34 +4834,34 @@
         <v>1.25</v>
       </c>
       <c r="CA10" t="n">
-        <v>5.35</v>
+        <v>5.46</v>
       </c>
       <c r="CB10" t="n">
-        <v>5.99</v>
+        <v>6.14</v>
       </c>
       <c r="CC10" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="CD10" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="CE10" t="n">
         <v>1.33</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="CH10" t="n">
         <v>1.49</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CJ10" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="CK10" t="n">
         <v>1.82</v>
@@ -4879,16 +4879,16 @@
         <v>1.22</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="CR10" t="n">
         <v>1.38</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CT10" t="n">
         <v>3.02</v>
@@ -4897,10 +4897,10 @@
         <v>1.5</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="CX10" t="n">
         <v>1.83</v>
@@ -4912,16 +4912,16 @@
         <v>2</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="DB10" t="n">
         <v>1.27</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="DE10" t="n">
         <v>0.09</v>
@@ -4930,73 +4930,73 @@
         <v>0.78</v>
       </c>
       <c r="DG10" t="n">
-        <v>3.73</v>
+        <v>3.65</v>
       </c>
       <c r="DH10" t="n">
-        <v>126.5</v>
+        <v>129.39</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="DK10" t="n">
-        <v>7.64</v>
+        <v>7.52</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="DM10" t="n">
-        <v>69.18000000000001</v>
+        <v>70</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="DO10" t="n">
-        <v>3.86</v>
+        <v>3.82</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.28</v>
+        <v>13.22</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.59</v>
+        <v>12.39</v>
       </c>
       <c r="DR10" t="n">
-        <v>4.41</v>
+        <v>4.35</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>62</v>
+        <v>62.61</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX10" t="n">
-        <v>18.45</v>
+        <v>18.56</v>
       </c>
       <c r="DY10" t="n">
-        <v>12.59</v>
+        <v>12.52</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.86</v>
+        <v>6.04</v>
       </c>
       <c r="EA10" t="n">
-        <v>27.09</v>
+        <v>26.96</v>
       </c>
       <c r="EB10" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="11">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="F11" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="G11" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="H11" t="n">
-        <v>109.45</v>
+        <v>107.67</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J11" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="K11" t="n">
-        <v>6.82</v>
+        <v>6.75</v>
       </c>
       <c r="L11" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="M11" t="n">
-        <v>62</v>
+        <v>61.42</v>
       </c>
       <c r="N11" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="P11" t="n">
-        <v>10.82</v>
+        <v>11</v>
       </c>
       <c r="Q11" t="n">
-        <v>12.73</v>
+        <v>13.17</v>
       </c>
       <c r="R11" t="n">
-        <v>4.36</v>
+        <v>4.33</v>
       </c>
       <c r="S11" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="T11" t="n">
         <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>62.64</v>
+        <v>62.75</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>15.91</v>
+        <v>16.42</v>
       </c>
       <c r="AA11" t="n">
-        <v>10.09</v>
+        <v>10.33</v>
       </c>
       <c r="AB11" t="n">
-        <v>5.82</v>
+        <v>6.08</v>
       </c>
       <c r="AC11" t="n">
-        <v>24.45</v>
+        <v>23.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AF11" t="n">
         <v>0.2</v>
@@ -5177,70 +5177,70 @@
         <v>1.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.710000000000001</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BN11" t="n">
         <v>1.14</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.81</v>
+        <v>3.77</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.9</v>
+        <v>4.86</v>
       </c>
       <c r="BR11" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BS11" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT11" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BU11" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BV11" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX11" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.73</v>
+        <v>4.79</v>
       </c>
       <c r="CB11" t="n">
-        <v>5.2</v>
+        <v>5.24</v>
       </c>
       <c r="CC11" t="n">
         <v>1.79</v>
@@ -5252,13 +5252,13 @@
         <v>1.34</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CG11" t="n">
         <v>3.12</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CI11" t="n">
         <v>1.75</v>
@@ -5267,13 +5267,13 @@
         <v>2.03</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CL11" t="n">
         <v>2.36</v>
       </c>
       <c r="CM11" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CN11" t="n">
         <v>1.59</v>
@@ -5282,124 +5282,124 @@
         <v>1.25</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="CR11" t="n">
         <v>1.39</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CT11" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="CU11" t="n">
         <v>1.47</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="DB11" t="n">
         <v>1.28</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.33</v>
+        <v>3.36</v>
       </c>
       <c r="DH11" t="n">
-        <v>108.57</v>
+        <v>107.64</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="DK11" t="n">
         <v>5.91</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="DM11" t="n">
-        <v>59.14</v>
+        <v>58.96</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.62</v>
+        <v>11.68</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.91</v>
+        <v>13.14</v>
       </c>
       <c r="DR11" t="n">
-        <v>4.76</v>
+        <v>4.73</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>62</v>
+        <v>62.09</v>
       </c>
       <c r="DW11" t="n">
         <v>0.05</v>
       </c>
       <c r="DX11" t="n">
-        <v>14.62</v>
+        <v>14.96</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.57</v>
+        <v>9.73</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.05</v>
+        <v>5.23</v>
       </c>
       <c r="EA11" t="n">
-        <v>23.9</v>
+        <v>23.55</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="12">
@@ -5812,94 +5812,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" t="n">
         <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="H13" t="n">
-        <v>99.59999999999999</v>
+        <v>97.45</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J13" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="K13" t="n">
-        <v>5.2</v>
+        <v>4.82</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="M13" t="n">
-        <v>64.3</v>
+        <v>62.09</v>
       </c>
       <c r="N13" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="O13" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="P13" t="n">
-        <v>16.2</v>
+        <v>15.91</v>
       </c>
       <c r="Q13" t="n">
-        <v>16.1</v>
+        <v>15.82</v>
       </c>
       <c r="R13" t="n">
-        <v>4.8</v>
+        <v>5.18</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="T13" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>53.8</v>
+        <v>52.73</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z13" t="n">
-        <v>13.8</v>
+        <v>13.45</v>
       </c>
       <c r="AA13" t="n">
-        <v>9.1</v>
+        <v>8.91</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.7</v>
+        <v>4.55</v>
       </c>
       <c r="AC13" t="n">
-        <v>22.8</v>
+        <v>22.09</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AF13" t="n">
         <v>0.27</v>
@@ -5983,70 +5983,70 @@
         <v>2.36</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="BH13" t="n">
-        <v>7.62</v>
+        <v>7.55</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.81</v>
+        <v>3.77</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3.71</v>
+        <v>3.68</v>
       </c>
       <c r="BR13" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS13" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT13" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BU13" t="n">
-        <v>19.05</v>
+        <v>22.73</v>
       </c>
       <c r="BV13" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BY13" t="n">
         <v>1.71</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.15</v>
+        <v>4.12</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="CC13" t="n">
         <v>2.43</v>
@@ -6055,49 +6055,49 @@
         <v>2.88</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CI13" t="n">
         <v>1.75</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="CM13" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CN13" t="n">
         <v>1.61</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.29</v>
+        <v>3.37</v>
       </c>
       <c r="CR13" t="n">
         <v>1.41</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CT13" t="n">
         <v>2.9</v>
@@ -6112,10 +6112,10 @@
         <v>2.15</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.01</v>
@@ -6124,88 +6124,88 @@
         <v>1.62</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.63</v>
+        <v>3.71</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="DH13" t="n">
-        <v>100.95</v>
+        <v>99.81999999999999</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.81</v>
+        <v>4.64</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="DM13" t="n">
-        <v>56.38</v>
+        <v>55.64</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="DP13" t="n">
-        <v>15.34</v>
+        <v>15.23</v>
       </c>
       <c r="DQ13" t="n">
-        <v>15.38</v>
+        <v>15.28</v>
       </c>
       <c r="DR13" t="n">
-        <v>5.52</v>
+        <v>5.68</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>54.66</v>
+        <v>54.09</v>
       </c>
       <c r="DW13" t="n">
         <v>0.09</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.72</v>
+        <v>12.59</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.289999999999999</v>
+        <v>8.23</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.43</v>
+        <v>4.36</v>
       </c>
       <c r="EA13" t="n">
-        <v>22.52</v>
+        <v>22.18</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="14">
@@ -6215,10 +6215,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
         <v>11</v>
@@ -6227,49 +6227,49 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="G14" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="H14" t="n">
-        <v>75.45</v>
+        <v>73.5</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="K14" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="L14" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="M14" t="n">
-        <v>35.45</v>
+        <v>34</v>
       </c>
       <c r="N14" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="O14" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="P14" t="n">
-        <v>15.64</v>
+        <v>14.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>13.91</v>
+        <v>13.75</v>
       </c>
       <c r="R14" t="n">
-        <v>7.45</v>
+        <v>7.83</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
       </c>
       <c r="T14" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6281,28 +6281,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>40.18</v>
+        <v>38.83</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>10.09</v>
+        <v>9.58</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.82</v>
+        <v>7.33</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>20.09</v>
+        <v>19.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6386,70 +6386,70 @@
         <v>2.82</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.68</v>
+        <v>8.57</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.18</v>
+        <v>4.13</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.45</v>
+        <v>4.39</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BU14" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV14" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BW14" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX14" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BY14" t="n">
-        <v>5.33</v>
+        <v>6.39</v>
       </c>
       <c r="BZ14" t="n">
-        <v>5.82</v>
+        <v>7.41</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.56</v>
+        <v>4.7</v>
       </c>
       <c r="CB14" t="n">
-        <v>5.21</v>
+        <v>5.39</v>
       </c>
       <c r="CC14" t="n">
         <v>10.46</v>
@@ -6461,25 +6461,25 @@
         <v>1.36</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="CH14" t="n">
         <v>1.44</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CM14" t="n">
         <v>1.96</v>
@@ -6488,19 +6488,19 @@
         <v>1.58</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="CR14" t="n">
         <v>1.41</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="CT14" t="n">
         <v>2.93</v>
@@ -6509,16 +6509,16 @@
         <v>1.48</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CZ14" t="n">
         <v>2</v>
@@ -6530,52 +6530,52 @@
         <v>1.31</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.39</v>
+        <v>3.36</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="DG14" t="n">
         <v>1.22</v>
       </c>
       <c r="DH14" t="n">
-        <v>64.95</v>
+        <v>64.39</v>
       </c>
       <c r="DI14" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.18</v>
+        <v>3.09</v>
       </c>
       <c r="DK14" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DM14" t="n">
-        <v>30.41</v>
+        <v>29.87</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="DO14" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="DP14" t="n">
-        <v>14.5</v>
+        <v>14.13</v>
       </c>
       <c r="DQ14" t="n">
-        <v>12.54</v>
+        <v>12.52</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.539999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="DS14" t="n">
         <v>0.04</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>37.18</v>
+        <v>36.61</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="DX14" t="n">
-        <v>7.91</v>
+        <v>7.74</v>
       </c>
       <c r="DY14" t="n">
-        <v>5.82</v>
+        <v>5.65</v>
       </c>
       <c r="DZ14" t="n">
         <v>2.09</v>
       </c>
       <c r="EA14" t="n">
-        <v>18.18</v>
+        <v>17.82</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="15">
@@ -6618,94 +6618,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
         <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="G15" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="H15" t="n">
-        <v>72.90000000000001</v>
+        <v>70.36</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J15" t="n">
-        <v>3.1</v>
+        <v>3.36</v>
       </c>
       <c r="K15" t="n">
-        <v>5</v>
+        <v>4.64</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="M15" t="n">
-        <v>33.5</v>
+        <v>31.82</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="O15" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="P15" t="n">
-        <v>14.1</v>
+        <v>14.64</v>
       </c>
       <c r="Q15" t="n">
-        <v>16.5</v>
+        <v>16.73</v>
       </c>
       <c r="R15" t="n">
-        <v>8</v>
+        <v>7.73</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>50.9</v>
+        <v>48.36</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z15" t="n">
-        <v>13.3</v>
+        <v>12.64</v>
       </c>
       <c r="AA15" t="n">
-        <v>9.6</v>
+        <v>8.91</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.7</v>
+        <v>3.73</v>
       </c>
       <c r="AC15" t="n">
-        <v>21.7</v>
+        <v>20.36</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.9</v>
+        <v>3.18</v>
       </c>
       <c r="AF15" t="n">
         <v>0.08</v>
@@ -6789,70 +6789,70 @@
         <v>3.17</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.18</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.77</v>
+        <v>3.78</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.36</v>
+        <v>5.3</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BT15" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BU15" t="n">
-        <v>9.09</v>
+        <v>13.04</v>
       </c>
       <c r="BV15" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW15" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX15" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BY15" t="n">
-        <v>3.77</v>
+        <v>4.24</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.88</v>
+        <v>4.54</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.75</v>
+        <v>3.82</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.9</v>
+        <v>3.98</v>
       </c>
       <c r="CC15" t="n">
         <v>6.24</v>
@@ -6867,37 +6867,37 @@
         <v>2.9</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CJ15" t="n">
         <v>2.01</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="CM15" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CO15" t="n">
         <v>1.32</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.57</v>
+        <v>3.54</v>
       </c>
       <c r="CR15" t="n">
         <v>1.44</v>
@@ -6912,19 +6912,19 @@
         <v>1.38</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CW15" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CZ15" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DA15" t="n">
         <v>1.57</v>
@@ -6933,85 +6933,85 @@
         <v>1.36</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.79</v>
+        <v>3.76</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF15" t="n">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="DH15" t="n">
-        <v>78.64</v>
+        <v>77.17</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.14</v>
+        <v>3.26</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.82</v>
+        <v>3.7</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="DM15" t="n">
-        <v>38.23</v>
+        <v>37.22</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="DP15" t="n">
-        <v>15.41</v>
+        <v>15.61</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.37</v>
+        <v>15.52</v>
       </c>
       <c r="DR15" t="n">
-        <v>8</v>
+        <v>7.87</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>49.45</v>
+        <v>48.3</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX15" t="n">
-        <v>11.46</v>
+        <v>11.22</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.87</v>
+        <v>7.61</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.59</v>
+        <v>3.61</v>
       </c>
       <c r="EA15" t="n">
-        <v>21.77</v>
+        <v>21.13</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="EC15" t="n">
-        <v>3.05</v>
+        <v>3.17</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
         <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F6" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="H6" t="n">
-        <v>84.73</v>
+        <v>86.08</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3.82</v>
+        <v>3.58</v>
       </c>
       <c r="K6" t="n">
-        <v>3.73</v>
+        <v>3.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="M6" t="n">
-        <v>43.64</v>
+        <v>42.67</v>
       </c>
       <c r="N6" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="P6" t="n">
-        <v>16.73</v>
+        <v>16.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>15.82</v>
+        <v>16.33</v>
       </c>
       <c r="R6" t="n">
-        <v>7.27</v>
+        <v>7.08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="T6" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3057,28 +3057,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>44.55</v>
+        <v>44.58</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>14.64</v>
+        <v>14</v>
       </c>
       <c r="AA6" t="n">
-        <v>10.09</v>
+        <v>9.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>17.82</v>
+        <v>18.33</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="AE6" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,70 +3162,70 @@
         <v>4.36</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.77</v>
+        <v>9.48</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BP6" t="n">
-        <v>5.27</v>
+        <v>5.13</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.41</v>
+        <v>4.26</v>
       </c>
       <c r="BR6" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS6" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT6" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BU6" t="n">
-        <v>31.82</v>
+        <v>34.78</v>
       </c>
       <c r="BV6" t="n">
-        <v>13.64</v>
+        <v>17.39</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BY6" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="CA6" t="n">
         <v>3.9</v>
       </c>
-      <c r="BZ6" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>3.87</v>
-      </c>
       <c r="CB6" t="n">
-        <v>3.85</v>
+        <v>3.88</v>
       </c>
       <c r="CC6" t="n">
         <v>5.54</v>
@@ -3234,19 +3234,19 @@
         <v>5.23</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CF6" t="n">
         <v>2.89</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="CH6" t="n">
         <v>1.39</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.93</v>
@@ -3264,13 +3264,13 @@
         <v>1.55</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="CR6" t="n">
         <v>1.44</v>
@@ -3285,19 +3285,19 @@
         <v>1.4</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CZ6" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DA6" t="n">
         <v>1.57</v>
@@ -3309,49 +3309,49 @@
         <v>2.11</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.77</v>
+        <v>3.75</v>
       </c>
       <c r="DE6" t="n">
         <v>0.04</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.68</v>
+        <v>2.61</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="DH6" t="n">
-        <v>81.95999999999999</v>
+        <v>82.78</v>
       </c>
       <c r="DI6" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ6" t="n">
-        <v>4.23</v>
+        <v>4.09</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.23</v>
+        <v>4.09</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="DM6" t="n">
-        <v>40.96</v>
+        <v>40.57</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.46</v>
+        <v>2.35</v>
       </c>
       <c r="DP6" t="n">
-        <v>17.78</v>
+        <v>17.61</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14.73</v>
+        <v>15.04</v>
       </c>
       <c r="DR6" t="n">
-        <v>8</v>
+        <v>7.87</v>
       </c>
       <c r="DS6" t="n">
         <v>0.04</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>45.64</v>
+        <v>45.61</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DX6" t="n">
-        <v>14.1</v>
+        <v>13.78</v>
       </c>
       <c r="DY6" t="n">
-        <v>9.220000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.86</v>
+        <v>4.83</v>
       </c>
       <c r="EA6" t="n">
-        <v>17.73</v>
+        <v>18</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="EC6" t="n">
-        <v>3.77</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="7">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
         <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
         <v>0.25</v>
@@ -4290,139 +4290,139 @@
         <v>1.83</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AI9" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AN9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12.7</v>
+        <v>12.18</v>
       </c>
       <c r="AR9" t="n">
-        <v>16</v>
+        <v>15.82</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.6</v>
+        <v>9.27</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AU9" t="n">
         <v>1</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>41</v>
+        <v>41.45</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.7</v>
+        <v>7.36</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.5</v>
+        <v>4.27</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="BD9" t="n">
-        <v>13.6</v>
+        <v>14.27</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.05</v>
+        <v>3.13</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.77</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.05</v>
+        <v>3.13</v>
       </c>
       <c r="BJ9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BL9" t="n">
         <v>1</v>
       </c>
-      <c r="BK9" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>0.95</v>
-      </c>
       <c r="BM9" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.68</v>
+        <v>4.61</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.05</v>
+        <v>3.96</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT9" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BU9" t="n">
-        <v>31.82</v>
+        <v>34.78</v>
       </c>
       <c r="BV9" t="n">
-        <v>9.09</v>
+        <v>13.04</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX9" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BY9" t="n">
         <v>3.37</v>
@@ -4431,16 +4431,16 @@
         <v>3.54</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.05</v>
+        <v>4.07</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.34</v>
+        <v>4.35</v>
       </c>
       <c r="CC9" t="n">
-        <v>7.56</v>
+        <v>7.51</v>
       </c>
       <c r="CD9" t="n">
-        <v>9.09</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="CE9" t="n">
         <v>1.38</v>
@@ -4455,25 +4455,25 @@
         <v>1.42</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="CM9" t="n">
         <v>2.02</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CP9" t="n">
         <v>1.9</v>
@@ -4482,22 +4482,22 @@
         <v>3.2</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CS9" t="n">
         <v>2.83</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="CU9" t="n">
         <v>1.46</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CX9" t="n">
         <v>1.75</v>
@@ -4521,79 +4521,79 @@
         <v>3.38</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="DH9" t="n">
-        <v>71.5</v>
+        <v>72.13</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="DK9" t="n">
-        <v>2.96</v>
+        <v>2.83</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DM9" t="n">
-        <v>26.14</v>
+        <v>27</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.27</v>
+        <v>13.95</v>
       </c>
       <c r="DQ9" t="n">
-        <v>16.41</v>
+        <v>16.31</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.550000000000001</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>43.55</v>
+        <v>43.65</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.73</v>
+        <v>8.52</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.36</v>
+        <v>5.21</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.27</v>
+        <v>16.48</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="10">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
         <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
         <v>0.25</v>
@@ -5096,139 +5096,139 @@
         <v>1.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG11" t="n">
         <v>1</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AI11" t="n">
-        <v>107.6</v>
+        <v>106.73</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.9</v>
+        <v>4.64</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AN11" t="n">
-        <v>56</v>
+        <v>54.91</v>
       </c>
       <c r="AO11" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>60.73</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>23.09</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="BK11" t="n">
         <v>0.7</v>
       </c>
-      <c r="AP11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>8.640000000000001</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>0.68</v>
-      </c>
       <c r="BL11" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.36</v>
+        <v>0.48</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.77</v>
+        <v>3.7</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.86</v>
+        <v>4.7</v>
       </c>
       <c r="BR11" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BS11" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT11" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BU11" t="n">
-        <v>22.73</v>
+        <v>26.09</v>
       </c>
       <c r="BV11" t="n">
-        <v>18.18</v>
+        <v>21.74</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX11" t="n">
-        <v>36.36</v>
+        <v>39.13</v>
       </c>
       <c r="BY11" t="n">
         <v>1.5</v>
@@ -5237,16 +5237,16 @@
         <v>1.54</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.79</v>
+        <v>4.77</v>
       </c>
       <c r="CB11" t="n">
-        <v>5.24</v>
+        <v>5.22</v>
       </c>
       <c r="CC11" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="CD11" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="CE11" t="n">
         <v>1.34</v>
@@ -5255,13 +5255,13 @@
         <v>2.6</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CJ11" t="n">
         <v>2.03</v>
@@ -5270,7 +5270,7 @@
         <v>1.75</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CM11" t="n">
         <v>2</v>
@@ -5285,7 +5285,7 @@
         <v>1.78</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="CR11" t="n">
         <v>1.39</v>
@@ -5300,10 +5300,10 @@
         <v>1.47</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CX11" t="n">
         <v>1.77</v>
@@ -5321,85 +5321,85 @@
         <v>1.28</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF11" t="n">
         <v>1.04</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.36</v>
+        <v>3.22</v>
       </c>
       <c r="DH11" t="n">
-        <v>107.64</v>
+        <v>107.22</v>
       </c>
       <c r="DI11" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.91</v>
+        <v>5.74</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM11" t="n">
-        <v>58.96</v>
+        <v>58.31</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.68</v>
+        <v>12.22</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13.14</v>
+        <v>13.26</v>
       </c>
       <c r="DR11" t="n">
-        <v>4.73</v>
+        <v>4.74</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>62.09</v>
+        <v>61.78</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX11" t="n">
-        <v>14.96</v>
+        <v>14.7</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.73</v>
+        <v>9.52</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.23</v>
+        <v>5.17</v>
       </c>
       <c r="EA11" t="n">
-        <v>23.55</v>
+        <v>23.43</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="12">
@@ -5812,94 +5812,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
         <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="F13" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="G13" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="H13" t="n">
-        <v>97.45</v>
+        <v>98.17</v>
       </c>
       <c r="I13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J13" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="K13" t="n">
-        <v>4.82</v>
+        <v>4.83</v>
       </c>
       <c r="L13" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="M13" t="n">
-        <v>62.09</v>
+        <v>61.92</v>
       </c>
       <c r="N13" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="O13" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="P13" t="n">
-        <v>15.91</v>
+        <v>15.67</v>
       </c>
       <c r="Q13" t="n">
-        <v>15.82</v>
+        <v>15.25</v>
       </c>
       <c r="R13" t="n">
-        <v>5.18</v>
+        <v>4.92</v>
       </c>
       <c r="S13" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="T13" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="U13" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="V13" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>52.73</v>
+        <v>52.83</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z13" t="n">
-        <v>13.45</v>
+        <v>13.83</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.91</v>
+        <v>8.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.55</v>
+        <v>5.33</v>
       </c>
       <c r="AC13" t="n">
-        <v>22.09</v>
+        <v>21.58</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AF13" t="n">
         <v>0.27</v>
@@ -5983,70 +5983,70 @@
         <v>2.36</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="BH13" t="n">
-        <v>7.55</v>
+        <v>7.43</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.77</v>
+        <v>3.74</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3.68</v>
+        <v>3.61</v>
       </c>
       <c r="BR13" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS13" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT13" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BU13" t="n">
-        <v>22.73</v>
+        <v>26.09</v>
       </c>
       <c r="BV13" t="n">
-        <v>9.09</v>
+        <v>13.04</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.12</v>
+        <v>4.14</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.4</v>
+        <v>4.41</v>
       </c>
       <c r="CC13" t="n">
         <v>2.43</v>
@@ -6067,7 +6067,7 @@
         <v>1.4</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CJ13" t="n">
         <v>2</v>
@@ -6076,10 +6076,10 @@
         <v>1.68</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CM13" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CN13" t="n">
         <v>1.61</v>
@@ -6091,7 +6091,7 @@
         <v>1.92</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
       <c r="CR13" t="n">
         <v>1.41</v>
@@ -6100,25 +6100,25 @@
         <v>2.93</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="CU13" t="n">
         <v>1.42</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="DA13" t="n">
         <v>1.62</v>
@@ -6127,85 +6127,85 @@
         <v>1.35</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.71</v>
+        <v>3.69</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="DH13" t="n">
-        <v>99.81999999999999</v>
+        <v>100.09</v>
       </c>
       <c r="DI13" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.64</v>
+        <v>4.65</v>
       </c>
       <c r="DL13" t="n">
         <v>0.22</v>
       </c>
       <c r="DM13" t="n">
-        <v>55.64</v>
+        <v>55.83</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="DP13" t="n">
-        <v>15.23</v>
+        <v>15.13</v>
       </c>
       <c r="DQ13" t="n">
-        <v>15.28</v>
+        <v>15</v>
       </c>
       <c r="DR13" t="n">
-        <v>5.68</v>
+        <v>5.52</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>54.09</v>
+        <v>54.08</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.59</v>
+        <v>12.83</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.23</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.36</v>
+        <v>4.78</v>
       </c>
       <c r="EA13" t="n">
-        <v>22.18</v>
+        <v>21.91</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="14">

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
         <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="F2" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="G2" t="n">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="H2" t="n">
-        <v>97.27</v>
+        <v>98.08</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="K2" t="n">
-        <v>5.18</v>
+        <v>5.33</v>
       </c>
       <c r="L2" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="M2" t="n">
-        <v>57.27</v>
+        <v>60.25</v>
       </c>
       <c r="N2" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="O2" t="n">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="P2" t="n">
-        <v>16</v>
+        <v>15.75</v>
       </c>
       <c r="Q2" t="n">
-        <v>14</v>
+        <v>13.92</v>
       </c>
       <c r="R2" t="n">
-        <v>5.18</v>
+        <v>5.25</v>
       </c>
       <c r="S2" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="T2" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="U2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>57.18</v>
+        <v>57.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z2" t="n">
-        <v>16.36</v>
+        <v>16.67</v>
       </c>
       <c r="AA2" t="n">
-        <v>11.18</v>
+        <v>11.25</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.18</v>
+        <v>5.42</v>
       </c>
       <c r="AC2" t="n">
-        <v>20.91</v>
+        <v>20.58</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="AF2" t="n">
         <v>0.08</v>
@@ -1550,70 +1550,70 @@
         <v>2.83</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.390000000000001</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BP2" t="n">
         <v>3.83</v>
       </c>
       <c r="BQ2" t="n">
-        <v>3.91</v>
+        <v>4</v>
       </c>
       <c r="BR2" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS2" t="n">
-        <v>65.22</v>
+        <v>62.5</v>
       </c>
       <c r="BT2" t="n">
-        <v>39.13</v>
+        <v>37.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BV2" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.54</v>
+        <v>4.59</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.93</v>
+        <v>5.01</v>
       </c>
       <c r="CC2" t="n">
         <v>1.94</v>
@@ -1622,31 +1622,31 @@
         <v>2.05</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="CH2" t="n">
         <v>1.44</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="CM2" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CN2" t="n">
         <v>1.58</v>
@@ -1655,16 +1655,16 @@
         <v>1.26</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="CR2" t="n">
         <v>1.39</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CT2" t="n">
         <v>3.01</v>
@@ -1673,16 +1673,16 @@
         <v>1.46</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CX2" t="n">
         <v>1.81</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.01</v>
@@ -1694,85 +1694,85 @@
         <v>1.29</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.27</v>
+        <v>3.24</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="DH2" t="n">
-        <v>95</v>
+        <v>95.5</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.39</v>
+        <v>5.46</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="DM2" t="n">
-        <v>55.39</v>
+        <v>56.96</v>
       </c>
       <c r="DN2" t="n">
         <v>1</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="DP2" t="n">
-        <v>15.91</v>
+        <v>15.79</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.74</v>
+        <v>13.71</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.09</v>
+        <v>6.08</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>58.35</v>
+        <v>58.46</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX2" t="n">
-        <v>15.22</v>
+        <v>15.42</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.48</v>
+        <v>10.54</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.74</v>
+        <v>4.88</v>
       </c>
       <c r="EA2" t="n">
-        <v>20.7</v>
+        <v>20.54</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
         <v>12</v>
@@ -1794,49 +1794,49 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="H3" t="n">
-        <v>95.18000000000001</v>
+        <v>93.17</v>
       </c>
       <c r="I3" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="J3" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.91</v>
+        <v>5.58</v>
       </c>
       <c r="L3" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="M3" t="n">
-        <v>47.82</v>
+        <v>47</v>
       </c>
       <c r="N3" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="O3" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="P3" t="n">
-        <v>14.18</v>
+        <v>14.33</v>
       </c>
       <c r="Q3" t="n">
-        <v>15.55</v>
+        <v>15.58</v>
       </c>
       <c r="R3" t="n">
-        <v>7.55</v>
+        <v>7.42</v>
       </c>
       <c r="S3" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="T3" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>52.91</v>
+        <v>51.33</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>15.09</v>
+        <v>14.42</v>
       </c>
       <c r="AA3" t="n">
-        <v>10.91</v>
+        <v>10.33</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.18</v>
+        <v>4.08</v>
       </c>
       <c r="AC3" t="n">
-        <v>21.27</v>
+        <v>21.08</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="AF3" t="n">
         <v>0.08</v>
@@ -1953,49 +1953,49 @@
         <v>2.08</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.09</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BP3" t="n">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.78</v>
+        <v>5.92</v>
       </c>
       <c r="BR3" t="n">
-        <v>86.95999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS3" t="n">
-        <v>65.22</v>
+        <v>62.5</v>
       </c>
       <c r="BT3" t="n">
-        <v>30.43</v>
+        <v>29.17</v>
       </c>
       <c r="BU3" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BV3" t="n">
         <v>0</v>
@@ -2004,19 +2004,19 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.72</v>
+        <v>2.65</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.59</v>
+        <v>3.57</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.72</v>
+        <v>3.69</v>
       </c>
       <c r="CC3" t="n">
         <v>3.73</v>
@@ -2025,43 +2025,43 @@
         <v>4.53</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CI3" t="n">
         <v>1.71</v>
       </c>
       <c r="CJ3" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CM3" t="n">
         <v>1.88</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.92</v>
+        <v>3.96</v>
       </c>
       <c r="CR3" t="n">
         <v>1.45</v>
@@ -2070,7 +2070,7 @@
         <v>3.09</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CU3" t="n">
         <v>1.37</v>
@@ -2094,55 +2094,55 @@
         <v>1.56</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.12</v>
+        <v>4.16</v>
       </c>
       <c r="DE3" t="n">
         <v>0.04</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.26</v>
+        <v>3.21</v>
       </c>
       <c r="DH3" t="n">
-        <v>91.56</v>
+        <v>90.70999999999999</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.13</v>
+        <v>5</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="DM3" t="n">
-        <v>42.35</v>
+        <v>42.16</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="DP3" t="n">
-        <v>15.22</v>
+        <v>15.25</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.78</v>
+        <v>14.83</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.13</v>
+        <v>7.08</v>
       </c>
       <c r="DS3" t="n">
         <v>0.04</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>51.52</v>
+        <v>50.79</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="DX3" t="n">
-        <v>12.87</v>
+        <v>12.62</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.220000000000001</v>
+        <v>9</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.17</v>
+        <v>20.12</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="4">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="n">
         <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2678,52 +2678,52 @@
         <v>2.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="AI5" t="n">
-        <v>73.27</v>
+        <v>74.75</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.73</v>
+        <v>4.08</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AN5" t="n">
-        <v>30.73</v>
+        <v>31.92</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AQ5" t="n">
-        <v>16.36</v>
+        <v>16.33</v>
       </c>
       <c r="AR5" t="n">
-        <v>14.64</v>
+        <v>14.83</v>
       </c>
       <c r="AS5" t="n">
-        <v>10.27</v>
+        <v>9.83</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -2735,82 +2735,82 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>45.45</v>
+        <v>47.17</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.18</v>
+        <v>8.42</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.45</v>
+        <v>5.83</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="BD5" t="n">
-        <v>20</v>
+        <v>20.08</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="BH5" t="n">
-        <v>8</v>
+        <v>8.08</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.78</v>
+        <v>3.67</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.22</v>
+        <v>4.42</v>
       </c>
       <c r="BR5" t="n">
-        <v>91.3</v>
+        <v>87.5</v>
       </c>
       <c r="BS5" t="n">
-        <v>65.22</v>
+        <v>62.5</v>
       </c>
       <c r="BT5" t="n">
-        <v>43.48</v>
+        <v>41.67</v>
       </c>
       <c r="BU5" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BV5" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>43.48</v>
+        <v>41.67</v>
       </c>
       <c r="BY5" t="n">
         <v>3.39</v>
@@ -2819,40 +2819,40 @@
         <v>3.7</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.61</v>
+        <v>3.58</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.86</v>
+        <v>3.83</v>
       </c>
       <c r="CC5" t="n">
-        <v>5.45</v>
+        <v>5.33</v>
       </c>
       <c r="CD5" t="n">
-        <v>6.42</v>
+        <v>6.24</v>
       </c>
       <c r="CE5" t="n">
         <v>1.43</v>
       </c>
       <c r="CF5" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CH5" t="n">
         <v>1.36</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CJ5" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CK5" t="n">
         <v>1.9</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CM5" t="n">
         <v>1.84</v>
@@ -2864,10 +2864,10 @@
         <v>1.34</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.74</v>
+        <v>3.79</v>
       </c>
       <c r="CR5" t="n">
         <v>1.44</v>
@@ -2876,7 +2876,7 @@
         <v>3.01</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="CU5" t="n">
         <v>1.4</v>
@@ -2885,7 +2885,7 @@
         <v>1.8</v>
       </c>
       <c r="CW5" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CX5" t="n">
         <v>1.96</v>
@@ -2900,88 +2900,88 @@
         <v>1.52</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.95</v>
+        <v>4.01</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="DH5" t="n">
-        <v>83.61</v>
+        <v>83.92</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.78</v>
+        <v>3.96</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="DM5" t="n">
-        <v>38.66</v>
+        <v>38.92</v>
       </c>
       <c r="DN5" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="DP5" t="n">
-        <v>15.39</v>
+        <v>15.42</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.22</v>
+        <v>15.29</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.52</v>
+        <v>7.42</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>50.47</v>
+        <v>51.12</v>
       </c>
       <c r="DW5" t="n">
         <v>0.04</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.13</v>
+        <v>10.17</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.26</v>
+        <v>7.38</v>
       </c>
       <c r="DZ5" t="n">
-        <v>2.87</v>
+        <v>2.79</v>
       </c>
       <c r="EA5" t="n">
-        <v>22.26</v>
+        <v>22.2</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="6">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" t="n">
         <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
         <v>0.08</v>
@@ -3487,136 +3487,136 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AI7" t="n">
-        <v>82.27</v>
+        <v>81.33</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.36</v>
+        <v>3.33</v>
       </c>
       <c r="AL7" t="n">
         <v>3</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AN7" t="n">
-        <v>32.18</v>
+        <v>32.92</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AQ7" t="n">
-        <v>16.64</v>
+        <v>16.33</v>
       </c>
       <c r="AR7" t="n">
-        <v>13.27</v>
+        <v>13.25</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.359999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>40.09</v>
+        <v>40</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BA7" t="n">
-        <v>10.73</v>
+        <v>10.58</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.91</v>
+        <v>6.92</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.82</v>
+        <v>3.67</v>
       </c>
       <c r="BD7" t="n">
-        <v>17.18</v>
+        <v>16.83</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BF7" t="n">
         <v>3</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.390000000000001</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.61</v>
+        <v>4.67</v>
       </c>
       <c r="BR7" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS7" t="n">
-        <v>82.61</v>
+        <v>79.17</v>
       </c>
       <c r="BT7" t="n">
-        <v>39.13</v>
+        <v>37.5</v>
       </c>
       <c r="BU7" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BV7" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW7" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX7" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BY7" t="n">
         <v>4.95</v>
@@ -3625,40 +3625,40 @@
         <v>5.13</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.78</v>
+        <v>3.86</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.76</v>
+        <v>3.89</v>
       </c>
       <c r="CC7" t="n">
-        <v>5.58</v>
+        <v>6.46</v>
       </c>
       <c r="CD7" t="n">
-        <v>5.64</v>
+        <v>6.46</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CK7" t="n">
         <v>1.88</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CM7" t="n">
         <v>1.85</v>
@@ -3667,91 +3667,91 @@
         <v>1.5</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="CR7" t="n">
         <v>1.45</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.07</v>
+        <v>3.03</v>
       </c>
       <c r="CT7" t="n">
         <v>2.78</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CZ7" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DA7" t="n">
         <v>1.53</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.03</v>
+        <v>3.98</v>
       </c>
       <c r="DE7" t="n">
         <v>0.04</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="DH7" t="n">
-        <v>83.48</v>
+        <v>82.95999999999999</v>
       </c>
       <c r="DI7" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DM7" t="n">
-        <v>33.3</v>
+        <v>33.62</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="DP7" t="n">
-        <v>16.53</v>
+        <v>16.38</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.48</v>
+        <v>14.42</v>
       </c>
       <c r="DR7" t="n">
         <v>8.039999999999999</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>42.52</v>
+        <v>42.38</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.26</v>
+        <v>11.16</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.35</v>
+        <v>7.34</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.91</v>
+        <v>3.83</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.39</v>
+        <v>17.2</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="8">

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -1607,13 +1607,13 @@
         <v>1.5</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CA2" t="n">
         <v>4.59</v>
       </c>
       <c r="CB2" t="n">
-        <v>5.01</v>
+        <v>5.06</v>
       </c>
       <c r="CC2" t="n">
         <v>1.94</v>
@@ -1664,7 +1664,7 @@
         <v>1.39</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="CT2" t="n">
         <v>3.01</v>
@@ -1676,13 +1676,13 @@
         <v>1.75</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CX2" t="n">
         <v>1.81</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.01</v>
@@ -2010,7 +2010,7 @@
         <v>2.65</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CA3" t="n">
         <v>3.57</v>
@@ -2070,7 +2070,7 @@
         <v>3.09</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="CU3" t="n">
         <v>1.37</v>
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
         <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F4" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="G4" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="H4" t="n">
-        <v>81.55</v>
+        <v>84.58</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="K4" t="n">
-        <v>5.45</v>
+        <v>5.33</v>
       </c>
       <c r="L4" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="M4" t="n">
-        <v>45.09</v>
+        <v>44.42</v>
       </c>
       <c r="N4" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="O4" t="n">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="P4" t="n">
-        <v>12.73</v>
+        <v>12.92</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.36</v>
+        <v>15.42</v>
       </c>
       <c r="R4" t="n">
-        <v>7.82</v>
+        <v>7.92</v>
       </c>
       <c r="S4" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="T4" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="U4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>46.45</v>
+        <v>47.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.82</v>
+        <v>9.67</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.18</v>
+        <v>6.33</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.64</v>
+        <v>3.33</v>
       </c>
       <c r="AC4" t="n">
-        <v>22.91</v>
+        <v>23.25</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE4" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,70 +2356,70 @@
         <v>3.08</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.83</v>
+        <v>9.67</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BP4" t="n">
-        <v>5</v>
+        <v>4.88</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.83</v>
+        <v>4.79</v>
       </c>
       <c r="BR4" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS4" t="n">
-        <v>73.91</v>
+        <v>70.83</v>
       </c>
       <c r="BT4" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BU4" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BV4" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX4" t="n">
-        <v>43.48</v>
+        <v>41.67</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.63</v>
+        <v>3.46</v>
       </c>
       <c r="BZ4" t="n">
-        <v>4.37</v>
+        <v>4.14</v>
       </c>
       <c r="CA4" t="n">
         <v>3.74</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.97</v>
+        <v>3.96</v>
       </c>
       <c r="CC4" t="n">
         <v>6.71</v>
@@ -2431,7 +2431,7 @@
         <v>1.43</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="CG4" t="n">
         <v>2.72</v>
@@ -2440,22 +2440,22 @@
         <v>1.36</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CK4" t="n">
         <v>1.83</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CM4" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CO4" t="n">
         <v>1.33</v>
@@ -2464,16 +2464,16 @@
         <v>2.06</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="CR4" t="n">
         <v>1.42</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="CU4" t="n">
         <v>1.39</v>
@@ -2482,13 +2482,13 @@
         <v>1.81</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CX4" t="n">
         <v>1.84</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CZ4" t="n">
         <v>1.98</v>
@@ -2497,88 +2497,88 @@
         <v>1.58</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="DC4" t="n">
         <v>2.13</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="DH4" t="n">
-        <v>78.34999999999999</v>
+        <v>80</v>
       </c>
       <c r="DI4" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.65</v>
+        <v>4.62</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="DM4" t="n">
-        <v>38.04</v>
+        <v>38</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.96</v>
+        <v>14</v>
       </c>
       <c r="DQ4" t="n">
-        <v>15.56</v>
+        <v>15.58</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.039999999999999</v>
+        <v>8.08</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>45.13</v>
+        <v>45.71</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="DX4" t="n">
-        <v>9.26</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="DY4" t="n">
-        <v>5.91</v>
+        <v>6</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.57</v>
+        <v>20.84</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="EC4" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -2828,7 +2828,7 @@
         <v>5.33</v>
       </c>
       <c r="CD5" t="n">
-        <v>6.24</v>
+        <v>6.27</v>
       </c>
       <c r="CE5" t="n">
         <v>1.43</v>
@@ -2876,7 +2876,7 @@
         <v>3.01</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="CU5" t="n">
         <v>1.4</v>
@@ -2891,10 +2891,10 @@
         <v>1.96</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CZ5" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DA5" t="n">
         <v>1.52</v>
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" t="n">
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
         <v>0.08</v>
@@ -3084,136 +3084,136 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AI6" t="n">
-        <v>79.18000000000001</v>
+        <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AK6" t="n">
-        <v>4.64</v>
+        <v>4.42</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.73</v>
+        <v>4.75</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AN6" t="n">
-        <v>38.27</v>
+        <v>38.58</v>
       </c>
       <c r="AO6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>47.58</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>18</v>
+      </c>
+      <c r="BE6" t="n">
         <v>1.45</v>
       </c>
-      <c r="AP6" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>18.82</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>13.64</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>8.73</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>46.73</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>13.55</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>8.359999999999999</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>5.18</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>17.64</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.49</v>
-      </c>
       <c r="BF6" t="n">
-        <v>4.36</v>
+        <v>4.17</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.48</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="BP6" t="n">
-        <v>5.13</v>
+        <v>5.08</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.26</v>
+        <v>4.38</v>
       </c>
       <c r="BR6" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS6" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BT6" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BU6" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BV6" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>69.56999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="BY6" t="n">
         <v>4.15</v>
@@ -3222,28 +3222,28 @@
         <v>4.33</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="CC6" t="n">
-        <v>5.54</v>
+        <v>5.32</v>
       </c>
       <c r="CD6" t="n">
-        <v>5.23</v>
+        <v>5.02</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CI6" t="n">
         <v>1.79</v>
@@ -3255,31 +3255,31 @@
         <v>1.77</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="CM6" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CN6" t="n">
         <v>1.55</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.57</v>
+        <v>3.59</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CU6" t="n">
         <v>1.4</v>
@@ -3306,52 +3306,52 @@
         <v>1.35</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.75</v>
+        <v>3.79</v>
       </c>
       <c r="DE6" t="n">
         <v>0.04</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="DH6" t="n">
-        <v>82.78</v>
+        <v>83.04000000000001</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DJ6" t="n">
-        <v>4.09</v>
+        <v>4</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.09</v>
+        <v>4.12</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="DM6" t="n">
-        <v>40.57</v>
+        <v>40.62</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="DP6" t="n">
-        <v>17.61</v>
+        <v>17.38</v>
       </c>
       <c r="DQ6" t="n">
-        <v>15.04</v>
+        <v>14.95</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.87</v>
+        <v>7.79</v>
       </c>
       <c r="DS6" t="n">
         <v>0.04</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>45.61</v>
+        <v>46.08</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.78</v>
+        <v>13.62</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.949999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.83</v>
+        <v>4.66</v>
       </c>
       <c r="EA6" t="n">
-        <v>18</v>
+        <v>18.16</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="EC6" t="n">
-        <v>3.65</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="7">
@@ -3628,13 +3628,13 @@
         <v>3.86</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.89</v>
+        <v>3.93</v>
       </c>
       <c r="CC7" t="n">
         <v>6.46</v>
       </c>
       <c r="CD7" t="n">
-        <v>6.46</v>
+        <v>6.8</v>
       </c>
       <c r="CE7" t="n">
         <v>1.43</v>
@@ -3679,22 +3679,22 @@
         <v>1.45</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.03</v>
+        <v>3.07</v>
       </c>
       <c r="CT7" t="n">
         <v>2.78</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CV7" t="n">
         <v>1.77</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CY7" t="n">
         <v>2.44</v>
@@ -3712,7 +3712,7 @@
         <v>2.2</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.98</v>
+        <v>3.97</v>
       </c>
       <c r="DE7" t="n">
         <v>0.04</v>
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
         <v>12</v>
       </c>
       <c r="E8" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="F8" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="G8" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="H8" t="n">
-        <v>95</v>
+        <v>95.25</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="K8" t="n">
-        <v>4.55</v>
+        <v>4.42</v>
       </c>
       <c r="L8" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="M8" t="n">
-        <v>40.18</v>
+        <v>41.67</v>
       </c>
       <c r="N8" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="O8" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="P8" t="n">
-        <v>12</v>
+        <v>12.08</v>
       </c>
       <c r="Q8" t="n">
-        <v>16.73</v>
+        <v>16.92</v>
       </c>
       <c r="R8" t="n">
-        <v>7</v>
+        <v>6.83</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T8" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="U8" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="V8" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>58.27</v>
+        <v>58.83</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>13.64</v>
+        <v>13.08</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.09</v>
+        <v>7.83</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.55</v>
+        <v>5.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>23.64</v>
+        <v>23.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AF8" t="n">
         <v>0.25</v>
@@ -3968,70 +3968,70 @@
         <v>2.25</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.35</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.52</v>
+        <v>0.58</v>
       </c>
       <c r="BL8" t="n">
         <v>1.04</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.96</v>
+        <v>4.92</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.39</v>
+        <v>4.29</v>
       </c>
       <c r="BR8" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS8" t="n">
-        <v>86.95999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BT8" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BU8" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BV8" t="n">
-        <v>26.09</v>
+        <v>29.17</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX8" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="CC8" t="n">
         <v>4.17</v>
@@ -4043,10 +4043,10 @@
         <v>1.39</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="CH8" t="n">
         <v>1.38</v>
@@ -4073,19 +4073,19 @@
         <v>1.3</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.47</v>
+        <v>3.49</v>
       </c>
       <c r="CR8" t="n">
         <v>1.41</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CU8" t="n">
         <v>1.39</v>
@@ -4094,7 +4094,7 @@
         <v>1.87</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CX8" t="n">
         <v>1.86</v>
@@ -4106,28 +4106,28 @@
         <v>1.95</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="DB8" t="n">
         <v>1.34</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.63</v>
+        <v>3.65</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DF8" t="n">
         <v>1.04</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="DH8" t="n">
-        <v>94.39</v>
+        <v>94.54000000000001</v>
       </c>
       <c r="DI8" t="n">
         <v>0.04</v>
@@ -4136,61 +4136,61 @@
         <v>1.92</v>
       </c>
       <c r="DK8" t="n">
-        <v>5</v>
+        <v>4.92</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="DM8" t="n">
-        <v>41.95</v>
+        <v>42.62</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="DP8" t="n">
-        <v>12.61</v>
+        <v>12.62</v>
       </c>
       <c r="DQ8" t="n">
-        <v>16.48</v>
+        <v>16.58</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.83</v>
+        <v>6.75</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>57.17</v>
+        <v>57.5</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.7</v>
+        <v>11.5</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.09</v>
+        <v>7</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.61</v>
+        <v>4.5</v>
       </c>
       <c r="EA8" t="n">
-        <v>22.3</v>
+        <v>22.17</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
         <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
         <v>0.25</v>
@@ -4290,139 +4290,139 @@
         <v>1.83</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AH9" t="n">
         <v>1</v>
       </c>
       <c r="AI9" t="n">
-        <v>66</v>
+        <v>66.5</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN9" t="n">
-        <v>26</v>
+        <v>26.92</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12.18</v>
+        <v>12</v>
       </c>
       <c r="AR9" t="n">
-        <v>15.82</v>
+        <v>15.42</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.27</v>
+        <v>9.42</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AU9" t="n">
         <v>1</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>41.45</v>
+        <v>42.58</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.36</v>
+        <v>7.75</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.27</v>
+        <v>4.67</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="BD9" t="n">
-        <v>14.27</v>
+        <v>14.83</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.13</v>
+        <v>3.08</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.609999999999999</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.13</v>
+        <v>3.08</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BL9" t="n">
         <v>1</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.61</v>
+        <v>4.71</v>
       </c>
       <c r="BQ9" t="n">
-        <v>3.96</v>
+        <v>4.04</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BT9" t="n">
-        <v>78.26000000000001</v>
+        <v>75</v>
       </c>
       <c r="BU9" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BV9" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX9" t="n">
-        <v>43.48</v>
+        <v>45.83</v>
       </c>
       <c r="BY9" t="n">
         <v>3.37</v>
@@ -4431,25 +4431,25 @@
         <v>3.54</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.07</v>
+        <v>4.03</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.35</v>
+        <v>4.3</v>
       </c>
       <c r="CC9" t="n">
-        <v>7.51</v>
+        <v>7.18</v>
       </c>
       <c r="CD9" t="n">
-        <v>9.119999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="CE9" t="n">
         <v>1.38</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="CH9" t="n">
         <v>1.42</v>
@@ -4464,7 +4464,7 @@
         <v>1.73</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CM9" t="n">
         <v>2.02</v>
@@ -4473,22 +4473,22 @@
         <v>1.63</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CQ9" t="n">
         <v>3.2</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CU9" t="n">
         <v>1.46</v>
@@ -4515,85 +4515,85 @@
         <v>1.3</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DH9" t="n">
-        <v>72.13</v>
+        <v>72.12</v>
       </c>
       <c r="DI9" t="n">
         <v>0.17</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="DK9" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DM9" t="n">
-        <v>27</v>
+        <v>27.42</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.95</v>
+        <v>13.79</v>
       </c>
       <c r="DQ9" t="n">
-        <v>16.31</v>
+        <v>16.08</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.390000000000001</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>43.65</v>
+        <v>44.12</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.52</v>
+        <v>8.67</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.21</v>
+        <v>5.38</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.48</v>
+        <v>16.67</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="10">
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
         <v>12</v>
@@ -4615,82 +4615,82 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="G10" t="n">
-        <v>3.91</v>
+        <v>3.92</v>
       </c>
       <c r="H10" t="n">
-        <v>133.64</v>
+        <v>134.33</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>9.27</v>
+        <v>9.17</v>
       </c>
       <c r="L10" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="M10" t="n">
-        <v>74.64</v>
+        <v>73.42</v>
       </c>
       <c r="N10" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="O10" t="n">
-        <v>5.27</v>
+        <v>5.17</v>
       </c>
       <c r="P10" t="n">
-        <v>10.91</v>
+        <v>10.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.82</v>
+        <v>12.67</v>
       </c>
       <c r="R10" t="n">
-        <v>4.27</v>
+        <v>4.08</v>
       </c>
       <c r="S10" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="T10" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="V10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>65</v>
+        <v>64.58</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z10" t="n">
-        <v>21.82</v>
+        <v>21.58</v>
       </c>
       <c r="AA10" t="n">
-        <v>15.36</v>
+        <v>15.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>6.45</v>
+        <v>6.08</v>
       </c>
       <c r="AC10" t="n">
-        <v>27.27</v>
+        <v>27.17</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.37</v>
+        <v>2.32</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AF10" t="n">
         <v>0.17</v>
@@ -4774,70 +4774,70 @@
         <v>1.83</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.74</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.52</v>
+        <v>4.54</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.17</v>
+        <v>5.21</v>
       </c>
       <c r="BR10" t="n">
-        <v>91.3</v>
+        <v>87.5</v>
       </c>
       <c r="BS10" t="n">
-        <v>78.26000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT10" t="n">
-        <v>39.13</v>
+        <v>37.5</v>
       </c>
       <c r="BU10" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BV10" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="CA10" t="n">
-        <v>5.46</v>
+        <v>5.37</v>
       </c>
       <c r="CB10" t="n">
-        <v>6.14</v>
+        <v>6.03</v>
       </c>
       <c r="CC10" t="n">
         <v>1.64</v>
@@ -4849,19 +4849,19 @@
         <v>1.33</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CI10" t="n">
         <v>1.6</v>
       </c>
       <c r="CJ10" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CK10" t="n">
         <v>1.82</v>
@@ -4879,28 +4879,28 @@
         <v>1.22</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CX10" t="n">
         <v>1.83</v>
@@ -4915,88 +4915,88 @@
         <v>1.61</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="DG10" t="n">
-        <v>3.65</v>
+        <v>3.67</v>
       </c>
       <c r="DH10" t="n">
-        <v>129.39</v>
+        <v>129.92</v>
       </c>
       <c r="DI10" t="n">
         <v>-0.08</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="DK10" t="n">
-        <v>7.52</v>
+        <v>7.54</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.61</v>
+        <v>0.71</v>
       </c>
       <c r="DM10" t="n">
-        <v>70</v>
+        <v>69.58</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="DO10" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.22</v>
+        <v>13.04</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.39</v>
+        <v>12.34</v>
       </c>
       <c r="DR10" t="n">
-        <v>4.35</v>
+        <v>4.25</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>62.61</v>
+        <v>62.5</v>
       </c>
       <c r="DW10" t="n">
         <v>0.08</v>
       </c>
       <c r="DX10" t="n">
-        <v>18.56</v>
+        <v>18.58</v>
       </c>
       <c r="DY10" t="n">
-        <v>12.52</v>
+        <v>12.71</v>
       </c>
       <c r="DZ10" t="n">
-        <v>6.04</v>
+        <v>5.88</v>
       </c>
       <c r="EA10" t="n">
-        <v>26.96</v>
+        <v>26.92</v>
       </c>
       <c r="EB10" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
         <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
         <v>0.25</v>
@@ -5096,139 +5096,139 @@
         <v>1.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG11" t="n">
         <v>1</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>106.73</v>
+        <v>103.75</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.64</v>
+        <v>4.5</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AN11" t="n">
-        <v>54.91</v>
+        <v>52.75</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.55</v>
+        <v>13.17</v>
       </c>
       <c r="AR11" t="n">
-        <v>13.36</v>
+        <v>13</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.18</v>
+        <v>5.58</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>60.73</v>
+        <v>59</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA11" t="n">
-        <v>12.82</v>
+        <v>12.17</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.640000000000001</v>
+        <v>8.25</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.18</v>
+        <v>3.92</v>
       </c>
       <c r="BD11" t="n">
-        <v>23.09</v>
+        <v>23.75</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.390000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="BR11" t="n">
-        <v>86.95999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS11" t="n">
-        <v>78.26000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT11" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BU11" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BV11" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX11" t="n">
-        <v>39.13</v>
+        <v>37.5</v>
       </c>
       <c r="BY11" t="n">
         <v>1.5</v>
@@ -5237,28 +5237,28 @@
         <v>1.54</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.77</v>
+        <v>4.72</v>
       </c>
       <c r="CB11" t="n">
-        <v>5.22</v>
+        <v>5.15</v>
       </c>
       <c r="CC11" t="n">
-        <v>1.76</v>
+        <v>1.96</v>
       </c>
       <c r="CD11" t="n">
-        <v>1.75</v>
+        <v>2.01</v>
       </c>
       <c r="CE11" t="n">
         <v>1.34</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CI11" t="n">
         <v>1.74</v>
@@ -5267,13 +5267,13 @@
         <v>2.03</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CM11" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CN11" t="n">
         <v>1.59</v>
@@ -5282,28 +5282,28 @@
         <v>1.25</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.98</v>
+        <v>3.03</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="CU11" t="n">
         <v>1.47</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CX11" t="n">
         <v>1.77</v>
@@ -5321,85 +5321,85 @@
         <v>1.28</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.18</v>
+        <v>3.23</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DF11" t="n">
         <v>1.04</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.22</v>
+        <v>3.17</v>
       </c>
       <c r="DH11" t="n">
-        <v>107.22</v>
+        <v>105.71</v>
       </c>
       <c r="DI11" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.74</v>
+        <v>5.62</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="DM11" t="n">
-        <v>58.31</v>
+        <v>57.08</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.22</v>
+        <v>12.08</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13.26</v>
+        <v>13.08</v>
       </c>
       <c r="DR11" t="n">
-        <v>4.74</v>
+        <v>4.96</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>61.78</v>
+        <v>60.88</v>
       </c>
       <c r="DW11" t="n">
         <v>0.04</v>
       </c>
       <c r="DX11" t="n">
-        <v>14.7</v>
+        <v>14.3</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.52</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.17</v>
+        <v>5</v>
       </c>
       <c r="EA11" t="n">
-        <v>23.43</v>
+        <v>23.75</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="12">
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D12" t="n">
         <v>12</v>
@@ -5421,82 +5421,82 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="G12" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>82</v>
+        <v>82.58</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="J12" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="K12" t="n">
-        <v>3.73</v>
+        <v>3.92</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>35.64</v>
+        <v>34.92</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="O12" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="P12" t="n">
-        <v>11.73</v>
+        <v>11.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>12.64</v>
+        <v>12.58</v>
       </c>
       <c r="R12" t="n">
-        <v>9.09</v>
+        <v>9.42</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="T12" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="U12" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="V12" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>45.27</v>
+        <v>45.08</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>8.27</v>
+        <v>8.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>6.18</v>
+        <v>6.42</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.09</v>
+        <v>2.33</v>
       </c>
       <c r="AC12" t="n">
-        <v>17.82</v>
+        <v>17.83</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.93</v>
+        <v>0.98</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AF12" t="n">
         <v>0.08</v>
@@ -5580,70 +5580,70 @@
         <v>2.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.65</v>
+        <v>8.75</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.26</v>
+        <v>4.25</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.35</v>
+        <v>4.46</v>
       </c>
       <c r="BR12" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS12" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BT12" t="n">
-        <v>43.48</v>
+        <v>45.83</v>
       </c>
       <c r="BU12" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BV12" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BW12" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX12" t="n">
-        <v>34.78</v>
+        <v>37.5</v>
       </c>
       <c r="BY12" t="n">
-        <v>5.44</v>
+        <v>5.2</v>
       </c>
       <c r="BZ12" t="n">
-        <v>5.7</v>
+        <v>5.47</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.98</v>
+        <v>3.94</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="CC12" t="n">
         <v>7.11</v>
@@ -5652,13 +5652,13 @@
         <v>8.52</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="CH12" t="n">
         <v>1.35</v>
@@ -5673,7 +5673,7 @@
         <v>1.87</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="CM12" t="n">
         <v>1.88</v>
@@ -5685,19 +5685,19 @@
         <v>1.34</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="CR12" t="n">
         <v>1.42</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="CU12" t="n">
         <v>1.4</v>
@@ -5706,103 +5706,103 @@
         <v>1.77</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CX12" t="n">
         <v>1.88</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CZ12" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="DB12" t="n">
         <v>1.36</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.84</v>
+        <v>3.88</v>
       </c>
       <c r="DE12" t="n">
         <v>0.04</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="DH12" t="n">
-        <v>77.09</v>
+        <v>77.58</v>
       </c>
       <c r="DI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="DK12" t="n">
-        <v>3.26</v>
+        <v>3.38</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DM12" t="n">
-        <v>32.74</v>
+        <v>32.5</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.31</v>
+        <v>13.25</v>
       </c>
       <c r="DQ12" t="n">
-        <v>13.05</v>
+        <v>13</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.130000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>42.17</v>
+        <v>42.21</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="DX12" t="n">
-        <v>8.17</v>
+        <v>8.42</v>
       </c>
       <c r="DY12" t="n">
-        <v>5.61</v>
+        <v>5.75</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="EA12" t="n">
-        <v>17.3</v>
+        <v>17.33</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" t="n">
         <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
         <v>0.42</v>
@@ -5902,139 +5902,139 @@
         <v>2.17</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="AI13" t="n">
-        <v>102.18</v>
+        <v>99</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>49.18</v>
+        <v>49.92</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ13" t="n">
-        <v>14.55</v>
+        <v>15</v>
       </c>
       <c r="AR13" t="n">
-        <v>14.73</v>
+        <v>14.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.18</v>
+        <v>6.17</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>55.45</v>
+        <v>53.75</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA13" t="n">
-        <v>11.73</v>
+        <v>11.92</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.55</v>
+        <v>7.42</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.18</v>
+        <v>4.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>22.27</v>
+        <v>22</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="BH13" t="n">
-        <v>7.43</v>
+        <v>7.38</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3.61</v>
+        <v>3.54</v>
       </c>
       <c r="BR13" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS13" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BT13" t="n">
-        <v>52.17</v>
+        <v>54.17</v>
       </c>
       <c r="BU13" t="n">
-        <v>26.09</v>
+        <v>29.17</v>
       </c>
       <c r="BV13" t="n">
-        <v>13.04</v>
+        <v>16.67</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>52.17</v>
+        <v>54.17</v>
       </c>
       <c r="BY13" t="n">
         <v>1.68</v>
@@ -6043,31 +6043,31 @@
         <v>1.84</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.14</v>
+        <v>4.1</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.41</v>
+        <v>4.36</v>
       </c>
       <c r="CC13" t="n">
         <v>2.43</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="CE13" t="n">
         <v>1.39</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="CH13" t="n">
         <v>1.4</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CJ13" t="n">
         <v>2</v>
@@ -6088,37 +6088,37 @@
         <v>1.3</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.36</v>
+        <v>3.39</v>
       </c>
       <c r="CR13" t="n">
         <v>1.41</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DA13" t="n">
         <v>1.62</v>
@@ -6127,85 +6127,85 @@
         <v>1.35</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.69</v>
+        <v>3.71</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="DH13" t="n">
-        <v>100.09</v>
+        <v>98.58</v>
       </c>
       <c r="DI13" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.65</v>
+        <v>4.58</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DM13" t="n">
-        <v>55.83</v>
+        <v>55.92</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="DP13" t="n">
-        <v>15.13</v>
+        <v>15.34</v>
       </c>
       <c r="DQ13" t="n">
-        <v>15</v>
+        <v>14.88</v>
       </c>
       <c r="DR13" t="n">
-        <v>5.52</v>
+        <v>5.54</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>54.08</v>
+        <v>53.29</v>
       </c>
       <c r="DW13" t="n">
         <v>0.08</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.83</v>
+        <v>12.88</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.050000000000001</v>
+        <v>7.96</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.78</v>
+        <v>4.92</v>
       </c>
       <c r="EA13" t="n">
-        <v>21.91</v>
+        <v>21.79</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C14" t="n">
         <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6308,136 +6308,136 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AI14" t="n">
-        <v>54.45</v>
+        <v>57.08</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN14" t="n">
-        <v>25.36</v>
+        <v>26.42</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AQ14" t="n">
-        <v>13.36</v>
+        <v>13.58</v>
       </c>
       <c r="AR14" t="n">
-        <v>11.18</v>
+        <v>11.75</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.640000000000001</v>
+        <v>9.83</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>34.18</v>
+        <v>34.75</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.73</v>
+        <v>6.08</v>
       </c>
       <c r="BB14" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="BD14" t="n">
-        <v>16.27</v>
+        <v>16.08</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.04</v>
+        <v>2.96</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.57</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.04</v>
+        <v>2.96</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.13</v>
+        <v>4.04</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.39</v>
+        <v>4.38</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>86.95999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT14" t="n">
-        <v>65.22</v>
+        <v>62.5</v>
       </c>
       <c r="BU14" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BV14" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BW14" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX14" t="n">
-        <v>43.48</v>
+        <v>41.67</v>
       </c>
       <c r="BY14" t="n">
         <v>6.39</v>
@@ -6446,25 +6446,25 @@
         <v>7.41</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.7</v>
+        <v>4.66</v>
       </c>
       <c r="CB14" t="n">
-        <v>5.39</v>
+        <v>5.32</v>
       </c>
       <c r="CC14" t="n">
-        <v>10.46</v>
+        <v>10.09</v>
       </c>
       <c r="CD14" t="n">
-        <v>13.39</v>
+        <v>12.75</v>
       </c>
       <c r="CE14" t="n">
         <v>1.36</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CH14" t="n">
         <v>1.44</v>
@@ -6479,37 +6479,37 @@
         <v>1.79</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CM14" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CW14" t="n">
         <v>2.2</v>
@@ -6530,52 +6530,52 @@
         <v>1.31</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="DG14" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="DH14" t="n">
-        <v>64.39</v>
+        <v>65.29000000000001</v>
       </c>
       <c r="DI14" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.09</v>
+        <v>3.12</v>
       </c>
       <c r="DK14" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DM14" t="n">
-        <v>29.87</v>
+        <v>30.21</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="DO14" t="n">
         <v>1</v>
       </c>
       <c r="DP14" t="n">
-        <v>14.13</v>
+        <v>14.2</v>
       </c>
       <c r="DQ14" t="n">
-        <v>12.52</v>
+        <v>12.75</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.699999999999999</v>
+        <v>8.83</v>
       </c>
       <c r="DS14" t="n">
         <v>0.04</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>36.61</v>
+        <v>36.79</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="DX14" t="n">
-        <v>7.74</v>
+        <v>7.83</v>
       </c>
       <c r="DY14" t="n">
-        <v>5.65</v>
+        <v>5.58</v>
       </c>
       <c r="DZ14" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.82</v>
+        <v>17.66</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="15">
@@ -6618,94 +6618,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
         <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F15" t="n">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="G15" t="n">
-        <v>2.64</v>
+        <v>2.83</v>
       </c>
       <c r="H15" t="n">
-        <v>70.36</v>
+        <v>72.33</v>
       </c>
       <c r="I15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J15" t="n">
-        <v>3.36</v>
+        <v>3.17</v>
       </c>
       <c r="K15" t="n">
-        <v>4.64</v>
+        <v>5</v>
       </c>
       <c r="L15" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="M15" t="n">
-        <v>31.82</v>
+        <v>33.08</v>
       </c>
       <c r="N15" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="O15" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="P15" t="n">
-        <v>14.64</v>
+        <v>14.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>16.73</v>
+        <v>16.17</v>
       </c>
       <c r="R15" t="n">
-        <v>7.73</v>
+        <v>7.58</v>
       </c>
       <c r="S15" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="V15" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>48.36</v>
+        <v>48.08</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z15" t="n">
-        <v>12.64</v>
+        <v>12.92</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.91</v>
+        <v>9</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.73</v>
+        <v>3.92</v>
       </c>
       <c r="AC15" t="n">
-        <v>20.36</v>
+        <v>20.25</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AE15" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="AF15" t="n">
         <v>0.08</v>
@@ -6789,70 +6789,70 @@
         <v>3.17</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.130000000000001</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.78</v>
+        <v>3.92</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.3</v>
+        <v>5.33</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="BT15" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BU15" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BV15" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>50</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="BZ15" t="n">
         <v>4.35</v>
       </c>
-      <c r="BW15" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>47.83</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="BZ15" t="n">
-        <v>4.54</v>
-      </c>
       <c r="CA15" t="n">
-        <v>3.82</v>
+        <v>3.79</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.98</v>
+        <v>3.94</v>
       </c>
       <c r="CC15" t="n">
         <v>6.24</v>
@@ -6867,13 +6867,13 @@
         <v>2.9</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CH15" t="n">
         <v>1.38</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CJ15" t="n">
         <v>2.01</v>
@@ -6882,7 +6882,7 @@
         <v>1.86</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CM15" t="n">
         <v>1.88</v>
@@ -6894,16 +6894,16 @@
         <v>1.32</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="CR15" t="n">
         <v>1.44</v>
       </c>
       <c r="CS15" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CT15" t="n">
         <v>2.82</v>
@@ -6912,10 +6912,10 @@
         <v>1.38</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CW15" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CX15" t="n">
         <v>1.89</v>
@@ -6933,7 +6933,7 @@
         <v>1.36</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="DD15" t="n">
         <v>3.76</v>
@@ -6942,76 +6942,76 @@
         <v>0.08</v>
       </c>
       <c r="DF15" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="DG15" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="DH15" t="n">
-        <v>77.17</v>
+        <v>77.88</v>
       </c>
       <c r="DI15" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.26</v>
+        <v>3.17</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.7</v>
+        <v>3.92</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="DM15" t="n">
-        <v>37.22</v>
+        <v>37.62</v>
       </c>
       <c r="DN15" t="n">
         <v>0.92</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="DP15" t="n">
-        <v>15.61</v>
+        <v>15.5</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.52</v>
+        <v>15.3</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.87</v>
+        <v>7.79</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>48.3</v>
+        <v>48.16</v>
       </c>
       <c r="DW15" t="n">
         <v>0.04</v>
       </c>
       <c r="DX15" t="n">
-        <v>11.22</v>
+        <v>11.42</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.61</v>
+        <v>7.71</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.61</v>
+        <v>3.71</v>
       </c>
       <c r="EA15" t="n">
-        <v>21.13</v>
+        <v>21.04</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="EC15" t="n">
-        <v>3.17</v>
+        <v>3.08</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -3144,10 +3144,10 @@
         <v>0.25</v>
       </c>
       <c r="BA6" t="n">
-        <v>13.25</v>
+        <v>13.17</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.42</v>
+        <v>8.33</v>
       </c>
       <c r="BC6" t="n">
         <v>4.83</v>
@@ -3369,10 +3369,10 @@
         <v>0.29</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.62</v>
+        <v>13.58</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.960000000000001</v>
+        <v>8.92</v>
       </c>
       <c r="DZ6" t="n">
         <v>4.66</v>
@@ -3842,7 +3842,7 @@
         <v>12.08</v>
       </c>
       <c r="Q8" t="n">
-        <v>16.92</v>
+        <v>17</v>
       </c>
       <c r="R8" t="n">
         <v>6.83</v>
@@ -3863,22 +3863,22 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>58.83</v>
+        <v>58.67</v>
       </c>
       <c r="Y8" t="n">
         <v>0.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>13.08</v>
+        <v>13.17</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.83</v>
+        <v>7.92</v>
       </c>
       <c r="AB8" t="n">
         <v>5.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>23.25</v>
+        <v>23.33</v>
       </c>
       <c r="AD8" t="n">
         <v>1.5</v>
@@ -4154,7 +4154,7 @@
         <v>12.62</v>
       </c>
       <c r="DQ8" t="n">
-        <v>16.58</v>
+        <v>16.62</v>
       </c>
       <c r="DR8" t="n">
         <v>6.75</v>
@@ -4169,22 +4169,22 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>57.5</v>
+        <v>57.42</v>
       </c>
       <c r="DW8" t="n">
         <v>0.08</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.5</v>
+        <v>11.54</v>
       </c>
       <c r="DY8" t="n">
-        <v>7</v>
+        <v>7.04</v>
       </c>
       <c r="DZ8" t="n">
         <v>4.5</v>
       </c>
       <c r="EA8" t="n">
-        <v>22.17</v>
+        <v>22.2</v>
       </c>
       <c r="EB8" t="n">
         <v>1.35</v>
@@ -5938,7 +5938,7 @@
         <v>15</v>
       </c>
       <c r="AR13" t="n">
-        <v>14.5</v>
+        <v>14.58</v>
       </c>
       <c r="AS13" t="n">
         <v>6.17</v>
@@ -5959,7 +5959,7 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>53.75</v>
+        <v>53.92</v>
       </c>
       <c r="AZ13" t="n">
         <v>0.08</v>
@@ -5974,7 +5974,7 @@
         <v>4.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>22</v>
+        <v>22.25</v>
       </c>
       <c r="BE13" t="n">
         <v>1.43</v>
@@ -6169,7 +6169,7 @@
         <v>15.34</v>
       </c>
       <c r="DQ13" t="n">
-        <v>14.88</v>
+        <v>14.92</v>
       </c>
       <c r="DR13" t="n">
         <v>5.54</v>
@@ -6184,7 +6184,7 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>53.29</v>
+        <v>53.38</v>
       </c>
       <c r="DW13" t="n">
         <v>0.08</v>
@@ -6199,7 +6199,7 @@
         <v>4.92</v>
       </c>
       <c r="EA13" t="n">
-        <v>21.79</v>
+        <v>21.92</v>
       </c>
       <c r="EB13" t="n">
         <v>1.56</v>

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="8.4" customWidth="1" min="76" max="76"/>
+    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" t="n">
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
         <v>0.17</v>
@@ -1472,136 +1472,136 @@
         <v>0.08</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.17</v>
+        <v>2.31</v>
       </c>
       <c r="AI2" t="n">
-        <v>92.92</v>
+        <v>92.84999999999999</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AK2" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="AL2" t="n">
-        <v>5.58</v>
+        <v>5.69</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AN2" t="n">
-        <v>53.67</v>
+        <v>55.23</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AQ2" t="n">
-        <v>15.83</v>
+        <v>15.85</v>
       </c>
       <c r="AR2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.92</v>
+        <v>6.85</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>59.42</v>
+        <v>59.77</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BA2" t="n">
-        <v>14.17</v>
+        <v>14.15</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.83</v>
+        <v>9.69</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.33</v>
+        <v>4.46</v>
       </c>
       <c r="BD2" t="n">
-        <v>20.5</v>
+        <v>21.15</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.460000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.71</v>
+        <v>0.76</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="BO2" t="n">
         <v>0.92</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.83</v>
+        <v>3.8</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4</v>
+        <v>4.04</v>
       </c>
       <c r="BR2" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS2" t="n">
-        <v>62.5</v>
+        <v>64</v>
       </c>
       <c r="BT2" t="n">
-        <v>37.5</v>
+        <v>40</v>
       </c>
       <c r="BU2" t="n">
-        <v>33.33</v>
+        <v>36</v>
       </c>
       <c r="BV2" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>33.33</v>
+        <v>36</v>
       </c>
       <c r="BY2" t="n">
         <v>1.5</v>
@@ -1610,25 +1610,25 @@
         <v>1.51</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.59</v>
+        <v>4.57</v>
       </c>
       <c r="CB2" t="n">
-        <v>5.06</v>
+        <v>5.04</v>
       </c>
       <c r="CC2" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CH2" t="n">
         <v>1.44</v>
@@ -1640,16 +1640,16 @@
         <v>2.09</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CM2" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CO2" t="n">
         <v>1.26</v>
@@ -1658,10 +1658,10 @@
         <v>1.85</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CS2" t="n">
         <v>2.78</v>
@@ -1670,22 +1670,22 @@
         <v>3.01</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CW2" t="n">
         <v>2.16</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="DA2" t="n">
         <v>1.61</v>
@@ -1694,85 +1694,85 @@
         <v>1.29</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="DE2" t="n">
         <v>0.12</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="DH2" t="n">
-        <v>95.5</v>
+        <v>95.36</v>
       </c>
       <c r="DI2" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.46</v>
+        <v>5.52</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="DM2" t="n">
-        <v>56.96</v>
+        <v>57.64</v>
       </c>
       <c r="DN2" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="DP2" t="n">
-        <v>15.79</v>
+        <v>15.8</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.71</v>
+        <v>13.96</v>
       </c>
       <c r="DR2" t="n">
         <v>6.08</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>58.46</v>
+        <v>58.68</v>
       </c>
       <c r="DW2" t="n">
         <v>0.12</v>
       </c>
       <c r="DX2" t="n">
-        <v>15.42</v>
+        <v>15.36</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.54</v>
+        <v>10.44</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.88</v>
+        <v>4.92</v>
       </c>
       <c r="EA2" t="n">
-        <v>20.54</v>
+        <v>20.88</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" t="n">
         <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1875,49 +1875,49 @@
         <v>0.08</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.17</v>
+        <v>3.08</v>
       </c>
       <c r="AI3" t="n">
-        <v>88.25</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="AJ3" t="n">
         <v>0.08</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.42</v>
+        <v>4.54</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AN3" t="n">
-        <v>37.33</v>
+        <v>37.15</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="AQ3" t="n">
-        <v>16.17</v>
+        <v>16.23</v>
       </c>
       <c r="AR3" t="n">
-        <v>14.08</v>
+        <v>13.85</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.75</v>
+        <v>6.54</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AV3" t="n">
         <v>0.08</v>
@@ -1929,73 +1929,73 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>50.25</v>
+        <v>50.92</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.83</v>
+        <v>10.69</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.67</v>
+        <v>7.62</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.17</v>
+        <v>3.08</v>
       </c>
       <c r="BD3" t="n">
-        <v>19.17</v>
+        <v>19</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.119999999999999</v>
+        <v>9.24</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="BP3" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.92</v>
+        <v>5.96</v>
       </c>
       <c r="BR3" t="n">
-        <v>83.33</v>
+        <v>80</v>
       </c>
       <c r="BS3" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="BT3" t="n">
-        <v>29.17</v>
+        <v>28</v>
       </c>
       <c r="BU3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BV3" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BY3" t="n">
         <v>2.65</v>
@@ -2013,22 +2013,22 @@
         <v>2.7</v>
       </c>
       <c r="CA3" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="CC3" t="n">
         <v>3.57</v>
       </c>
-      <c r="CB3" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="CC3" t="n">
-        <v>3.73</v>
-      </c>
       <c r="CD3" t="n">
-        <v>4.53</v>
+        <v>4.33</v>
       </c>
       <c r="CE3" t="n">
         <v>1.45</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="CG3" t="n">
         <v>2.61</v>
@@ -2037,7 +2037,7 @@
         <v>1.33</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CJ3" t="n">
         <v>2.03</v>
@@ -2061,31 +2061,31 @@
         <v>2.14</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.96</v>
+        <v>3.99</v>
       </c>
       <c r="CR3" t="n">
         <v>1.45</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CZ3" t="n">
         <v>1.93</v>
@@ -2097,52 +2097,52 @@
         <v>1.4</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.16</v>
+        <v>4.2</v>
       </c>
       <c r="DE3" t="n">
         <v>0.04</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.21</v>
+        <v>3.16</v>
       </c>
       <c r="DH3" t="n">
-        <v>90.70999999999999</v>
+        <v>91.23999999999999</v>
       </c>
       <c r="DI3" t="n">
         <v>0.16</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="DK3" t="n">
-        <v>5</v>
+        <v>5.04</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DM3" t="n">
-        <v>42.16</v>
+        <v>41.88</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="DP3" t="n">
-        <v>15.25</v>
+        <v>15.32</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.83</v>
+        <v>14.68</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.08</v>
+        <v>6.96</v>
       </c>
       <c r="DS3" t="n">
         <v>0.04</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>50.79</v>
+        <v>51.12</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DX3" t="n">
-        <v>12.62</v>
+        <v>12.48</v>
       </c>
       <c r="DY3" t="n">
-        <v>9</v>
+        <v>8.92</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.62</v>
+        <v>3.56</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.12</v>
+        <v>20</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" t="n">
         <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
         <v>0.17</v>
@@ -2281,133 +2281,133 @@
         <v>2</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>75.42</v>
+        <v>76.08</v>
       </c>
       <c r="AJ4" t="n">
         <v>0.08</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AN4" t="n">
-        <v>31.58</v>
+        <v>31.15</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ4" t="n">
-        <v>15.08</v>
+        <v>14.92</v>
       </c>
       <c r="AR4" t="n">
-        <v>15.75</v>
+        <v>15.62</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.25</v>
+        <v>8.23</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>43.92</v>
+        <v>43.15</v>
       </c>
       <c r="AZ4" t="n">
         <v>0.08</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.75</v>
+        <v>9.23</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.67</v>
+        <v>6.15</v>
       </c>
       <c r="BC4" t="n">
         <v>3.08</v>
       </c>
       <c r="BD4" t="n">
-        <v>18.42</v>
+        <v>18.46</v>
       </c>
       <c r="BE4" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.67</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.88</v>
+        <v>5.04</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.79</v>
+        <v>4.68</v>
       </c>
       <c r="BR4" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BS4" t="n">
-        <v>70.83</v>
+        <v>72</v>
       </c>
       <c r="BT4" t="n">
-        <v>45.83</v>
+        <v>44</v>
       </c>
       <c r="BU4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BV4" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX4" t="n">
-        <v>41.67</v>
+        <v>44</v>
       </c>
       <c r="BY4" t="n">
         <v>3.46</v>
@@ -2416,25 +2416,25 @@
         <v>4.14</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.96</v>
+        <v>3.93</v>
       </c>
       <c r="CC4" t="n">
-        <v>6.71</v>
+        <v>6.46</v>
       </c>
       <c r="CD4" t="n">
-        <v>6.78</v>
+        <v>6.62</v>
       </c>
       <c r="CE4" t="n">
         <v>1.43</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CH4" t="n">
         <v>1.36</v>
@@ -2449,37 +2449,37 @@
         <v>1.83</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CM4" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CO4" t="n">
         <v>1.33</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.58</v>
+        <v>3.61</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CS4" t="n">
         <v>3</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CU4" t="n">
         <v>1.39</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CW4" t="n">
         <v>2.09</v>
@@ -2488,7 +2488,7 @@
         <v>1.84</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CZ4" t="n">
         <v>1.98</v>
@@ -2500,10 +2500,10 @@
         <v>1.36</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.83</v>
+        <v>3.87</v>
       </c>
       <c r="DE4" t="n">
         <v>0.08</v>
@@ -2512,37 +2512,37 @@
         <v>1.96</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="DH4" t="n">
-        <v>80</v>
+        <v>80.16</v>
       </c>
       <c r="DI4" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.62</v>
+        <v>4.64</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="DM4" t="n">
-        <v>38</v>
+        <v>37.52</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="DP4" t="n">
-        <v>14</v>
+        <v>13.96</v>
       </c>
       <c r="DQ4" t="n">
-        <v>15.58</v>
+        <v>15.52</v>
       </c>
       <c r="DR4" t="n">
         <v>8.08</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>45.71</v>
+        <v>45.24</v>
       </c>
       <c r="DW4" t="n">
         <v>0.16</v>
       </c>
       <c r="DX4" t="n">
-        <v>9.210000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="DY4" t="n">
-        <v>6</v>
+        <v>6.24</v>
       </c>
       <c r="DZ4" t="n">
         <v>3.2</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.84</v>
+        <v>20.76</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="EC4" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="5">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
         <v>12</v>
@@ -2600,61 +2600,61 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="G5" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="H5" t="n">
-        <v>93.08</v>
+        <v>91.08</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="K5" t="n">
-        <v>3.83</v>
+        <v>3.62</v>
       </c>
       <c r="L5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="M5" t="n">
-        <v>45.92</v>
+        <v>43.69</v>
       </c>
       <c r="N5" t="n">
         <v>0.92</v>
       </c>
       <c r="O5" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="P5" t="n">
-        <v>14.5</v>
+        <v>14.85</v>
       </c>
       <c r="Q5" t="n">
-        <v>15.75</v>
+        <v>15.85</v>
       </c>
       <c r="R5" t="n">
-        <v>5</v>
+        <v>5.15</v>
       </c>
       <c r="S5" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T5" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="V5" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>55.08</v>
+        <v>53.62</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -2663,19 +2663,19 @@
         <v>11.92</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.92</v>
+        <v>8.69</v>
       </c>
       <c r="AB5" t="n">
-        <v>3</v>
+        <v>3.23</v>
       </c>
       <c r="AC5" t="n">
-        <v>24.33</v>
+        <v>23.38</v>
       </c>
       <c r="AD5" t="n">
         <v>1.3</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AF5" t="n">
         <v>0.17</v>
@@ -2759,70 +2759,70 @@
         <v>2.83</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="BH5" t="n">
         <v>8.08</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="BO5" t="n">
         <v>1.04</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.67</v>
+        <v>3.64</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.42</v>
+        <v>4.44</v>
       </c>
       <c r="BR5" t="n">
-        <v>87.5</v>
+        <v>88</v>
       </c>
       <c r="BS5" t="n">
-        <v>62.5</v>
+        <v>64</v>
       </c>
       <c r="BT5" t="n">
-        <v>41.67</v>
+        <v>44</v>
       </c>
       <c r="BU5" t="n">
-        <v>16.67</v>
+        <v>20</v>
       </c>
       <c r="BV5" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>41.67</v>
+        <v>44</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.39</v>
+        <v>3.59</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3.7</v>
+        <v>4.08</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.83</v>
+        <v>3.86</v>
       </c>
       <c r="CC5" t="n">
         <v>5.33</v>
@@ -2834,7 +2834,7 @@
         <v>1.43</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CG5" t="n">
         <v>2.68</v>
@@ -2852,7 +2852,7 @@
         <v>1.9</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CM5" t="n">
         <v>1.84</v>
@@ -2864,25 +2864,25 @@
         <v>1.34</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.79</v>
+        <v>3.77</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CS5" t="n">
         <v>3.01</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CU5" t="n">
         <v>1.4</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CW5" t="n">
         <v>2.08</v>
@@ -2891,10 +2891,10 @@
         <v>1.96</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CZ5" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="DA5" t="n">
         <v>1.52</v>
@@ -2903,52 +2903,52 @@
         <v>1.38</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DD5" t="n">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="DE5" t="n">
         <v>0.08</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="DH5" t="n">
-        <v>83.92</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="DI5" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.96</v>
+        <v>3.84</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DM5" t="n">
-        <v>38.92</v>
+        <v>38.04</v>
       </c>
       <c r="DN5" t="n">
         <v>1.04</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="DP5" t="n">
-        <v>15.42</v>
+        <v>15.56</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.29</v>
+        <v>15.36</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.42</v>
+        <v>7.4</v>
       </c>
       <c r="DS5" t="n">
         <v>0.12</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>51.12</v>
+        <v>50.52</v>
       </c>
       <c r="DW5" t="n">
         <v>0.04</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.17</v>
+        <v>10.24</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.38</v>
+        <v>7.32</v>
       </c>
       <c r="DZ5" t="n">
-        <v>2.79</v>
+        <v>2.92</v>
       </c>
       <c r="EA5" t="n">
-        <v>22.2</v>
+        <v>21.8</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="6">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
         <v>12</v>
@@ -3003,49 +3003,49 @@
         <v>0.08</v>
       </c>
       <c r="F6" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
         <v>1.92</v>
       </c>
       <c r="H6" t="n">
-        <v>86.08</v>
+        <v>86</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3.58</v>
+        <v>3.46</v>
       </c>
       <c r="K6" t="n">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="L6" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="M6" t="n">
-        <v>42.67</v>
+        <v>42.62</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="O6" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="P6" t="n">
-        <v>16.5</v>
+        <v>16.77</v>
       </c>
       <c r="Q6" t="n">
-        <v>16.33</v>
+        <v>16.23</v>
       </c>
       <c r="R6" t="n">
-        <v>7.08</v>
+        <v>7.38</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="T6" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3057,28 +3057,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>44.58</v>
+        <v>45.31</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="Z6" t="n">
-        <v>14</v>
+        <v>13.85</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.5</v>
+        <v>9.15</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.5</v>
+        <v>4.69</v>
       </c>
       <c r="AC6" t="n">
-        <v>18.33</v>
+        <v>18.31</v>
       </c>
       <c r="AD6" t="n">
         <v>1.51</v>
       </c>
       <c r="AE6" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,70 +3162,70 @@
         <v>4.17</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.539999999999999</v>
+        <v>9.52</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BP6" t="n">
-        <v>5.08</v>
+        <v>5.12</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.38</v>
+        <v>4.32</v>
       </c>
       <c r="BR6" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS6" t="n">
-        <v>83.33</v>
+        <v>84</v>
       </c>
       <c r="BT6" t="n">
-        <v>58.33</v>
+        <v>56</v>
       </c>
       <c r="BU6" t="n">
-        <v>33.33</v>
+        <v>32</v>
       </c>
       <c r="BV6" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>70.83</v>
+        <v>68</v>
       </c>
       <c r="BY6" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="BZ6" t="n">
-        <v>4.33</v>
+        <v>4.17</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="CC6" t="n">
         <v>5.32</v>
@@ -3237,7 +3237,7 @@
         <v>1.41</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="CG6" t="n">
         <v>2.74</v>
@@ -3255,10 +3255,10 @@
         <v>1.77</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="CM6" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CN6" t="n">
         <v>1.55</v>
@@ -3270,88 +3270,88 @@
         <v>2.03</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="CR6" t="n">
         <v>1.45</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CT6" t="n">
         <v>2.78</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CV6" t="n">
         <v>1.84</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CX6" t="n">
         <v>1.87</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CZ6" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="DA6" t="n">
         <v>1.57</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.79</v>
+        <v>3.8</v>
       </c>
       <c r="DE6" t="n">
         <v>0.04</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="DG6" t="n">
         <v>1.84</v>
       </c>
       <c r="DH6" t="n">
-        <v>83.04000000000001</v>
+        <v>83.12</v>
       </c>
       <c r="DI6" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ6" t="n">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.12</v>
+        <v>4.08</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="DM6" t="n">
-        <v>40.62</v>
+        <v>40.68</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="DP6" t="n">
-        <v>17.38</v>
+        <v>17.48</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14.95</v>
+        <v>14.96</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.79</v>
+        <v>7.92</v>
       </c>
       <c r="DS6" t="n">
         <v>0.04</v>
@@ -3363,19 +3363,19 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>46.08</v>
+        <v>46.4</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.58</v>
+        <v>13.52</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.92</v>
+        <v>8.76</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.66</v>
+        <v>4.76</v>
       </c>
       <c r="EA6" t="n">
         <v>18.16</v>
@@ -3384,7 +3384,7 @@
         <v>1.48</v>
       </c>
       <c r="EC6" t="n">
-        <v>3.58</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="7">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
         <v>12</v>
@@ -3406,82 +3406,82 @@
         <v>0.08</v>
       </c>
       <c r="F7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H7" t="n">
+        <v>85.77</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="M7" t="n">
+        <v>35.46</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="O7" t="n">
         <v>2</v>
       </c>
-      <c r="G7" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="H7" t="n">
-        <v>84.58</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="M7" t="n">
-        <v>34.33</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.67</v>
-      </c>
       <c r="P7" t="n">
-        <v>16.42</v>
+        <v>16.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>15.58</v>
+        <v>15.54</v>
       </c>
       <c r="R7" t="n">
-        <v>6.83</v>
+        <v>7.15</v>
       </c>
       <c r="S7" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="T7" t="n">
         <v>0.92</v>
       </c>
       <c r="U7" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="V7" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>44.75</v>
+        <v>46.38</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>11.75</v>
+        <v>12</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="AB7" t="n">
         <v>4</v>
       </c>
       <c r="AC7" t="n">
-        <v>17.58</v>
+        <v>17.38</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE7" t="n">
-        <v>3.75</v>
+        <v>3.69</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,70 +3565,70 @@
         <v>3</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.460000000000001</v>
+        <v>8.56</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.71</v>
+        <v>3.92</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.67</v>
+        <v>4.56</v>
       </c>
       <c r="BR7" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS7" t="n">
-        <v>79.17</v>
+        <v>80</v>
       </c>
       <c r="BT7" t="n">
-        <v>37.5</v>
+        <v>36</v>
       </c>
       <c r="BU7" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BV7" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BW7" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX7" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="BY7" t="n">
-        <v>4.95</v>
+        <v>4.73</v>
       </c>
       <c r="BZ7" t="n">
-        <v>5.13</v>
+        <v>4.88</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.86</v>
+        <v>3.83</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.93</v>
+        <v>3.91</v>
       </c>
       <c r="CC7" t="n">
         <v>6.46</v>
@@ -3637,13 +3637,13 @@
         <v>6.8</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CH7" t="n">
         <v>1.36</v>
@@ -3658,7 +3658,7 @@
         <v>1.88</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CM7" t="n">
         <v>1.85</v>
@@ -3667,13 +3667,13 @@
         <v>1.5</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.7</v>
+        <v>3.73</v>
       </c>
       <c r="CR7" t="n">
         <v>1.45</v>
@@ -3682,7 +3682,7 @@
         <v>3.07</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CU7" t="n">
         <v>1.38</v>
@@ -3709,85 +3709,85 @@
         <v>1.38</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.97</v>
+        <v>4.01</v>
       </c>
       <c r="DE7" t="n">
         <v>0.04</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="DG7" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DH7" t="n">
-        <v>82.95999999999999</v>
+        <v>83.64</v>
       </c>
       <c r="DI7" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.54</v>
+        <v>3.64</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.3</v>
+        <v>0.44</v>
       </c>
       <c r="DM7" t="n">
-        <v>33.62</v>
+        <v>34.24</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.54</v>
+        <v>1.72</v>
       </c>
       <c r="DP7" t="n">
-        <v>16.38</v>
+        <v>16.24</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.42</v>
+        <v>14.44</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.039999999999999</v>
+        <v>8.16</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>42.38</v>
+        <v>43.32</v>
       </c>
       <c r="DW7" t="n">
         <v>0.12</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.16</v>
+        <v>11.32</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.34</v>
+        <v>7.48</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.83</v>
+        <v>3.84</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.2</v>
+        <v>17.12</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
         <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E8" t="n">
         <v>0.33</v>
@@ -3887,52 +3887,52 @@
         <v>1.33</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AI8" t="n">
-        <v>93.83</v>
+        <v>90.23</v>
       </c>
       <c r="AJ8" t="n">
         <v>0.08</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AL8" t="n">
-        <v>5.42</v>
+        <v>5.31</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AN8" t="n">
-        <v>43.58</v>
+        <v>41.69</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AP8" t="n">
         <v>2.92</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13.17</v>
+        <v>12.85</v>
       </c>
       <c r="AR8" t="n">
-        <v>16.25</v>
+        <v>16.15</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.67</v>
+        <v>6.46</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AV8" t="n">
         <v>0.08</v>
@@ -3944,82 +3944,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>56.17</v>
+        <v>54.62</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.92</v>
+        <v>9.31</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.17</v>
+        <v>5.77</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.75</v>
+        <v>3.54</v>
       </c>
       <c r="BD8" t="n">
-        <v>21.08</v>
+        <v>20.69</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.210000000000001</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="BJ8" t="n">
         <v>1.04</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="BN8" t="n">
         <v>1.88</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.92</v>
+        <v>5.08</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.29</v>
+        <v>4.28</v>
       </c>
       <c r="BR8" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS8" t="n">
-        <v>87.5</v>
+        <v>88</v>
       </c>
       <c r="BT8" t="n">
-        <v>66.67</v>
+        <v>68</v>
       </c>
       <c r="BU8" t="n">
-        <v>58.33</v>
+        <v>56</v>
       </c>
       <c r="BV8" t="n">
-        <v>29.17</v>
+        <v>28</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BX8" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="BY8" t="n">
         <v>2.74</v>
@@ -4028,40 +4028,40 @@
         <v>2.8</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.67</v>
+        <v>3.74</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.85</v>
+        <v>3.93</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.17</v>
+        <v>4.54</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.19</v>
+        <v>4.8</v>
       </c>
       <c r="CE8" t="n">
         <v>1.39</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="CH8" t="n">
         <v>1.38</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CK8" t="n">
         <v>1.83</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="CM8" t="n">
         <v>1.91</v>
@@ -4073,10 +4073,10 @@
         <v>1.3</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="CR8" t="n">
         <v>1.41</v>
@@ -4091,10 +4091,10 @@
         <v>1.39</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CX8" t="n">
         <v>1.86</v>
@@ -4106,28 +4106,28 @@
         <v>1.95</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="DB8" t="n">
         <v>1.34</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="DH8" t="n">
-        <v>94.54000000000001</v>
+        <v>92.64</v>
       </c>
       <c r="DI8" t="n">
         <v>0.04</v>
@@ -4136,61 +4136,61 @@
         <v>1.92</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.92</v>
+        <v>4.88</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="DM8" t="n">
-        <v>42.62</v>
+        <v>41.68</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="DP8" t="n">
-        <v>12.62</v>
+        <v>12.48</v>
       </c>
       <c r="DQ8" t="n">
-        <v>16.62</v>
+        <v>16.56</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.75</v>
+        <v>6.64</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>57.42</v>
+        <v>56.56</v>
       </c>
       <c r="DW8" t="n">
         <v>0.08</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.54</v>
+        <v>11.16</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.04</v>
+        <v>6.8</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.5</v>
+        <v>4.36</v>
       </c>
       <c r="EA8" t="n">
-        <v>22.2</v>
+        <v>21.96</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9">
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" t="n">
         <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="H9" t="n">
-        <v>77.75</v>
+        <v>75.45999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="J9" t="n">
         <v>2.08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.17</v>
+        <v>2.92</v>
       </c>
       <c r="L9" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="M9" t="n">
-        <v>27.92</v>
+        <v>26.62</v>
       </c>
       <c r="N9" t="n">
         <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="P9" t="n">
-        <v>15.58</v>
+        <v>14.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>16.75</v>
+        <v>16.62</v>
       </c>
       <c r="R9" t="n">
-        <v>9.5</v>
+        <v>9.85</v>
       </c>
       <c r="S9" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="T9" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="U9" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="V9" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>45.67</v>
+        <v>45.31</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.58</v>
+        <v>9</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.08</v>
+        <v>5.69</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.5</v>
+        <v>3.31</v>
       </c>
       <c r="AC9" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AF9" t="n">
         <v>0.33</v>
@@ -4374,67 +4374,67 @@
         <v>3.08</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.789999999999999</v>
+        <v>8.48</v>
       </c>
       <c r="BI9" t="n">
         <v>3.08</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL9" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.54</v>
+        <v>0.6</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.71</v>
+        <v>4.56</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.04</v>
+        <v>3.88</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>83.33</v>
+        <v>84</v>
       </c>
       <c r="BT9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BU9" t="n">
-        <v>33.33</v>
+        <v>32</v>
       </c>
       <c r="BV9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX9" t="n">
-        <v>45.83</v>
+        <v>44</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.37</v>
+        <v>3.88</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.54</v>
+        <v>4.08</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.03</v>
+        <v>4.08</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.3</v>
+        <v>4.35</v>
       </c>
       <c r="CC9" t="n">
         <v>7.18</v>
@@ -4446,10 +4446,10 @@
         <v>1.38</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CH9" t="n">
         <v>1.42</v>
@@ -4464,7 +4464,7 @@
         <v>1.73</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CM9" t="n">
         <v>2.02</v>
@@ -4476,34 +4476,34 @@
         <v>1.27</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="CU9" t="n">
         <v>1.46</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CX9" t="n">
         <v>1.75</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.08</v>
@@ -4515,52 +4515,52 @@
         <v>1.3</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="DH9" t="n">
-        <v>72.12</v>
+        <v>71.16</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="DK9" t="n">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DM9" t="n">
-        <v>27.42</v>
+        <v>26.76</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.79</v>
+        <v>13.52</v>
       </c>
       <c r="DQ9" t="n">
-        <v>16.08</v>
+        <v>16.04</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.460000000000001</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="DS9" t="n">
         <v>0.16</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>44.12</v>
+        <v>44</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.67</v>
+        <v>8.4</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.38</v>
+        <v>5.2</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.67</v>
+        <v>16.48</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
         <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4693,139 +4693,139 @@
         <v>0.83</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AG10" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.42</v>
+        <v>3.15</v>
       </c>
       <c r="AI10" t="n">
-        <v>125.5</v>
+        <v>127.69</v>
       </c>
       <c r="AJ10" t="n">
         <v>-0.08</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AL10" t="n">
-        <v>5.92</v>
+        <v>5.54</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AN10" t="n">
-        <v>65.75</v>
+        <v>65.08</v>
       </c>
       <c r="AO10" t="n">
         <v>0.92</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AQ10" t="n">
-        <v>15.33</v>
+        <v>14.69</v>
       </c>
       <c r="AR10" t="n">
         <v>12</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.42</v>
+        <v>4.31</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>60.42</v>
+        <v>60.31</v>
       </c>
       <c r="AZ10" t="n">
         <v>0.08</v>
       </c>
       <c r="BA10" t="n">
-        <v>15.58</v>
+        <v>15.46</v>
       </c>
       <c r="BB10" t="n">
-        <v>9.92</v>
+        <v>9.69</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.67</v>
+        <v>5.77</v>
       </c>
       <c r="BD10" t="n">
-        <v>26.67</v>
+        <v>26.69</v>
       </c>
       <c r="BE10" t="n">
         <v>1.86</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.789999999999999</v>
+        <v>9.44</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.54</v>
+        <v>4.4</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.21</v>
+        <v>5</v>
       </c>
       <c r="BR10" t="n">
-        <v>87.5</v>
+        <v>88</v>
       </c>
       <c r="BS10" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BT10" t="n">
-        <v>37.5</v>
+        <v>40</v>
       </c>
       <c r="BU10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BV10" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>33.33</v>
+        <v>32</v>
       </c>
       <c r="BY10" t="n">
         <v>1.3</v>
@@ -4837,13 +4837,13 @@
         <v>5.37</v>
       </c>
       <c r="CB10" t="n">
-        <v>6.03</v>
+        <v>6.01</v>
       </c>
       <c r="CC10" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="CD10" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="CE10" t="n">
         <v>1.33</v>
@@ -4852,25 +4852,25 @@
         <v>2.58</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="CH10" t="n">
         <v>1.48</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CJ10" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CK10" t="n">
         <v>1.82</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="CM10" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CN10" t="n">
         <v>1.56</v>
@@ -4882,16 +4882,16 @@
         <v>1.8</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="CU10" t="n">
         <v>1.49</v>
@@ -4900,13 +4900,13 @@
         <v>1.65</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CZ10" t="n">
         <v>2</v>
@@ -4918,85 +4918,85 @@
         <v>1.28</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="DE10" t="n">
         <v>0.08</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="DG10" t="n">
-        <v>3.67</v>
+        <v>3.52</v>
       </c>
       <c r="DH10" t="n">
-        <v>129.92</v>
+        <v>130.88</v>
       </c>
       <c r="DI10" t="n">
         <v>-0.08</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="DK10" t="n">
-        <v>7.54</v>
+        <v>7.28</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="DM10" t="n">
-        <v>69.58</v>
+        <v>69.08</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="DO10" t="n">
-        <v>3.83</v>
+        <v>3.72</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.04</v>
+        <v>12.8</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.34</v>
+        <v>12.32</v>
       </c>
       <c r="DR10" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>62.5</v>
+        <v>62.36</v>
       </c>
       <c r="DW10" t="n">
         <v>0.08</v>
       </c>
       <c r="DX10" t="n">
-        <v>18.58</v>
+        <v>18.4</v>
       </c>
       <c r="DY10" t="n">
-        <v>12.71</v>
+        <v>12.48</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.88</v>
+        <v>5.92</v>
       </c>
       <c r="EA10" t="n">
         <v>26.92</v>
       </c>
       <c r="EB10" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="11">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
         <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="F11" t="n">
         <v>1.08</v>
       </c>
       <c r="G11" t="n">
-        <v>3.83</v>
+        <v>3.77</v>
       </c>
       <c r="H11" t="n">
-        <v>107.67</v>
+        <v>108.23</v>
       </c>
       <c r="I11" t="n">
         <v>0.08</v>
       </c>
       <c r="J11" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="K11" t="n">
-        <v>6.75</v>
+        <v>6.92</v>
       </c>
       <c r="L11" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>61.42</v>
+        <v>61.38</v>
       </c>
       <c r="N11" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="O11" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="P11" t="n">
-        <v>11</v>
+        <v>11.31</v>
       </c>
       <c r="Q11" t="n">
-        <v>13.17</v>
+        <v>12.85</v>
       </c>
       <c r="R11" t="n">
-        <v>4.33</v>
+        <v>4.08</v>
       </c>
       <c r="S11" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="U11" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="V11" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>62.75</v>
+        <v>62.85</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>16.42</v>
+        <v>15.85</v>
       </c>
       <c r="AA11" t="n">
-        <v>10.33</v>
+        <v>10</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.08</v>
+        <v>5.85</v>
       </c>
       <c r="AC11" t="n">
-        <v>23.75</v>
+        <v>23.85</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AF11" t="n">
         <v>0.17</v>
@@ -5177,70 +5177,70 @@
         <v>1.58</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.5</v>
+        <v>8.68</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.75</v>
+        <v>3.96</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.75</v>
+        <v>4.72</v>
       </c>
       <c r="BR11" t="n">
-        <v>83.33</v>
+        <v>84</v>
       </c>
       <c r="BS11" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BT11" t="n">
-        <v>54.17</v>
+        <v>56</v>
       </c>
       <c r="BU11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BV11" t="n">
-        <v>20.83</v>
+        <v>20</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX11" t="n">
-        <v>37.5</v>
+        <v>36</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.72</v>
+        <v>4.74</v>
       </c>
       <c r="CB11" t="n">
-        <v>5.15</v>
+        <v>5.17</v>
       </c>
       <c r="CC11" t="n">
         <v>1.96</v>
@@ -5264,16 +5264,16 @@
         <v>1.74</v>
       </c>
       <c r="CJ11" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CK11" t="n">
         <v>1.76</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="CM11" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CN11" t="n">
         <v>1.59</v>
@@ -5282,10 +5282,10 @@
         <v>1.25</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="CR11" t="n">
         <v>1.4</v>
@@ -5300,10 +5300,10 @@
         <v>1.47</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CX11" t="n">
         <v>1.77</v>
@@ -5321,85 +5321,85 @@
         <v>1.28</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="DD11" t="n">
         <v>3.23</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="DF11" t="n">
         <v>1.04</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="DH11" t="n">
-        <v>105.71</v>
+        <v>106.08</v>
       </c>
       <c r="DI11" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.62</v>
+        <v>5.76</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM11" t="n">
-        <v>57.08</v>
+        <v>57.24</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.08</v>
+        <v>12.2</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13.08</v>
+        <v>12.92</v>
       </c>
       <c r="DR11" t="n">
-        <v>4.96</v>
+        <v>4.8</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>60.88</v>
+        <v>61</v>
       </c>
       <c r="DW11" t="n">
         <v>0.04</v>
       </c>
       <c r="DX11" t="n">
-        <v>14.3</v>
+        <v>14.08</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.289999999999999</v>
+        <v>9.16</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5</v>
+        <v>4.92</v>
       </c>
       <c r="EA11" t="n">
-        <v>23.75</v>
+        <v>23.8</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12" t="n">
         <v>12</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5502,49 +5502,49 @@
         <v>0.08</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AI12" t="n">
-        <v>72.58</v>
+        <v>72.92</v>
       </c>
       <c r="AJ12" t="n">
         <v>0.08</v>
       </c>
       <c r="AK12" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AN12" t="n">
-        <v>30.08</v>
+        <v>30.23</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.08</v>
+        <v>1.31</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14.75</v>
+        <v>14.62</v>
       </c>
       <c r="AR12" t="n">
-        <v>13.42</v>
+        <v>13.15</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.17</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,82 +5556,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>39.33</v>
+        <v>39.62</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BA12" t="n">
-        <v>8.08</v>
+        <v>8.31</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.08</v>
+        <v>5.31</v>
       </c>
       <c r="BC12" t="n">
         <v>3</v>
       </c>
       <c r="BD12" t="n">
-        <v>16.83</v>
+        <v>17</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.75</v>
+        <v>8.84</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.25</v>
+        <v>4.36</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.46</v>
+        <v>4.44</v>
       </c>
       <c r="BR12" t="n">
-        <v>95.83</v>
+        <v>92</v>
       </c>
       <c r="BS12" t="n">
-        <v>66.67</v>
+        <v>64</v>
       </c>
       <c r="BT12" t="n">
-        <v>45.83</v>
+        <v>44</v>
       </c>
       <c r="BU12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BV12" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BW12" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BX12" t="n">
-        <v>37.5</v>
+        <v>36</v>
       </c>
       <c r="BY12" t="n">
         <v>5.2</v>
@@ -5640,25 +5640,25 @@
         <v>5.47</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="CB12" t="n">
         <v>4.2</v>
       </c>
       <c r="CC12" t="n">
-        <v>7.11</v>
+        <v>7.19</v>
       </c>
       <c r="CD12" t="n">
-        <v>8.52</v>
+        <v>8.41</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CH12" t="n">
         <v>1.35</v>
@@ -5667,28 +5667,28 @@
         <v>1.68</v>
       </c>
       <c r="CJ12" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CO12" t="n">
         <v>1.34</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="CR12" t="n">
         <v>1.42</v>
@@ -5697,7 +5697,7 @@
         <v>2.98</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="CU12" t="n">
         <v>1.4</v>
@@ -5706,7 +5706,7 @@
         <v>1.77</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CX12" t="n">
         <v>1.88</v>
@@ -5733,43 +5733,43 @@
         <v>0.04</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="DG12" t="n">
         <v>1.84</v>
       </c>
       <c r="DH12" t="n">
-        <v>77.58</v>
+        <v>77.56</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="DK12" t="n">
-        <v>3.38</v>
+        <v>3.48</v>
       </c>
       <c r="DL12" t="n">
         <v>0.08</v>
       </c>
       <c r="DM12" t="n">
-        <v>32.5</v>
+        <v>32.48</v>
       </c>
       <c r="DN12" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.25</v>
+        <v>13.24</v>
       </c>
       <c r="DQ12" t="n">
-        <v>13</v>
+        <v>12.88</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.300000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="DS12" t="n">
         <v>0.16</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>42.21</v>
+        <v>42.24</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DX12" t="n">
-        <v>8.42</v>
+        <v>8.52</v>
       </c>
       <c r="DY12" t="n">
-        <v>5.75</v>
+        <v>5.84</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="EA12" t="n">
-        <v>17.33</v>
+        <v>17.4</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="13">
@@ -5812,94 +5812,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13" t="n">
         <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="F13" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="G13" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="H13" t="n">
-        <v>98.17</v>
+        <v>98.84999999999999</v>
       </c>
       <c r="I13" t="n">
         <v>0.08</v>
       </c>
       <c r="J13" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="K13" t="n">
-        <v>4.83</v>
+        <v>4.85</v>
       </c>
       <c r="L13" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="M13" t="n">
-        <v>61.92</v>
+        <v>62.46</v>
       </c>
       <c r="N13" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="O13" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="P13" t="n">
-        <v>15.67</v>
+        <v>15.23</v>
       </c>
       <c r="Q13" t="n">
-        <v>15.25</v>
+        <v>15.15</v>
       </c>
       <c r="R13" t="n">
-        <v>4.92</v>
+        <v>5.15</v>
       </c>
       <c r="S13" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="T13" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="U13" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="V13" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>52.83</v>
+        <v>53.15</v>
       </c>
       <c r="Y13" t="n">
         <v>0.08</v>
       </c>
       <c r="Z13" t="n">
-        <v>13.83</v>
+        <v>14.08</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.5</v>
+        <v>8.69</v>
       </c>
       <c r="AB13" t="n">
-        <v>5.33</v>
+        <v>5.38</v>
       </c>
       <c r="AC13" t="n">
-        <v>21.58</v>
+        <v>21.08</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
         <v>0.25</v>
@@ -5983,70 +5983,70 @@
         <v>2.42</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.79</v>
+        <v>2.68</v>
       </c>
       <c r="BH13" t="n">
-        <v>7.38</v>
+        <v>7.52</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.79</v>
+        <v>2.68</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3.54</v>
+        <v>3.56</v>
       </c>
       <c r="BR13" t="n">
-        <v>95.83</v>
+        <v>92</v>
       </c>
       <c r="BS13" t="n">
-        <v>83.33</v>
+        <v>80</v>
       </c>
       <c r="BT13" t="n">
-        <v>54.17</v>
+        <v>52</v>
       </c>
       <c r="BU13" t="n">
-        <v>29.17</v>
+        <v>28</v>
       </c>
       <c r="BV13" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>54.17</v>
+        <v>52</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.1</v>
+        <v>4.12</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.36</v>
+        <v>4.35</v>
       </c>
       <c r="CC13" t="n">
         <v>2.43</v>
@@ -6058,7 +6058,7 @@
         <v>1.39</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CG13" t="n">
         <v>2.83</v>
@@ -6067,10 +6067,10 @@
         <v>1.4</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CK13" t="n">
         <v>1.68</v>
@@ -6079,7 +6079,7 @@
         <v>2.3</v>
       </c>
       <c r="CM13" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CN13" t="n">
         <v>1.61</v>
@@ -6097,7 +6097,7 @@
         <v>1.41</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="CT13" t="n">
         <v>2.91</v>
@@ -6130,82 +6130,82 @@
         <v>2.08</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.71</v>
+        <v>3.72</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="DH13" t="n">
-        <v>98.58</v>
+        <v>98.92</v>
       </c>
       <c r="DI13" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.58</v>
+        <v>4.6</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DM13" t="n">
-        <v>55.92</v>
+        <v>56.44</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="DP13" t="n">
-        <v>15.34</v>
+        <v>15.12</v>
       </c>
       <c r="DQ13" t="n">
-        <v>14.92</v>
+        <v>14.88</v>
       </c>
       <c r="DR13" t="n">
-        <v>5.54</v>
+        <v>5.64</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>53.38</v>
+        <v>53.52</v>
       </c>
       <c r="DW13" t="n">
         <v>0.08</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.88</v>
+        <v>13.04</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.96</v>
+        <v>8.08</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.92</v>
+        <v>4.96</v>
       </c>
       <c r="EA13" t="n">
-        <v>21.92</v>
+        <v>21.64</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="14">
@@ -6215,10 +6215,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D14" t="n">
         <v>12</v>
@@ -6227,28 +6227,28 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="G14" t="n">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="H14" t="n">
-        <v>73.5</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="K14" t="n">
-        <v>2.33</v>
+        <v>2.62</v>
       </c>
       <c r="L14" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="M14" t="n">
-        <v>34</v>
+        <v>33.77</v>
       </c>
       <c r="N14" t="n">
         <v>0.92</v>
@@ -6257,19 +6257,19 @@
         <v>1.08</v>
       </c>
       <c r="P14" t="n">
-        <v>14.83</v>
+        <v>14.46</v>
       </c>
       <c r="Q14" t="n">
-        <v>13.75</v>
+        <v>14</v>
       </c>
       <c r="R14" t="n">
-        <v>7.83</v>
+        <v>8.15</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="T14" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6281,28 +6281,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>38.83</v>
+        <v>39</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="Z14" t="n">
-        <v>9.58</v>
+        <v>9.85</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.33</v>
+        <v>7.38</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.25</v>
+        <v>2.46</v>
       </c>
       <c r="AC14" t="n">
-        <v>19.25</v>
+        <v>19.15</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6386,70 +6386,70 @@
         <v>2.92</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.460000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.04</v>
+        <v>4.08</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.38</v>
+        <v>4.48</v>
       </c>
       <c r="BR14" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="BS14" t="n">
-        <v>83.33</v>
+        <v>80</v>
       </c>
       <c r="BT14" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="BU14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BV14" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BW14" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX14" t="n">
-        <v>41.67</v>
+        <v>40</v>
       </c>
       <c r="BY14" t="n">
-        <v>6.39</v>
+        <v>6.24</v>
       </c>
       <c r="BZ14" t="n">
-        <v>7.41</v>
+        <v>7.22</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.66</v>
+        <v>4.6</v>
       </c>
       <c r="CB14" t="n">
-        <v>5.32</v>
+        <v>5.25</v>
       </c>
       <c r="CC14" t="n">
         <v>10.09</v>
@@ -6458,19 +6458,19 @@
         <v>12.75</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CJ14" t="n">
         <v>2.11</v>
@@ -6482,100 +6482,100 @@
         <v>2.42</v>
       </c>
       <c r="CM14" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CV14" t="n">
         <v>1.74</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DA14" t="n">
         <v>1.61</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.4</v>
+        <v>3.47</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="DG14" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="DH14" t="n">
-        <v>65.29000000000001</v>
+        <v>65.8</v>
       </c>
       <c r="DI14" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.12</v>
+        <v>3.04</v>
       </c>
       <c r="DK14" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="DM14" t="n">
-        <v>30.21</v>
+        <v>30.24</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DO14" t="n">
         <v>1</v>
       </c>
       <c r="DP14" t="n">
-        <v>14.2</v>
+        <v>14.04</v>
       </c>
       <c r="DQ14" t="n">
-        <v>12.75</v>
+        <v>12.92</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.83</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="DS14" t="n">
         <v>0.04</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>36.79</v>
+        <v>36.96</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DX14" t="n">
-        <v>7.83</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="DY14" t="n">
-        <v>5.58</v>
+        <v>5.68</v>
       </c>
       <c r="DZ14" t="n">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.66</v>
+        <v>17.68</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C15" t="n">
         <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E15" t="n">
         <v>0.08</v>
@@ -6714,46 +6714,46 @@
         <v>2</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AI15" t="n">
-        <v>83.42</v>
+        <v>82.69</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.25</v>
+        <v>0.38</v>
       </c>
       <c r="AN15" t="n">
-        <v>42.17</v>
+        <v>42.62</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="AQ15" t="n">
-        <v>16.5</v>
+        <v>16.38</v>
       </c>
       <c r="AR15" t="n">
-        <v>14.42</v>
+        <v>14.92</v>
       </c>
       <c r="AS15" t="n">
-        <v>8</v>
+        <v>7.92</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AU15" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6765,82 +6765,82 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>48.25</v>
+        <v>48.08</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.92</v>
+        <v>10</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.42</v>
+        <v>6.62</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="BD15" t="n">
-        <v>21.83</v>
+        <v>21.62</v>
       </c>
       <c r="BE15" t="n">
         <v>1.18</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.289999999999999</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.33</v>
+        <v>5.24</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BT15" t="n">
-        <v>45.83</v>
+        <v>44</v>
       </c>
       <c r="BU15" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BV15" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BW15" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX15" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BY15" t="n">
         <v>4.07</v>
@@ -6849,40 +6849,40 @@
         <v>4.35</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.79</v>
+        <v>3.76</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.94</v>
+        <v>3.91</v>
       </c>
       <c r="CC15" t="n">
-        <v>6.24</v>
+        <v>6.01</v>
       </c>
       <c r="CD15" t="n">
-        <v>6.55</v>
+        <v>6.34</v>
       </c>
       <c r="CE15" t="n">
         <v>1.4</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="CG15" t="n">
         <v>2.75</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CI15" t="n">
         <v>1.78</v>
       </c>
       <c r="CJ15" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CK15" t="n">
         <v>1.86</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="CM15" t="n">
         <v>1.88</v>
@@ -6897,13 +6897,13 @@
         <v>2.04</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="CR15" t="n">
         <v>1.44</v>
       </c>
       <c r="CS15" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CT15" t="n">
         <v>2.82</v>
@@ -6915,16 +6915,16 @@
         <v>1.82</v>
       </c>
       <c r="CW15" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="CZ15" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="DA15" t="n">
         <v>1.57</v>
@@ -6936,49 +6936,49 @@
         <v>2.12</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="DE15" t="n">
         <v>0.08</v>
       </c>
       <c r="DF15" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="DH15" t="n">
-        <v>77.88</v>
+        <v>77.72</v>
       </c>
       <c r="DI15" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.34</v>
+        <v>0.4</v>
       </c>
       <c r="DM15" t="n">
-        <v>37.62</v>
+        <v>38.04</v>
       </c>
       <c r="DN15" t="n">
         <v>0.92</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="DP15" t="n">
-        <v>15.5</v>
+        <v>15.48</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.3</v>
+        <v>15.52</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.79</v>
+        <v>7.76</v>
       </c>
       <c r="DS15" t="n">
         <v>0.16</v>
@@ -6990,22 +6990,22 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>48.16</v>
+        <v>48.08</v>
       </c>
       <c r="DW15" t="n">
         <v>0.04</v>
       </c>
       <c r="DX15" t="n">
-        <v>11.42</v>
+        <v>11.4</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.71</v>
+        <v>7.76</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.71</v>
+        <v>3.64</v>
       </c>
       <c r="EA15" t="n">
-        <v>21.04</v>
+        <v>20.96</v>
       </c>
       <c r="EB15" t="n">
         <v>1.18</v>

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -1541,7 +1541,7 @@
         <v>4.46</v>
       </c>
       <c r="BD2" t="n">
-        <v>21.15</v>
+        <v>21.31</v>
       </c>
       <c r="BE2" t="n">
         <v>1.6</v>
@@ -1766,7 +1766,7 @@
         <v>4.92</v>
       </c>
       <c r="EA2" t="n">
-        <v>20.88</v>
+        <v>20.96</v>
       </c>
       <c r="EB2" t="n">
         <v>1.72</v>
@@ -1929,7 +1929,7 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>50.92</v>
+        <v>50.85</v>
       </c>
       <c r="AZ3" t="n">
         <v>0.15</v>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>51.12</v>
+        <v>51.08</v>
       </c>
       <c r="DW3" t="n">
         <v>0.2</v>
@@ -2338,16 +2338,16 @@
         <v>0.08</v>
       </c>
       <c r="BA4" t="n">
-        <v>9.23</v>
+        <v>9.31</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.15</v>
+        <v>6.23</v>
       </c>
       <c r="BC4" t="n">
         <v>3.08</v>
       </c>
       <c r="BD4" t="n">
-        <v>18.46</v>
+        <v>18.62</v>
       </c>
       <c r="BE4" t="n">
         <v>1.03</v>
@@ -2563,16 +2563,16 @@
         <v>0.16</v>
       </c>
       <c r="DX4" t="n">
-        <v>9.44</v>
+        <v>9.48</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.24</v>
+        <v>6.28</v>
       </c>
       <c r="DZ4" t="n">
         <v>3.2</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.76</v>
+        <v>20.84</v>
       </c>
       <c r="EB4" t="n">
         <v>1.1</v>
@@ -3442,7 +3442,7 @@
         <v>15.54</v>
       </c>
       <c r="R7" t="n">
-        <v>7.15</v>
+        <v>7.23</v>
       </c>
       <c r="S7" t="n">
         <v>1.62</v>
@@ -3754,7 +3754,7 @@
         <v>14.44</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.16</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DS7" t="n">
         <v>0.2</v>
@@ -6281,7 +6281,7 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>39</v>
+        <v>39.08</v>
       </c>
       <c r="Y14" t="n">
         <v>0.31</v>
@@ -6587,7 +6587,7 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>36.96</v>
+        <v>37</v>
       </c>
       <c r="DW14" t="n">
         <v>0.36</v>

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
+    <col width="8.4" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
         <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="F2" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="G2" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="H2" t="n">
-        <v>98.08</v>
+        <v>95.62</v>
       </c>
       <c r="I2" t="n">
         <v>0.08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="K2" t="n">
-        <v>5.33</v>
+        <v>5.15</v>
       </c>
       <c r="L2" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>60.25</v>
+        <v>57.62</v>
       </c>
       <c r="N2" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="O2" t="n">
-        <v>2.67</v>
+        <v>2.46</v>
       </c>
       <c r="P2" t="n">
-        <v>15.75</v>
+        <v>15.77</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.92</v>
+        <v>14.08</v>
       </c>
       <c r="R2" t="n">
-        <v>5.25</v>
+        <v>5.62</v>
       </c>
       <c r="S2" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="T2" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="U2" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="V2" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>57.5</v>
+        <v>57.46</v>
       </c>
       <c r="Y2" t="n">
         <v>0.08</v>
       </c>
       <c r="Z2" t="n">
-        <v>16.67</v>
+        <v>16.31</v>
       </c>
       <c r="AA2" t="n">
-        <v>11.25</v>
+        <v>10.92</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.42</v>
+        <v>5.38</v>
       </c>
       <c r="AC2" t="n">
-        <v>20.58</v>
+        <v>20.46</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="AF2" t="n">
         <v>0.08</v>
@@ -1550,70 +1550,70 @@
         <v>2.77</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.44</v>
+        <v>8.42</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.52</v>
+        <v>0.62</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.04</v>
+        <v>4.19</v>
       </c>
       <c r="BR2" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BS2" t="n">
-        <v>64</v>
+        <v>65.38</v>
       </c>
       <c r="BT2" t="n">
-        <v>40</v>
+        <v>42.31</v>
       </c>
       <c r="BU2" t="n">
-        <v>36</v>
+        <v>34.62</v>
       </c>
       <c r="BV2" t="n">
-        <v>16</v>
+        <v>15.38</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>36</v>
+        <v>34.62</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.57</v>
+        <v>4.62</v>
       </c>
       <c r="CB2" t="n">
-        <v>5.04</v>
+        <v>5.13</v>
       </c>
       <c r="CC2" t="n">
         <v>1.91</v>
@@ -1622,13 +1622,13 @@
         <v>2</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="CH2" t="n">
         <v>1.44</v>
@@ -1640,139 +1640,139 @@
         <v>2.09</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CM2" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="CR2" t="n">
         <v>1.38</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CT2" t="n">
         <v>3.01</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CV2" t="n">
         <v>1.74</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="DA2" t="n">
         <v>1.61</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="DH2" t="n">
-        <v>95.36</v>
+        <v>94.23</v>
       </c>
       <c r="DI2" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.52</v>
+        <v>5.42</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="DM2" t="n">
-        <v>57.64</v>
+        <v>56.42</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="DP2" t="n">
-        <v>15.8</v>
+        <v>15.81</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.96</v>
+        <v>14.04</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.08</v>
+        <v>6.24</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>58.68</v>
+        <v>58.62</v>
       </c>
       <c r="DW2" t="n">
         <v>0.12</v>
       </c>
       <c r="DX2" t="n">
-        <v>15.36</v>
+        <v>15.23</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.44</v>
+        <v>10.3</v>
       </c>
       <c r="DZ2" t="n">
         <v>4.92</v>
       </c>
       <c r="EA2" t="n">
-        <v>20.96</v>
+        <v>20.88</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
         <v>13</v>
@@ -1794,49 +1794,49 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="G3" t="n">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="H3" t="n">
-        <v>93.17</v>
+        <v>93.92</v>
       </c>
       <c r="I3" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="J3" t="n">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="K3" t="n">
-        <v>5.58</v>
+        <v>5.69</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="M3" t="n">
-        <v>47</v>
+        <v>49.62</v>
       </c>
       <c r="N3" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="O3" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="P3" t="n">
-        <v>14.33</v>
+        <v>14.23</v>
       </c>
       <c r="Q3" t="n">
-        <v>15.58</v>
+        <v>15.46</v>
       </c>
       <c r="R3" t="n">
-        <v>7.42</v>
+        <v>7.08</v>
       </c>
       <c r="S3" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="T3" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>51.33</v>
+        <v>51.38</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="Z3" t="n">
-        <v>14.42</v>
+        <v>16</v>
       </c>
       <c r="AA3" t="n">
-        <v>10.33</v>
+        <v>11.46</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.08</v>
+        <v>4.54</v>
       </c>
       <c r="AC3" t="n">
-        <v>21.08</v>
+        <v>21.15</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.54</v>
+        <v>1.69</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
       <c r="AF3" t="n">
         <v>0.08</v>
@@ -1953,49 +1953,49 @@
         <v>2</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.24</v>
+        <v>9.27</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="BN3" t="n">
         <v>1.04</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BP3" t="n">
-        <v>2.64</v>
+        <v>2.73</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.96</v>
+        <v>5.92</v>
       </c>
       <c r="BR3" t="n">
-        <v>80</v>
+        <v>80.77</v>
       </c>
       <c r="BS3" t="n">
-        <v>60</v>
+        <v>61.54</v>
       </c>
       <c r="BT3" t="n">
-        <v>28</v>
+        <v>26.92</v>
       </c>
       <c r="BU3" t="n">
-        <v>12</v>
+        <v>11.54</v>
       </c>
       <c r="BV3" t="n">
         <v>0</v>
@@ -2004,19 +2004,19 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>48</v>
+        <v>46.15</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="CC3" t="n">
         <v>3.57</v>
@@ -2031,7 +2031,7 @@
         <v>3.06</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CH3" t="n">
         <v>1.33</v>
@@ -2043,13 +2043,13 @@
         <v>2.03</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CN3" t="n">
         <v>1.53</v>
@@ -2061,7 +2061,7 @@
         <v>2.14</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.99</v>
+        <v>3.97</v>
       </c>
       <c r="CR3" t="n">
         <v>1.45</v>
@@ -2082,13 +2082,13 @@
         <v>2.12</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CZ3" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="DA3" t="n">
         <v>1.56</v>
@@ -2097,52 +2097,52 @@
         <v>1.4</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="DE3" t="n">
         <v>0.04</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.16</v>
+        <v>3.23</v>
       </c>
       <c r="DH3" t="n">
-        <v>91.23999999999999</v>
+        <v>91.69</v>
       </c>
       <c r="DI3" t="n">
         <v>0.16</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.64</v>
+        <v>2.69</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.04</v>
+        <v>5.12</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DM3" t="n">
-        <v>41.88</v>
+        <v>43.38</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="DP3" t="n">
-        <v>15.32</v>
+        <v>15.23</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.68</v>
+        <v>14.66</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.96</v>
+        <v>6.81</v>
       </c>
       <c r="DS3" t="n">
         <v>0.04</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>51.08</v>
+        <v>51.12</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX3" t="n">
-        <v>12.48</v>
+        <v>13.34</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.92</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.56</v>
+        <v>3.81</v>
       </c>
       <c r="EA3" t="n">
-        <v>20</v>
+        <v>20.08</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="4">
@@ -2185,61 +2185,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
         <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="F4" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="G4" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="H4" t="n">
-        <v>84.58</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="J4" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.33</v>
+        <v>5.08</v>
       </c>
       <c r="L4" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="M4" t="n">
-        <v>44.42</v>
+        <v>42.92</v>
       </c>
       <c r="N4" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="O4" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="P4" t="n">
-        <v>12.92</v>
+        <v>12.77</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.42</v>
+        <v>15.54</v>
       </c>
       <c r="R4" t="n">
-        <v>7.92</v>
+        <v>7.85</v>
       </c>
       <c r="S4" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="T4" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="U4" t="n">
         <v>0.08</v>
@@ -2251,28 +2251,28 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>47.5</v>
+        <v>46.62</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.67</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.33</v>
+        <v>6.31</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
       <c r="AC4" t="n">
-        <v>23.25</v>
+        <v>22.77</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.92</v>
+        <v>2.77</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,70 +2356,70 @@
         <v>3</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.720000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.04</v>
+        <v>5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.68</v>
+        <v>4.62</v>
       </c>
       <c r="BR4" t="n">
-        <v>92</v>
+        <v>92.31</v>
       </c>
       <c r="BS4" t="n">
-        <v>72</v>
+        <v>73.08</v>
       </c>
       <c r="BT4" t="n">
-        <v>44</v>
+        <v>46.15</v>
       </c>
       <c r="BU4" t="n">
-        <v>24</v>
+        <v>23.08</v>
       </c>
       <c r="BV4" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BW4" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BX4" t="n">
-        <v>44</v>
+        <v>46.15</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.46</v>
+        <v>3.56</v>
       </c>
       <c r="BZ4" t="n">
-        <v>4.14</v>
+        <v>4.31</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.93</v>
+        <v>3.92</v>
       </c>
       <c r="CC4" t="n">
         <v>6.46</v>
@@ -2431,13 +2431,13 @@
         <v>1.43</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CI4" t="n">
         <v>1.74</v>
@@ -2458,19 +2458,19 @@
         <v>1.54</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.61</v>
+        <v>3.63</v>
       </c>
       <c r="CR4" t="n">
         <v>1.43</v>
       </c>
       <c r="CS4" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="CT4" t="n">
         <v>2.85</v>
@@ -2482,7 +2482,7 @@
         <v>1.8</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CX4" t="n">
         <v>1.84</v>
@@ -2491,10 +2491,10 @@
         <v>2.35</v>
       </c>
       <c r="CZ4" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="DB4" t="n">
         <v>1.36</v>
@@ -2503,49 +2503,49 @@
         <v>2.15</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.87</v>
+        <v>3.88</v>
       </c>
       <c r="DE4" t="n">
         <v>0.08</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="DH4" t="n">
-        <v>80.16</v>
+        <v>79.95999999999999</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.64</v>
+        <v>4.54</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="DM4" t="n">
-        <v>37.52</v>
+        <v>37.04</v>
       </c>
       <c r="DN4" t="n">
         <v>1.16</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.96</v>
+        <v>13.84</v>
       </c>
       <c r="DQ4" t="n">
-        <v>15.52</v>
+        <v>15.58</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.08</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="DS4" t="n">
         <v>0.12</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>45.24</v>
+        <v>44.88</v>
       </c>
       <c r="DW4" t="n">
         <v>0.16</v>
       </c>
       <c r="DX4" t="n">
-        <v>9.48</v>
+        <v>9.42</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.28</v>
+        <v>6.27</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.84</v>
+        <v>20.69</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" t="n">
         <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2678,19 +2678,19 @@
         <v>2.46</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AI5" t="n">
-        <v>74.75</v>
+        <v>75.62</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AK5" t="n">
         <v>2.92</v>
@@ -2699,31 +2699,31 @@
         <v>4.08</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AN5" t="n">
-        <v>31.92</v>
+        <v>33.62</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AQ5" t="n">
-        <v>16.33</v>
+        <v>16.85</v>
       </c>
       <c r="AR5" t="n">
-        <v>14.83</v>
+        <v>14.85</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.83</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="AT5" t="n">
         <v>1</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -2735,82 +2735,82 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>47.17</v>
+        <v>47.38</v>
       </c>
       <c r="AZ5" t="n">
         <v>0.08</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.42</v>
+        <v>8.77</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.83</v>
+        <v>6.08</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
       <c r="BD5" t="n">
-        <v>20.08</v>
+        <v>19.69</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.08</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.64</v>
+        <v>3.69</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.44</v>
+        <v>4.35</v>
       </c>
       <c r="BR5" t="n">
-        <v>88</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="BS5" t="n">
-        <v>64</v>
+        <v>61.54</v>
       </c>
       <c r="BT5" t="n">
-        <v>44</v>
+        <v>42.31</v>
       </c>
       <c r="BU5" t="n">
-        <v>20</v>
+        <v>19.23</v>
       </c>
       <c r="BV5" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>44</v>
+        <v>42.31</v>
       </c>
       <c r="BY5" t="n">
         <v>3.59</v>
@@ -2819,25 +2819,25 @@
         <v>4.08</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.86</v>
+        <v>3.83</v>
       </c>
       <c r="CC5" t="n">
-        <v>5.33</v>
+        <v>5.19</v>
       </c>
       <c r="CD5" t="n">
-        <v>6.27</v>
+        <v>6.11</v>
       </c>
       <c r="CE5" t="n">
         <v>1.43</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CH5" t="n">
         <v>1.36</v>
@@ -2882,7 +2882,7 @@
         <v>1.4</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CW5" t="n">
         <v>2.08</v>
@@ -2903,52 +2903,52 @@
         <v>1.38</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="DE5" t="n">
         <v>0.08</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="DG5" t="n">
         <v>2.08</v>
       </c>
       <c r="DH5" t="n">
-        <v>83.23999999999999</v>
+        <v>83.34999999999999</v>
       </c>
       <c r="DI5" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="DM5" t="n">
-        <v>38.04</v>
+        <v>38.66</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DP5" t="n">
-        <v>15.56</v>
+        <v>15.85</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.36</v>
+        <v>15.35</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.4</v>
+        <v>7.31</v>
       </c>
       <c r="DS5" t="n">
         <v>0.12</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>50.52</v>
+        <v>50.5</v>
       </c>
       <c r="DW5" t="n">
         <v>0.04</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.24</v>
+        <v>10.34</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.32</v>
+        <v>7.38</v>
       </c>
       <c r="DZ5" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.8</v>
+        <v>21.54</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" t="n">
         <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
         <v>0.08</v>
@@ -3084,49 +3084,49 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AI6" t="n">
-        <v>80</v>
+        <v>81.77</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AK6" t="n">
-        <v>4.42</v>
+        <v>4.38</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.75</v>
+        <v>4.77</v>
       </c>
       <c r="AM6" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AN6" t="n">
-        <v>38.58</v>
+        <v>38.77</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AP6" t="n">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="AQ6" t="n">
-        <v>18.25</v>
+        <v>18.08</v>
       </c>
       <c r="AR6" t="n">
-        <v>13.58</v>
+        <v>13.69</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.5</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AV6" t="n">
         <v>0.08</v>
@@ -3138,82 +3138,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>47.58</v>
+        <v>47.23</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="BA6" t="n">
-        <v>13.17</v>
+        <v>13.23</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.33</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.83</v>
+        <v>4.77</v>
       </c>
       <c r="BD6" t="n">
-        <v>18</v>
+        <v>17.38</v>
       </c>
       <c r="BE6" t="n">
         <v>1.45</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.17</v>
+        <v>4.15</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.52</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.68</v>
+        <v>0.77</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="BP6" t="n">
-        <v>5.12</v>
+        <v>4.92</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.32</v>
+        <v>4.46</v>
       </c>
       <c r="BR6" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BS6" t="n">
-        <v>84</v>
+        <v>84.62</v>
       </c>
       <c r="BT6" t="n">
-        <v>56</v>
+        <v>57.69</v>
       </c>
       <c r="BU6" t="n">
-        <v>32</v>
+        <v>30.77</v>
       </c>
       <c r="BV6" t="n">
-        <v>16</v>
+        <v>15.38</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>68</v>
+        <v>65.38</v>
       </c>
       <c r="BY6" t="n">
         <v>4</v>
@@ -3222,136 +3222,136 @@
         <v>4.17</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.82</v>
+        <v>3.9</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.82</v>
+        <v>3.95</v>
       </c>
       <c r="CC6" t="n">
-        <v>5.32</v>
+        <v>6.03</v>
       </c>
       <c r="CD6" t="n">
-        <v>5.02</v>
+        <v>5.81</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CK6" t="n">
         <v>1.77</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="CM6" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="CR6" t="n">
         <v>1.45</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.03</v>
+        <v>2.99</v>
       </c>
       <c r="CT6" t="n">
         <v>2.78</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="CV6" t="n">
         <v>1.84</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="CZ6" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="DE6" t="n">
         <v>0.04</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="DH6" t="n">
-        <v>83.12</v>
+        <v>83.88</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="DJ6" t="n">
         <v>3.92</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.08</v>
+        <v>4.11</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="DM6" t="n">
-        <v>40.68</v>
+        <v>40.7</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="DP6" t="n">
-        <v>17.48</v>
+        <v>17.42</v>
       </c>
       <c r="DQ6" t="n">
         <v>14.96</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.92</v>
+        <v>7.88</v>
       </c>
       <c r="DS6" t="n">
         <v>0.04</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>46.4</v>
+        <v>46.27</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.52</v>
+        <v>13.54</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.76</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.76</v>
+        <v>4.73</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.16</v>
+        <v>17.84</v>
       </c>
       <c r="EB6" t="n">
         <v>1.48</v>
       </c>
       <c r="EC6" t="n">
-        <v>3.52</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" t="n">
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
         <v>0.08</v>
@@ -3487,136 +3487,136 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AI7" t="n">
-        <v>81.33</v>
+        <v>79.77</v>
       </c>
       <c r="AJ7" t="n">
         <v>0.08</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="AL7" t="n">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AN7" t="n">
-        <v>32.92</v>
+        <v>31.23</v>
       </c>
       <c r="AO7" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ7" t="n">
-        <v>16.33</v>
+        <v>15.77</v>
       </c>
       <c r="AR7" t="n">
-        <v>13.25</v>
+        <v>13.38</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.25</v>
+        <v>10.15</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>40</v>
+        <v>39.62</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="BA7" t="n">
-        <v>10.58</v>
+        <v>10</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.92</v>
+        <v>6.46</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.67</v>
+        <v>3.54</v>
       </c>
       <c r="BD7" t="n">
-        <v>16.83</v>
+        <v>16.69</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="BF7" t="n">
         <v>3</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.56</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.92</v>
+        <v>3.96</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.56</v>
+        <v>4.58</v>
       </c>
       <c r="BR7" t="n">
-        <v>96</v>
+        <v>92.31</v>
       </c>
       <c r="BS7" t="n">
-        <v>80</v>
+        <v>76.92</v>
       </c>
       <c r="BT7" t="n">
-        <v>36</v>
+        <v>34.62</v>
       </c>
       <c r="BU7" t="n">
-        <v>16</v>
+        <v>15.38</v>
       </c>
       <c r="BV7" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="BW7" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BX7" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="BY7" t="n">
         <v>4.73</v>
@@ -3625,169 +3625,169 @@
         <v>4.88</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.83</v>
+        <v>3.93</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.91</v>
+        <v>4.22</v>
       </c>
       <c r="CC7" t="n">
-        <v>6.46</v>
+        <v>7.3</v>
       </c>
       <c r="CD7" t="n">
-        <v>6.8</v>
+        <v>9.31</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CN7" t="n">
         <v>1.5</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.73</v>
+        <v>3.67</v>
       </c>
       <c r="CR7" t="n">
         <v>1.45</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.07</v>
+        <v>3.01</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="CZ7" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.01</v>
+        <v>3.93</v>
       </c>
       <c r="DE7" t="n">
         <v>0.04</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="DH7" t="n">
-        <v>83.64</v>
+        <v>82.77</v>
       </c>
       <c r="DI7" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="DM7" t="n">
-        <v>34.24</v>
+        <v>33.34</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="DP7" t="n">
-        <v>16.24</v>
+        <v>15.96</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.44</v>
+        <v>14.46</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.69</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>43.32</v>
+        <v>43</v>
       </c>
       <c r="DW7" t="n">
         <v>0.12</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.32</v>
+        <v>11</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.48</v>
+        <v>7.23</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.84</v>
+        <v>3.77</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.12</v>
+        <v>17.04</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="8">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
         <v>13</v>
       </c>
       <c r="E8" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="F8" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="G8" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>95.25</v>
+        <v>94.08</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="K8" t="n">
-        <v>4.42</v>
+        <v>4.31</v>
       </c>
       <c r="L8" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>41.67</v>
+        <v>42.15</v>
       </c>
       <c r="N8" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="O8" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="P8" t="n">
-        <v>12.08</v>
+        <v>12.31</v>
       </c>
       <c r="Q8" t="n">
-        <v>17</v>
+        <v>17.77</v>
       </c>
       <c r="R8" t="n">
-        <v>6.83</v>
+        <v>6.77</v>
       </c>
       <c r="S8" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="T8" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="U8" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="V8" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>58.67</v>
+        <v>58</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="Z8" t="n">
-        <v>13.17</v>
+        <v>12.92</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.92</v>
+        <v>7.85</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.25</v>
+        <v>5.08</v>
       </c>
       <c r="AC8" t="n">
-        <v>23.33</v>
+        <v>23.08</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="AF8" t="n">
         <v>0.23</v>
@@ -3968,70 +3968,70 @@
         <v>2.23</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.48</v>
+        <v>3.38</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.359999999999999</v>
+        <v>9.27</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.48</v>
+        <v>3.38</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="BL8" t="n">
         <v>1.08</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="BP8" t="n">
         <v>5.08</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.28</v>
+        <v>4.19</v>
       </c>
       <c r="BR8" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BS8" t="n">
-        <v>88</v>
+        <v>84.62</v>
       </c>
       <c r="BT8" t="n">
-        <v>68</v>
+        <v>65.38</v>
       </c>
       <c r="BU8" t="n">
-        <v>56</v>
+        <v>53.85</v>
       </c>
       <c r="BV8" t="n">
-        <v>28</v>
+        <v>26.92</v>
       </c>
       <c r="BW8" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="BX8" t="n">
-        <v>60</v>
+        <v>57.69</v>
       </c>
       <c r="BY8" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="BZ8" t="n">
         <v>2.74</v>
       </c>
-      <c r="BZ8" t="n">
-        <v>2.8</v>
-      </c>
       <c r="CA8" t="n">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.93</v>
+        <v>3.9</v>
       </c>
       <c r="CC8" t="n">
         <v>4.54</v>
@@ -4043,10 +4043,10 @@
         <v>1.39</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="CH8" t="n">
         <v>1.38</v>
@@ -4076,7 +4076,7 @@
         <v>2.01</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="CR8" t="n">
         <v>1.41</v>
@@ -4100,97 +4100,97 @@
         <v>1.86</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CZ8" t="n">
         <v>1.95</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="DB8" t="n">
         <v>1.34</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.63</v>
+        <v>3.65</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="DH8" t="n">
-        <v>92.64</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="DI8" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.88</v>
+        <v>4.81</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="DM8" t="n">
-        <v>41.68</v>
+        <v>41.92</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="DP8" t="n">
-        <v>12.48</v>
+        <v>12.58</v>
       </c>
       <c r="DQ8" t="n">
-        <v>16.56</v>
+        <v>16.96</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.64</v>
+        <v>6.62</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>56.56</v>
+        <v>56.31</v>
       </c>
       <c r="DW8" t="n">
         <v>0.08</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.16</v>
+        <v>11.12</v>
       </c>
       <c r="DY8" t="n">
-        <v>6.8</v>
+        <v>6.81</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.36</v>
+        <v>4.31</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.96</v>
+        <v>21.88</v>
       </c>
       <c r="EB8" t="n">
         <v>1.31</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
         <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
         <v>0.23</v>
@@ -4290,52 +4290,52 @@
         <v>1.85</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AH9" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AI9" t="n">
-        <v>66.5</v>
+        <v>66.69</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AN9" t="n">
-        <v>26.92</v>
+        <v>26.85</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12</v>
+        <v>12.15</v>
       </c>
       <c r="AR9" t="n">
-        <v>15.42</v>
+        <v>15.23</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.42</v>
+        <v>9.77</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AU9" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AV9" t="n">
         <v>0.08</v>
@@ -4347,82 +4347,82 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>42.58</v>
+        <v>43</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.75</v>
+        <v>7.77</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.67</v>
+        <v>4.62</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="BD9" t="n">
-        <v>14.83</v>
+        <v>15</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.48</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.56</v>
+        <v>4.58</v>
       </c>
       <c r="BQ9" t="n">
-        <v>3.88</v>
+        <v>3.92</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>84</v>
+        <v>84.62</v>
       </c>
       <c r="BT9" t="n">
-        <v>76</v>
+        <v>73.08</v>
       </c>
       <c r="BU9" t="n">
-        <v>32</v>
+        <v>30.77</v>
       </c>
       <c r="BV9" t="n">
-        <v>12</v>
+        <v>11.54</v>
       </c>
       <c r="BW9" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BX9" t="n">
-        <v>44</v>
+        <v>42.31</v>
       </c>
       <c r="BY9" t="n">
         <v>3.88</v>
@@ -4431,16 +4431,16 @@
         <v>4.08</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.35</v>
+        <v>4.32</v>
       </c>
       <c r="CC9" t="n">
-        <v>7.18</v>
+        <v>7.01</v>
       </c>
       <c r="CD9" t="n">
-        <v>8.67</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="CE9" t="n">
         <v>1.38</v>
@@ -4449,22 +4449,22 @@
         <v>2.79</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CH9" t="n">
         <v>1.42</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CK9" t="n">
         <v>1.73</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CM9" t="n">
         <v>2.02</v>
@@ -4476,22 +4476,22 @@
         <v>1.27</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="CR9" t="n">
         <v>1.4</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CV9" t="n">
         <v>1.91</v>
@@ -4500,13 +4500,13 @@
         <v>1.96</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CY9" t="n">
         <v>2.2</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DA9" t="n">
         <v>1.66</v>
@@ -4515,52 +4515,52 @@
         <v>1.3</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.37</v>
+        <v>3.39</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="DH9" t="n">
-        <v>71.16</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="DK9" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DM9" t="n">
-        <v>26.76</v>
+        <v>26.74</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.52</v>
+        <v>13.54</v>
       </c>
       <c r="DQ9" t="n">
-        <v>16.04</v>
+        <v>15.92</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.640000000000001</v>
+        <v>9.81</v>
       </c>
       <c r="DS9" t="n">
         <v>0.16</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>44</v>
+        <v>44.16</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.4</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.2</v>
+        <v>5.16</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.48</v>
+        <v>16.5</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="10">
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D10" t="n">
         <v>13</v>
@@ -4615,82 +4615,82 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="G10" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>134.33</v>
+        <v>136.31</v>
       </c>
       <c r="I10" t="n">
         <v>-0.08</v>
       </c>
       <c r="J10" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="K10" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
-        <v>9.17</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.92</v>
-      </c>
       <c r="M10" t="n">
-        <v>73.42</v>
+        <v>77.54000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="O10" t="n">
-        <v>5.17</v>
+        <v>5.15</v>
       </c>
       <c r="P10" t="n">
-        <v>10.75</v>
+        <v>11.15</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.67</v>
+        <v>12.46</v>
       </c>
       <c r="R10" t="n">
-        <v>4.08</v>
+        <v>3.85</v>
       </c>
       <c r="S10" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="U10" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="V10" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>64.58</v>
+        <v>64.62</v>
       </c>
       <c r="Y10" t="n">
         <v>0.08</v>
       </c>
       <c r="Z10" t="n">
-        <v>21.58</v>
+        <v>22.62</v>
       </c>
       <c r="AA10" t="n">
-        <v>15.5</v>
+        <v>16.46</v>
       </c>
       <c r="AB10" t="n">
-        <v>6.08</v>
+        <v>6.15</v>
       </c>
       <c r="AC10" t="n">
-        <v>27.17</v>
+        <v>27.92</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AF10" t="n">
         <v>0.15</v>
@@ -4774,70 +4774,70 @@
         <v>1.92</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.44</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.4</v>
+        <v>4.42</v>
       </c>
       <c r="BQ10" t="n">
         <v>5</v>
       </c>
       <c r="BR10" t="n">
-        <v>88</v>
+        <v>84.62</v>
       </c>
       <c r="BS10" t="n">
-        <v>76</v>
+        <v>73.08</v>
       </c>
       <c r="BT10" t="n">
-        <v>40</v>
+        <v>38.46</v>
       </c>
       <c r="BU10" t="n">
-        <v>12</v>
+        <v>11.54</v>
       </c>
       <c r="BV10" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>32</v>
+        <v>30.77</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CA10" t="n">
-        <v>5.37</v>
+        <v>5.41</v>
       </c>
       <c r="CB10" t="n">
-        <v>6.01</v>
+        <v>6.25</v>
       </c>
       <c r="CC10" t="n">
         <v>1.61</v>
@@ -4849,19 +4849,19 @@
         <v>1.33</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CJ10" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CK10" t="n">
         <v>1.82</v>
@@ -4873,130 +4873,130 @@
         <v>1.9</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CO10" t="n">
         <v>1.22</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="CR10" t="n">
         <v>1.38</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.17</v>
+        <v>3.12</v>
       </c>
       <c r="DE10" t="n">
         <v>0.08</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="DG10" t="n">
-        <v>3.52</v>
+        <v>3.58</v>
       </c>
       <c r="DH10" t="n">
-        <v>130.88</v>
+        <v>132</v>
       </c>
       <c r="DI10" t="n">
         <v>-0.08</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="DK10" t="n">
-        <v>7.28</v>
+        <v>7.38</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.72</v>
+        <v>0.77</v>
       </c>
       <c r="DM10" t="n">
-        <v>69.08</v>
+        <v>71.31</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="DO10" t="n">
-        <v>3.72</v>
+        <v>3.76</v>
       </c>
       <c r="DP10" t="n">
-        <v>12.8</v>
+        <v>12.92</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.32</v>
+        <v>12.23</v>
       </c>
       <c r="DR10" t="n">
-        <v>4.2</v>
+        <v>4.08</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>62.36</v>
+        <v>62.46</v>
       </c>
       <c r="DW10" t="n">
         <v>0.08</v>
       </c>
       <c r="DX10" t="n">
-        <v>18.4</v>
+        <v>19.04</v>
       </c>
       <c r="DY10" t="n">
-        <v>12.48</v>
+        <v>13.08</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.92</v>
+        <v>5.96</v>
       </c>
       <c r="EA10" t="n">
-        <v>26.92</v>
+        <v>27.31</v>
       </c>
       <c r="EB10" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
         <v>13</v>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E11" t="n">
         <v>0.31</v>
@@ -5096,139 +5096,139 @@
         <v>1.54</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AG11" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AI11" t="n">
-        <v>103.75</v>
+        <v>105.08</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.5</v>
+        <v>4.62</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AN11" t="n">
-        <v>52.75</v>
+        <v>55.38</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AP11" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.17</v>
+        <v>12.85</v>
       </c>
       <c r="AR11" t="n">
-        <v>13</v>
+        <v>12.85</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.58</v>
+        <v>5.77</v>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AU11" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>59</v>
+        <v>60.15</v>
       </c>
       <c r="AZ11" t="n">
         <v>0.08</v>
       </c>
       <c r="BA11" t="n">
-        <v>12.17</v>
+        <v>11.92</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.25</v>
+        <v>8</v>
       </c>
       <c r="BC11" t="n">
         <v>3.92</v>
       </c>
       <c r="BD11" t="n">
-        <v>23.75</v>
+        <v>24.38</v>
       </c>
       <c r="BE11" t="n">
         <v>1.43</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.68</v>
+        <v>8.69</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.72</v>
+        <v>4.69</v>
       </c>
       <c r="BR11" t="n">
-        <v>84</v>
+        <v>84.62</v>
       </c>
       <c r="BS11" t="n">
-        <v>76</v>
+        <v>76.92</v>
       </c>
       <c r="BT11" t="n">
-        <v>56</v>
+        <v>57.69</v>
       </c>
       <c r="BU11" t="n">
-        <v>24</v>
+        <v>23.08</v>
       </c>
       <c r="BV11" t="n">
-        <v>20</v>
+        <v>19.23</v>
       </c>
       <c r="BW11" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BX11" t="n">
-        <v>36</v>
+        <v>38.46</v>
       </c>
       <c r="BY11" t="n">
         <v>1.48</v>
@@ -5237,16 +5237,16 @@
         <v>1.52</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.74</v>
+        <v>4.78</v>
       </c>
       <c r="CB11" t="n">
         <v>5.17</v>
       </c>
       <c r="CC11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CD11" t="n">
         <v>1.96</v>
-      </c>
-      <c r="CD11" t="n">
-        <v>2.01</v>
       </c>
       <c r="CE11" t="n">
         <v>1.34</v>
@@ -5255,16 +5255,16 @@
         <v>2.63</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CH11" t="n">
         <v>1.46</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CJ11" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CK11" t="n">
         <v>1.76</v>
@@ -5273,7 +5273,7 @@
         <v>2.36</v>
       </c>
       <c r="CM11" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CN11" t="n">
         <v>1.59</v>
@@ -5288,7 +5288,7 @@
         <v>3.02</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CS11" t="n">
         <v>2.77</v>
@@ -5297,22 +5297,22 @@
         <v>3</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CX11" t="n">
         <v>1.77</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DA11" t="n">
         <v>1.64</v>
@@ -5321,85 +5321,85 @@
         <v>1.28</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DD11" t="n">
         <v>3.23</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="DG11" t="n">
         <v>3.16</v>
       </c>
       <c r="DH11" t="n">
-        <v>106.08</v>
+        <v>106.65</v>
       </c>
       <c r="DI11" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.76</v>
+        <v>5.77</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="DM11" t="n">
-        <v>57.24</v>
+        <v>58.38</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.2</v>
+        <v>12.08</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.92</v>
+        <v>12.85</v>
       </c>
       <c r="DR11" t="n">
-        <v>4.8</v>
+        <v>4.92</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>61</v>
+        <v>61.5</v>
       </c>
       <c r="DW11" t="n">
         <v>0.04</v>
       </c>
       <c r="DX11" t="n">
-        <v>14.08</v>
+        <v>13.88</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.16</v>
+        <v>9</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.92</v>
+        <v>4.88</v>
       </c>
       <c r="EA11" t="n">
-        <v>23.8</v>
+        <v>24.12</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="12">
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
         <v>13</v>
@@ -5421,79 +5421,79 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="H12" t="n">
-        <v>82.58</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="I12" t="n">
         <v>-0.08</v>
       </c>
       <c r="J12" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="K12" t="n">
-        <v>3.92</v>
+        <v>4.31</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="M12" t="n">
-        <v>34.92</v>
+        <v>37</v>
       </c>
       <c r="N12" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="O12" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="P12" t="n">
-        <v>11.75</v>
+        <v>11.54</v>
       </c>
       <c r="Q12" t="n">
-        <v>12.58</v>
+        <v>12.15</v>
       </c>
       <c r="R12" t="n">
-        <v>9.42</v>
+        <v>8.69</v>
       </c>
       <c r="S12" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="T12" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="U12" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="V12" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>45.08</v>
+        <v>47.77</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="Z12" t="n">
-        <v>8.75</v>
+        <v>9.77</v>
       </c>
       <c r="AA12" t="n">
-        <v>6.42</v>
+        <v>7.38</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AC12" t="n">
-        <v>17.83</v>
+        <v>18.31</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.98</v>
+        <v>1.06</v>
       </c>
       <c r="AE12" t="n">
         <v>2.08</v>
@@ -5580,70 +5580,70 @@
         <v>2.38</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.84</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.36</v>
+        <v>4.42</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.44</v>
+        <v>4.42</v>
       </c>
       <c r="BR12" t="n">
-        <v>92</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="BS12" t="n">
-        <v>64</v>
+        <v>61.54</v>
       </c>
       <c r="BT12" t="n">
-        <v>44</v>
+        <v>42.31</v>
       </c>
       <c r="BU12" t="n">
-        <v>24</v>
+        <v>23.08</v>
       </c>
       <c r="BV12" t="n">
-        <v>16</v>
+        <v>15.38</v>
       </c>
       <c r="BW12" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="BX12" t="n">
-        <v>36</v>
+        <v>34.62</v>
       </c>
       <c r="BY12" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="BZ12" t="n">
         <v>5.2</v>
       </c>
-      <c r="BZ12" t="n">
-        <v>5.47</v>
-      </c>
       <c r="CA12" t="n">
-        <v>3.96</v>
+        <v>3.93</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.2</v>
+        <v>4.16</v>
       </c>
       <c r="CC12" t="n">
         <v>7.19</v>
@@ -5652,13 +5652,13 @@
         <v>8.41</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="CH12" t="n">
         <v>1.35</v>
@@ -5667,16 +5667,16 @@
         <v>1.68</v>
       </c>
       <c r="CJ12" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CN12" t="n">
         <v>1.53</v>
@@ -5685,31 +5685,31 @@
         <v>1.34</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.74</v>
+        <v>3.76</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CS12" t="n">
         <v>2.98</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="CU12" t="n">
         <v>1.4</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CW12" t="n">
         <v>2.15</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CY12" t="n">
         <v>2.35</v>
@@ -5721,55 +5721,55 @@
         <v>1.58</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.88</v>
+        <v>3.91</v>
       </c>
       <c r="DE12" t="n">
         <v>0.04</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="DH12" t="n">
-        <v>77.56</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="DK12" t="n">
-        <v>3.48</v>
+        <v>3.7</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="DM12" t="n">
-        <v>32.48</v>
+        <v>33.62</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.24</v>
+        <v>13.08</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.88</v>
+        <v>12.65</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.44</v>
+        <v>9.08</v>
       </c>
       <c r="DS12" t="n">
         <v>0.16</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>42.24</v>
+        <v>43.7</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DX12" t="n">
-        <v>8.52</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="DY12" t="n">
-        <v>5.84</v>
+        <v>6.34</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="EA12" t="n">
-        <v>17.4</v>
+        <v>17.65</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.97</v>
+        <v>1.01</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C13" t="n">
         <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E13" t="n">
         <v>0.38</v>
@@ -5902,64 +5902,64 @@
         <v>2</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AI13" t="n">
-        <v>99</v>
+        <v>97.92</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AL13" t="n">
-        <v>4.33</v>
+        <v>4.38</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>49.92</v>
+        <v>49.69</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ13" t="n">
         <v>15</v>
       </c>
       <c r="AR13" t="n">
-        <v>14.58</v>
+        <v>14.31</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.17</v>
+        <v>6.15</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.33</v>
+        <v>0.46</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.33</v>
+        <v>0.46</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>53.92</v>
+        <v>54.69</v>
       </c>
       <c r="AZ13" t="n">
         <v>0.08</v>
@@ -5968,73 +5968,73 @@
         <v>11.92</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.42</v>
+        <v>7.38</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.5</v>
+        <v>4.54</v>
       </c>
       <c r="BD13" t="n">
-        <v>22.25</v>
+        <v>21.77</v>
       </c>
       <c r="BE13" t="n">
         <v>1.43</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="BH13" t="n">
-        <v>7.52</v>
+        <v>7.5</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.48</v>
+        <v>0.54</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BP13" t="n">
         <v>3.88</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="BR13" t="n">
-        <v>92</v>
+        <v>92.31</v>
       </c>
       <c r="BS13" t="n">
-        <v>80</v>
+        <v>80.77</v>
       </c>
       <c r="BT13" t="n">
-        <v>52</v>
+        <v>53.85</v>
       </c>
       <c r="BU13" t="n">
-        <v>28</v>
+        <v>26.92</v>
       </c>
       <c r="BV13" t="n">
-        <v>16</v>
+        <v>15.38</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>52</v>
+        <v>53.85</v>
       </c>
       <c r="BY13" t="n">
         <v>1.65</v>
@@ -6043,40 +6043,40 @@
         <v>1.81</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.12</v>
+        <v>4.08</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.43</v>
+        <v>2.37</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="CE13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="CH13" t="n">
         <v>1.39</v>
       </c>
-      <c r="CF13" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="CG13" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="CH13" t="n">
-        <v>1.4</v>
-      </c>
       <c r="CI13" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CJ13" t="n">
         <v>2.01</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CM13" t="n">
         <v>1.93</v>
@@ -6085,22 +6085,22 @@
         <v>1.61</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.39</v>
+        <v>3.42</v>
       </c>
       <c r="CR13" t="n">
         <v>1.41</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CU13" t="n">
         <v>1.41</v>
@@ -6121,91 +6121,91 @@
         <v>2.01</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="DB13" t="n">
         <v>1.35</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.72</v>
+        <v>3.73</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="DH13" t="n">
-        <v>98.92</v>
+        <v>98.38</v>
       </c>
       <c r="DI13" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.6</v>
+        <v>4.62</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DM13" t="n">
-        <v>56.44</v>
+        <v>56.08</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="DP13" t="n">
         <v>15.12</v>
       </c>
       <c r="DQ13" t="n">
-        <v>14.88</v>
+        <v>14.73</v>
       </c>
       <c r="DR13" t="n">
-        <v>5.64</v>
+        <v>5.65</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.28</v>
+        <v>0.34</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.28</v>
+        <v>0.34</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>53.52</v>
+        <v>53.92</v>
       </c>
       <c r="DW13" t="n">
         <v>0.08</v>
       </c>
       <c r="DX13" t="n">
-        <v>13.04</v>
+        <v>13</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.08</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="DZ13" t="n">
         <v>4.96</v>
       </c>
       <c r="EA13" t="n">
-        <v>21.64</v>
+        <v>21.42</v>
       </c>
       <c r="EB13" t="n">
         <v>1.58</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C14" t="n">
         <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6308,49 +6308,49 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AI14" t="n">
-        <v>57.08</v>
+        <v>56.62</v>
       </c>
       <c r="AJ14" t="n">
         <v>0.08</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.58</v>
+        <v>3.46</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AN14" t="n">
-        <v>26.42</v>
+        <v>26.46</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AP14" t="n">
         <v>0.92</v>
       </c>
       <c r="AQ14" t="n">
-        <v>13.58</v>
+        <v>13.15</v>
       </c>
       <c r="AR14" t="n">
-        <v>11.75</v>
+        <v>11.62</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.83</v>
+        <v>10</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AV14" t="n">
         <v>0.08</v>
@@ -6362,82 +6362,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>34.75</v>
+        <v>33.62</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="BA14" t="n">
-        <v>6.08</v>
+        <v>6.31</v>
       </c>
       <c r="BB14" t="n">
-        <v>3.83</v>
+        <v>4.15</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="BD14" t="n">
-        <v>16.08</v>
+        <v>15.85</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.84</v>
+        <v>2.73</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.6</v>
+        <v>8.65</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.84</v>
+        <v>2.73</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.08</v>
+        <v>4.15</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.48</v>
+        <v>4.46</v>
       </c>
       <c r="BR14" t="n">
-        <v>96</v>
+        <v>92.31</v>
       </c>
       <c r="BS14" t="n">
-        <v>80</v>
+        <v>76.92</v>
       </c>
       <c r="BT14" t="n">
-        <v>60</v>
+        <v>57.69</v>
       </c>
       <c r="BU14" t="n">
-        <v>24</v>
+        <v>23.08</v>
       </c>
       <c r="BV14" t="n">
-        <v>16</v>
+        <v>15.38</v>
       </c>
       <c r="BW14" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BX14" t="n">
-        <v>40</v>
+        <v>38.46</v>
       </c>
       <c r="BY14" t="n">
         <v>6.24</v>
@@ -6446,28 +6446,28 @@
         <v>7.22</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.6</v>
+        <v>4.54</v>
       </c>
       <c r="CB14" t="n">
-        <v>5.25</v>
+        <v>5.17</v>
       </c>
       <c r="CC14" t="n">
-        <v>10.09</v>
+        <v>9.67</v>
       </c>
       <c r="CD14" t="n">
-        <v>12.75</v>
+        <v>12.15</v>
       </c>
       <c r="CE14" t="n">
         <v>1.37</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="CG14" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CI14" t="n">
         <v>1.71</v>
@@ -6491,10 +6491,10 @@
         <v>1.27</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.25</v>
+        <v>3.29</v>
       </c>
       <c r="CR14" t="n">
         <v>1.43</v>
@@ -6503,7 +6503,7 @@
         <v>2.81</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="CU14" t="n">
         <v>1.46</v>
@@ -6530,52 +6530,52 @@
         <v>1.32</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.47</v>
+        <v>3.52</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="DG14" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="DH14" t="n">
-        <v>65.8</v>
+        <v>65.23999999999999</v>
       </c>
       <c r="DI14" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="DK14" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DM14" t="n">
-        <v>30.24</v>
+        <v>30.12</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="DO14" t="n">
         <v>1</v>
       </c>
       <c r="DP14" t="n">
-        <v>14.04</v>
+        <v>13.81</v>
       </c>
       <c r="DQ14" t="n">
-        <v>12.92</v>
+        <v>12.81</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.960000000000001</v>
+        <v>9.07</v>
       </c>
       <c r="DS14" t="n">
         <v>0.04</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>37</v>
+        <v>36.35</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DX14" t="n">
-        <v>8.039999999999999</v>
+        <v>8.08</v>
       </c>
       <c r="DY14" t="n">
-        <v>5.68</v>
+        <v>5.76</v>
       </c>
       <c r="DZ14" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.68</v>
+        <v>17.5</v>
       </c>
       <c r="EB14" t="n">
         <v>0.86</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="15">
@@ -6618,10 +6618,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D15" t="n">
         <v>13</v>
@@ -6630,82 +6630,82 @@
         <v>0.08</v>
       </c>
       <c r="F15" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="G15" t="n">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="H15" t="n">
-        <v>72.33</v>
+        <v>71.23</v>
       </c>
       <c r="I15" t="n">
         <v>0.08</v>
       </c>
       <c r="J15" t="n">
-        <v>3.17</v>
+        <v>3.23</v>
       </c>
       <c r="K15" t="n">
-        <v>5</v>
+        <v>4.85</v>
       </c>
       <c r="L15" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="M15" t="n">
-        <v>33.08</v>
+        <v>32.15</v>
       </c>
       <c r="N15" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="O15" t="n">
         <v>2.08</v>
       </c>
       <c r="P15" t="n">
-        <v>14.5</v>
+        <v>14.23</v>
       </c>
       <c r="Q15" t="n">
-        <v>16.17</v>
+        <v>15.62</v>
       </c>
       <c r="R15" t="n">
-        <v>7.58</v>
+        <v>7.85</v>
       </c>
       <c r="S15" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="U15" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="V15" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>48.08</v>
+        <v>46.38</v>
       </c>
       <c r="Y15" t="n">
         <v>0.08</v>
       </c>
       <c r="Z15" t="n">
-        <v>12.92</v>
+        <v>12.62</v>
       </c>
       <c r="AA15" t="n">
-        <v>9</v>
+        <v>8.77</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.92</v>
+        <v>3.85</v>
       </c>
       <c r="AC15" t="n">
-        <v>20.25</v>
+        <v>20.54</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AE15" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="AF15" t="n">
         <v>0.08</v>
@@ -6789,70 +6789,70 @@
         <v>3.15</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.279999999999999</v>
+        <v>9.27</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.72</v>
+        <v>0.77</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BP15" t="n">
-        <v>4</v>
+        <v>4.04</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.24</v>
+        <v>5.19</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>76</v>
+        <v>76.92</v>
       </c>
       <c r="BT15" t="n">
-        <v>44</v>
+        <v>46.15</v>
       </c>
       <c r="BU15" t="n">
-        <v>12</v>
+        <v>11.54</v>
       </c>
       <c r="BV15" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BW15" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BX15" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BY15" t="n">
-        <v>4.07</v>
+        <v>4.76</v>
       </c>
       <c r="BZ15" t="n">
-        <v>4.35</v>
+        <v>4.98</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.76</v>
+        <v>3.84</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.91</v>
+        <v>3.96</v>
       </c>
       <c r="CC15" t="n">
         <v>6.01</v>
@@ -6864,28 +6864,28 @@
         <v>1.4</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CJ15" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CK15" t="n">
         <v>1.86</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CM15" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CN15" t="n">
         <v>1.52</v>
@@ -6894,28 +6894,28 @@
         <v>1.32</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="CR15" t="n">
         <v>1.44</v>
       </c>
       <c r="CS15" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CU15" t="n">
         <v>1.38</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CW15" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="CX15" t="n">
         <v>1.9</v>
@@ -6927,7 +6927,7 @@
         <v>1.91</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="DB15" t="n">
         <v>1.36</v>
@@ -6936,49 +6936,49 @@
         <v>2.12</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="DE15" t="n">
         <v>0.08</v>
       </c>
       <c r="DF15" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="DH15" t="n">
-        <v>77.72</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="DI15" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="DK15" t="n">
-        <v>4</v>
+        <v>3.97</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM15" t="n">
-        <v>38.04</v>
+        <v>37.38</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="DO15" t="n">
         <v>1.88</v>
       </c>
       <c r="DP15" t="n">
-        <v>15.48</v>
+        <v>15.3</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.52</v>
+        <v>15.27</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.76</v>
+        <v>7.88</v>
       </c>
       <c r="DS15" t="n">
         <v>0.16</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>48.08</v>
+        <v>47.23</v>
       </c>
       <c r="DW15" t="n">
         <v>0.04</v>
       </c>
       <c r="DX15" t="n">
-        <v>11.4</v>
+        <v>11.31</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.76</v>
+        <v>7.69</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.64</v>
+        <v>3.62</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.96</v>
+        <v>21.08</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="EC15" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -5454,7 +5454,7 @@
         <v>11.54</v>
       </c>
       <c r="Q12" t="n">
-        <v>12.15</v>
+        <v>12.23</v>
       </c>
       <c r="R12" t="n">
         <v>8.69</v>
@@ -5490,7 +5490,7 @@
         <v>2.38</v>
       </c>
       <c r="AC12" t="n">
-        <v>18.31</v>
+        <v>18.46</v>
       </c>
       <c r="AD12" t="n">
         <v>1.06</v>
@@ -5766,7 +5766,7 @@
         <v>13.08</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.65</v>
+        <v>12.69</v>
       </c>
       <c r="DR12" t="n">
         <v>9.08</v>
@@ -5796,7 +5796,7 @@
         <v>2.69</v>
       </c>
       <c r="EA12" t="n">
-        <v>17.65</v>
+        <v>17.73</v>
       </c>
       <c r="EB12" t="n">
         <v>1.01</v>
@@ -6344,7 +6344,7 @@
         <v>11.62</v>
       </c>
       <c r="AS14" t="n">
-        <v>10</v>
+        <v>10.08</v>
       </c>
       <c r="AT14" t="n">
         <v>2.38</v>
@@ -6377,7 +6377,7 @@
         <v>2.15</v>
       </c>
       <c r="BD14" t="n">
-        <v>15.85</v>
+        <v>16</v>
       </c>
       <c r="BE14" t="n">
         <v>0.68</v>
@@ -6575,7 +6575,7 @@
         <v>12.81</v>
       </c>
       <c r="DR14" t="n">
-        <v>9.07</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="DS14" t="n">
         <v>0.04</v>
@@ -6602,7 +6602,7 @@
         <v>2.31</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.5</v>
+        <v>17.58</v>
       </c>
       <c r="EB14" t="n">
         <v>0.86</v>
@@ -6699,7 +6699,7 @@
         <v>3.85</v>
       </c>
       <c r="AC15" t="n">
-        <v>20.54</v>
+        <v>20.62</v>
       </c>
       <c r="AD15" t="n">
         <v>1.17</v>
@@ -7005,7 +7005,7 @@
         <v>3.62</v>
       </c>
       <c r="EA15" t="n">
-        <v>21.08</v>
+        <v>21.12</v>
       </c>
       <c r="EB15" t="n">
         <v>1.17</v>

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -2735,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>47.38</v>
+        <v>47.31</v>
       </c>
       <c r="AZ5" t="n">
         <v>0.08</v>
@@ -2960,7 +2960,7 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>50.5</v>
+        <v>50.46</v>
       </c>
       <c r="DW5" t="n">
         <v>0.04</v>
@@ -3863,7 +3863,7 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>58</v>
+        <v>58.08</v>
       </c>
       <c r="Y8" t="n">
         <v>0.15</v>
@@ -4169,7 +4169,7 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>56.31</v>
+        <v>56.35</v>
       </c>
       <c r="DW8" t="n">
         <v>0.08</v>

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -1475,7 +1475,7 @@
         <v>1.85</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.31</v>
+        <v>2.62</v>
       </c>
       <c r="AI2" t="n">
         <v>92.84999999999999</v>
@@ -1490,7 +1490,7 @@
         <v>5.69</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.54</v>
+        <v>0.62</v>
       </c>
       <c r="AN2" t="n">
         <v>55.23</v>
@@ -1499,7 +1499,7 @@
         <v>1.08</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.77</v>
+        <v>3.08</v>
       </c>
       <c r="AQ2" t="n">
         <v>15.85</v>
@@ -1577,10 +1577,10 @@
         <v>1</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.65</v>
+        <v>3.92</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.19</v>
+        <v>4.5</v>
       </c>
       <c r="BR2" t="n">
         <v>96.15000000000001</v>
@@ -1706,7 +1706,7 @@
         <v>1.81</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="DH2" t="n">
         <v>94.23</v>
@@ -1721,7 +1721,7 @@
         <v>5.42</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.62</v>
+        <v>0.66</v>
       </c>
       <c r="DM2" t="n">
         <v>56.42</v>
@@ -1730,7 +1730,7 @@
         <v>0.92</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="DP2" t="n">
         <v>15.81</v>
@@ -1797,7 +1797,7 @@
         <v>2.08</v>
       </c>
       <c r="G3" t="n">
-        <v>3.38</v>
+        <v>3.77</v>
       </c>
       <c r="H3" t="n">
         <v>93.92</v>
@@ -1812,7 +1812,7 @@
         <v>5.69</v>
       </c>
       <c r="L3" t="n">
-        <v>0.46</v>
+        <v>0.62</v>
       </c>
       <c r="M3" t="n">
         <v>49.62</v>
@@ -1821,7 +1821,7 @@
         <v>0.85</v>
       </c>
       <c r="O3" t="n">
-        <v>1.54</v>
+        <v>1.85</v>
       </c>
       <c r="P3" t="n">
         <v>14.23</v>
@@ -1980,10 +1980,10 @@
         <v>0.77</v>
       </c>
       <c r="BP3" t="n">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.92</v>
+        <v>6.23</v>
       </c>
       <c r="BR3" t="n">
         <v>80.77</v>
@@ -2109,7 +2109,7 @@
         <v>1.77</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.23</v>
+        <v>3.42</v>
       </c>
       <c r="DH3" t="n">
         <v>91.69</v>
@@ -2124,7 +2124,7 @@
         <v>5.12</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.34</v>
+        <v>0.43</v>
       </c>
       <c r="DM3" t="n">
         <v>43.38</v>
@@ -2133,7 +2133,7 @@
         <v>0.77</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="DP3" t="n">
         <v>15.23</v>
@@ -2197,7 +2197,7 @@
         <v>0.15</v>
       </c>
       <c r="F4" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="G4" t="n">
         <v>2.54</v>
@@ -2209,7 +2209,7 @@
         <v>0.15</v>
       </c>
       <c r="J4" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
         <v>5.08</v>
@@ -2272,7 +2272,7 @@
         <v>1.14</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2509,7 +2509,7 @@
         <v>0.08</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="DG4" t="n">
         <v>2.34</v>
@@ -2521,7 +2521,7 @@
         <v>0.12</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="DK4" t="n">
         <v>4.54</v>
@@ -2578,7 +2578,7 @@
         <v>1.08</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="5">
@@ -2612,7 +2612,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="K5" t="n">
         <v>3.62</v>
@@ -2624,7 +2624,7 @@
         <v>43.69</v>
       </c>
       <c r="N5" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
         <v>1.31</v>
@@ -2675,7 +2675,7 @@
         <v>1.3</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="AF5" t="n">
         <v>0.15</v>
@@ -2924,7 +2924,7 @@
         <v>0.08</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="DK5" t="n">
         <v>3.85</v>
@@ -2936,7 +2936,7 @@
         <v>38.66</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="DO5" t="n">
         <v>1.77</v>
@@ -2981,7 +2981,7 @@
         <v>1.14</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="6">
@@ -6723,7 +6723,7 @@
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="AL15" t="n">
         <v>3.08</v>
@@ -6735,7 +6735,7 @@
         <v>42.62</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AP15" t="n">
         <v>1.69</v>
@@ -6786,7 +6786,7 @@
         <v>1.18</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="BG15" t="n">
         <v>2.46</v>
@@ -6954,7 +6954,7 @@
         <v>0.04</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.19</v>
+        <v>3.16</v>
       </c>
       <c r="DK15" t="n">
         <v>3.97</v>
@@ -6966,7 +6966,7 @@
         <v>37.38</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="DO15" t="n">
         <v>1.88</v>
@@ -7011,7 +7011,7 @@
         <v>1.17</v>
       </c>
       <c r="EC15" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -5824,7 +5824,7 @@
         <v>0.38</v>
       </c>
       <c r="F13" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="G13" t="n">
         <v>2.31</v>
@@ -5836,7 +5836,7 @@
         <v>0.08</v>
       </c>
       <c r="J13" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="K13" t="n">
         <v>4.85</v>
@@ -5854,7 +5854,7 @@
         <v>2.54</v>
       </c>
       <c r="P13" t="n">
-        <v>15.23</v>
+        <v>15.15</v>
       </c>
       <c r="Q13" t="n">
         <v>15.15</v>
@@ -5899,7 +5899,7 @@
         <v>1.72</v>
       </c>
       <c r="AE13" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AF13" t="n">
         <v>0.23</v>
@@ -6136,7 +6136,7 @@
         <v>0.31</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="DG13" t="n">
         <v>2.34</v>
@@ -6148,7 +6148,7 @@
         <v>0.04</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="DK13" t="n">
         <v>4.62</v>
@@ -6166,7 +6166,7 @@
         <v>2.2</v>
       </c>
       <c r="DP13" t="n">
-        <v>15.12</v>
+        <v>15.08</v>
       </c>
       <c r="DQ13" t="n">
         <v>14.73</v>
@@ -6205,7 +6205,7 @@
         <v>1.58</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="14">
@@ -6723,7 +6723,7 @@
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="AL15" t="n">
         <v>3.08</v>
@@ -6735,13 +6735,13 @@
         <v>42.62</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AP15" t="n">
         <v>1.69</v>
       </c>
       <c r="AQ15" t="n">
-        <v>16.38</v>
+        <v>16.31</v>
       </c>
       <c r="AR15" t="n">
         <v>14.92</v>
@@ -6786,7 +6786,7 @@
         <v>1.18</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="BG15" t="n">
         <v>2.46</v>
@@ -6954,7 +6954,7 @@
         <v>0.04</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="DK15" t="n">
         <v>3.97</v>
@@ -6966,13 +6966,13 @@
         <v>37.38</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="DO15" t="n">
         <v>1.88</v>
       </c>
       <c r="DP15" t="n">
-        <v>15.3</v>
+        <v>15.27</v>
       </c>
       <c r="DQ15" t="n">
         <v>15.27</v>
@@ -7011,7 +7011,7 @@
         <v>1.17</v>
       </c>
       <c r="EC15" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
         <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F4" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="G4" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="H4" t="n">
-        <v>83.84999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="I4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="K4" t="n">
-        <v>5.08</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="M4" t="n">
-        <v>42.92</v>
+        <v>41.86</v>
       </c>
       <c r="N4" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="O4" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="P4" t="n">
-        <v>12.77</v>
+        <v>12.93</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.54</v>
+        <v>14.64</v>
       </c>
       <c r="R4" t="n">
-        <v>7.85</v>
+        <v>7.93</v>
       </c>
       <c r="S4" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="T4" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="U4" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>46.62</v>
+        <v>46</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.539999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.31</v>
+        <v>6.36</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.23</v>
+        <v>3.29</v>
       </c>
       <c r="AC4" t="n">
-        <v>22.77</v>
+        <v>22.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.69</v>
+        <v>2.57</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -2356,70 +2356,70 @@
         <v>3</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.619999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.85</v>
+        <v>0.89</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BP4" t="n">
         <v>5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.62</v>
+        <v>4.7</v>
       </c>
       <c r="BR4" t="n">
-        <v>92.31</v>
+        <v>92.59</v>
       </c>
       <c r="BS4" t="n">
-        <v>73.08</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>46.15</v>
+        <v>48.15</v>
       </c>
       <c r="BU4" t="n">
-        <v>23.08</v>
+        <v>25.93</v>
       </c>
       <c r="BV4" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BW4" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BX4" t="n">
-        <v>46.15</v>
+        <v>48.15</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.56</v>
+        <v>3.48</v>
       </c>
       <c r="BZ4" t="n">
-        <v>4.31</v>
+        <v>4.17</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="CC4" t="n">
         <v>6.46</v>
@@ -2428,13 +2428,13 @@
         <v>6.62</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF4" t="n">
         <v>2.97</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="CH4" t="n">
         <v>1.35</v>
@@ -2449,10 +2449,10 @@
         <v>1.83</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CM4" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CN4" t="n">
         <v>1.54</v>
@@ -2464,7 +2464,7 @@
         <v>2.09</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.63</v>
+        <v>3.68</v>
       </c>
       <c r="CR4" t="n">
         <v>1.43</v>
@@ -2473,7 +2473,7 @@
         <v>3.02</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="CU4" t="n">
         <v>1.39</v>
@@ -2485,10 +2485,10 @@
         <v>2.1</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CZ4" t="n">
         <v>1.97</v>
@@ -2500,85 +2500,85 @@
         <v>1.36</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="DH4" t="n">
-        <v>79.95999999999999</v>
+        <v>80.45</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.54</v>
+        <v>4.52</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="DM4" t="n">
-        <v>37.04</v>
+        <v>36.7</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.84</v>
+        <v>13.89</v>
       </c>
       <c r="DQ4" t="n">
-        <v>15.58</v>
+        <v>15.11</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.039999999999999</v>
+        <v>8.07</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>44.88</v>
+        <v>44.63</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX4" t="n">
-        <v>9.42</v>
+        <v>9.48</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.27</v>
+        <v>6.3</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.69</v>
+        <v>20.63</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="n">
         <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2678,46 +2678,46 @@
         <v>2.54</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.85</v>
+        <v>2.21</v>
       </c>
       <c r="AI5" t="n">
-        <v>75.62</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.08</v>
+        <v>4.5</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AN5" t="n">
-        <v>33.62</v>
+        <v>35.29</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AQ5" t="n">
-        <v>16.85</v>
+        <v>17</v>
       </c>
       <c r="AR5" t="n">
-        <v>14.85</v>
+        <v>14.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.460000000000001</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="AT5" t="n">
         <v>1</v>
@@ -2735,49 +2735,49 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>47.31</v>
+        <v>48.71</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.77</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.08</v>
+        <v>6.07</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.69</v>
+        <v>2.79</v>
       </c>
       <c r="BD5" t="n">
-        <v>19.69</v>
+        <v>19.43</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.99</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.85</v>
+        <v>2.79</v>
       </c>
       <c r="BG5" t="n">
         <v>2.15</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.039999999999999</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="BI5" t="n">
         <v>2.15</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="BN5" t="n">
         <v>1.15</v>
@@ -2786,31 +2786,31 @@
         <v>1</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.69</v>
+        <v>3.78</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.35</v>
+        <v>4.44</v>
       </c>
       <c r="BR5" t="n">
-        <v>88.45999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS5" t="n">
-        <v>61.54</v>
+        <v>62.96</v>
       </c>
       <c r="BT5" t="n">
-        <v>42.31</v>
+        <v>40.74</v>
       </c>
       <c r="BU5" t="n">
-        <v>19.23</v>
+        <v>18.52</v>
       </c>
       <c r="BV5" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>42.31</v>
+        <v>44.44</v>
       </c>
       <c r="BY5" t="n">
         <v>3.59</v>
@@ -2819,28 +2819,28 @@
         <v>4.08</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.83</v>
+        <v>3.8</v>
       </c>
       <c r="CC5" t="n">
-        <v>5.19</v>
+        <v>5.02</v>
       </c>
       <c r="CD5" t="n">
-        <v>6.11</v>
+        <v>5.88</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CG5" t="n">
         <v>2.67</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CI5" t="n">
         <v>1.73</v>
@@ -2852,7 +2852,7 @@
         <v>1.9</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CM5" t="n">
         <v>1.84</v>
@@ -2861,13 +2861,13 @@
         <v>1.49</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.77</v>
+        <v>3.8</v>
       </c>
       <c r="CR5" t="n">
         <v>1.43</v>
@@ -2903,85 +2903,85 @@
         <v>1.38</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.99</v>
+        <v>4.02</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="DH5" t="n">
-        <v>83.34999999999999</v>
+        <v>83.73999999999999</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.85</v>
+        <v>4.08</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="DM5" t="n">
-        <v>38.66</v>
+        <v>39.33</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="DP5" t="n">
-        <v>15.85</v>
+        <v>15.96</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.35</v>
+        <v>15.15</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.31</v>
+        <v>7.26</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>50.46</v>
+        <v>51.07</v>
       </c>
       <c r="DW5" t="n">
         <v>0.04</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.34</v>
+        <v>10.33</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.38</v>
+        <v>7.33</v>
       </c>
       <c r="DZ5" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.54</v>
+        <v>21.33</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="6">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
         <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="G6" t="n">
-        <v>1.92</v>
+        <v>2.14</v>
       </c>
       <c r="H6" t="n">
-        <v>86</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3.46</v>
+        <v>3.57</v>
       </c>
       <c r="K6" t="n">
-        <v>3.46</v>
+        <v>3.86</v>
       </c>
       <c r="L6" t="n">
-        <v>0.23</v>
+        <v>0.36</v>
       </c>
       <c r="M6" t="n">
-        <v>42.62</v>
+        <v>43.36</v>
       </c>
       <c r="N6" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="O6" t="n">
-        <v>1.54</v>
+        <v>1.71</v>
       </c>
       <c r="P6" t="n">
-        <v>16.77</v>
+        <v>17.21</v>
       </c>
       <c r="Q6" t="n">
-        <v>16.23</v>
+        <v>16</v>
       </c>
       <c r="R6" t="n">
-        <v>7.38</v>
+        <v>7.21</v>
       </c>
       <c r="S6" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="T6" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>45.31</v>
+        <v>46.79</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="Z6" t="n">
-        <v>13.85</v>
+        <v>14</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.15</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.69</v>
+        <v>4.79</v>
       </c>
       <c r="AC6" t="n">
-        <v>18.31</v>
+        <v>19.43</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.92</v>
+        <v>3.07</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3165,61 +3165,61 @@
         <v>2.85</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.460000000000001</v>
+        <v>9.48</v>
       </c>
       <c r="BI6" t="n">
         <v>2.85</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BL6" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.92</v>
+        <v>4.93</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.46</v>
+        <v>4.48</v>
       </c>
       <c r="BR6" t="n">
-        <v>96.15000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="BS6" t="n">
-        <v>84.62</v>
+        <v>85.19</v>
       </c>
       <c r="BT6" t="n">
-        <v>57.69</v>
+        <v>59.26</v>
       </c>
       <c r="BU6" t="n">
-        <v>30.77</v>
+        <v>29.63</v>
       </c>
       <c r="BV6" t="n">
-        <v>15.38</v>
+        <v>14.81</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>65.38</v>
+        <v>66.67</v>
       </c>
       <c r="BY6" t="n">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="BZ6" t="n">
-        <v>4.17</v>
+        <v>3.99</v>
       </c>
       <c r="CA6" t="n">
         <v>3.9</v>
@@ -3249,13 +3249,13 @@
         <v>1.78</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CK6" t="n">
         <v>1.77</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="CM6" t="n">
         <v>1.84</v>
@@ -3270,7 +3270,7 @@
         <v>2.01</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="CR6" t="n">
         <v>1.45</v>
@@ -3291,13 +3291,13 @@
         <v>2.02</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CZ6" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="DA6" t="n">
         <v>1.58</v>
@@ -3315,76 +3315,76 @@
         <v>0.04</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.96</v>
+        <v>2.07</v>
       </c>
       <c r="DH6" t="n">
-        <v>83.88</v>
+        <v>85.11</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ6" t="n">
-        <v>3.92</v>
+        <v>3.96</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.11</v>
+        <v>4.3</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
       <c r="DM6" t="n">
-        <v>40.7</v>
+        <v>41.15</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="DP6" t="n">
-        <v>17.42</v>
+        <v>17.63</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14.96</v>
+        <v>14.89</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.88</v>
+        <v>7.77</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>46.27</v>
+        <v>47</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.54</v>
+        <v>13.63</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.85</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.73</v>
+        <v>4.78</v>
       </c>
       <c r="EA6" t="n">
-        <v>17.84</v>
+        <v>18.44</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="EC6" t="n">
-        <v>3.53</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="n">
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
         <v>0.08</v>
@@ -3487,136 +3487,136 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.46</v>
+        <v>1.71</v>
       </c>
       <c r="AI7" t="n">
-        <v>79.77</v>
+        <v>83</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.31</v>
+        <v>3.21</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.77</v>
+        <v>3.14</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AN7" t="n">
-        <v>31.23</v>
+        <v>33.14</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AQ7" t="n">
-        <v>15.77</v>
+        <v>14.86</v>
       </c>
       <c r="AR7" t="n">
-        <v>13.38</v>
+        <v>13.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>10.15</v>
+        <v>10</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>39.62</v>
+        <v>41.21</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="BA7" t="n">
-        <v>10</v>
+        <v>10.07</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.46</v>
+        <v>6.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.54</v>
+        <v>3.57</v>
       </c>
       <c r="BD7" t="n">
-        <v>16.69</v>
+        <v>17.14</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="BF7" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.619999999999999</v>
+        <v>8.74</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="BO7" t="n">
         <v>1.19</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.58</v>
+        <v>4.67</v>
       </c>
       <c r="BR7" t="n">
-        <v>92.31</v>
+        <v>92.59</v>
       </c>
       <c r="BS7" t="n">
-        <v>76.92</v>
+        <v>77.78</v>
       </c>
       <c r="BT7" t="n">
-        <v>34.62</v>
+        <v>37.04</v>
       </c>
       <c r="BU7" t="n">
-        <v>15.38</v>
+        <v>18.52</v>
       </c>
       <c r="BV7" t="n">
-        <v>7.69</v>
+        <v>7.41</v>
       </c>
       <c r="BW7" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BX7" t="n">
-        <v>50</v>
+        <v>51.85</v>
       </c>
       <c r="BY7" t="n">
         <v>4.73</v>
@@ -3625,25 +3625,25 @@
         <v>4.88</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.93</v>
+        <v>3.89</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.22</v>
+        <v>4.18</v>
       </c>
       <c r="CC7" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="CD7" t="n">
-        <v>9.31</v>
+        <v>8.91</v>
       </c>
       <c r="CE7" t="n">
         <v>1.43</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CH7" t="n">
         <v>1.37</v>
@@ -3661,19 +3661,19 @@
         <v>2.59</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CN7" t="n">
         <v>1.5</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CP7" t="n">
         <v>2.07</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.67</v>
+        <v>3.72</v>
       </c>
       <c r="CR7" t="n">
         <v>1.45</v>
@@ -3682,7 +3682,7 @@
         <v>3.01</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="CU7" t="n">
         <v>1.4</v>
@@ -3697,7 +3697,7 @@
         <v>1.91</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CZ7" t="n">
         <v>1.9</v>
@@ -3706,13 +3706,13 @@
         <v>1.54</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.93</v>
+        <v>3.96</v>
       </c>
       <c r="DE7" t="n">
         <v>0.04</v>
@@ -3721,73 +3721,73 @@
         <v>2.19</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="DH7" t="n">
-        <v>82.77</v>
+        <v>84.33</v>
       </c>
       <c r="DI7" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.5</v>
+        <v>3.66</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DM7" t="n">
-        <v>33.34</v>
+        <v>34.26</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="DP7" t="n">
-        <v>15.96</v>
+        <v>15.48</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.46</v>
+        <v>14.48</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.69</v>
+        <v>8.67</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>43</v>
+        <v>43.7</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX7" t="n">
         <v>11</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.23</v>
+        <v>7.22</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.77</v>
+        <v>3.78</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.04</v>
+        <v>17.26</v>
       </c>
       <c r="EB7" t="n">
         <v>1.21</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="8">
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D12" t="n">
         <v>13</v>
@@ -5421,82 +5421,82 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="G12" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>87.15000000000001</v>
+        <v>85.86</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="K12" t="n">
-        <v>4.31</v>
+        <v>4.21</v>
       </c>
       <c r="L12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M12" t="n">
         <v>37</v>
       </c>
       <c r="N12" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="O12" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="P12" t="n">
-        <v>11.54</v>
+        <v>11.43</v>
       </c>
       <c r="Q12" t="n">
-        <v>12.23</v>
+        <v>12.71</v>
       </c>
       <c r="R12" t="n">
-        <v>8.69</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="T12" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="U12" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="V12" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>47.77</v>
+        <v>46.71</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="Z12" t="n">
-        <v>9.77</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.38</v>
+        <v>7.29</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AC12" t="n">
-        <v>18.46</v>
+        <v>18.43</v>
       </c>
       <c r="AD12" t="n">
         <v>1.06</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AF12" t="n">
         <v>0.08</v>
@@ -5580,70 +5580,70 @@
         <v>2.38</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.880000000000001</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.42</v>
+        <v>4.48</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.42</v>
+        <v>4.52</v>
       </c>
       <c r="BR12" t="n">
-        <v>88.45999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS12" t="n">
-        <v>61.54</v>
+        <v>62.96</v>
       </c>
       <c r="BT12" t="n">
-        <v>42.31</v>
+        <v>40.74</v>
       </c>
       <c r="BU12" t="n">
-        <v>23.08</v>
+        <v>22.22</v>
       </c>
       <c r="BV12" t="n">
-        <v>15.38</v>
+        <v>14.81</v>
       </c>
       <c r="BW12" t="n">
-        <v>7.69</v>
+        <v>7.41</v>
       </c>
       <c r="BX12" t="n">
-        <v>34.62</v>
+        <v>37.04</v>
       </c>
       <c r="BY12" t="n">
-        <v>4.94</v>
+        <v>4.79</v>
       </c>
       <c r="BZ12" t="n">
-        <v>5.2</v>
+        <v>5.04</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.93</v>
+        <v>3.89</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.16</v>
+        <v>4.12</v>
       </c>
       <c r="CC12" t="n">
         <v>7.19</v>
@@ -5655,40 +5655,40 @@
         <v>1.44</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CG12" t="n">
         <v>2.67</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CI12" t="n">
         <v>1.68</v>
       </c>
       <c r="CJ12" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CL12" t="n">
         <v>2.53</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CN12" t="n">
         <v>1.53</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.76</v>
+        <v>3.79</v>
       </c>
       <c r="CR12" t="n">
         <v>1.43</v>
@@ -5709,82 +5709,82 @@
         <v>2.15</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CZ12" t="n">
         <v>1.94</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="DB12" t="n">
         <v>1.37</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.91</v>
+        <v>3.94</v>
       </c>
       <c r="DE12" t="n">
         <v>0.04</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="DH12" t="n">
-        <v>80.04000000000001</v>
+        <v>79.63</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="DK12" t="n">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DM12" t="n">
-        <v>33.62</v>
+        <v>33.74</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.08</v>
+        <v>12.97</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.69</v>
+        <v>12.92</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.08</v>
+        <v>9.15</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>43.7</v>
+        <v>43.3</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DX12" t="n">
         <v>9.039999999999999</v>
@@ -5793,16 +5793,16 @@
         <v>6.34</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="EA12" t="n">
-        <v>17.73</v>
+        <v>17.74</v>
       </c>
       <c r="EB12" t="n">
         <v>1.01</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="13">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" t="n">
         <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6308,136 +6308,136 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AI14" t="n">
-        <v>56.62</v>
+        <v>56.57</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.46</v>
+        <v>3.36</v>
       </c>
       <c r="AL14" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AN14" t="n">
-        <v>26.46</v>
+        <v>26.93</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AQ14" t="n">
-        <v>13.15</v>
+        <v>13.21</v>
       </c>
       <c r="AR14" t="n">
-        <v>11.62</v>
+        <v>12.43</v>
       </c>
       <c r="AS14" t="n">
-        <v>10.08</v>
+        <v>10.07</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>33.62</v>
+        <v>33.64</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BA14" t="n">
-        <v>6.31</v>
+        <v>6.29</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.15</v>
+        <v>4.07</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="BD14" t="n">
-        <v>16</v>
+        <v>16.43</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.85</v>
+        <v>2.79</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.65</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.15</v>
+        <v>4.19</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.46</v>
+        <v>4.48</v>
       </c>
       <c r="BR14" t="n">
-        <v>92.31</v>
+        <v>92.59</v>
       </c>
       <c r="BS14" t="n">
-        <v>76.92</v>
+        <v>77.78</v>
       </c>
       <c r="BT14" t="n">
-        <v>57.69</v>
+        <v>59.26</v>
       </c>
       <c r="BU14" t="n">
-        <v>23.08</v>
+        <v>22.22</v>
       </c>
       <c r="BV14" t="n">
-        <v>15.38</v>
+        <v>14.81</v>
       </c>
       <c r="BW14" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BX14" t="n">
-        <v>38.46</v>
+        <v>40.74</v>
       </c>
       <c r="BY14" t="n">
         <v>6.24</v>
@@ -6446,16 +6446,16 @@
         <v>7.22</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.54</v>
+        <v>4.51</v>
       </c>
       <c r="CB14" t="n">
-        <v>5.17</v>
+        <v>5.12</v>
       </c>
       <c r="CC14" t="n">
-        <v>9.67</v>
+        <v>9.31</v>
       </c>
       <c r="CD14" t="n">
-        <v>12.15</v>
+        <v>11.68</v>
       </c>
       <c r="CE14" t="n">
         <v>1.37</v>
@@ -6464,22 +6464,22 @@
         <v>2.79</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="CH14" t="n">
         <v>1.42</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CK14" t="n">
         <v>1.79</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="CM14" t="n">
         <v>1.96</v>
@@ -6500,7 +6500,7 @@
         <v>1.43</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="CT14" t="n">
         <v>2.84</v>
@@ -6518,52 +6518,52 @@
         <v>1.83</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CZ14" t="n">
         <v>1.99</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="DC14" t="n">
         <v>2.01</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.52</v>
+        <v>3.53</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="DG14" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="DH14" t="n">
-        <v>65.23999999999999</v>
+        <v>64.89</v>
       </c>
       <c r="DI14" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="DK14" t="n">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DM14" t="n">
-        <v>30.12</v>
+        <v>30.22</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="DO14" t="n">
         <v>1</v>
@@ -6572,10 +6572,10 @@
         <v>13.81</v>
       </c>
       <c r="DQ14" t="n">
-        <v>12.81</v>
+        <v>13.19</v>
       </c>
       <c r="DR14" t="n">
-        <v>9.119999999999999</v>
+        <v>9.15</v>
       </c>
       <c r="DS14" t="n">
         <v>0.04</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>36.35</v>
+        <v>36.26</v>
       </c>
       <c r="DW14" t="n">
         <v>0.34</v>
       </c>
       <c r="DX14" t="n">
-        <v>8.08</v>
+        <v>8</v>
       </c>
       <c r="DY14" t="n">
-        <v>5.76</v>
+        <v>5.66</v>
       </c>
       <c r="DZ14" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.58</v>
+        <v>17.74</v>
       </c>
       <c r="EB14" t="n">
         <v>0.86</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="15">

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="n">
         <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
         <v>0.23</v>
@@ -1469,139 +1469,139 @@
         <v>2.46</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AI2" t="n">
-        <v>92.84999999999999</v>
+        <v>93.64</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AK2" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="AL2" t="n">
-        <v>5.69</v>
+        <v>5.5</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AN2" t="n">
-        <v>55.23</v>
+        <v>54.29</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.08</v>
+        <v>2.86</v>
       </c>
       <c r="AQ2" t="n">
-        <v>15.85</v>
+        <v>15.86</v>
       </c>
       <c r="AR2" t="n">
-        <v>14</v>
+        <v>13.86</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.85</v>
+        <v>7</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>59.77</v>
+        <v>58.14</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="BA2" t="n">
-        <v>14.15</v>
+        <v>13.64</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.69</v>
+        <v>9.43</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.46</v>
+        <v>4.21</v>
       </c>
       <c r="BD2" t="n">
-        <v>21.31</v>
+        <v>21.36</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.42</v>
+        <v>8.41</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="BO2" t="n">
         <v>1</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.92</v>
+        <v>3.93</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.5</v>
+        <v>4.48</v>
       </c>
       <c r="BR2" t="n">
-        <v>96.15000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="BS2" t="n">
-        <v>65.38</v>
+        <v>62.96</v>
       </c>
       <c r="BT2" t="n">
-        <v>42.31</v>
+        <v>40.74</v>
       </c>
       <c r="BU2" t="n">
-        <v>34.62</v>
+        <v>33.33</v>
       </c>
       <c r="BV2" t="n">
-        <v>15.38</v>
+        <v>14.81</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>34.62</v>
+        <v>33.33</v>
       </c>
       <c r="BY2" t="n">
         <v>1.48</v>
@@ -1610,16 +1610,16 @@
         <v>1.49</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.62</v>
+        <v>4.57</v>
       </c>
       <c r="CB2" t="n">
-        <v>5.13</v>
+        <v>5.06</v>
       </c>
       <c r="CC2" t="n">
-        <v>1.91</v>
+        <v>2.07</v>
       </c>
       <c r="CD2" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="CE2" t="n">
         <v>1.35</v>
@@ -1628,7 +1628,7 @@
         <v>2.68</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="CH2" t="n">
         <v>1.44</v>
@@ -1637,7 +1637,7 @@
         <v>1.69</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CK2" t="n">
         <v>1.78</v>
@@ -1646,7 +1646,7 @@
         <v>2.39</v>
       </c>
       <c r="CM2" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CN2" t="n">
         <v>1.58</v>
@@ -1655,19 +1655,19 @@
         <v>1.25</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CU2" t="n">
         <v>1.46</v>
@@ -1694,85 +1694,85 @@
         <v>1.28</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="DG2" t="n">
         <v>2.66</v>
       </c>
       <c r="DH2" t="n">
-        <v>94.23</v>
+        <v>94.59</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.42</v>
+        <v>5.33</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="DM2" t="n">
-        <v>56.42</v>
+        <v>55.89</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.77</v>
+        <v>2.67</v>
       </c>
       <c r="DP2" t="n">
-        <v>15.81</v>
+        <v>15.82</v>
       </c>
       <c r="DQ2" t="n">
-        <v>14.04</v>
+        <v>13.97</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.24</v>
+        <v>6.34</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>58.62</v>
+        <v>57.81</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX2" t="n">
-        <v>15.23</v>
+        <v>14.93</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.3</v>
+        <v>10.15</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.92</v>
+        <v>4.77</v>
       </c>
       <c r="EA2" t="n">
-        <v>20.88</v>
+        <v>20.93</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="n">
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1872,130 +1872,130 @@
         <v>2.69</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="AI3" t="n">
-        <v>89.45999999999999</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.54</v>
+        <v>4.43</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AN3" t="n">
-        <v>37.15</v>
+        <v>36.71</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ3" t="n">
-        <v>16.23</v>
+        <v>16.29</v>
       </c>
       <c r="AR3" t="n">
-        <v>13.85</v>
+        <v>13.93</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.54</v>
+        <v>6.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>50.85</v>
+        <v>50.07</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.69</v>
+        <v>10.86</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.62</v>
+        <v>7.79</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="BD3" t="n">
-        <v>19</v>
+        <v>19.14</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="BF3" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="BG3" t="n">
         <v>1.81</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.27</v>
+        <v>9.19</v>
       </c>
       <c r="BI3" t="n">
         <v>1.81</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="BN3" t="n">
         <v>1.04</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="BP3" t="n">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.23</v>
+        <v>6.07</v>
       </c>
       <c r="BR3" t="n">
-        <v>80.77</v>
+        <v>81.48</v>
       </c>
       <c r="BS3" t="n">
-        <v>61.54</v>
+        <v>62.96</v>
       </c>
       <c r="BT3" t="n">
-        <v>26.92</v>
+        <v>25.93</v>
       </c>
       <c r="BU3" t="n">
-        <v>11.54</v>
+        <v>11.11</v>
       </c>
       <c r="BV3" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>46.15</v>
+        <v>48.15</v>
       </c>
       <c r="BY3" t="n">
         <v>2.57</v>
@@ -2013,16 +2013,16 @@
         <v>2.62</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.67</v>
+        <v>3.64</v>
       </c>
       <c r="CC3" t="n">
-        <v>3.57</v>
+        <v>3.53</v>
       </c>
       <c r="CD3" t="n">
-        <v>4.33</v>
+        <v>4.24</v>
       </c>
       <c r="CE3" t="n">
         <v>1.45</v>
@@ -2037,10 +2037,10 @@
         <v>1.33</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CJ3" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CK3" t="n">
         <v>1.84</v>
@@ -2058,19 +2058,19 @@
         <v>1.37</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CQ3" t="n">
         <v>3.97</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CS3" t="n">
         <v>3.11</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CU3" t="n">
         <v>1.36</v>
@@ -2094,55 +2094,55 @@
         <v>1.56</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="DE3" t="n">
         <v>0.04</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.42</v>
+        <v>3.37</v>
       </c>
       <c r="DH3" t="n">
-        <v>91.69</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.12</v>
+        <v>5.04</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="DM3" t="n">
-        <v>43.38</v>
+        <v>42.93</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="DP3" t="n">
-        <v>15.23</v>
+        <v>15.3</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.66</v>
+        <v>14.67</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.81</v>
+        <v>6.78</v>
       </c>
       <c r="DS3" t="n">
         <v>0.04</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>51.12</v>
+        <v>50.7</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX3" t="n">
-        <v>13.34</v>
+        <v>13.33</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.539999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.81</v>
+        <v>3.78</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.08</v>
+        <v>20.11</v>
       </c>
       <c r="EB3" t="n">
         <v>1.42</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="4">
@@ -2233,7 +2233,7 @@
         <v>14.64</v>
       </c>
       <c r="R4" t="n">
-        <v>7.93</v>
+        <v>8</v>
       </c>
       <c r="S4" t="n">
         <v>1.43</v>
@@ -2545,7 +2545,7 @@
         <v>15.11</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.07</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="DS4" t="n">
         <v>0.11</v>
@@ -3523,7 +3523,7 @@
         <v>13.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>10</v>
+        <v>9.93</v>
       </c>
       <c r="AT7" t="n">
         <v>1.5</v>
@@ -3754,7 +3754,7 @@
         <v>14.48</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.67</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="DS7" t="n">
         <v>0.18</v>
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
         <v>13</v>
       </c>
       <c r="E8" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="F8" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="H8" t="n">
-        <v>94.08</v>
+        <v>94.20999999999999</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="K8" t="n">
-        <v>4.31</v>
+        <v>4.29</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="M8" t="n">
-        <v>42.15</v>
+        <v>41.36</v>
       </c>
       <c r="N8" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="O8" t="n">
-        <v>2.31</v>
+        <v>2.43</v>
       </c>
       <c r="P8" t="n">
-        <v>12.31</v>
+        <v>12.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>17.77</v>
+        <v>17.71</v>
       </c>
       <c r="R8" t="n">
-        <v>6.77</v>
+        <v>6.93</v>
       </c>
       <c r="S8" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T8" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="U8" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="V8" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>58.08</v>
+        <v>58.21</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="Z8" t="n">
-        <v>12.92</v>
+        <v>12.64</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.85</v>
+        <v>7.79</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.08</v>
+        <v>4.86</v>
       </c>
       <c r="AC8" t="n">
-        <v>23.08</v>
+        <v>23.14</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AF8" t="n">
         <v>0.23</v>
@@ -3968,70 +3968,70 @@
         <v>2.23</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.38</v>
+        <v>3.33</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.27</v>
+        <v>9.19</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.38</v>
+        <v>3.33</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="BP8" t="n">
-        <v>5.08</v>
+        <v>5.07</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.19</v>
+        <v>4.11</v>
       </c>
       <c r="BR8" t="n">
-        <v>96.15000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="BS8" t="n">
-        <v>84.62</v>
+        <v>85.19</v>
       </c>
       <c r="BT8" t="n">
-        <v>65.38</v>
+        <v>62.96</v>
       </c>
       <c r="BU8" t="n">
-        <v>53.85</v>
+        <v>51.85</v>
       </c>
       <c r="BV8" t="n">
-        <v>26.92</v>
+        <v>25.93</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.69</v>
+        <v>7.41</v>
       </c>
       <c r="BX8" t="n">
-        <v>57.69</v>
+        <v>59.26</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="CC8" t="n">
         <v>4.54</v>
@@ -4040,16 +4040,16 @@
         <v>4.8</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CI8" t="n">
         <v>1.79</v>
@@ -4070,13 +4070,13 @@
         <v>1.54</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="CR8" t="n">
         <v>1.41</v>
@@ -4085,7 +4085,7 @@
         <v>3.02</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="CU8" t="n">
         <v>1.39</v>
@@ -4112,52 +4112,52 @@
         <v>1.34</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.65</v>
+        <v>3.69</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="DH8" t="n">
-        <v>92.15000000000001</v>
+        <v>92.29000000000001</v>
       </c>
       <c r="DI8" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.81</v>
+        <v>4.78</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="DM8" t="n">
-        <v>41.92</v>
+        <v>41.52</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="DP8" t="n">
-        <v>12.58</v>
+        <v>12.67</v>
       </c>
       <c r="DQ8" t="n">
         <v>16.96</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.62</v>
+        <v>6.7</v>
       </c>
       <c r="DS8" t="n">
         <v>0.23</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>56.35</v>
+        <v>56.48</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.12</v>
+        <v>11.04</v>
       </c>
       <c r="DY8" t="n">
-        <v>6.81</v>
+        <v>6.82</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.31</v>
+        <v>4.22</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.88</v>
+        <v>21.96</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
         <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E9" t="n">
         <v>0.23</v>
@@ -4290,139 +4290,139 @@
         <v>1.85</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AI9" t="n">
-        <v>66.69</v>
+        <v>68.36</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="AN9" t="n">
-        <v>26.85</v>
+        <v>27.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12.15</v>
+        <v>12.29</v>
       </c>
       <c r="AR9" t="n">
-        <v>15.23</v>
+        <v>15.43</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.77</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>43</v>
+        <v>44.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.77</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.62</v>
+        <v>4.93</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.15</v>
+        <v>3.36</v>
       </c>
       <c r="BD9" t="n">
-        <v>15</v>
+        <v>15.43</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.77</v>
+        <v>2.64</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.539999999999999</v>
+        <v>8.52</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.58</v>
+        <v>4.59</v>
       </c>
       <c r="BQ9" t="n">
-        <v>3.92</v>
+        <v>3.89</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>84.62</v>
+        <v>85.19</v>
       </c>
       <c r="BT9" t="n">
-        <v>73.08</v>
+        <v>70.37</v>
       </c>
       <c r="BU9" t="n">
-        <v>30.77</v>
+        <v>29.63</v>
       </c>
       <c r="BV9" t="n">
-        <v>11.54</v>
+        <v>11.11</v>
       </c>
       <c r="BW9" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BX9" t="n">
-        <v>42.31</v>
+        <v>44.44</v>
       </c>
       <c r="BY9" t="n">
         <v>3.88</v>
@@ -4431,40 +4431,40 @@
         <v>4.08</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.07</v>
+        <v>4.04</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.32</v>
+        <v>4.28</v>
       </c>
       <c r="CC9" t="n">
-        <v>7.01</v>
+        <v>6.72</v>
       </c>
       <c r="CD9" t="n">
-        <v>8.470000000000001</v>
+        <v>8.09</v>
       </c>
       <c r="CE9" t="n">
         <v>1.38</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CI9" t="n">
         <v>1.87</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CK9" t="n">
         <v>1.73</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CM9" t="n">
         <v>2.02</v>
@@ -4476,10 +4476,10 @@
         <v>1.27</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CR9" t="n">
         <v>1.4</v>
@@ -4518,82 +4518,82 @@
         <v>1.98</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="DH9" t="n">
-        <v>71.06999999999999</v>
+        <v>71.78</v>
       </c>
       <c r="DI9" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>27.08</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>16</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="DS9" t="n">
         <v>0.15</v>
       </c>
-      <c r="DJ9" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="DK9" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="DL9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="DM9" t="n">
-        <v>26.74</v>
-      </c>
-      <c r="DN9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="DO9" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="DP9" t="n">
-        <v>13.54</v>
-      </c>
-      <c r="DQ9" t="n">
-        <v>15.92</v>
-      </c>
-      <c r="DR9" t="n">
-        <v>9.81</v>
-      </c>
-      <c r="DS9" t="n">
-        <v>0.16</v>
-      </c>
       <c r="DT9" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>44.16</v>
+        <v>44.89</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.380000000000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.16</v>
+        <v>5.3</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.23</v>
+        <v>3.34</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.5</v>
+        <v>16.67</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="10">
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10" t="n">
         <v>13</v>
@@ -4615,82 +4615,82 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="G10" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="H10" t="n">
+        <v>136.71</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="K10" t="n">
+        <v>8.93</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="M10" t="n">
+        <v>76.29000000000001</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="O10" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="P10" t="n">
+        <v>11.21</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="R10" t="n">
         <v>4</v>
       </c>
-      <c r="H10" t="n">
-        <v>136.31</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="K10" t="n">
-        <v>9.23</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>77.54000000000001</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="O10" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="P10" t="n">
-        <v>11.15</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>12.46</v>
-      </c>
-      <c r="R10" t="n">
-        <v>3.85</v>
-      </c>
       <c r="S10" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="T10" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="U10" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="V10" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>64.62</v>
+        <v>64.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z10" t="n">
-        <v>22.62</v>
+        <v>21.36</v>
       </c>
       <c r="AA10" t="n">
-        <v>16.46</v>
+        <v>15.57</v>
       </c>
       <c r="AB10" t="n">
-        <v>6.15</v>
+        <v>5.79</v>
       </c>
       <c r="AC10" t="n">
-        <v>27.92</v>
+        <v>27.79</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AF10" t="n">
         <v>0.15</v>
@@ -4774,70 +4774,70 @@
         <v>1.92</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.460000000000001</v>
+        <v>9.41</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.42</v>
+        <v>4.41</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5</v>
+        <v>4.96</v>
       </c>
       <c r="BR10" t="n">
-        <v>84.62</v>
+        <v>85.19</v>
       </c>
       <c r="BS10" t="n">
-        <v>73.08</v>
+        <v>70.37</v>
       </c>
       <c r="BT10" t="n">
-        <v>38.46</v>
+        <v>37.04</v>
       </c>
       <c r="BU10" t="n">
-        <v>11.54</v>
+        <v>11.11</v>
       </c>
       <c r="BV10" t="n">
-        <v>7.69</v>
+        <v>7.41</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>30.77</v>
+        <v>29.63</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="CA10" t="n">
-        <v>5.41</v>
+        <v>5.33</v>
       </c>
       <c r="CB10" t="n">
-        <v>6.25</v>
+        <v>6.14</v>
       </c>
       <c r="CC10" t="n">
         <v>1.61</v>
@@ -4849,19 +4849,19 @@
         <v>1.33</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CJ10" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="CK10" t="n">
         <v>1.82</v>
@@ -4873,25 +4873,25 @@
         <v>1.9</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CO10" t="n">
         <v>1.22</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="CR10" t="n">
         <v>1.38</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="CU10" t="n">
         <v>1.5</v>
@@ -4918,85 +4918,85 @@
         <v>1.27</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="DG10" t="n">
-        <v>3.58</v>
+        <v>3.48</v>
       </c>
       <c r="DH10" t="n">
-        <v>132</v>
+        <v>132.37</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="DK10" t="n">
-        <v>7.38</v>
+        <v>7.3</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="DM10" t="n">
-        <v>71.31</v>
+        <v>70.89</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="DO10" t="n">
-        <v>3.76</v>
+        <v>3.77</v>
       </c>
       <c r="DP10" t="n">
-        <v>12.92</v>
+        <v>12.89</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.23</v>
+        <v>12.37</v>
       </c>
       <c r="DR10" t="n">
-        <v>4.08</v>
+        <v>4.15</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>62.46</v>
+        <v>62.48</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX10" t="n">
-        <v>19.04</v>
+        <v>18.52</v>
       </c>
       <c r="DY10" t="n">
-        <v>13.08</v>
+        <v>12.74</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.96</v>
+        <v>5.78</v>
       </c>
       <c r="EA10" t="n">
-        <v>27.31</v>
+        <v>27.26</v>
       </c>
       <c r="EB10" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="11">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D11" t="n">
         <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="F11" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="G11" t="n">
-        <v>3.77</v>
+        <v>3.57</v>
       </c>
       <c r="H11" t="n">
-        <v>108.23</v>
+        <v>107.93</v>
       </c>
       <c r="I11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="K11" t="n">
-        <v>6.92</v>
+        <v>6.57</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="M11" t="n">
-        <v>61.38</v>
+        <v>61.29</v>
       </c>
       <c r="N11" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="O11" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>11.31</v>
+        <v>11.86</v>
       </c>
       <c r="Q11" t="n">
-        <v>12.85</v>
+        <v>13</v>
       </c>
       <c r="R11" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="S11" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="T11" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="U11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="V11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>62.85</v>
+        <v>62.29</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>15.85</v>
+        <v>15.21</v>
       </c>
       <c r="AA11" t="n">
-        <v>10</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AB11" t="n">
-        <v>5.85</v>
+        <v>5.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>23.85</v>
+        <v>24.07</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AF11" t="n">
         <v>0.15</v>
@@ -5177,70 +5177,70 @@
         <v>1.46</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.69</v>
+        <v>8.59</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="BP11" t="n">
-        <v>4</v>
+        <v>3.93</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.69</v>
+        <v>4.67</v>
       </c>
       <c r="BR11" t="n">
-        <v>84.62</v>
+        <v>81.48</v>
       </c>
       <c r="BS11" t="n">
-        <v>76.92</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="BT11" t="n">
-        <v>57.69</v>
+        <v>55.56</v>
       </c>
       <c r="BU11" t="n">
-        <v>23.08</v>
+        <v>22.22</v>
       </c>
       <c r="BV11" t="n">
-        <v>19.23</v>
+        <v>18.52</v>
       </c>
       <c r="BW11" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BX11" t="n">
-        <v>38.46</v>
+        <v>37.04</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.78</v>
+        <v>4.74</v>
       </c>
       <c r="CB11" t="n">
-        <v>5.17</v>
+        <v>5.11</v>
       </c>
       <c r="CC11" t="n">
         <v>1.91</v>
@@ -5249,13 +5249,13 @@
         <v>1.96</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="CH11" t="n">
         <v>1.46</v>
@@ -5267,13 +5267,13 @@
         <v>2.05</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CL11" t="n">
         <v>2.36</v>
       </c>
       <c r="CM11" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CN11" t="n">
         <v>1.59</v>
@@ -5285,16 +5285,16 @@
         <v>1.8</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="CT11" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="CU11" t="n">
         <v>1.46</v>
@@ -5318,88 +5318,88 @@
         <v>1.64</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="DC11" t="n">
         <v>1.89</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF11" t="n">
         <v>1</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.16</v>
+        <v>3.07</v>
       </c>
       <c r="DH11" t="n">
-        <v>106.65</v>
+        <v>106.56</v>
       </c>
       <c r="DI11" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.77</v>
+        <v>5.63</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="DM11" t="n">
-        <v>58.38</v>
+        <v>58.44</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.08</v>
+        <v>12.34</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.85</v>
+        <v>12.93</v>
       </c>
       <c r="DR11" t="n">
-        <v>4.92</v>
+        <v>4.89</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>61.5</v>
+        <v>61.26</v>
       </c>
       <c r="DW11" t="n">
         <v>0.04</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.88</v>
+        <v>13.63</v>
       </c>
       <c r="DY11" t="n">
-        <v>9</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.88</v>
+        <v>4.74</v>
       </c>
       <c r="EA11" t="n">
-        <v>24.12</v>
+        <v>24.22</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="12">
@@ -5457,7 +5457,7 @@
         <v>12.71</v>
       </c>
       <c r="R12" t="n">
-        <v>8.859999999999999</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="S12" t="n">
         <v>1.71</v>
@@ -5769,7 +5769,7 @@
         <v>12.92</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.15</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="DS12" t="n">
         <v>0.15</v>
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" t="n">
         <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E13" t="n">
         <v>0.38</v>
@@ -5902,139 +5902,139 @@
         <v>2.08</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AI13" t="n">
-        <v>97.92</v>
+        <v>98.20999999999999</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AL13" t="n">
-        <v>4.38</v>
+        <v>4.36</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>49.69</v>
+        <v>49.64</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ13" t="n">
         <v>15</v>
       </c>
       <c r="AR13" t="n">
-        <v>14.31</v>
+        <v>14.64</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.15</v>
+        <v>6</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>54.69</v>
+        <v>54</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BA13" t="n">
-        <v>11.92</v>
+        <v>11.71</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.38</v>
+        <v>7.36</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.54</v>
+        <v>4.36</v>
       </c>
       <c r="BD13" t="n">
-        <v>21.77</v>
+        <v>21.71</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="BH13" t="n">
-        <v>7.5</v>
+        <v>7.44</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.88</v>
+        <v>3.81</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3.54</v>
+        <v>3.56</v>
       </c>
       <c r="BR13" t="n">
-        <v>92.31</v>
+        <v>88.89</v>
       </c>
       <c r="BS13" t="n">
-        <v>80.77</v>
+        <v>77.78</v>
       </c>
       <c r="BT13" t="n">
-        <v>53.85</v>
+        <v>51.85</v>
       </c>
       <c r="BU13" t="n">
-        <v>26.92</v>
+        <v>25.93</v>
       </c>
       <c r="BV13" t="n">
-        <v>15.38</v>
+        <v>14.81</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>53.85</v>
+        <v>51.85</v>
       </c>
       <c r="BY13" t="n">
         <v>1.65</v>
@@ -6043,22 +6043,22 @@
         <v>1.81</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="CE13" t="n">
         <v>1.4</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CG13" t="n">
         <v>2.81</v>
@@ -6073,16 +6073,16 @@
         <v>2.01</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CL13" t="n">
         <v>2.31</v>
       </c>
       <c r="CM13" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CO13" t="n">
         <v>1.31</v>
@@ -6091,19 +6091,19 @@
         <v>1.94</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.42</v>
+        <v>3.43</v>
       </c>
       <c r="CR13" t="n">
         <v>1.41</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CV13" t="n">
         <v>1.76</v>
@@ -6130,82 +6130,82 @@
         <v>2.09</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="DH13" t="n">
-        <v>98.38</v>
+        <v>98.52</v>
       </c>
       <c r="DI13" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.62</v>
+        <v>4.6</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DM13" t="n">
-        <v>56.08</v>
+        <v>55.81</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="DP13" t="n">
-        <v>15.08</v>
+        <v>15.07</v>
       </c>
       <c r="DQ13" t="n">
-        <v>14.73</v>
+        <v>14.89</v>
       </c>
       <c r="DR13" t="n">
-        <v>5.65</v>
+        <v>5.59</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>53.92</v>
+        <v>53.59</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX13" t="n">
-        <v>13</v>
+        <v>12.85</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.039999999999999</v>
+        <v>8</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.96</v>
+        <v>4.85</v>
       </c>
       <c r="EA13" t="n">
-        <v>21.42</v>
+        <v>21.41</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="14">
@@ -6618,94 +6618,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D15" t="n">
         <v>13</v>
       </c>
       <c r="E15" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="G15" t="n">
-        <v>2.69</v>
+        <v>2.57</v>
       </c>
       <c r="H15" t="n">
-        <v>71.23</v>
+        <v>71.14</v>
       </c>
       <c r="I15" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>3.23</v>
+        <v>3.29</v>
       </c>
       <c r="K15" t="n">
-        <v>4.85</v>
+        <v>4.71</v>
       </c>
       <c r="L15" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="M15" t="n">
-        <v>32.15</v>
+        <v>32.57</v>
       </c>
       <c r="N15" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="O15" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="P15" t="n">
-        <v>14.23</v>
+        <v>14.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>15.62</v>
+        <v>15.5</v>
       </c>
       <c r="R15" t="n">
-        <v>7.85</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T15" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="U15" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="V15" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>46.38</v>
+        <v>45.64</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z15" t="n">
-        <v>12.62</v>
+        <v>12.36</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.77</v>
+        <v>8.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="AC15" t="n">
-        <v>20.62</v>
+        <v>20.64</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE15" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AF15" t="n">
         <v>0.08</v>
@@ -6789,70 +6789,70 @@
         <v>3.15</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.27</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.04</v>
+        <v>4.07</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.19</v>
+        <v>5.11</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>76.92</v>
+        <v>77.78</v>
       </c>
       <c r="BT15" t="n">
-        <v>46.15</v>
+        <v>44.44</v>
       </c>
       <c r="BU15" t="n">
-        <v>11.54</v>
+        <v>11.11</v>
       </c>
       <c r="BV15" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BW15" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BX15" t="n">
-        <v>50</v>
+        <v>51.85</v>
       </c>
       <c r="BY15" t="n">
-        <v>4.76</v>
+        <v>4.58</v>
       </c>
       <c r="BZ15" t="n">
-        <v>4.98</v>
+        <v>4.78</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="CC15" t="n">
         <v>6.01</v>
@@ -6873,19 +6873,19 @@
         <v>1.38</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CJ15" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CL15" t="n">
         <v>2.6</v>
       </c>
       <c r="CM15" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CN15" t="n">
         <v>1.52</v>
@@ -6897,7 +6897,7 @@
         <v>2.03</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="CR15" t="n">
         <v>1.44</v>
@@ -6927,10 +6927,10 @@
         <v>1.91</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DC15" t="n">
         <v>2.12</v>
@@ -6939,79 +6939,79 @@
         <v>3.76</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF15" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="DH15" t="n">
-        <v>76.95999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="DI15" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.19</v>
+        <v>3.22</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.97</v>
+        <v>3.93</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="DM15" t="n">
-        <v>37.38</v>
+        <v>37.41</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DP15" t="n">
-        <v>15.27</v>
+        <v>15.37</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.27</v>
+        <v>15.22</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.88</v>
+        <v>8.07</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>47.23</v>
+        <v>46.81</v>
       </c>
       <c r="DW15" t="n">
         <v>0.04</v>
       </c>
       <c r="DX15" t="n">
-        <v>11.31</v>
+        <v>11.22</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.69</v>
+        <v>7.59</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.62</v>
+        <v>3.63</v>
       </c>
       <c r="EA15" t="n">
-        <v>21.12</v>
+        <v>21.11</v>
       </c>
       <c r="EB15" t="n">
         <v>1.17</v>
       </c>
       <c r="EC15" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" t="n">
         <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4" t="n">
         <v>0.14</v>
@@ -2281,133 +2281,133 @@
         <v>2</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AI4" t="n">
-        <v>76.08</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.15</v>
+        <v>3.07</v>
       </c>
       <c r="AL4" t="n">
         <v>4</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AN4" t="n">
-        <v>31.15</v>
+        <v>31.86</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14.92</v>
+        <v>14.71</v>
       </c>
       <c r="AR4" t="n">
-        <v>15.62</v>
+        <v>15.64</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.23</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>43.15</v>
+        <v>43.93</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BA4" t="n">
-        <v>9.31</v>
+        <v>8.93</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.23</v>
+        <v>6</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.08</v>
+        <v>2.93</v>
       </c>
       <c r="BD4" t="n">
-        <v>18.62</v>
+        <v>18.21</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.48</v>
+        <v>2.39</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.699999999999999</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.48</v>
+        <v>2.39</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="BP4" t="n">
-        <v>5</v>
+        <v>5.04</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.7</v>
+        <v>4.68</v>
       </c>
       <c r="BR4" t="n">
-        <v>92.59</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="BS4" t="n">
-        <v>74.06999999999999</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT4" t="n">
-        <v>48.15</v>
+        <v>46.43</v>
       </c>
       <c r="BU4" t="n">
-        <v>25.93</v>
+        <v>25</v>
       </c>
       <c r="BV4" t="n">
-        <v>3.7</v>
+        <v>3.57</v>
       </c>
       <c r="BW4" t="n">
-        <v>3.7</v>
+        <v>3.57</v>
       </c>
       <c r="BX4" t="n">
-        <v>48.15</v>
+        <v>46.43</v>
       </c>
       <c r="BY4" t="n">
         <v>3.48</v>
@@ -2416,22 +2416,22 @@
         <v>4.17</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.67</v>
+        <v>3.65</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.9</v>
+        <v>3.87</v>
       </c>
       <c r="CC4" t="n">
-        <v>6.46</v>
+        <v>6.19</v>
       </c>
       <c r="CD4" t="n">
-        <v>6.62</v>
+        <v>6.33</v>
       </c>
       <c r="CE4" t="n">
         <v>1.44</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="CG4" t="n">
         <v>2.68</v>
@@ -2440,13 +2440,13 @@
         <v>1.35</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CJ4" t="n">
         <v>2.03</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CL4" t="n">
         <v>2.52</v>
@@ -2455,16 +2455,16 @@
         <v>1.92</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CO4" t="n">
         <v>1.34</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.68</v>
+        <v>3.74</v>
       </c>
       <c r="CR4" t="n">
         <v>1.43</v>
@@ -2485,67 +2485,67 @@
         <v>2.1</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CZ4" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="DA4" t="n">
         <v>1.57</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="DE4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="DH4" t="n">
-        <v>80.45</v>
+        <v>80.72</v>
       </c>
       <c r="DI4" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.52</v>
+        <v>4.5</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="DM4" t="n">
-        <v>36.7</v>
+        <v>36.86</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.89</v>
+        <v>13.82</v>
       </c>
       <c r="DQ4" t="n">
-        <v>15.11</v>
+        <v>15.14</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.109999999999999</v>
+        <v>8.18</v>
       </c>
       <c r="DS4" t="n">
         <v>0.11</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>44.63</v>
+        <v>44.96</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX4" t="n">
-        <v>9.48</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.3</v>
+        <v>6.18</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.19</v>
+        <v>3.11</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.63</v>
+        <v>20.36</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="5">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
         <v>14</v>
@@ -2600,82 +2600,82 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="G5" t="n">
-        <v>2.31</v>
+        <v>2.43</v>
       </c>
       <c r="H5" t="n">
-        <v>91.08</v>
+        <v>92.5</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="K5" t="n">
-        <v>3.62</v>
+        <v>3.64</v>
       </c>
       <c r="L5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="M5" t="n">
-        <v>43.69</v>
+        <v>44.71</v>
       </c>
       <c r="N5" t="n">
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="P5" t="n">
-        <v>14.85</v>
+        <v>14.86</v>
       </c>
       <c r="Q5" t="n">
-        <v>15.85</v>
+        <v>16.14</v>
       </c>
       <c r="R5" t="n">
-        <v>5.15</v>
+        <v>4.93</v>
       </c>
       <c r="S5" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="U5" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="V5" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>53.62</v>
+        <v>54.21</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.92</v>
+        <v>11.93</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.69</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.23</v>
+        <v>3.07</v>
       </c>
       <c r="AC5" t="n">
-        <v>23.38</v>
+        <v>22.86</v>
       </c>
       <c r="AD5" t="n">
         <v>1.3</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="AF5" t="n">
         <v>0.14</v>
@@ -2759,70 +2759,70 @@
         <v>2.79</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.220000000000001</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="BO5" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.78</v>
+        <v>3.71</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.44</v>
+        <v>4.43</v>
       </c>
       <c r="BR5" t="n">
-        <v>88.89</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS5" t="n">
-        <v>62.96</v>
+        <v>60.71</v>
       </c>
       <c r="BT5" t="n">
-        <v>40.74</v>
+        <v>39.29</v>
       </c>
       <c r="BU5" t="n">
-        <v>18.52</v>
+        <v>17.86</v>
       </c>
       <c r="BV5" t="n">
-        <v>3.7</v>
+        <v>3.57</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>44.44</v>
+        <v>42.86</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.59</v>
+        <v>3.5</v>
       </c>
       <c r="BZ5" t="n">
-        <v>4.08</v>
+        <v>3.97</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.8</v>
+        <v>3.77</v>
       </c>
       <c r="CC5" t="n">
         <v>5.02</v>
@@ -2834,25 +2834,25 @@
         <v>1.44</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CH5" t="n">
         <v>1.35</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CJ5" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CM5" t="n">
         <v>1.84</v>
@@ -2864,22 +2864,22 @@
         <v>1.35</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CQ5" t="n">
         <v>3.8</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CV5" t="n">
         <v>1.8</v>
@@ -2906,82 +2906,82 @@
         <v>2.21</v>
       </c>
       <c r="DD5" t="n">
-        <v>4.02</v>
+        <v>4.03</v>
       </c>
       <c r="DE5" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="DH5" t="n">
-        <v>83.73999999999999</v>
+        <v>84.72</v>
       </c>
       <c r="DI5" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="DM5" t="n">
-        <v>39.33</v>
+        <v>40</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DP5" t="n">
-        <v>15.96</v>
+        <v>15.93</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.15</v>
+        <v>15.32</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.26</v>
+        <v>7.07</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>51.07</v>
+        <v>51.46</v>
       </c>
       <c r="DW5" t="n">
         <v>0.04</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.33</v>
+        <v>10.39</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.33</v>
+        <v>7.46</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.33</v>
+        <v>21.14</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C6" t="n">
         <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
         <v>0.07000000000000001</v>
@@ -3084,136 +3084,136 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="AH6" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AI6" t="n">
-        <v>81.77</v>
+        <v>81.70999999999999</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AK6" t="n">
-        <v>4.38</v>
+        <v>4.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.77</v>
+        <v>4.57</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AN6" t="n">
-        <v>38.77</v>
+        <v>37.86</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="AQ6" t="n">
-        <v>18.08</v>
+        <v>18.21</v>
       </c>
       <c r="AR6" t="n">
-        <v>13.69</v>
+        <v>13.79</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.380000000000001</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>47.23</v>
+        <v>46.57</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="BA6" t="n">
-        <v>13.23</v>
+        <v>12.71</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.460000000000001</v>
+        <v>8.07</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.77</v>
+        <v>4.64</v>
       </c>
       <c r="BD6" t="n">
-        <v>17.38</v>
+        <v>17.29</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.15</v>
+        <v>4.21</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.48</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.93</v>
+        <v>4.82</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.48</v>
+        <v>4.46</v>
       </c>
       <c r="BR6" t="n">
-        <v>96.3</v>
+        <v>92.86</v>
       </c>
       <c r="BS6" t="n">
-        <v>85.19</v>
+        <v>82.14</v>
       </c>
       <c r="BT6" t="n">
-        <v>59.26</v>
+        <v>57.14</v>
       </c>
       <c r="BU6" t="n">
-        <v>29.63</v>
+        <v>28.57</v>
       </c>
       <c r="BV6" t="n">
-        <v>14.81</v>
+        <v>14.29</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>66.67</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY6" t="n">
         <v>3.83</v>
@@ -3222,25 +3222,25 @@
         <v>3.99</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.9</v>
+        <v>3.87</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.95</v>
+        <v>3.92</v>
       </c>
       <c r="CC6" t="n">
-        <v>6.03</v>
+        <v>5.84</v>
       </c>
       <c r="CD6" t="n">
-        <v>5.81</v>
+        <v>5.62</v>
       </c>
       <c r="CE6" t="n">
         <v>1.4</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CH6" t="n">
         <v>1.39</v>
@@ -3255,19 +3255,19 @@
         <v>1.77</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CM6" t="n">
         <v>1.84</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CO6" t="n">
         <v>1.31</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CQ6" t="n">
         <v>3.55</v>
@@ -3276,13 +3276,13 @@
         <v>1.45</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="CT6" t="n">
         <v>2.78</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CV6" t="n">
         <v>1.84</v>
@@ -3294,64 +3294,64 @@
         <v>1.87</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CZ6" t="n">
         <v>1.95</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="DB6" t="n">
         <v>1.35</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="DE6" t="n">
         <v>0.04</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.55</v>
+        <v>2.68</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="DH6" t="n">
-        <v>85.11</v>
+        <v>84.95999999999999</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ6" t="n">
-        <v>3.96</v>
+        <v>4.03</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.3</v>
+        <v>4.22</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="DM6" t="n">
-        <v>41.15</v>
+        <v>40.61</v>
       </c>
       <c r="DN6" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DP6" t="n">
-        <v>17.63</v>
+        <v>17.71</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14.89</v>
+        <v>14.9</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.77</v>
+        <v>7.92</v>
       </c>
       <c r="DS6" t="n">
         <v>0.07000000000000001</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>47</v>
+        <v>46.68</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.63</v>
+        <v>13.36</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.85</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.78</v>
+        <v>4.71</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.44</v>
+        <v>18.36</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="EC6" t="n">
-        <v>3.59</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="7">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
         <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="G7" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="H7" t="n">
-        <v>85.77</v>
+        <v>85.93000000000001</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>3.69</v>
+        <v>3.71</v>
       </c>
       <c r="K7" t="n">
-        <v>4.23</v>
+        <v>4.29</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="M7" t="n">
-        <v>35.46</v>
+        <v>36.21</v>
       </c>
       <c r="N7" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="P7" t="n">
-        <v>16.15</v>
+        <v>16.07</v>
       </c>
       <c r="Q7" t="n">
-        <v>15.54</v>
+        <v>15.57</v>
       </c>
       <c r="R7" t="n">
-        <v>7.23</v>
+        <v>7.07</v>
       </c>
       <c r="S7" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="T7" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="U7" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="V7" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>46.38</v>
+        <v>46.79</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z7" t="n">
-        <v>12</v>
+        <v>12.07</v>
       </c>
       <c r="AA7" t="n">
-        <v>8</v>
+        <v>8.07</v>
       </c>
       <c r="AB7" t="n">
         <v>4</v>
       </c>
       <c r="AC7" t="n">
-        <v>17.38</v>
+        <v>17.29</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE7" t="n">
-        <v>3.69</v>
+        <v>3.57</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,70 +3565,70 @@
         <v>2.93</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.74</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BP7" t="n">
         <v>4</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.67</v>
+        <v>4.57</v>
       </c>
       <c r="BR7" t="n">
-        <v>92.59</v>
+        <v>92.86</v>
       </c>
       <c r="BS7" t="n">
-        <v>77.78</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>37.04</v>
+        <v>39.29</v>
       </c>
       <c r="BU7" t="n">
-        <v>18.52</v>
+        <v>17.86</v>
       </c>
       <c r="BV7" t="n">
-        <v>7.41</v>
+        <v>7.14</v>
       </c>
       <c r="BW7" t="n">
-        <v>3.7</v>
+        <v>3.57</v>
       </c>
       <c r="BX7" t="n">
-        <v>51.85</v>
+        <v>53.57</v>
       </c>
       <c r="BY7" t="n">
-        <v>4.73</v>
+        <v>4.57</v>
       </c>
       <c r="BZ7" t="n">
-        <v>4.88</v>
+        <v>4.72</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.89</v>
+        <v>3.86</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.18</v>
+        <v>4.14</v>
       </c>
       <c r="CC7" t="n">
         <v>7</v>
@@ -3637,31 +3637,31 @@
         <v>8.91</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CI7" t="n">
         <v>1.72</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CN7" t="n">
         <v>1.5</v>
@@ -3670,10 +3670,10 @@
         <v>1.34</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="CR7" t="n">
         <v>1.45</v>
@@ -3694,7 +3694,7 @@
         <v>2.16</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CY7" t="n">
         <v>2.43</v>
@@ -3709,52 +3709,52 @@
         <v>1.38</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.96</v>
+        <v>3.99</v>
       </c>
       <c r="DE7" t="n">
         <v>0.04</v>
       </c>
       <c r="DF7" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DG7" t="n">
         <v>1.96</v>
       </c>
       <c r="DH7" t="n">
-        <v>84.33</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="DI7" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.44</v>
+        <v>3.46</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.66</v>
+        <v>3.72</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="DM7" t="n">
-        <v>34.26</v>
+        <v>34.68</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="DP7" t="n">
-        <v>15.48</v>
+        <v>15.46</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.48</v>
+        <v>14.54</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.630000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="DS7" t="n">
         <v>0.18</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>43.7</v>
+        <v>44</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="DX7" t="n">
-        <v>11</v>
+        <v>11.07</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.22</v>
+        <v>7.29</v>
       </c>
       <c r="DZ7" t="n">
         <v>3.78</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.26</v>
+        <v>17.22</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="8">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
         <v>14</v>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5499,52 +5499,52 @@
         <v>2.07</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AI12" t="n">
-        <v>72.92</v>
+        <v>74.14</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.08</v>
+        <v>2.93</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AN12" t="n">
-        <v>30.23</v>
+        <v>31</v>
       </c>
       <c r="AO12" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14.62</v>
+        <v>14.71</v>
       </c>
       <c r="AR12" t="n">
-        <v>13.15</v>
+        <v>13.29</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.460000000000001</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,82 +5556,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>39.62</v>
+        <v>40.21</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BA12" t="n">
-        <v>8.31</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.31</v>
+        <v>5.29</v>
       </c>
       <c r="BC12" t="n">
         <v>3</v>
       </c>
       <c r="BD12" t="n">
-        <v>17</v>
+        <v>17.14</v>
       </c>
       <c r="BE12" t="n">
         <v>0.96</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.039999999999999</v>
+        <v>8.93</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.48</v>
+        <v>4.46</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.52</v>
+        <v>4.43</v>
       </c>
       <c r="BR12" t="n">
-        <v>88.89</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="BS12" t="n">
-        <v>62.96</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>40.74</v>
+        <v>42.86</v>
       </c>
       <c r="BU12" t="n">
-        <v>22.22</v>
+        <v>21.43</v>
       </c>
       <c r="BV12" t="n">
-        <v>14.81</v>
+        <v>14.29</v>
       </c>
       <c r="BW12" t="n">
-        <v>7.41</v>
+        <v>7.14</v>
       </c>
       <c r="BX12" t="n">
-        <v>37.04</v>
+        <v>39.29</v>
       </c>
       <c r="BY12" t="n">
         <v>4.79</v>
@@ -5640,25 +5640,25 @@
         <v>5.04</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.89</v>
+        <v>3.86</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.12</v>
+        <v>4.08</v>
       </c>
       <c r="CC12" t="n">
-        <v>7.19</v>
+        <v>6.93</v>
       </c>
       <c r="CD12" t="n">
-        <v>8.41</v>
+        <v>8.02</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF12" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CH12" t="n">
         <v>1.34</v>
@@ -5673,7 +5673,7 @@
         <v>1.86</v>
       </c>
       <c r="CL12" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CM12" t="n">
         <v>1.89</v>
@@ -5688,7 +5688,7 @@
         <v>2.14</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.79</v>
+        <v>3.81</v>
       </c>
       <c r="CR12" t="n">
         <v>1.43</v>
@@ -5724,85 +5724,85 @@
         <v>1.37</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.94</v>
+        <v>3.97</v>
       </c>
       <c r="DE12" t="n">
         <v>0.04</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="DG12" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="DH12" t="n">
-        <v>79.63</v>
+        <v>80</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="DK12" t="n">
-        <v>3.67</v>
+        <v>3.57</v>
       </c>
       <c r="DL12" t="n">
         <v>0.11</v>
       </c>
       <c r="DM12" t="n">
-        <v>33.74</v>
+        <v>34</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.97</v>
+        <v>13.07</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.92</v>
+        <v>13</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.109999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>43.3</v>
+        <v>43.46</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DX12" t="n">
-        <v>9.039999999999999</v>
+        <v>9</v>
       </c>
       <c r="DY12" t="n">
-        <v>6.34</v>
+        <v>6.29</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="EA12" t="n">
-        <v>17.74</v>
+        <v>17.78</v>
       </c>
       <c r="EB12" t="n">
         <v>1.01</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="13">
@@ -6215,10 +6215,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D14" t="n">
         <v>14</v>
@@ -6227,49 +6227,49 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="G14" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="H14" t="n">
-        <v>73.84999999999999</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="K14" t="n">
-        <v>2.62</v>
+        <v>2.86</v>
       </c>
       <c r="L14" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="M14" t="n">
-        <v>33.77</v>
+        <v>33.93</v>
       </c>
       <c r="N14" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="O14" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="P14" t="n">
-        <v>14.46</v>
+        <v>14.57</v>
       </c>
       <c r="Q14" t="n">
-        <v>14</v>
+        <v>13.86</v>
       </c>
       <c r="R14" t="n">
-        <v>8.15</v>
+        <v>7.86</v>
       </c>
       <c r="S14" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="T14" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6281,28 +6281,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>39.08</v>
+        <v>39.57</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="Z14" t="n">
-        <v>9.85</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.38</v>
+        <v>7.36</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>19.15</v>
+        <v>19.64</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6386,70 +6386,70 @@
         <v>2.79</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.699999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.19</v>
+        <v>4.25</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.48</v>
+        <v>4.46</v>
       </c>
       <c r="BR14" t="n">
-        <v>92.59</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="BS14" t="n">
-        <v>77.78</v>
+        <v>75</v>
       </c>
       <c r="BT14" t="n">
-        <v>59.26</v>
+        <v>57.14</v>
       </c>
       <c r="BU14" t="n">
-        <v>22.22</v>
+        <v>21.43</v>
       </c>
       <c r="BV14" t="n">
-        <v>14.81</v>
+        <v>14.29</v>
       </c>
       <c r="BW14" t="n">
-        <v>3.7</v>
+        <v>3.57</v>
       </c>
       <c r="BX14" t="n">
-        <v>40.74</v>
+        <v>39.29</v>
       </c>
       <c r="BY14" t="n">
-        <v>6.24</v>
+        <v>5.99</v>
       </c>
       <c r="BZ14" t="n">
-        <v>7.22</v>
+        <v>6.93</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.51</v>
+        <v>4.46</v>
       </c>
       <c r="CB14" t="n">
-        <v>5.12</v>
+        <v>5.04</v>
       </c>
       <c r="CC14" t="n">
         <v>9.31</v>
@@ -6458,43 +6458,43 @@
         <v>11.68</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="CH14" t="n">
         <v>1.42</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CL14" t="n">
         <v>2.44</v>
       </c>
       <c r="CM14" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.29</v>
+        <v>3.36</v>
       </c>
       <c r="CR14" t="n">
         <v>1.43</v>
@@ -6515,13 +6515,13 @@
         <v>2.21</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CZ14" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DA14" t="n">
         <v>1.6</v>
@@ -6530,52 +6530,52 @@
         <v>1.33</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.53</v>
+        <v>3.59</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="DG14" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="DH14" t="n">
-        <v>64.89</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="DI14" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.97</v>
+        <v>2.93</v>
       </c>
       <c r="DK14" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="DM14" t="n">
-        <v>30.22</v>
+        <v>30.43</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="DO14" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.81</v>
+        <v>13.89</v>
       </c>
       <c r="DQ14" t="n">
-        <v>13.19</v>
+        <v>13.14</v>
       </c>
       <c r="DR14" t="n">
-        <v>9.15</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="DS14" t="n">
         <v>0.04</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>36.26</v>
+        <v>36.61</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="DX14" t="n">
-        <v>8</v>
+        <v>8.07</v>
       </c>
       <c r="DY14" t="n">
-        <v>5.66</v>
+        <v>5.72</v>
       </c>
       <c r="DZ14" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.74</v>
+        <v>18.04</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="15">

--- a/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Greece_Super_League_2025-2026.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -706,667 +694,667 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team_name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>total_games</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>home_games</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>away_games</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>home_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>home_avg_2h_cards</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>home_avg_2h_corners</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>home_avg_attacks</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>home_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>home_avg_cards_num</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>home_avg_corners</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>home_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>home_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>home_avg_fh_cards</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>home_avg_fh_corners</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>home_avg_fouls</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>home_avg_freekicks</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>home_avg_goalkicks</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>home_avg_goals_conceded</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>home_avg_goals_scored</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>home_avg_penalties_won</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>home_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>home_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>home_avg_possession</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>home_avg_red_cards</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>home_avg_shots</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>home_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>home_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>home_avg_throwins</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>home_avg_xg</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>home_avg_yellow_cards</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>away_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>away_avg_2h_cards</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>away_avg_2h_corners</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>away_avg_attacks</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>away_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>away_avg_cards_num</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>away_avg_corners</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>away_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>away_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>away_avg_fh_cards</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>away_avg_fh_corners</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>away_avg_fouls</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>away_avg_freekicks</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>away_avg_goalkicks</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>away_avg_goals_conceded</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>away_avg_goals_scored</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>away_avg_penalties_won</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>away_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>away_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>away_avg_possession</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>away_avg_red_cards</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>away_avg_shots</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>away_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>away_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>away_avg_throwins</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>away_avg_xg</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>away_avg_yellow_cards</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>totalGoalCount</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>totalCornerCount</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>overallGoalCount</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>ht_goals_team_a</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>ht_goals_team_b</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>goals_2hg_team_a</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>goals_2hg_team_b</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>GoalCount_2hg</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>HTGoalCount</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>corner_fh_count</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>corner_2h_count</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>over05</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>over15</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>over25</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>over35</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>over45</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>over55</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>btts</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>avg_odds_ft_1</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_1_odd</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>avg_odds_ft_x</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_x_odd</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>avg_odds_ft_2</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_2_odd</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_over05</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_over15</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_under05</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_under15</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>avg_odds_btts_no</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>avg_odds_btts_yes</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>avg_odds_corners_over_85</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>avg_odds_corners_over_95</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>avg_odds_corners_under_85</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>avg_odds_corners_under_95</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over15</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over25</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over35</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_over05_odd</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_over15_odd</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_under05_odd</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_under15_odd</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>avg_pinnacle_btts_no_odd</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>avg_pinnacle_btts_yes_odd</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_over_85_odd</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_over_95_odd</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_under_85_odd</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_under_95_odd</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over15_odd</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over25_odd</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over35_odd</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>total_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>total_avg_2h_cards</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>total_avg_2h_corners</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>total_avg_attacks</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>total_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>total_avg_cards_num</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>total_avg_corners</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>total_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>total_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>total_avg_fh_cards</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>total_avg_fh_corners</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>total_avg_fouls</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>total_avg_freekicks</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>total_avg_goalkicks</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>total_avg_penalties_won</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>total_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>total_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>total_avg_possession</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>total_avg_red_cards</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>total_avg_shots</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>total_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>total_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>total_avg_throwins</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>total_avg_xg</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>total_avg_yellow_cards</t>
         </is>
@@ -1379,298 +1367,298 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="F2" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="G2" t="n">
         <v>2.69</v>
       </c>
       <c r="H2" t="n">
-        <v>95.62</v>
+        <v>95.5</v>
       </c>
       <c r="I2" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="J2" t="n">
         <v>2.62</v>
       </c>
       <c r="K2" t="n">
-        <v>5.15</v>
+        <v>5.31</v>
       </c>
       <c r="L2" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>57.62</v>
+        <v>56</v>
       </c>
       <c r="N2" t="n">
-        <v>0.77</v>
+        <v>0.93999